--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N916"/>
+  <dimension ref="A1:N917"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51334,6 +51334,60 @@
         </is>
       </c>
     </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>Alertan que USI de La Gaviota sería presuntamente usada como guarida de delincuentes</t>
+        </is>
+      </c>
+      <c r="B917" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiwgFBVV95cUxNb1hwc2JzQUFtbm1ySGRGa0xrZWJBdFdIOXFRamtlam42RURINTBKemdfR09xT2JMMUdNR0Z0OFdXeFBJdGQ1dEtOYzRxTWdKZXlvVVFIOEZFUnd0LUMxY25JZjl0X2JwUGpIa3prd2ttWHlpdjE4MW1qX1NpVUFFNHhtdW44WVh5ZGJjNDFoVjE5Y1IwWWxWYlNxenc0Q29oSFFsaDVDMTg0RWtwTGxOZDJsQmtYQUxQRFZMQ3ZzdG1Xdw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C917" t="inlineStr">
+        <is>
+          <t>Ecos del Combeima</t>
+        </is>
+      </c>
+      <c r="D917" t="inlineStr"/>
+      <c r="E917" t="inlineStr"/>
+      <c r="F917" t="n">
+        <v>0</v>
+      </c>
+      <c r="G917" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H917" t="n">
+        <v>3</v>
+      </c>
+      <c r="I917" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J917" t="n">
+        <v>2</v>
+      </c>
+      <c r="K917" t="inlineStr">
+        <is>
+          <t>guarida</t>
+        </is>
+      </c>
+      <c r="L917" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M917" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N917" t="inlineStr">
+        <is>
+          <t>haunt</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N917"/>
+  <dimension ref="A1:N922"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51388,6 +51388,288 @@
         </is>
       </c>
     </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>Una nueva etapa: así se transforma «¿Me conoces?» para llegar a tiempo por la niñez</t>
+        </is>
+      </c>
+      <c r="B918" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiogFBVV95cUxNVXFUYmpObzdzNkJCVjZxQkgyMjZ4ZVJfRWZPa3E1WXpudXBoTy16R09ZY0s4a1c5UThJNFgzYXVVR2Y2cDVTZnJfbVVkdmgxajl2ZmVRYWFqb0VZTHp2UGdvVW94bENNbllHUVJaOXpMYXp5bVQ0ME03a1Q0VHh4TEUwLVdJZTBabzJGaTdRbGsyYXhNS3NVelZGa3JfY3U3LWc?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C918" t="inlineStr">
+        <is>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D918" t="inlineStr"/>
+      <c r="E918" t="inlineStr"/>
+      <c r="F918" t="n">
+        <v>0</v>
+      </c>
+      <c r="G918" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H918" t="n">
+        <v>3</v>
+      </c>
+      <c r="I918" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J918" t="n">
+        <v>2</v>
+      </c>
+      <c r="K918" t="inlineStr">
+        <is>
+          <t>llegar</t>
+        </is>
+      </c>
+      <c r="L918" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M918" t="n">
+        <v>1</v>
+      </c>
+      <c r="N918" t="inlineStr">
+        <is>
+          <t>reaching</t>
+        </is>
+      </c>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>Una nueva etapa: así se transforma «¿Me conoces?» para llegar a tiempo por la niñez</t>
+        </is>
+      </c>
+      <c r="B919" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiogFBVV95cUxNVXFUYmpObzdzNkJCVjZxQkgyMjZ4ZVJfRWZPa3E1WXpudXBoTy16R09ZY0s4a1c5UThJNFgzYXVVR2Y2cDVTZnJfbVVkdmgxajl2ZmVRYWFqb0VZTHp2UGdvVW94bENNbllHUVJaOXpMYXp5bVQ0ME03a1Q0VHh4TEUwLVdJZTBabzJGaTdRbGsyYXhNS3NVelZGa3JfY3U3LWc?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C919" t="inlineStr">
+        <is>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D919" t="inlineStr"/>
+      <c r="E919" t="inlineStr"/>
+      <c r="F919" t="n">
+        <v>0</v>
+      </c>
+      <c r="G919" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H919" t="n">
+        <v>3</v>
+      </c>
+      <c r="I919" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J919" t="n">
+        <v>2</v>
+      </c>
+      <c r="K919" t="inlineStr">
+        <is>
+          <t>tiempo</t>
+        </is>
+      </c>
+      <c r="L919" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M919" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N919" t="inlineStr">
+        <is>
+          <t>tense</t>
+        </is>
+      </c>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar fortalece la atención integral para más de 6.000 niños, niñas y adolescentes afectados por la emergencia en Córdoba</t>
+        </is>
+      </c>
+      <c r="B920" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiswFBVV95cUxOaG5MMjg3QmxmSFM5MWtaNW51MWFGeUVBY0haVmZxRWZlSXF6NlA5QWxwR3UxdHViNEx5T1RXZWs3NGM0YXpjWC1aWHhNNmhmamY0WVdMSmc3cy1nODNnVG5ldnNLVWpEWFRFZkJvTl9RdXF5QV9Pd2JLRDBhNGNDbDhfdUlsNXFpcFNMSW53a0dSQjVQN2U3OFRMUU9yUGNKM2dMT2tpZ2E3ajhEM1NDWXpKZw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C920" t="inlineStr">
+        <is>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D920" t="inlineStr"/>
+      <c r="E920" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="F920" t="n">
+        <v>0</v>
+      </c>
+      <c r="G920" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H920" t="n">
+        <v>3</v>
+      </c>
+      <c r="I920" t="inlineStr">
+        <is>
+          <t>domingo</t>
+        </is>
+      </c>
+      <c r="J920" t="n">
+        <v>1</v>
+      </c>
+      <c r="K920" t="inlineStr">
+        <is>
+          <t>fortalece</t>
+        </is>
+      </c>
+      <c r="L920" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M920" t="n">
+        <v>2</v>
+      </c>
+      <c r="N920" t="inlineStr">
+        <is>
+          <t>strengthens</t>
+        </is>
+      </c>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar fortalece la atención integral para más de 6.000 niños, niñas y adolescentes afectados por la emergencia en Córdoba</t>
+        </is>
+      </c>
+      <c r="B921" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiswFBVV95cUxOaG5MMjg3QmxmSFM5MWtaNW51MWFGeUVBY0haVmZxRWZlSXF6NlA5QWxwR3UxdHViNEx5T1RXZWs3NGM0YXpjWC1aWHhNNmhmamY0WVdMSmc3cy1nODNnVG5ldnNLVWpEWFRFZkJvTl9RdXF5QV9Pd2JLRDBhNGNDbDhfdUlsNXFpcFNMSW53a0dSQjVQN2U3OFRMUU9yUGNKM2dMT2tpZ2E3ajhEM1NDWXpKZw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C921" t="inlineStr">
+        <is>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D921" t="inlineStr"/>
+      <c r="E921" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="F921" t="n">
+        <v>0</v>
+      </c>
+      <c r="G921" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H921" t="n">
+        <v>3</v>
+      </c>
+      <c r="I921" t="inlineStr">
+        <is>
+          <t>domingo</t>
+        </is>
+      </c>
+      <c r="J921" t="n">
+        <v>1</v>
+      </c>
+      <c r="K921" t="inlineStr">
+        <is>
+          <t>emergencia</t>
+        </is>
+      </c>
+      <c r="L921" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M921" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N921" t="inlineStr">
+        <is>
+          <t>emergency</t>
+        </is>
+      </c>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>ICBF y hospitales de Santander ponen en marcha convenio para prevenir la desnutrición infantil: 1.200 niños y madres gestantes serán beneficiados</t>
+        </is>
+      </c>
+      <c r="B922" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi-gFBVV95cUxNMy10NVE5bHpicmN5dlBDZ0lud3VmdkExR0g2c2JobzJLRXhVam8xTFhqTERhTTFWZG9RWVNWZ0hkNGNPZm8zXzJfVGZjNm1tT1Y3cXdDNk40bXJYbHhMc09fUVVacWd5ZHVXaW1pWFozMnBvRjNWejlqbm5XREV5ZVhhOW1qTlhVV2VHVHBoOHRlcEZRY2Z1WS1sWEJGdXRaem9NakxLLVBBMUtjZzV5bmQybzVlamphOUNvSGREckt4d200aG8wWHg2RHBDYnpoX3ZjQ0ZFb3h0ZDZUR1RNeHBMcXlOTk9tZktzTzQ3UC1WeEpHRGZXMU5n?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C922" t="inlineStr">
+        <is>
+          <t>Canal TRO</t>
+        </is>
+      </c>
+      <c r="D922" t="inlineStr"/>
+      <c r="E922" t="inlineStr">
+        <is>
+          <t>Santander</t>
+        </is>
+      </c>
+      <c r="F922" t="n">
+        <v>0</v>
+      </c>
+      <c r="G922" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H922" t="n">
+        <v>8</v>
+      </c>
+      <c r="I922" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J922" t="n">
+        <v>28</v>
+      </c>
+      <c r="K922" t="inlineStr">
+        <is>
+          <t>infantil</t>
+        </is>
+      </c>
+      <c r="L922" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M922" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N922" t="inlineStr">
+        <is>
+          <t>childish</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N922"/>
+  <dimension ref="A1:N926"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51670,6 +51670,222 @@
         </is>
       </c>
     </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>De mansión del narco a refugio de esperanza: así nace el primer centro para niños migrantes en Urabá</t>
+        </is>
+      </c>
+      <c r="B923" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi0gFBVV95cUxOcGtrOFRZQ0ZtdjVmQ0FLU2dmREJvUGlSVnBzQmdEZGhtQlZrWnVKMUN3OEVHSlVndjh4RXhLa3ZqSFk1R0Z0S0tnQ3lPRGs2SVRpWlB3bzUxZ0hTbFYyV2FEZm0zTEx3eUdRZzRmaGF2bzVsRFlZcEpTRmZ4bWRNS3FHU2taeF93NXNYaldhN1Rsc2FXa0RsN3ZENF9SNzRZZHdDc2cxeTVPRUUzRXhERkw5cGZBRTRJWGZGb1RqN3RVV21vVm9uaGY4dloySGpJbVHSAdcBQVVfeXFMUG5KcHpJZnlCTWhJV0YyZEVWRGtlVnZuT2tiZkxOQlpwTkpKWXZWMktYSGJ2dWUyYjFKVFRVMGlGbnBDajVUU0UxR3Y0MG9xbm80dlFZRWh1dnc0OXYzQUNLMEhGaW9zY0NLQkJtc09PLVJpZHpLdEZsc3ZvT3ZIT2FGaks3YTZmaldGS0d4bnladHJFUGZvY3NqTF9VLUh2c3poU253Wm5odGJwR21BaDliYW5tQlp6X3pDNk12ZVJIamJSSEZtUGZLalM3djlvU1paejVrWGs?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C923" t="inlineStr">
+        <is>
+          <t>Pulzo</t>
+        </is>
+      </c>
+      <c r="D923" t="inlineStr"/>
+      <c r="E923" t="inlineStr"/>
+      <c r="F923" t="n">
+        <v>0</v>
+      </c>
+      <c r="G923" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H923" t="n">
+        <v>3</v>
+      </c>
+      <c r="I923" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J923" t="n">
+        <v>3</v>
+      </c>
+      <c r="K923" t="inlineStr">
+        <is>
+          <t>esperanza</t>
+        </is>
+      </c>
+      <c r="L923" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M923" t="n">
+        <v>2</v>
+      </c>
+      <c r="N923" t="inlineStr">
+        <is>
+          <t>hope</t>
+        </is>
+      </c>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>“Me duele”: mamá de víctima de Freddy Castellanos, presunto agresor en jardín del ICBF</t>
+        </is>
+      </c>
+      <c r="B924" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMixgFBVV95cUxOOW9JcUlCWjZpdE9OTkxLUHpVS2hYMDAwdGFBZXlPampzSW9GZkFNRnJneTcyckRMWkpKeUJmTzJMeWxEYkdraHJOTGhSZS00YWJ5aVBTN1U4NHNqdDhWdzNBTVF6WVBYSTctN1dTelJ6dVhYWVJQV0Z4dGptQk9YRmg2VzJDc1RsN2tIZFR5NlFhTWMwNzFITU0tdUExUlpUSm05Y1luYzhGbUxwTkY2eDVVa1gwNVVHcG9LckV0dUZGYUctYXc?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C924" t="inlineStr">
+        <is>
+          <t>Tropicana Colombia</t>
+        </is>
+      </c>
+      <c r="D924" t="inlineStr"/>
+      <c r="E924" t="inlineStr"/>
+      <c r="F924" t="n">
+        <v>0</v>
+      </c>
+      <c r="G924" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H924" t="n">
+        <v>5</v>
+      </c>
+      <c r="I924" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J924" t="n">
+        <v>8</v>
+      </c>
+      <c r="K924" t="inlineStr">
+        <is>
+          <t>duele</t>
+        </is>
+      </c>
+      <c r="L924" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M924" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N924" t="inlineStr">
+        <is>
+          <t>hurts</t>
+        </is>
+      </c>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>“Me duele”: mamá de víctima de Freddy Castellanos, presunto agresor en jardín del ICBF</t>
+        </is>
+      </c>
+      <c r="B925" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMixgFBVV95cUxOOW9JcUlCWjZpdE9OTkxLUHpVS2hYMDAwdGFBZXlPampzSW9GZkFNRnJneTcyckRMWkpKeUJmTzJMeWxEYkdraHJOTGhSZS00YWJ5aVBTN1U4NHNqdDhWdzNBTVF6WVBYSTctN1dTelJ6dVhYWVJQV0Z4dGptQk9YRmg2VzJDc1RsN2tIZFR5NlFhTWMwNzFITU0tdUExUlpUSm05Y1luYzhGbUxwTkY2eDVVa1gwNVVHcG9LckV0dUZGYUctYXc?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C925" t="inlineStr">
+        <is>
+          <t>Tropicana Colombia</t>
+        </is>
+      </c>
+      <c r="D925" t="inlineStr"/>
+      <c r="E925" t="inlineStr"/>
+      <c r="F925" t="n">
+        <v>0</v>
+      </c>
+      <c r="G925" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H925" t="n">
+        <v>5</v>
+      </c>
+      <c r="I925" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J925" t="n">
+        <v>8</v>
+      </c>
+      <c r="K925" t="inlineStr">
+        <is>
+          <t>víctima</t>
+        </is>
+      </c>
+      <c r="L925" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M925" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N925" t="inlineStr">
+        <is>
+          <t>casualty</t>
+        </is>
+      </c>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>“Me duele”: mamá de víctima de Freddy Castellanos, presunto agresor en jardín del ICBF</t>
+        </is>
+      </c>
+      <c r="B926" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMixgFBVV95cUxOOW9JcUlCWjZpdE9OTkxLUHpVS2hYMDAwdGFBZXlPampzSW9GZkFNRnJneTcyckRMWkpKeUJmTzJMeWxEYkdraHJOTGhSZS00YWJ5aVBTN1U4NHNqdDhWdzNBTVF6WVBYSTctN1dTelJ6dVhYWVJQV0Z4dGptQk9YRmg2VzJDc1RsN2tIZFR5NlFhTWMwNzFITU0tdUExUlpUSm05Y1luYzhGbUxwTkY2eDVVa1gwNVVHcG9LckV0dUZGYUctYXc?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C926" t="inlineStr">
+        <is>
+          <t>Tropicana Colombia</t>
+        </is>
+      </c>
+      <c r="D926" t="inlineStr"/>
+      <c r="E926" t="inlineStr"/>
+      <c r="F926" t="n">
+        <v>0</v>
+      </c>
+      <c r="G926" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H926" t="n">
+        <v>5</v>
+      </c>
+      <c r="I926" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J926" t="n">
+        <v>8</v>
+      </c>
+      <c r="K926" t="inlineStr">
+        <is>
+          <t>agresor</t>
+        </is>
+      </c>
+      <c r="L926" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M926" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N926" t="inlineStr">
+        <is>
+          <t>attacking</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N926"/>
+  <dimension ref="A1:N929"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -51886,6 +51886,172 @@
         </is>
       </c>
     </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>ICBF dice que Clan del Golfo no ha entregado menores reclutados, un acuerdo de mesa de paz</t>
+        </is>
+      </c>
+      <c r="B927" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi8wFBVV95cUxPaVl5SzdtcU1qSWxuemx0TkdfLXZ2a1NudUZrTHA1eU54U2F1Y0hScFRqVVBueGw0dHR1UmRQY1RNNnZDa3AtcnFYNzFsa21pQnNrTU16NHFXOWoyTl9XcjNqTEtNQmNnNHUzeGYwb3J3dHE2UXM0UVEtVGEwSmg1c0d1cHNqX043UEJWMUdqOHdFQ2RmM051WkNqWXBhVi1sVzRxZFFCaGZVU3RZTGFBMjRrZXFGcEVrenowUi1YSVQ3UlZRcXNGVUpnUE9KWWVtdHo3QzFtNVdEb3ppY3djVTBIQ2pSbGk2d2V3enZWU1d3ZG_SAYcCQVVfeXFMT2loa21TY0J4OFBWc3R3QVhNdDZSbmRYUm1PV1FuUXlIcXpxdEN3bkVTUzllU3NSU1JTeVY1LXdUTVg3Z0NpWnBDZ2ZTTGxwclpTa3h0b0V6M21qT0xHQTVnNmxNdWFfSjhIVElPbzY2ZUJLMlZSNmZzX05ZTWFnd0t3ckFVY09OYTJIUlBGb1JrX0dCUFBHamltU1NhSjdYTkszdXJ1M3d4eldTc3oxa19MZ1BhT1hxTmxtcks1d3IzcUdYb3pleUJyMWl0b2Z4Nkd5Vi1xREkxSHVQbllYNGRlYnYwSWJZaVVQZ3Q0clJPYUFyTUZaUWVNYW5USDJFUEszYzIwc2M?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C927" t="inlineStr">
+        <is>
+          <t>El Espectador</t>
+        </is>
+      </c>
+      <c r="D927" t="inlineStr"/>
+      <c r="E927" t="inlineStr"/>
+      <c r="F927" t="n">
+        <v>0</v>
+      </c>
+      <c r="G927" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H927" t="n">
+        <v>3</v>
+      </c>
+      <c r="I927" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J927" t="n">
+        <v>3</v>
+      </c>
+      <c r="K927" t="inlineStr">
+        <is>
+          <t>acuerdo</t>
+        </is>
+      </c>
+      <c r="L927" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M927" t="n">
+        <v>1</v>
+      </c>
+      <c r="N927" t="inlineStr">
+        <is>
+          <t>agreement</t>
+        </is>
+      </c>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>ICBF dice que Clan del Golfo no ha entregado menores reclutados, un acuerdo de mesa de paz</t>
+        </is>
+      </c>
+      <c r="B928" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi8wFBVV95cUxPaVl5SzdtcU1qSWxuemx0TkdfLXZ2a1NudUZrTHA1eU54U2F1Y0hScFRqVVBueGw0dHR1UmRQY1RNNnZDa3AtcnFYNzFsa21pQnNrTU16NHFXOWoyTl9XcjNqTEtNQmNnNHUzeGYwb3J3dHE2UXM0UVEtVGEwSmg1c0d1cHNqX043UEJWMUdqOHdFQ2RmM051WkNqWXBhVi1sVzRxZFFCaGZVU3RZTGFBMjRrZXFGcEVrenowUi1YSVQ3UlZRcXNGVUpnUE9KWWVtdHo3QzFtNVdEb3ppY3djVTBIQ2pSbGk2d2V3enZWU1d3ZG_SAYcCQVVfeXFMT2loa21TY0J4OFBWc3R3QVhNdDZSbmRYUm1PV1FuUXlIcXpxdEN3bkVTUzllU3NSU1JTeVY1LXdUTVg3Z0NpWnBDZ2ZTTGxwclpTa3h0b0V6M21qT0xHQTVnNmxNdWFfSjhIVElPbzY2ZUJLMlZSNmZzX05ZTWFnd0t3ckFVY09OYTJIUlBGb1JrX0dCUFBHamltU1NhSjdYTkszdXJ1M3d4eldTc3oxa19MZ1BhT1hxTmxtcks1d3IzcUdYb3pleUJyMWl0b2Z4Nkd5Vi1xREkxSHVQbllYNGRlYnYwSWJZaVVQZ3Q0clJPYUFyTUZaUWVNYW5USDJFUEszYzIwc2M?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C928" t="inlineStr">
+        <is>
+          <t>El Espectador</t>
+        </is>
+      </c>
+      <c r="D928" t="inlineStr"/>
+      <c r="E928" t="inlineStr"/>
+      <c r="F928" t="n">
+        <v>0</v>
+      </c>
+      <c r="G928" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H928" t="n">
+        <v>3</v>
+      </c>
+      <c r="I928" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J928" t="n">
+        <v>3</v>
+      </c>
+      <c r="K928" t="inlineStr">
+        <is>
+          <t>paz</t>
+        </is>
+      </c>
+      <c r="L928" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M928" t="n">
+        <v>2</v>
+      </c>
+      <c r="N928" t="inlineStr">
+        <is>
+          <t>peace</t>
+        </is>
+      </c>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar articula estrategia para prevenir el trabajo infantil en Yopal</t>
+        </is>
+      </c>
+      <c r="B929" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMitAFBVV95cUxPLU0wZUY1UTFaR0RsMWJqN21UYnRYRkFxdkVnLXpzODdKSnJDSjFfYlByZGwzRGFXYTRuem9rZENaQWVDSVNCblcxR3hWMjRDV180NkxUTnNhTTRTUzZ3MlJWeXVuSTc3Tk05ZG53OElORHdUbkNVOTdHb0ttMUROZzFFQUZ6bS1RSDlOSFVjOE1sclhkaTFvOVV1LUxYZ0wzdDRacElIQjRadzZtaURURE9mcVE?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C929" t="inlineStr">
+        <is>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D929" t="inlineStr">
+        <is>
+          <t>Yopal</t>
+        </is>
+      </c>
+      <c r="E929" t="inlineStr"/>
+      <c r="F929" t="n">
+        <v>0</v>
+      </c>
+      <c r="G929" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H929" t="n">
+        <v>3</v>
+      </c>
+      <c r="I929" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J929" t="n">
+        <v>3</v>
+      </c>
+      <c r="K929" t="inlineStr">
+        <is>
+          <t>infantil</t>
+        </is>
+      </c>
+      <c r="L929" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M929" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N929" t="inlineStr">
+        <is>
+          <t>childish</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N929"/>
+  <dimension ref="A1:N934"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52052,6 +52052,288 @@
         </is>
       </c>
     </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>ICBF confirma que el Clan del Golfo no ha devuelto ni un solo niño reclutado: Angélica Lozano</t>
+        </is>
+      </c>
+      <c r="B930" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiyAFBVV95cUxNQlFmUi1PUVpXeTlMRWVFTXJYRDNMWHNiU0I0TnhrWlJPSi1mWjFyRFc2V1l6TUJfU25seVVBMTZ5amRKbFpvY2F6enFILWVWYjBFZ0s3aHR5ZFg2LUk0dkJsN1hhSVNpa2s1cTJyejNuR1RGcm5Wd1MzZXFGN0dqcXRWZVIxOWhKSGFYUnFveEJxUURidE9TSjI3UVZNbFRWVmE0TWE2dzZGVzlWR1NWdnQxb084RHBLcEtzTWVsT0VGTjNfX1BYMNIB1gFBVV95cUxQU0FwdENTajdqTFJaWlh1V1o4RUwydUhHWFJ5d0dXZFJ6YjY2U200Z3BJZVBzNnNzVEgzUTFyNlAtZmt2ZFZTUFZRSEFWM19zazR2c3A3NklZdjNaLXlLYzdDMWFIcGN2OWNTUVItN1h3Z1hrZGZjMV9IX1JuRHZpckZTUTFDU2VUaGxaMlJBYVlQRzg1T1VIMWtrVUVqNXNpb0hKMEFlRUFIUHNERnF5bnhpTGp6VTBxQ3VSeWREckpnQlJMeDZGU0tSdEZTMW94RXhud0hB?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C930" t="inlineStr">
+        <is>
+          <t>Blu Radio</t>
+        </is>
+      </c>
+      <c r="D930" t="inlineStr"/>
+      <c r="E930" t="inlineStr"/>
+      <c r="F930" t="n">
+        <v>0</v>
+      </c>
+      <c r="G930" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H930" t="n">
+        <v>3</v>
+      </c>
+      <c r="I930" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J930" t="n">
+        <v>3</v>
+      </c>
+      <c r="K930" t="inlineStr">
+        <is>
+          <t>solo</t>
+        </is>
+      </c>
+      <c r="L930" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M930" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N930" t="inlineStr">
+        <is>
+          <t>alone</t>
+        </is>
+      </c>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>Vivienda recuperada por la SAE servirá para atender a la niñez migrante no acompañada y en riesgo</t>
+        </is>
+      </c>
+      <c r="B931" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMizAFBVV95cUxQeFNlZmFkUTIxMktfbUIyTkJNdTBTZTdrRFEyUGQ3c2lqeTBFdFZ1SEIxeDVuUlVvSUJNd1M2LThCVEM2WFIyb1Y5Tk1SVFNaNWw4R05qMTVfNHc2NEFmUW45SFgzMW5DLS13Uk1aODFfeWFhX0xRZFpiZmNsV3FndU01dmJFaHl6U3NpaFBCdmtHTmlpQXp5WmUzWUF4Q1JtRmRGRDN6LUhPcGRZa3huTEtCMDlHcnlXSG9EMXRYQ3hiRXhMMm9lUE5UYkLSAeABQVVfeXFMT1dKNFJYQUhadTV4Y0VnbDdjejhYYkR2dG1lV0FKT3JpbVVmaUd5VVYwZUZ5Q0JRWmVIcUtobmVBZGRFRnJuOTJMelRrWEhsY0NrU29VX3VCSHhUSXFHdEY1cG14WG5tQUtjMXRJRzgzQjZ3R2dZM0dobzhsaFFHZWxlLUVVSFVoMldsOS1FcVVxV2dVc0JvSGNTT2ViSmJ4bE95SXJUVTRZeXF5MnJQbmhwUTZzMmlibUgyT0VRQlhCQWtSc3RVVFRiaHR5Njlhd3NmRF9FYTNRNWpTMUpEeVQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C931" t="inlineStr">
+        <is>
+          <t>Caracol Radio</t>
+        </is>
+      </c>
+      <c r="D931" t="inlineStr"/>
+      <c r="E931" t="inlineStr"/>
+      <c r="F931" t="n">
+        <v>0</v>
+      </c>
+      <c r="G931" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H931" t="n">
+        <v>3</v>
+      </c>
+      <c r="I931" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J931" t="n">
+        <v>3</v>
+      </c>
+      <c r="K931" t="inlineStr">
+        <is>
+          <t>riesgo</t>
+        </is>
+      </c>
+      <c r="L931" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M931" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N931" t="inlineStr">
+        <is>
+          <t>risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>En Quindío se exaltó la labor de defensores y defensoras de familia</t>
+        </is>
+      </c>
+      <c r="B932" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiogFBVV95cUxPc3E1aEs0bHZNeW91QVNDUXl3N2Eyak15NDRvT2J4T1E2MWtqNjJfbkxHVlBVNldrWW1QM3hMN28tbzdqZTBjcm9WWjRhd2c3b212ZE9DdmF1d0ZSbzJ4RndrLUpMUVlob1R3NWd1MDVhLXM5RzUtT2taNW9aV21rSTJmclNaYjVlWk5lQ1pQOTNvd2l5Y1NVX0tRMTNOb0F3eUE?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C932" t="inlineStr">
+        <is>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D932" t="inlineStr"/>
+      <c r="E932" t="inlineStr">
+        <is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="F932" t="n">
+        <v>0</v>
+      </c>
+      <c r="G932" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H932" t="n">
+        <v>3</v>
+      </c>
+      <c r="I932" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J932" t="n">
+        <v>3</v>
+      </c>
+      <c r="K932" t="inlineStr">
+        <is>
+          <t>defensores</t>
+        </is>
+      </c>
+      <c r="L932" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M932" t="n">
+        <v>2</v>
+      </c>
+      <c r="N932" t="inlineStr">
+        <is>
+          <t>defenders</t>
+        </is>
+      </c>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>Alcalde de Rionegro respalda paro de servidores del ICBF Regional Antioquia y pide pronta solución</t>
+        </is>
+      </c>
+      <c r="B933" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMizgFBVV95cUxPZ296VnlaOHdrZFJWai0zeGo4Tk1sbEVYaThCZU9kUTdJV2pvRnJBV19qNkJGSENKOFg3NEQ5N1Z3YV9iVXlwdzg4UlhzWjhlMERoR3ptYTUwMEdDR0EzbDNGZEFrbzRCVmk2d1UxeVZuYlZ5V3BPa0xuWUZMNnFFRW82ckJGUW0zd3FabEtOLVVjWVpUaENpNWlraENoS0dDX19PS1dqNEVQWlc3ajIxekhhZ3hENHpMS2FBUmxXYmNGSDBaYXc1cVNlMGlYZ9IB4gFBVV95cUxOalU2aWR2bmZOODJ2eFlFdXdCTlBRcXVaeVgzSGpzbnRXd3dVUG1sd1U4cVU3c3hYQTJhTEh4Sno0WlBQb2tpZFZYeTlNMXZNcUFKdEdBdnUweFlTTmJOLW1XeEVQaEFBeE9BZWVXdGJFdkpTZ2g5WlhESmlxX2VXY3cyT3dueFdMN0VBcHZuU0NTM1ZEZUlvZHh4MTJJaWhMQXROZzRIbDBDSkNfUDRtS3E4dnpSZzByd3RtVWFudG5VWW1MT0E5c2lrTGxxeTlsZTVQTUlPcDJ4SFlNSTZNYVFB?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C933" t="inlineStr">
+        <is>
+          <t>Caracol Radio</t>
+        </is>
+      </c>
+      <c r="D933" t="inlineStr"/>
+      <c r="E933" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="F933" t="n">
+        <v>0</v>
+      </c>
+      <c r="G933" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H933" t="n">
+        <v>8</v>
+      </c>
+      <c r="I933" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J933" t="n">
+        <v>14</v>
+      </c>
+      <c r="K933" t="inlineStr">
+        <is>
+          <t>respalda</t>
+        </is>
+      </c>
+      <c r="L933" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M933" t="n">
+        <v>2</v>
+      </c>
+      <c r="N933" t="inlineStr">
+        <is>
+          <t>endorses</t>
+        </is>
+      </c>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>Alcalde de Rionegro respalda paro de servidores del ICBF Regional Antioquia y pide pronta solución</t>
+        </is>
+      </c>
+      <c r="B934" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMizgFBVV95cUxPZ296VnlaOHdrZFJWai0zeGo4Tk1sbEVYaThCZU9kUTdJV2pvRnJBV19qNkJGSENKOFg3NEQ5N1Z3YV9iVXlwdzg4UlhzWjhlMERoR3ptYTUwMEdDR0EzbDNGZEFrbzRCVmk2d1UxeVZuYlZ5V3BPa0xuWUZMNnFFRW82ckJGUW0zd3FabEtOLVVjWVpUaENpNWlraENoS0dDX19PS1dqNEVQWlc3ajIxekhhZ3hENHpMS2FBUmxXYmNGSDBaYXc1cVNlMGlYZ9IB4gFBVV95cUxOalU2aWR2bmZOODJ2eFlFdXdCTlBRcXVaeVgzSGpzbnRXd3dVUG1sd1U4cVU3c3hYQTJhTEh4Sno0WlBQb2tpZFZYeTlNMXZNcUFKdEdBdnUweFlTTmJOLW1XeEVQaEFBeE9BZWVXdGJFdkpTZ2g5WlhESmlxX2VXY3cyT3dueFdMN0VBcHZuU0NTM1ZEZUlvZHh4MTJJaWhMQXROZzRIbDBDSkNfUDRtS3E4dnpSZzByd3RtVWFudG5VWW1MT0E5c2lrTGxxeTlsZTVQTUlPcDJ4SFlNSTZNYVFB?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C934" t="inlineStr">
+        <is>
+          <t>Caracol Radio</t>
+        </is>
+      </c>
+      <c r="D934" t="inlineStr"/>
+      <c r="E934" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="F934" t="n">
+        <v>0</v>
+      </c>
+      <c r="G934" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H934" t="n">
+        <v>8</v>
+      </c>
+      <c r="I934" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J934" t="n">
+        <v>14</v>
+      </c>
+      <c r="K934" t="inlineStr">
+        <is>
+          <t>solución</t>
+        </is>
+      </c>
+      <c r="L934" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M934" t="n">
+        <v>1</v>
+      </c>
+      <c r="N934" t="inlineStr">
+        <is>
+          <t>solution</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N934"/>
+  <dimension ref="A1:N935"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52334,6 +52334,64 @@
         </is>
       </c>
     </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>SIC abre dos investigaciones por presunta colusión en contratación pública en el Icbf y en licitación de infraestructura en La Mesa, Cundinamarca</t>
+        </is>
+      </c>
+      <c r="B935" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMipwJBVV95cUxPOF9VU2ZYckpSY2JDVEtlZUVUQjJadU55MVN0S2ZiS1FYRXNzOFJ5YWQ2dFBMQmFUdXdqM2l1ZmE1UTd2ZWJ4anlUREpCWHMtNlZqUzV5SDdsQ052Z2NzaXNjRy1yYm9MRDdYNklyUzhwRFdKUE5BU2FxUHBBWUppcGtCSVNCbmgwVU1fS0c3QlBVUFoxNllWLUNKREJEcmQyRVFRbG1xd0pNU2lsbUk1c0FfSlpBNWNxWVM2VWVVNHhKc2tqS1RMajFERzNXTXVVRmN3akdVZmdPVTltS21iWWtMbzFPd1VpUWE5VW1rNjF1TE53bmZLME03NFdwNWF1ODdWOEVmd2haYlZhSGw5Uy1ObUVBd19Lc1YyYXgyTDM2N0ZLMm800gGsAkFVX3lxTE5PQWZkdTdlM01xYV9MZHI4Sk1UWnhfVVNBT1V3UUc4TDJfc2plYUJOMHhKdV9jRTJQVnFvWHFITENQX1dCNTJZYkNTLWVYTUpnRndOQWFVWWd5VFhIS0xWOC1OaHg4TTA2bnNXcG9ieG9nSExvOEYyMG9BSDAwOGQ0OW1IZW5mZ3pIZDVFODhEWXhmeFN0WV9NV1ZEV1A5YXJjOHZ4ZHZxT2dlNDBQX1RqZXNWaU1wMGZ1VTdOSVlDcUdCam5jaFFZTHhNSmVoellzYTFEM1hBYktLWnVJampXSzIxTHVKa0RJdUtFMTV2MXdyZWlMbVdCVXJEaWFrZ0lJWFZRblFObjhyTUNjdVdjSTNIRWxISmNia1o0eU1oWHpIMk5GS2s1M1BWUA?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C935" t="inlineStr">
+        <is>
+          <t>ELTIEMPO.COM</t>
+        </is>
+      </c>
+      <c r="D935" t="inlineStr"/>
+      <c r="E935" t="inlineStr">
+        <is>
+          <t>Cundinamarca</t>
+        </is>
+      </c>
+      <c r="F935" t="n">
+        <v>0</v>
+      </c>
+      <c r="G935" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H935" t="n">
+        <v>3</v>
+      </c>
+      <c r="I935" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J935" t="n">
+        <v>4</v>
+      </c>
+      <c r="K935" t="inlineStr">
+        <is>
+          <t>colusión</t>
+        </is>
+      </c>
+      <c r="L935" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M935" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N935" t="inlineStr">
+        <is>
+          <t>colluding</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N935"/>
+  <dimension ref="A1:N940"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52392,6 +52392,280 @@
         </is>
       </c>
     </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>El Icbf convirtió un inmueble incautado al narcotráfico en centro de emergencia para niños migrantes en el Urabá</t>
+        </is>
+      </c>
+      <c r="B936" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi7gFBVV95cUxPY3B1YnpJVVprb3hoZTg2Snh1a1IyOWdOQ2tFWEw1bkc4Vm42NVRuUFhUenJzWEplUkhySGQwZ3d6RzhUX2JUNDc2WDY4SVQySjR3SG44bGVnQkF6Z0VaMlhnb09HemhQcHFONi1jZERMZ2o2MFh2cjVLazN2QTItXzJSeWVCNGdZTUs0VE9UR2hyU2s3S3JiQ1JrdGdEcDVkN3M4czF0NG1XZVd0MkpiVjJscG5aUkRIOTZNTGNWaTZhQ2RWQzhjSGtHRm01eDFwMDhQUHlZbkM2MVdNakhkNEVwRC1ZZ3ZyN0p6emNn0gGIAkFVX3lxTE84UUIxMnI1X0tLNmNNNWp0MWM1YVpRdWh2LUphamVTWEJmS0ZleUZ3NXIxVmp3X3FpMjBOb2VmeVh4eTVyRGpabVh3VlVmZ2dhMkllSWkxYXdoelh5N29ySjRTaVZwaHpHSGs0RHBJbGdMYlV5eVV1VlJXRDJieHloRmYzNDhHRUlJN2lmSlVLdXFGSlFJZnI3dW92X2RxakRyUWVYWG1Ibjh5b1FtT0ZVQ01JWU41OUR4MmxibFJfSms0LURmYkxCZENZbGNENlZId3hud0VwTmtsMmlibXlqbGtsU0pFVkdhUEFRSFFQeFBLdWQzT3I2YUxrVXYyMW5zcndNeTdUTA?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C936" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D936" t="inlineStr"/>
+      <c r="E936" t="inlineStr"/>
+      <c r="F936" t="n">
+        <v>0</v>
+      </c>
+      <c r="G936" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H936" t="n">
+        <v>3</v>
+      </c>
+      <c r="I936" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J936" t="n">
+        <v>4</v>
+      </c>
+      <c r="K936" t="inlineStr">
+        <is>
+          <t>emergencia</t>
+        </is>
+      </c>
+      <c r="L936" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M936" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N936" t="inlineStr">
+        <is>
+          <t>emergency</t>
+        </is>
+      </c>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar fortalece procesos de memoria, resignificación y acompañamiento psicosocial en Ciudad Bolívar</t>
+        </is>
+      </c>
+      <c r="B937" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivAFBVV95cUxNTkpHdnFqc1FlQ0JpZHRsRmhabXFDSFIwa0hFcXV4cW93b3Rkcld2NHpGRDl3cklaWjVMTFhjMl9VWTQ4aHFOZXUwY3JXNllYejJMNkRvcUNsOWNnck0yVkt6S0RBSWcxSDhrMmgxUGxvaWV0TF9vTmhMNFo4cG00TTJnQmJfMkNINkZid0VlRXZlUXFwdTVFMDJXM0R0aDBNZGhZLVVTeWN2NHBqVjRtNXJiZUsxaDI4SHdmNA?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C937" t="inlineStr">
+        <is>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D937" t="inlineStr"/>
+      <c r="E937" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="F937" t="n">
+        <v>0</v>
+      </c>
+      <c r="G937" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H937" t="n">
+        <v>3</v>
+      </c>
+      <c r="I937" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J937" t="n">
+        <v>4</v>
+      </c>
+      <c r="K937" t="inlineStr">
+        <is>
+          <t>fortalece</t>
+        </is>
+      </c>
+      <c r="L937" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M937" t="n">
+        <v>2</v>
+      </c>
+      <c r="N937" t="inlineStr">
+        <is>
+          <t>strengthens</t>
+        </is>
+      </c>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>Nunca más la niñez en la guerra: Bienestar Familiar reitera su llamado a dejar a los niños y niñas por fuera del conflicto</t>
+        </is>
+      </c>
+      <c r="B938" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivAFBVV95cUxNRmNwei1tTGdKdWl3Q0JIQm1aWlg2bk1kN0NmTVZOS3UtYmZ2RzFmbTFYWVYxV3dHUmcwc3JZUDdSa3ZYeGZHS3ZaTHBETmFOc25falh3WkVxdVJ1RExkMWdPcC1yUTdWemhqc1l0VGVGMHJFZnUzVlFFZGpaazNpNGFLX0pqWTkxalF3a0ZydTljeGN0MjQyYjdJcmQ5YU5MVHEtbEpYVGVuX0dRc2NvQkQ1bG41X1g5cVdOMQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C938" t="inlineStr">
+        <is>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D938" t="inlineStr"/>
+      <c r="E938" t="inlineStr"/>
+      <c r="F938" t="n">
+        <v>0</v>
+      </c>
+      <c r="G938" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H938" t="n">
+        <v>3</v>
+      </c>
+      <c r="I938" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J938" t="n">
+        <v>4</v>
+      </c>
+      <c r="K938" t="inlineStr">
+        <is>
+          <t>guerra</t>
+        </is>
+      </c>
+      <c r="L938" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M938" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N938" t="inlineStr">
+        <is>
+          <t>war</t>
+        </is>
+      </c>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>Nunca más la niñez en la guerra: Bienestar Familiar reitera su llamado a dejar a los niños y niñas por fuera del conflicto</t>
+        </is>
+      </c>
+      <c r="B939" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivAFBVV95cUxNRmNwei1tTGdKdWl3Q0JIQm1aWlg2bk1kN0NmTVZOS3UtYmZ2RzFmbTFYWVYxV3dHUmcwc3JZUDdSa3ZYeGZHS3ZaTHBETmFOc25falh3WkVxdVJ1RExkMWdPcC1yUTdWemhqc1l0VGVGMHJFZnUzVlFFZGpaazNpNGFLX0pqWTkxalF3a0ZydTljeGN0MjQyYjdJcmQ5YU5MVHEtbEpYVGVuX0dRc2NvQkQ1bG41X1g5cVdOMQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C939" t="inlineStr">
+        <is>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D939" t="inlineStr"/>
+      <c r="E939" t="inlineStr"/>
+      <c r="F939" t="n">
+        <v>0</v>
+      </c>
+      <c r="G939" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H939" t="n">
+        <v>3</v>
+      </c>
+      <c r="I939" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J939" t="n">
+        <v>4</v>
+      </c>
+      <c r="K939" t="inlineStr">
+        <is>
+          <t>dejar</t>
+        </is>
+      </c>
+      <c r="L939" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M939" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N939" t="inlineStr">
+        <is>
+          <t>leave</t>
+        </is>
+      </c>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>Nunca más la niñez en la guerra: Bienestar Familiar reitera su llamado a dejar a los niños y niñas por fuera del conflicto</t>
+        </is>
+      </c>
+      <c r="B940" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivAFBVV95cUxNRmNwei1tTGdKdWl3Q0JIQm1aWlg2bk1kN0NmTVZOS3UtYmZ2RzFmbTFYWVYxV3dHUmcwc3JZUDdSa3ZYeGZHS3ZaTHBETmFOc25falh3WkVxdVJ1RExkMWdPcC1yUTdWemhqc1l0VGVGMHJFZnUzVlFFZGpaazNpNGFLX0pqWTkxalF3a0ZydTljeGN0MjQyYjdJcmQ5YU5MVHEtbEpYVGVuX0dRc2NvQkQ1bG41X1g5cVdOMQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C940" t="inlineStr">
+        <is>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D940" t="inlineStr"/>
+      <c r="E940" t="inlineStr"/>
+      <c r="F940" t="n">
+        <v>0</v>
+      </c>
+      <c r="G940" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H940" t="n">
+        <v>3</v>
+      </c>
+      <c r="I940" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J940" t="n">
+        <v>4</v>
+      </c>
+      <c r="K940" t="inlineStr">
+        <is>
+          <t>conflicto</t>
+        </is>
+      </c>
+      <c r="L940" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M940" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N940" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N940"/>
+  <dimension ref="A1:N942"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52666,6 +52666,114 @@
         </is>
       </c>
     </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>Ni un menor entregado: Icbf confirmó que el Clan del Golfo no ha cumplido el punto más sensible de la mesa con el Gobierno</t>
+        </is>
+      </c>
+      <c r="B941" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi-gFBVV95cUxQRVpSNE5NX1FWcUtYWHFnR3g4N1hOZWsyVF8xYUw0c3U1MDJFeVMwcmFacHFxZGtjQ3J6TzE0Mjc2T0ktQnBnMERwRWh0TmV3bVR0R1BpWko5QkhhV2wzNko2WDhBTWxtcVYzNXZBcU1pczFiVVlQbjdaZHQxVVhvLVU3cTRGNS0tV0IybndEUHhiZHpkTXlCbk82NjJVSVEwcEJGbFRqeVFiWkFuSkNRNkhTNWc0dUdZZjZXaWkwTFpuUWxhNkRLeXhlZWxHODNhNVFPaEF6WHlUeUtLUXhtLS1Tb2h5azhPQ1RFMm96WTlCWjNtS1dEZXFn0gGUAkFVX3lxTFBybjltSEpuS0hhalkwUXVEcEJPd3dUbFQ2al9uR3l3Y2U1eHJaSEUtWi1WMFBVUGJrZXBReDAwM0RVdFh4VHlNZWVib0JiYWdxem9WS1RZMGZXb1d6NVBOVmZ2Tk56Yy1HdEFCRXdGUjV1UTB6dzc4eXpsVVJEdUdldWNJb2ZMQUM1OUxWZkJVOUVSSjJJWktVVWtVNEVlUnhfSXRVWEh3emNuT3ZMQ1pkTFlkYXFqRVpJXzlkaW1UdFhqcnlQM0lsVDA1Z2J3MDBoYzRVT0FHUEROMFRMd1R6QVV4T3o4eDFFNUVTODlXb0ppbU9kU0pFS0dMTERRSXZjcHJqUG9yT1NMRHk2bjBNRS1lZw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C941" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D941" t="inlineStr"/>
+      <c r="E941" t="inlineStr"/>
+      <c r="F941" t="n">
+        <v>0</v>
+      </c>
+      <c r="G941" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H941" t="n">
+        <v>3</v>
+      </c>
+      <c r="I941" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J941" t="n">
+        <v>4</v>
+      </c>
+      <c r="K941" t="inlineStr">
+        <is>
+          <t>cumplido</t>
+        </is>
+      </c>
+      <c r="L941" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M941" t="n">
+        <v>2</v>
+      </c>
+      <c r="N941" t="inlineStr">
+        <is>
+          <t>fulfilled</t>
+        </is>
+      </c>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>Ni un menor entregado: Icbf confirmó que el Clan del Golfo no ha cumplido el punto más sensible de la mesa con el Gobierno</t>
+        </is>
+      </c>
+      <c r="B942" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi-gFBVV95cUxQRVpSNE5NX1FWcUtYWHFnR3g4N1hOZWsyVF8xYUw0c3U1MDJFeVMwcmFacHFxZGtjQ3J6TzE0Mjc2T0ktQnBnMERwRWh0TmV3bVR0R1BpWko5QkhhV2wzNko2WDhBTWxtcVYzNXZBcU1pczFiVVlQbjdaZHQxVVhvLVU3cTRGNS0tV0IybndEUHhiZHpkTXlCbk82NjJVSVEwcEJGbFRqeVFiWkFuSkNRNkhTNWc0dUdZZjZXaWkwTFpuUWxhNkRLeXhlZWxHODNhNVFPaEF6WHlUeUtLUXhtLS1Tb2h5azhPQ1RFMm96WTlCWjNtS1dEZXFn0gGUAkFVX3lxTFBybjltSEpuS0hhalkwUXVEcEJPd3dUbFQ2al9uR3l3Y2U1eHJaSEUtWi1WMFBVUGJrZXBReDAwM0RVdFh4VHlNZWVib0JiYWdxem9WS1RZMGZXb1d6NVBOVmZ2Tk56Yy1HdEFCRXdGUjV1UTB6dzc4eXpsVVJEdUdldWNJb2ZMQUM1OUxWZkJVOUVSSjJJWktVVWtVNEVlUnhfSXRVWEh3emNuT3ZMQ1pkTFlkYXFqRVpJXzlkaW1UdFhqcnlQM0lsVDA1Z2J3MDBoYzRVT0FHUEROMFRMd1R6QVV4T3o4eDFFNUVTODlXb0ppbU9kU0pFS0dMTERRSXZjcHJqUG9yT1NMRHk2bjBNRS1lZw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C942" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D942" t="inlineStr"/>
+      <c r="E942" t="inlineStr"/>
+      <c r="F942" t="n">
+        <v>0</v>
+      </c>
+      <c r="G942" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H942" t="n">
+        <v>3</v>
+      </c>
+      <c r="I942" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J942" t="n">
+        <v>4</v>
+      </c>
+      <c r="K942" t="inlineStr">
+        <is>
+          <t>sensible</t>
+        </is>
+      </c>
+      <c r="L942" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M942" t="n">
+        <v>2</v>
+      </c>
+      <c r="N942" t="inlineStr">
+        <is>
+          <t>responsive</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N942"/>
+  <dimension ref="A1:N944"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52774,6 +52774,118 @@
         </is>
       </c>
     </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>CityNoticias: familias protestan por presuntos abusos a menores por el ICBF</t>
+        </is>
+      </c>
+      <c r="B943" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMitAFBVV95cUxQTzNkZmNXVWZlQ3R2akFuS3podTRMOFVGOEdjenVLMHh4ZXhOX1pmd0xqbTZCaFJOQmh1Y1dmNmdqQmNfY0pKUURkRXNXYUdhcEJubzY0VHN2aDJBQk52a1V3ZmtuWEFtanlqTUNDTlFmTUFMRVhnM2ZWcXZVSHlqbFBIQzZBT2RxT2ZwaWJoaW96Tzk5OXlZSHJ5NHE4RjRTZUxoYmNKRDBRNk5Kc2ZBdWhQYWzSAboBQVVfeXFMUERBYjU5SWgzVEUwc1JyQjYtTlBqM1BSWjFGVWIzZndGWGppZTFIWjBWNWlRc3VqVjN1UTZqREpZWEZZM0ZNMDdBSUQwYjJNdmZnalJLaThjZU1iQ2p4NXlBajBVc2lkNl9DdnNmbWNzTkJac3A5R0RfLU54SGNpNEg3U0cwMzh0WlVZNTF4ektrX1dBRFNOVUFweFZ3dm9uQUNwQUtfczYzS25jdW9XSU1HRjR1Vl9NdmZR?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C943" t="inlineStr">
+        <is>
+          <t>ELTIEMPO.com</t>
+        </is>
+      </c>
+      <c r="D943" t="inlineStr"/>
+      <c r="E943" t="inlineStr"/>
+      <c r="F943" t="n">
+        <v>0</v>
+      </c>
+      <c r="G943" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H943" t="n">
+        <v>3</v>
+      </c>
+      <c r="I943" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J943" t="n">
+        <v>6</v>
+      </c>
+      <c r="K943" t="inlineStr">
+        <is>
+          <t>abusos</t>
+        </is>
+      </c>
+      <c r="L943" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M943" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N943" t="inlineStr">
+        <is>
+          <t>abuses</t>
+        </is>
+      </c>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>Madres bloquearon la carrera 68 en Bogotá por presuntos abusos contra menores en centros del ICBF; Policía envió a la UNDMO para despejar la vía</t>
+        </is>
+      </c>
+      <c r="B944" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMikAJBVV95cUxPSElaU0RXNlRBeVVfeE5uS2xpdkZzWHE5X0VfTUROaHFhNkx6MGZtT2dqUHhpVmdvZUZ0MjYxY3ppby1tZW15T1gza3g1dTdhbWJHZEctbG5mbHZfNWFqSEtGMEdIbDVZSVRSb2FNeVFGbHRfT0d3LXByRDRCTWIzSDRkdnN2SUNSR01BSDZUOG01QUtKSE9PRFJTRUF6THlIMzVoSC1MR2tQRnEzWDRkay1TLTV5Y2VuNk00LXk3ZUQ3M0tUdkZuY3lwM3FPMFg4SENrWl84dXZKUndmWThjTGxRQlIxT053WDYtb3RLMVpmTTFmalBZSzlzR3VGbVlNN1lPblpmYTI5cjVJZFlhQ9IBlgJBVV95cUxOTl9rZnlxZGVYQjVlMFlzR2hBVVEtSjZnOG42V1RwSVV5LVl6SW51cU1HWlo4TlRJVXo1eU13SlFhWFczbmp4ZF9vNVVXVENiS1BWVXN4UldYMldrS0FmVHJpWWtpaFMxSnBJdUJvTmctN1ZXLVQ3ZHV2aHk3RmFGRHYwN2JQcGxMbDQzWVZtVVdhUnQ2TDJ2a3hUcFNTY29yTHFleFhxWEVaNVlSWk9LMzVmbUVwWlVCNkEwYmRod1FaWXhnMzVHTWdWQzVxTDJ6aTJtUENqUGFmVktRM0tHeDNLMjYtNURNbGFRODV6bTdoM2J4RUd5LVhDSjZ5dThZM0QyS1RYdFNTTUo2VWxrcHdEem00QQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C944" t="inlineStr">
+        <is>
+          <t>ELTIEMPO.com</t>
+        </is>
+      </c>
+      <c r="D944" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E944" t="inlineStr"/>
+      <c r="F944" t="n">
+        <v>0</v>
+      </c>
+      <c r="G944" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H944" t="n">
+        <v>3</v>
+      </c>
+      <c r="I944" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J944" t="n">
+        <v>6</v>
+      </c>
+      <c r="K944" t="inlineStr">
+        <is>
+          <t>abusos</t>
+        </is>
+      </c>
+      <c r="L944" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M944" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N944" t="inlineStr">
+        <is>
+          <t>abuses</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N944"/>
+  <dimension ref="A1:N945"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52886,6 +52886,64 @@
         </is>
       </c>
     </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>Arte y territorio: adolescentes del Cauca crean un mural por la paz</t>
+        </is>
+      </c>
+      <c r="B945" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMioAFBVV95cUxOYmlVcDVOQ3lJUXA1eFphSGhqcUsxLUNnOWxLVFUtNUY0Y2FYRDhiNFk0SjNKb0s1SmZSUlpnSmF4aGNqZE5NRUMxNDNvRGtiZGtRN2IxZmxUVy05ZTFIcmt2Zy1ZaWlZZFhVYTBNUV90TmRldC1NcVJzeEFNRVp3Qk1QQ2ZBcXlRVUJJbmJtamFsR3lDVUVJeWNoU093NFlD?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C945" t="inlineStr">
+        <is>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D945" t="inlineStr"/>
+      <c r="E945" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="F945" t="n">
+        <v>0</v>
+      </c>
+      <c r="G945" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H945" t="n">
+        <v>3</v>
+      </c>
+      <c r="I945" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J945" t="n">
+        <v>6</v>
+      </c>
+      <c r="K945" t="inlineStr">
+        <is>
+          <t>paz</t>
+        </is>
+      </c>
+      <c r="L945" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M945" t="n">
+        <v>2</v>
+      </c>
+      <c r="N945" t="inlineStr">
+        <is>
+          <t>peace</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N945"/>
+  <dimension ref="A1:N946"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52944,6 +52944,60 @@
         </is>
       </c>
     </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>Esta es la propiedad que pertenecía al narcotráfico y ahora será un centro de emergencia para niños migrantes en el Urabá</t>
+        </is>
+      </c>
+      <c r="B946" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi7gFBVV95cUxPY3B1YnpJVVprb3hoZTg2Snh1a1IyOWdOQ2tFWEw1bkc4Vm42NVRuUFhUenJzWEplUkhySGQwZ3d6RzhUX2JUNDc2WDY4SVQySjR3SG44bGVnQkF6Z0VaMlhnb09HemhQcHFONi1jZERMZ2o2MFh2cjVLazN2QTItXzJSeWVCNGdZTUs0VE9UR2hyU2s3S3JiQ1JrdGdEcDVkN3M4czF0NG1XZVd0MkpiVjJscG5aUkRIOTZNTGNWaTZhQ2RWQzhjSGtHRm01eDFwMDhQUHlZbkM2MVdNakhkNEVwRC1ZZ3ZyN0p6emNn0gGIAkFVX3lxTE84UUIxMnI1X0tLNmNNNWp0MWM1YVpRdWh2LUphamVTWEJmS0ZleUZ3NXIxVmp3X3FpMjBOb2VmeVh4eTVyRGpabVh3VlVmZ2dhMkllSWkxYXdoelh5N29ySjRTaVZwaHpHSGs0RHBJbGdMYlV5eVV1VlJXRDJieHloRmYzNDhHRUlJN2lmSlVLdXFGSlFJZnI3dW92X2RxakRyUWVYWG1Ibjh5b1FtT0ZVQ01JWU41OUR4MmxibFJfSms0LURmYkxCZENZbGNENlZId3hud0VwTmtsMmlibXlqbGtsU0pFVkdhUEFRSFFQeFBLdWQzT3I2YUxrVXYyMW5zcndNeTdUTA?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C946" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D946" t="inlineStr"/>
+      <c r="E946" t="inlineStr"/>
+      <c r="F946" t="n">
+        <v>0</v>
+      </c>
+      <c r="G946" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H946" t="n">
+        <v>3</v>
+      </c>
+      <c r="I946" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J946" t="n">
+        <v>4</v>
+      </c>
+      <c r="K946" t="inlineStr">
+        <is>
+          <t>emergencia</t>
+        </is>
+      </c>
+      <c r="L946" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M946" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N946" t="inlineStr">
+        <is>
+          <t>emergency</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N946"/>
+  <dimension ref="A1:N947"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -52998,6 +52998,64 @@
         </is>
       </c>
     </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>La Guajira fortalece su soberanía alimentaria y el bienestar de las familias a través de proyectos productivos</t>
+        </is>
+      </c>
+      <c r="B947" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivAFBVV95cUxNUDM1ZmRKVmQwQTlad1JoVG1ySnBqT3FlaENkUTJPLURESnZKUnRBVHdMQnNYRllEa2hHaVV0OW5OSENTa1JEaWFMVE5yWnRwb3ZNYlNfLW5sdEZUVENmekp3QndtYkVNVG9jdVBqNzRqLUJJa0FTa3o1eTFENkYwVlFnc0lLVTdEeUtfWHctdDJ0V3dfbkd5cER0aWJxVUZRanpZWGRxSThPNXVXSlJxYnV4b0ZTbG83cy1uYg?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C947" t="inlineStr">
+        <is>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D947" t="inlineStr"/>
+      <c r="E947" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="F947" t="n">
+        <v>0</v>
+      </c>
+      <c r="G947" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H947" t="n">
+        <v>3</v>
+      </c>
+      <c r="I947" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="J947" t="n">
+        <v>7</v>
+      </c>
+      <c r="K947" t="inlineStr">
+        <is>
+          <t>fortalece</t>
+        </is>
+      </c>
+      <c r="L947" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M947" t="n">
+        <v>2</v>
+      </c>
+      <c r="N947" t="inlineStr">
+        <is>
+          <t>strengthens</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N947"/>
+  <dimension ref="A1:N949"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53056,6 +53056,114 @@
         </is>
       </c>
     </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>ICBF y Ministerio del Trabajo comienzan pagos de subsidio de más de $ 1 millón en 2026: beneficio llega par...</t>
+        </is>
+      </c>
+      <c r="B948" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMigwJBVV95cUxPZDQxMVZSNzRWNWMtZUxpZmpJSmN1QldBUU5CclhUNkUxT0h5aHVKblI2RWNBMzd4YXh1SkhYa29XRTFCYmdXbENBZ1FfbEJZVW4yRlEzaUxENUJ4UUdkQ2ZUcDRfeVIxaTJvN0N5RjMwLU9qWXpsc0dxcTZaR0VZa0dtdUdzRE0yb0pqTFUyYWowb1p5QWFJZmp0TmFGSFBxNjd3alo2WGwydThjOGFXSEFkc2NseWk0cDk2cU8zOEN6M2tIdHBpWTNVbFpMMlhfZldaMkd6QnhLcF8ya052MHRsMVlFT0V3SEdRdzRRQ0VxbkdMWU50a0RwWmo2TUNucEtR0gGIAkFVX3lxTE5tOTh5cUxnMjlYVVFidGFqQ2lLM21OYVdrcmZNUXdvbS1PbHRDdEk2eFhxZHJZYW1pTmtoXzJXOHlUN2NFaDlteTdyakpzTmNjNWFmRmtNNG82Rnhhdy1nMFpwakc3QWE1aWhKNGlSWnc1R3RWNTBNSldNYnFnTGluTUFjYWl3eFJUby0yRWxVZmpuR0RrbFV1LUJfV3FfM3ZuNm5HYklOdDRHSnlTNlVkalFtUVRfdUlEbUc0N21ObGJraGtkUVBITllHdlZaMm9sVTNEWEQzeTdYRkRGdDdWY2luakI3YU1tb0wxbEZEVnd3bjZ4M3VQOG9haERVVG1XZTcyM3RHdQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C948" t="inlineStr">
+        <is>
+          <t>redmas.com.co</t>
+        </is>
+      </c>
+      <c r="D948" t="inlineStr"/>
+      <c r="E948" t="inlineStr"/>
+      <c r="F948" t="n">
+        <v>0</v>
+      </c>
+      <c r="G948" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H948" t="n">
+        <v>3</v>
+      </c>
+      <c r="I948" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="J948" t="n">
+        <v>7</v>
+      </c>
+      <c r="K948" t="inlineStr">
+        <is>
+          <t>beneficio</t>
+        </is>
+      </c>
+      <c r="L948" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M948" t="n">
+        <v>2</v>
+      </c>
+      <c r="N948" t="inlineStr">
+        <is>
+          <t>benefit</t>
+        </is>
+      </c>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>Operativo en la Comuna 1 de Soacha permitió el rescate de dos menores de edad</t>
+        </is>
+      </c>
+      <c r="B949" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiygFBVV95cUxPMkEtWHpsaE5mNFJTcGlZMl9yVUs5NmpKUjNfNm1pZVJKV3FaZlg1MVVTdVNXZ1pPanlnMnROdmhpNVRneGpRMnU0YkhLaEtpNWFtQXEzWnhFUzhxUVJKSW9jcU9TdWlSMjN2cnpweUh6cjJwQTlKcmcwWE9Ra091ZExIZXVXbXFwQ2hVWTdhMFhJenpvNGFnOXNrRG5OdHJWNWdlSEJnMjlNNEY2N1drMFNORkZmbzBzajVUdGdWanZCSWRaSDFpYVdn0gHSAUFVX3lxTFByTDFmY25lQUhJV1lXSzhzY1ZIQ0ZDT0NpMk50YVc4aDBFcXFWVHFaYnp1V2lsdlN1MUl3Qnd3UmRLNVliV3RBWFRmbndNdkVpbGhNZlEwbTBaQ0tzV1BBalNjNXNRVDQ3MktJMHhrbm0yelJseWRrNTNmMzNZTkw0eW9hWHVseThxSlQtdFNpeU1VTVVwQjdxOC1IY2ItR0ViYWdhSlBydzgtOHI1Y3B1OWxQOGpadHRzcmZPZHJwWEFXWGFuUlJrNGZheTlMcHdtdw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C949" t="inlineStr">
+        <is>
+          <t>City Tv</t>
+        </is>
+      </c>
+      <c r="D949" t="inlineStr"/>
+      <c r="E949" t="inlineStr"/>
+      <c r="F949" t="n">
+        <v>0</v>
+      </c>
+      <c r="G949" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H949" t="n">
+        <v>3</v>
+      </c>
+      <c r="I949" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="J949" t="n">
+        <v>7</v>
+      </c>
+      <c r="K949" t="inlineStr">
+        <is>
+          <t>rescate</t>
+        </is>
+      </c>
+      <c r="L949" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M949" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N949" t="inlineStr">
+        <is>
+          <t>bailout</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N949"/>
+  <dimension ref="A1:N950"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53164,6 +53164,60 @@
         </is>
       </c>
     </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>Rescatan a dos menores en presunto estado de abandono durante operativo en la Comuna 1 de Soacha tras alerta de los vecinos: esto se sabe</t>
+        </is>
+      </c>
+      <c r="B950" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiggJBVV95cUxPQkthN3NTQ1IwUERlOW1lTk14MFI3LWVkV3MxSnRZZ1RfVUxCaWhVTFJxT0x2VTlPNDlRWGxpcVB2Q09Gb3RHX1FpVWlpZ09iVEVyd3ZWNFA5WVFZRmtNclk5dkZNNkl2ZHJOS3RQZFdCeEZfQzc4VFU5TkQwUzJCYklFWnM4Ti1mZHQtcC1fX0dJOTk2a19vZVRnZ2szVGNqN1RDYlhZVlpZSnJ0MlNuc0VQT2JIZkt4QWF2S3pCaW5GQjdQVWtYa0VodlhlR1NMcDFSYmlxdm1Ya3VpMTRBdzdmZVRscnMwa1NNZnY3aVBUcVRyTUdKcktFQ2pESGM3X3fSAYcCQVVfeXFMTzVUZHJveE0zMTZ4bXFHQllCSHlQYUZ1NlNmZmkyZHpnbjU4RDhLbGViUHVBZjdwMDdhcGptYUJBSDU4NlE1UzB2Ul9qVEltUm9GSlhNcTJ6SFVFNm5SZ09xYVNYR0FZelNoSlZldG1rNTZIYktSZThpQXJ0Yy1YVzFRUk5fNGJJUlBWalh1ZGwtb2lIdGFHMU81dER2alZlbE9SNHp5bV80cWY4S2VNNy1nU0dPV2hYMVI0ejVjaE1MdmdkVmZOMVdBQWVFNWQ4eVZCWEQzeVVBZzJVUmRwYjJ5X2JBNk9FeWx6aFdJcnR4NWc0VWh6djRpSVlyRjFvdkt6MTNDRHM?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C950" t="inlineStr">
+        <is>
+          <t>ELTIEMPO.com</t>
+        </is>
+      </c>
+      <c r="D950" t="inlineStr"/>
+      <c r="E950" t="inlineStr"/>
+      <c r="F950" t="n">
+        <v>0</v>
+      </c>
+      <c r="G950" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H950" t="n">
+        <v>3</v>
+      </c>
+      <c r="I950" t="inlineStr">
+        <is>
+          <t>domingo</t>
+        </is>
+      </c>
+      <c r="J950" t="n">
+        <v>8</v>
+      </c>
+      <c r="K950" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="L950" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M950" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N950" t="inlineStr">
+        <is>
+          <t>alert</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N950"/>
+  <dimension ref="A1:N951"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53218,6 +53218,60 @@
         </is>
       </c>
     </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>Astrid Cáceres, nueva diretora del ICBF se propone transformar la entidad y dar respuesta oportuna y eficaz para la atención de la niñez – ALTERNATIVACARIBE</t>
+        </is>
+      </c>
+      <c r="B951" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiigJBVV95cUxOaDlScVljR0JNNGhITUxIaDhjejhwMlJvNGRwRmJzVnVfTkdaVlhUZjdaWm05U3VJcDZaM2U4a0o5WlJQTWl2U090Mi1nc3doeWxDSERRQ2o4RlQ3U2p2THlncUVZaHJFSDA1aU5OdUNtNFplemxHRmNzbGtrcFNudVJjdVQ2ZnJkcVJrNG91U0VuY2dHeUFZeUZZWkY2XzhEOFJnTXRzYzlCZllHQTFCNHhlSE5YMURkWkJibWg1WUl4TFdrUUNqM3lDS2dIbVk4cDBSVHJxcWtTbUVuUVhPZDBaSVZ5WTQ4MjY5R1hab3d2WWdUZkdyYUVGdWwxZVkxSDZ2aUhyVmZvUQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C951" t="inlineStr">
+        <is>
+          <t>Alternativa Caribe</t>
+        </is>
+      </c>
+      <c r="D951" t="inlineStr"/>
+      <c r="E951" t="inlineStr"/>
+      <c r="F951" t="n">
+        <v>0</v>
+      </c>
+      <c r="G951" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H951" t="n">
+        <v>2</v>
+      </c>
+      <c r="I951" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J951" t="n">
+        <v>9</v>
+      </c>
+      <c r="K951" t="inlineStr">
+        <is>
+          <t>eficaz</t>
+        </is>
+      </c>
+      <c r="L951" t="inlineStr">
+        <is>
+          <t>Astrid Cáceres</t>
+        </is>
+      </c>
+      <c r="M951" t="n">
+        <v>2</v>
+      </c>
+      <c r="N951" t="inlineStr">
+        <is>
+          <t>effective</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N951"/>
+  <dimension ref="A1:N952"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53272,6 +53272,60 @@
         </is>
       </c>
     </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>ICBF y Ministerio del Trabajo pagarán subsidio de más de $ 1 millón en 2026: beneficio llega a miles de muj...</t>
+        </is>
+      </c>
+      <c r="B952" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMigwJBVV95cUxPZDQxMVZSNzRWNWMtZUxpZmpJSmN1QldBUU5CclhUNkUxT0h5aHVKblI2RWNBMzd4YXh1SkhYa29XRTFCYmdXbENBZ1FfbEJZVW4yRlEzaUxENUJ4UUdkQ2ZUcDRfeVIxaTJvN0N5RjMwLU9qWXpsc0dxcTZaR0VZa0dtdUdzRE0yb0pqTFUyYWowb1p5QWFJZmp0TmFGSFBxNjd3alo2WGwydThjOGFXSEFkc2NseWk0cDk2cU8zOEN6M2tIdHBpWTNVbFpMMlhfZldaMkd6QnhLcF8ya052MHRsMVlFT0V3SEdRdzRRQ0VxbkdMWU50a0RwWmo2TUNucEtR0gGIAkFVX3lxTE5tOTh5cUxnMjlYVVFidGFqQ2lLM21OYVdrcmZNUXdvbS1PbHRDdEk2eFhxZHJZYW1pTmtoXzJXOHlUN2NFaDlteTdyakpzTmNjNWFmRmtNNG82Rnhhdy1nMFpwakc3QWE1aWhKNGlSWnc1R3RWNTBNSldNYnFnTGluTUFjYWl3eFJUby0yRWxVZmpuR0RrbFV1LUJfV3FfM3ZuNm5HYklOdDRHSnlTNlVkalFtUVRfdUlEbUc0N21ObGJraGtkUVBITllHdlZaMm9sVTNEWEQzeTdYRkRGdDdWY2luakI3YU1tb0wxbEZEVnd3bjZ4M3VQOG9haERVVG1XZTcyM3RHdQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C952" t="inlineStr">
+        <is>
+          <t>redmas.com.co</t>
+        </is>
+      </c>
+      <c r="D952" t="inlineStr"/>
+      <c r="E952" t="inlineStr"/>
+      <c r="F952" t="n">
+        <v>0</v>
+      </c>
+      <c r="G952" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H952" t="n">
+        <v>3</v>
+      </c>
+      <c r="I952" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="J952" t="n">
+        <v>7</v>
+      </c>
+      <c r="K952" t="inlineStr">
+        <is>
+          <t>beneficio</t>
+        </is>
+      </c>
+      <c r="L952" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M952" t="n">
+        <v>2</v>
+      </c>
+      <c r="N952" t="inlineStr">
+        <is>
+          <t>benefit</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N952"/>
+  <dimension ref="A1:N953"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53326,6 +53326,60 @@
         </is>
       </c>
     </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>Bienestar familiar fortalece el talento artístico de la niñez y adolescencia con discapacidad</t>
+        </is>
+      </c>
+      <c r="B953" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiuAFBVV95cUxNV1pRd2NuYUdwVFRFdW1fbjc0d2JyTHFEU2xLXzBlUEt1ejZGa2JGWXl6cVlta0xYWmFyVFdXejNtRzI3YVZ6dXZ3U3pUSjRtcUhTUlZVR1JRX18wcVJPWjhGT1hDeW5rZ3QwcC1QT0lmdVd0YjVtZVNlbjZ3YlhQSTFmMHFPcHpNdW5FUGpaOUtlWXJSMUUyU1dzUnp4RUZBVVQ1QXB2azVUVm5Cd1BwSEt5aExCU245?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C953" t="inlineStr">
+        <is>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D953" t="inlineStr"/>
+      <c r="E953" t="inlineStr"/>
+      <c r="F953" t="n">
+        <v>0</v>
+      </c>
+      <c r="G953" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H953" t="n">
+        <v>5</v>
+      </c>
+      <c r="I953" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J953" t="n">
+        <v>19</v>
+      </c>
+      <c r="K953" t="inlineStr">
+        <is>
+          <t>fortalece</t>
+        </is>
+      </c>
+      <c r="L953" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M953" t="n">
+        <v>2</v>
+      </c>
+      <c r="N953" t="inlineStr">
+        <is>
+          <t>strengthens</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N953"/>
+  <dimension ref="A1:N954"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53380,6 +53380,60 @@
         </is>
       </c>
     </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>La aprobación de la reforma laboral permitirá la formalización de 60 mil madres comunitarias, sustitutas y trabajadoras de hogares infantiles | Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="B954" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMisgFBVV95cUxPVDVzVHpFNC1JMDU4Z052RzBQN0RtaTdFa1lnb1c5YWRTZ0VZNHpyVVJDQmVndXRad0pfaUtiRWFXLWZjOWl2TXRtaGFycmsyLXZfWkVaQVRHSEJvcHhnM2FBWTl3S3pIcXk5Qm5fQ2JUY1ZEUmNhV2VGM25fRHBsMlB3ZFQ5clVUbjRfbDdFeTZlSUFiczhLcFdaY3NhN3FiN3BGc1RmNUw0SjRXVWRVWUt3?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C954" t="inlineStr">
+        <is>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D954" t="inlineStr"/>
+      <c r="E954" t="inlineStr"/>
+      <c r="F954" t="n">
+        <v>0</v>
+      </c>
+      <c r="G954" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H954" t="n">
+        <v>3</v>
+      </c>
+      <c r="I954" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J954" t="n">
+        <v>13</v>
+      </c>
+      <c r="K954" t="inlineStr">
+        <is>
+          <t>aprobación</t>
+        </is>
+      </c>
+      <c r="L954" t="inlineStr">
+        <is>
+          <t>Astrid Cáceres</t>
+        </is>
+      </c>
+      <c r="M954" t="n">
+        <v>2</v>
+      </c>
+      <c r="N954" t="inlineStr">
+        <is>
+          <t>approval</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N954"/>
+  <dimension ref="A1:N959"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53434,6 +53434,300 @@
         </is>
       </c>
     </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar articula acciones para fortalecer la protección de la niñez en contextos migratorios en Arauca</t>
+        </is>
+      </c>
+      <c r="B955" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMitAFBVV95cUxOQm5KVmtnN3FKNzNlbnRpcDNnbWRDUTJCSDFkUGpkd2xaWGdyZ1JFOWlhX3ZudWxvTWFWTnVQLVdIUGZMbUlWd2p5UmRfMWRUR0JkVXF6aVJ1cHM4cnRUQTVKb3Z2aFRDdlVhWnRiSGoxYXFPRi1mNG9HMHBkUTlIRDFJOHpiXy1mWmRscFd0dFZkclNzbnBXcDRNZFNnd0I3MlpYMEphcm9jald6WWpxMXFLcFo?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C955" t="inlineStr">
+        <is>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D955" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="E955" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="F955" t="n">
+        <v>0</v>
+      </c>
+      <c r="G955" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H955" t="n">
+        <v>3</v>
+      </c>
+      <c r="I955" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J955" t="n">
+        <v>10</v>
+      </c>
+      <c r="K955" t="inlineStr">
+        <is>
+          <t>fortalecer</t>
+        </is>
+      </c>
+      <c r="L955" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M955" t="n">
+        <v>2</v>
+      </c>
+      <c r="N955" t="inlineStr">
+        <is>
+          <t>strengthen</t>
+        </is>
+      </c>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>La Regional Antioquia del Bienestar Familiar fortalece el acceso a la justicia para niñas, niños y adolescentes víctimas de violencia intrafamiliar | Portal ICBF - Instituto Colombiano de Bienestar</t>
+        </is>
+      </c>
+      <c r="B956" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivAFBVV95cUxPbTNQMWZzWHhkNEI5dWtCOGlYbWkxbEtCWE9VSEpVVjN3SndtaWtFWnhpQnJSOTItOEl0cjJ4WmlDLW15UThvRVJOcTFLWjNqZWl3YllXbl9BeVplbzNMMl95TGtGeEtRLUFzNFBHM0FEeGEyWmJWdGRXYkFSRl9ZU0g0Sl9KaFdiYlc5UVpFdmh1eXZyTnRSTDhJa3JaRU1vajQ0SUVCeHBzY2tTQ0lrNHpCWHpfZDVsWHZuYw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C956" t="inlineStr">
+        <is>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D956" t="inlineStr"/>
+      <c r="E956" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="F956" t="n">
+        <v>0</v>
+      </c>
+      <c r="G956" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H956" t="n">
+        <v>3</v>
+      </c>
+      <c r="I956" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J956" t="n">
+        <v>6</v>
+      </c>
+      <c r="K956" t="inlineStr">
+        <is>
+          <t>fortalece</t>
+        </is>
+      </c>
+      <c r="L956" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M956" t="n">
+        <v>2</v>
+      </c>
+      <c r="N956" t="inlineStr">
+        <is>
+          <t>strengthens</t>
+        </is>
+      </c>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>La Regional Antioquia del Bienestar Familiar fortalece el acceso a la justicia para niñas, niños y adolescentes víctimas de violencia intrafamiliar | Portal ICBF - Instituto Colombiano de Bienestar</t>
+        </is>
+      </c>
+      <c r="B957" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivAFBVV95cUxPbTNQMWZzWHhkNEI5dWtCOGlYbWkxbEtCWE9VSEpVVjN3SndtaWtFWnhpQnJSOTItOEl0cjJ4WmlDLW15UThvRVJOcTFLWjNqZWl3YllXbl9BeVplbzNMMl95TGtGeEtRLUFzNFBHM0FEeGEyWmJWdGRXYkFSRl9ZU0g0Sl9KaFdiYlc5UVpFdmh1eXZyTnRSTDhJa3JaRU1vajQ0SUVCeHBzY2tTQ0lrNHpCWHpfZDVsWHZuYw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C957" t="inlineStr">
+        <is>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D957" t="inlineStr"/>
+      <c r="E957" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="F957" t="n">
+        <v>0</v>
+      </c>
+      <c r="G957" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H957" t="n">
+        <v>3</v>
+      </c>
+      <c r="I957" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J957" t="n">
+        <v>6</v>
+      </c>
+      <c r="K957" t="inlineStr">
+        <is>
+          <t>justicia</t>
+        </is>
+      </c>
+      <c r="L957" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M957" t="n">
+        <v>2</v>
+      </c>
+      <c r="N957" t="inlineStr">
+        <is>
+          <t>justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>La Regional Antioquia del Bienestar Familiar fortalece el acceso a la justicia para niñas, niños y adolescentes víctimas de violencia intrafamiliar | Portal ICBF - Instituto Colombiano de Bienestar</t>
+        </is>
+      </c>
+      <c r="B958" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivAFBVV95cUxPbTNQMWZzWHhkNEI5dWtCOGlYbWkxbEtCWE9VSEpVVjN3SndtaWtFWnhpQnJSOTItOEl0cjJ4WmlDLW15UThvRVJOcTFLWjNqZWl3YllXbl9BeVplbzNMMl95TGtGeEtRLUFzNFBHM0FEeGEyWmJWdGRXYkFSRl9ZU0g0Sl9KaFdiYlc5UVpFdmh1eXZyTnRSTDhJa3JaRU1vajQ0SUVCeHBzY2tTQ0lrNHpCWHpfZDVsWHZuYw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C958" t="inlineStr">
+        <is>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D958" t="inlineStr"/>
+      <c r="E958" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="F958" t="n">
+        <v>0</v>
+      </c>
+      <c r="G958" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H958" t="n">
+        <v>3</v>
+      </c>
+      <c r="I958" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J958" t="n">
+        <v>6</v>
+      </c>
+      <c r="K958" t="inlineStr">
+        <is>
+          <t>víctimas</t>
+        </is>
+      </c>
+      <c r="L958" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M958" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N958" t="inlineStr">
+        <is>
+          <t>victimized</t>
+        </is>
+      </c>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>La Regional Antioquia del Bienestar Familiar fortalece el acceso a la justicia para niñas, niños y adolescentes víctimas de violencia intrafamiliar | Portal ICBF - Instituto Colombiano de Bienestar</t>
+        </is>
+      </c>
+      <c r="B959" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivAFBVV95cUxPbTNQMWZzWHhkNEI5dWtCOGlYbWkxbEtCWE9VSEpVVjN3SndtaWtFWnhpQnJSOTItOEl0cjJ4WmlDLW15UThvRVJOcTFLWjNqZWl3YllXbl9BeVplbzNMMl95TGtGeEtRLUFzNFBHM0FEeGEyWmJWdGRXYkFSRl9ZU0g0Sl9KaFdiYlc5UVpFdmh1eXZyTnRSTDhJa3JaRU1vajQ0SUVCeHBzY2tTQ0lrNHpCWHpfZDVsWHZuYw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C959" t="inlineStr">
+        <is>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D959" t="inlineStr"/>
+      <c r="E959" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="F959" t="n">
+        <v>0</v>
+      </c>
+      <c r="G959" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H959" t="n">
+        <v>3</v>
+      </c>
+      <c r="I959" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J959" t="n">
+        <v>6</v>
+      </c>
+      <c r="K959" t="inlineStr">
+        <is>
+          <t>violencia</t>
+        </is>
+      </c>
+      <c r="L959" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M959" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N959" t="inlineStr">
+        <is>
+          <t>violence</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N959"/>
+  <dimension ref="A1:N965"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -53728,6 +53728,346 @@
         </is>
       </c>
     </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>El Icbf habría entregado a cuatro niños a una familia en Jordania; uno de ellos murió torturado por sus padres adoptivos</t>
+        </is>
+      </c>
+      <c r="B960" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi9wFBVV95cUxQR1JpS0liWk1rTUtQanNlVnIzUmZZbVlFWi0tRUJPSmlVTk5uVjdLR0d4c1AwZHpieUdlcVZ5Wkh0cEZCSU5rbHJKQnNpMFloLVRRNUpVQTJtZHl6X1lkU1o4S0MxV2pQazBIUktCOWRmREJOMnl3bzFsZl9pRmxoNmJ5ejd2TGlqd2hxaW54b0tjX1hLUkZkbWM5REVZdVVVM0tjZ2RPTkVEa0JDT0l2dVlBVzRwZFNvcE9GZmFEdEFQemw3bkw1UDJTR3JSZG5mek9MVE1odmFzZjVuV2ZRNFd2Tjk0RXY2bF9zaElMcWE5TFZ2bklr0gGSAkFVX3lxTE1QejR4M2tVRlAyeE50ZHoyVWxucnRzNEJ1NEhvZGJ2aHRJX28wcHdleE9tNWFDVEV6RkxXNnhiaElyeE93YWpvSWsyZ2FhMmdndElZYmczRnE2S3dsVGN3QTZQTGM5b29BYnZiMDJ3UGJqd1F4TlVyVm5tSy1iUF82MUhLRFVTSGNMcXIxSGRNM1V0VVAwVVZtZEFLc0F0VjJKVjFabGdzMUQ1Vm9kNmJYNDE1TXZHWnZiTGhLMHBNdHRvUmhhX3JCWHF2ZHN0RHloX21nSTFlbkRuczFoX1htYXFNczZyZ3ZhejNFV3o1UmRlSmhLLXV2MUg4SzZTa3ZFckdwTWd4SW04WkdOMUNYRFE?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C960" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D960" t="inlineStr"/>
+      <c r="E960" t="inlineStr"/>
+      <c r="F960" t="n">
+        <v>0</v>
+      </c>
+      <c r="G960" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H960" t="n">
+        <v>3</v>
+      </c>
+      <c r="I960" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J960" t="n">
+        <v>11</v>
+      </c>
+      <c r="K960" t="inlineStr">
+        <is>
+          <t>murió</t>
+        </is>
+      </c>
+      <c r="L960" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M960" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N960" t="inlineStr">
+        <is>
+          <t>died</t>
+        </is>
+      </c>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>El Icbf habría entregado a cuatro niños a una familia en Jordania; uno de ellos murió torturado por sus padres adoptivos</t>
+        </is>
+      </c>
+      <c r="B961" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi9wFBVV95cUxQR1JpS0liWk1rTUtQanNlVnIzUmZZbVlFWi0tRUJPSmlVTk5uVjdLR0d4c1AwZHpieUdlcVZ5Wkh0cEZCSU5rbHJKQnNpMFloLVRRNUpVQTJtZHl6X1lkU1o4S0MxV2pQazBIUktCOWRmREJOMnl3bzFsZl9pRmxoNmJ5ejd2TGlqd2hxaW54b0tjX1hLUkZkbWM5REVZdVVVM0tjZ2RPTkVEa0JDT0l2dVlBVzRwZFNvcE9GZmFEdEFQemw3bkw1UDJTR3JSZG5mek9MVE1odmFzZjVuV2ZRNFd2Tjk0RXY2bF9zaElMcWE5TFZ2bklr0gGSAkFVX3lxTE1QejR4M2tVRlAyeE50ZHoyVWxucnRzNEJ1NEhvZGJ2aHRJX28wcHdleE9tNWFDVEV6RkxXNnhiaElyeE93YWpvSWsyZ2FhMmdndElZYmczRnE2S3dsVGN3QTZQTGM5b29BYnZiMDJ3UGJqd1F4TlVyVm5tSy1iUF82MUhLRFVTSGNMcXIxSGRNM1V0VVAwVVZtZEFLc0F0VjJKVjFabGdzMUQ1Vm9kNmJYNDE1TXZHWnZiTGhLMHBNdHRvUmhhX3JCWHF2ZHN0RHloX21nSTFlbkRuczFoX1htYXFNczZyZ3ZhejNFV3o1UmRlSmhLLXV2MUg4SzZTa3ZFckdwTWd4SW04WkdOMUNYRFE?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C961" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D961" t="inlineStr"/>
+      <c r="E961" t="inlineStr"/>
+      <c r="F961" t="n">
+        <v>0</v>
+      </c>
+      <c r="G961" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H961" t="n">
+        <v>3</v>
+      </c>
+      <c r="I961" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J961" t="n">
+        <v>11</v>
+      </c>
+      <c r="K961" t="inlineStr">
+        <is>
+          <t>torturado</t>
+        </is>
+      </c>
+      <c r="L961" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M961" t="n">
+        <v>-4</v>
+      </c>
+      <c r="N961" t="inlineStr">
+        <is>
+          <t>tortured</t>
+        </is>
+      </c>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>La Regional Antioquia del Bienestar Familiar fortalece el acceso a la justicia para niñas, niños y adolescentes víctimas de violencia intrafamiliar</t>
+        </is>
+      </c>
+      <c r="B962" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivAFBVV95cUxPbTNQMWZzWHhkNEI5dWtCOGlYbWkxbEtCWE9VSEpVVjN3SndtaWtFWnhpQnJSOTItOEl0cjJ4WmlDLW15UThvRVJOcTFLWjNqZWl3YllXbl9BeVplbzNMMl95TGtGeEtRLUFzNFBHM0FEeGEyWmJWdGRXYkFSRl9ZU0g0Sl9KaFdiYlc5UVpFdmh1eXZyTnRSTDhJa3JaRU1vajQ0SUVCeHBzY2tTQ0lrNHpCWHpfZDVsWHZuYw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C962" t="inlineStr">
+        <is>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D962" t="inlineStr"/>
+      <c r="E962" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="F962" t="n">
+        <v>0</v>
+      </c>
+      <c r="G962" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H962" t="n">
+        <v>3</v>
+      </c>
+      <c r="I962" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J962" t="n">
+        <v>6</v>
+      </c>
+      <c r="K962" t="inlineStr">
+        <is>
+          <t>fortalece</t>
+        </is>
+      </c>
+      <c r="L962" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M962" t="n">
+        <v>2</v>
+      </c>
+      <c r="N962" t="inlineStr">
+        <is>
+          <t>strengthens</t>
+        </is>
+      </c>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>La Regional Antioquia del Bienestar Familiar fortalece el acceso a la justicia para niñas, niños y adolescentes víctimas de violencia intrafamiliar</t>
+        </is>
+      </c>
+      <c r="B963" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivAFBVV95cUxPbTNQMWZzWHhkNEI5dWtCOGlYbWkxbEtCWE9VSEpVVjN3SndtaWtFWnhpQnJSOTItOEl0cjJ4WmlDLW15UThvRVJOcTFLWjNqZWl3YllXbl9BeVplbzNMMl95TGtGeEtRLUFzNFBHM0FEeGEyWmJWdGRXYkFSRl9ZU0g0Sl9KaFdiYlc5UVpFdmh1eXZyTnRSTDhJa3JaRU1vajQ0SUVCeHBzY2tTQ0lrNHpCWHpfZDVsWHZuYw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C963" t="inlineStr">
+        <is>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D963" t="inlineStr"/>
+      <c r="E963" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="F963" t="n">
+        <v>0</v>
+      </c>
+      <c r="G963" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H963" t="n">
+        <v>3</v>
+      </c>
+      <c r="I963" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J963" t="n">
+        <v>6</v>
+      </c>
+      <c r="K963" t="inlineStr">
+        <is>
+          <t>justicia</t>
+        </is>
+      </c>
+      <c r="L963" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M963" t="n">
+        <v>2</v>
+      </c>
+      <c r="N963" t="inlineStr">
+        <is>
+          <t>justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>La Regional Antioquia del Bienestar Familiar fortalece el acceso a la justicia para niñas, niños y adolescentes víctimas de violencia intrafamiliar</t>
+        </is>
+      </c>
+      <c r="B964" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivAFBVV95cUxPbTNQMWZzWHhkNEI5dWtCOGlYbWkxbEtCWE9VSEpVVjN3SndtaWtFWnhpQnJSOTItOEl0cjJ4WmlDLW15UThvRVJOcTFLWjNqZWl3YllXbl9BeVplbzNMMl95TGtGeEtRLUFzNFBHM0FEeGEyWmJWdGRXYkFSRl9ZU0g0Sl9KaFdiYlc5UVpFdmh1eXZyTnRSTDhJa3JaRU1vajQ0SUVCeHBzY2tTQ0lrNHpCWHpfZDVsWHZuYw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C964" t="inlineStr">
+        <is>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D964" t="inlineStr"/>
+      <c r="E964" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="F964" t="n">
+        <v>0</v>
+      </c>
+      <c r="G964" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H964" t="n">
+        <v>3</v>
+      </c>
+      <c r="I964" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J964" t="n">
+        <v>6</v>
+      </c>
+      <c r="K964" t="inlineStr">
+        <is>
+          <t>víctimas</t>
+        </is>
+      </c>
+      <c r="L964" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M964" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N964" t="inlineStr">
+        <is>
+          <t>victimized</t>
+        </is>
+      </c>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>La Regional Antioquia del Bienestar Familiar fortalece el acceso a la justicia para niñas, niños y adolescentes víctimas de violencia intrafamiliar</t>
+        </is>
+      </c>
+      <c r="B965" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivAFBVV95cUxPbTNQMWZzWHhkNEI5dWtCOGlYbWkxbEtCWE9VSEpVVjN3SndtaWtFWnhpQnJSOTItOEl0cjJ4WmlDLW15UThvRVJOcTFLWjNqZWl3YllXbl9BeVplbzNMMl95TGtGeEtRLUFzNFBHM0FEeGEyWmJWdGRXYkFSRl9ZU0g0Sl9KaFdiYlc5UVpFdmh1eXZyTnRSTDhJa3JaRU1vajQ0SUVCeHBzY2tTQ0lrNHpCWHpfZDVsWHZuYw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C965" t="inlineStr">
+        <is>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D965" t="inlineStr"/>
+      <c r="E965" t="inlineStr">
+        <is>
+          <t>Antioquia</t>
+        </is>
+      </c>
+      <c r="F965" t="n">
+        <v>0</v>
+      </c>
+      <c r="G965" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H965" t="n">
+        <v>3</v>
+      </c>
+      <c r="I965" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J965" t="n">
+        <v>6</v>
+      </c>
+      <c r="K965" t="inlineStr">
+        <is>
+          <t>violencia</t>
+        </is>
+      </c>
+      <c r="L965" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M965" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N965" t="inlineStr">
+        <is>
+          <t>violence</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N965"/>
+  <dimension ref="A1:N969"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54068,6 +54068,222 @@
         </is>
       </c>
     </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>Crimen de Sofía Delgado | Directora del ICBF condena asesinato de la menor en Candelaria, Valle: “No hay dolor más grande que este”</t>
+        </is>
+      </c>
+      <c r="B966" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiiAJBVV95cUxPOHM0VHk3YVZkSFMzbXdJTlh2eXF4Z3lILTdiNExsOUkzT1VqX203V1A1UHBoOUxoeXZjdy1OMjVWRmQyT3hoQXk3VnBmZVBkakNTenNTOGk4YUs1NE0zbTVjUDRiZGxEYU9hbTNZZHlEUEw1R3BBSlo4WWVnb2VxVm9LclJvSjBMOU5icnVRQU5JMGdJaUlBUTRFQklhT0FidDA0WDM2d3BMeHd1Z3RaSUx2OVVDSnlGTUZEaEpoc2NVaFVtVExYeXhCZk5CRXdJdjZpUDUxV1AwaGRyTzJHWWVZZ0JnNHNhVXBZTkk4bXBRX1dMRzVBZDJqNFRKNTBXWm1YQlhYb2_SAY4CQVVfeXFMTXhYS1NaZDktdExaNlpSZXNiWlp2OW9xaTJhOHRUZFg4UUgzRVQ2YThRZjFHcDVEQXdZZXRBQkdMaldjOHgxbENXODFUXzVZOEkzenJtRjdNWVhrUGR4bldsQWI3dlpuRHZmOWVTX2lpejdXTTJYMlBpWmxOR3JlNkVCbDZ3R3E1R1loTDlYam0yVlFZU1RRdzJqSFdPTXlvSHgwS3ltT2hjQUl1enpIdERDeGZlNlcyeVBRaWZ1cVFQb2FhOTZSb1J0eU93QjllT2I5VmN5VWNYNEQ3dmVZblBLcGFNVzRxNkhDa0RmUm5EWDgwNjA3Q2hJZkRzWGtrNGtqYWFQVGRMeUlqWHpR?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C966" t="inlineStr">
+        <is>
+          <t>Semana.com</t>
+        </is>
+      </c>
+      <c r="D966" t="inlineStr"/>
+      <c r="E966" t="inlineStr"/>
+      <c r="F966" t="n">
+        <v>0</v>
+      </c>
+      <c r="G966" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H966" t="n">
+        <v>10</v>
+      </c>
+      <c r="I966" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J966" t="n">
+        <v>17</v>
+      </c>
+      <c r="K966" t="inlineStr">
+        <is>
+          <t>condena</t>
+        </is>
+      </c>
+      <c r="L966" t="inlineStr">
+        <is>
+          <t>Astrid Cáceres</t>
+        </is>
+      </c>
+      <c r="M966" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N966" t="inlineStr">
+        <is>
+          <t>condemns</t>
+        </is>
+      </c>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>Crimen de Sofía Delgado | Directora del ICBF condena asesinato de la menor en Candelaria, Valle: “No hay dolor más grande que este”</t>
+        </is>
+      </c>
+      <c r="B967" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiiAJBVV95cUxPOHM0VHk3YVZkSFMzbXdJTlh2eXF4Z3lILTdiNExsOUkzT1VqX203V1A1UHBoOUxoeXZjdy1OMjVWRmQyT3hoQXk3VnBmZVBkakNTenNTOGk4YUs1NE0zbTVjUDRiZGxEYU9hbTNZZHlEUEw1R3BBSlo4WWVnb2VxVm9LclJvSjBMOU5icnVRQU5JMGdJaUlBUTRFQklhT0FidDA0WDM2d3BMeHd1Z3RaSUx2OVVDSnlGTUZEaEpoc2NVaFVtVExYeXhCZk5CRXdJdjZpUDUxV1AwaGRyTzJHWWVZZ0JnNHNhVXBZTkk4bXBRX1dMRzVBZDJqNFRKNTBXWm1YQlhYb2_SAY4CQVVfeXFMTXhYS1NaZDktdExaNlpSZXNiWlp2OW9xaTJhOHRUZFg4UUgzRVQ2YThRZjFHcDVEQXdZZXRBQkdMaldjOHgxbENXODFUXzVZOEkzenJtRjdNWVhrUGR4bldsQWI3dlpuRHZmOWVTX2lpejdXTTJYMlBpWmxOR3JlNkVCbDZ3R3E1R1loTDlYam0yVlFZU1RRdzJqSFdPTXlvSHgwS3ltT2hjQUl1enpIdERDeGZlNlcyeVBRaWZ1cVFQb2FhOTZSb1J0eU93QjllT2I5VmN5VWNYNEQ3dmVZblBLcGFNVzRxNkhDa0RmUm5EWDgwNjA3Q2hJZkRzWGtrNGtqYWFQVGRMeUlqWHpR?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C967" t="inlineStr">
+        <is>
+          <t>Semana.com</t>
+        </is>
+      </c>
+      <c r="D967" t="inlineStr"/>
+      <c r="E967" t="inlineStr"/>
+      <c r="F967" t="n">
+        <v>0</v>
+      </c>
+      <c r="G967" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H967" t="n">
+        <v>10</v>
+      </c>
+      <c r="I967" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J967" t="n">
+        <v>17</v>
+      </c>
+      <c r="K967" t="inlineStr">
+        <is>
+          <t>asesinato</t>
+        </is>
+      </c>
+      <c r="L967" t="inlineStr">
+        <is>
+          <t>Astrid Cáceres</t>
+        </is>
+      </c>
+      <c r="M967" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N967" t="inlineStr">
+        <is>
+          <t>assassination</t>
+        </is>
+      </c>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>Crimen de Sofía Delgado | Directora del ICBF condena asesinato de la menor en Candelaria, Valle: “No hay dolor más grande que este”</t>
+        </is>
+      </c>
+      <c r="B968" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiiAJBVV95cUxPOHM0VHk3YVZkSFMzbXdJTlh2eXF4Z3lILTdiNExsOUkzT1VqX203V1A1UHBoOUxoeXZjdy1OMjVWRmQyT3hoQXk3VnBmZVBkakNTenNTOGk4YUs1NE0zbTVjUDRiZGxEYU9hbTNZZHlEUEw1R3BBSlo4WWVnb2VxVm9LclJvSjBMOU5icnVRQU5JMGdJaUlBUTRFQklhT0FidDA0WDM2d3BMeHd1Z3RaSUx2OVVDSnlGTUZEaEpoc2NVaFVtVExYeXhCZk5CRXdJdjZpUDUxV1AwaGRyTzJHWWVZZ0JnNHNhVXBZTkk4bXBRX1dMRzVBZDJqNFRKNTBXWm1YQlhYb2_SAY4CQVVfeXFMTXhYS1NaZDktdExaNlpSZXNiWlp2OW9xaTJhOHRUZFg4UUgzRVQ2YThRZjFHcDVEQXdZZXRBQkdMaldjOHgxbENXODFUXzVZOEkzenJtRjdNWVhrUGR4bldsQWI3dlpuRHZmOWVTX2lpejdXTTJYMlBpWmxOR3JlNkVCbDZ3R3E1R1loTDlYam0yVlFZU1RRdzJqSFdPTXlvSHgwS3ltT2hjQUl1enpIdERDeGZlNlcyeVBRaWZ1cVFQb2FhOTZSb1J0eU93QjllT2I5VmN5VWNYNEQ3dmVZblBLcGFNVzRxNkhDa0RmUm5EWDgwNjA3Q2hJZkRzWGtrNGtqYWFQVGRMeUlqWHpR?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C968" t="inlineStr">
+        <is>
+          <t>Semana.com</t>
+        </is>
+      </c>
+      <c r="D968" t="inlineStr"/>
+      <c r="E968" t="inlineStr"/>
+      <c r="F968" t="n">
+        <v>0</v>
+      </c>
+      <c r="G968" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H968" t="n">
+        <v>10</v>
+      </c>
+      <c r="I968" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J968" t="n">
+        <v>17</v>
+      </c>
+      <c r="K968" t="inlineStr">
+        <is>
+          <t>dolor</t>
+        </is>
+      </c>
+      <c r="L968" t="inlineStr">
+        <is>
+          <t>Astrid Cáceres</t>
+        </is>
+      </c>
+      <c r="M968" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N968" t="inlineStr">
+        <is>
+          <t>ache</t>
+        </is>
+      </c>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>Crimen de Sofía Delgado | Directora del ICBF condena asesinato de la menor en Candelaria, Valle: “No hay dolor más grande que este”</t>
+        </is>
+      </c>
+      <c r="B969" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiiAJBVV95cUxPOHM0VHk3YVZkSFMzbXdJTlh2eXF4Z3lILTdiNExsOUkzT1VqX203V1A1UHBoOUxoeXZjdy1OMjVWRmQyT3hoQXk3VnBmZVBkakNTenNTOGk4YUs1NE0zbTVjUDRiZGxEYU9hbTNZZHlEUEw1R3BBSlo4WWVnb2VxVm9LclJvSjBMOU5icnVRQU5JMGdJaUlBUTRFQklhT0FidDA0WDM2d3BMeHd1Z3RaSUx2OVVDSnlGTUZEaEpoc2NVaFVtVExYeXhCZk5CRXdJdjZpUDUxV1AwaGRyTzJHWWVZZ0JnNHNhVXBZTkk4bXBRX1dMRzVBZDJqNFRKNTBXWm1YQlhYb2_SAY4CQVVfeXFMTXhYS1NaZDktdExaNlpSZXNiWlp2OW9xaTJhOHRUZFg4UUgzRVQ2YThRZjFHcDVEQXdZZXRBQkdMaldjOHgxbENXODFUXzVZOEkzenJtRjdNWVhrUGR4bldsQWI3dlpuRHZmOWVTX2lpejdXTTJYMlBpWmxOR3JlNkVCbDZ3R3E1R1loTDlYam0yVlFZU1RRdzJqSFdPTXlvSHgwS3ltT2hjQUl1enpIdERDeGZlNlcyeVBRaWZ1cVFQb2FhOTZSb1J0eU93QjllT2I5VmN5VWNYNEQ3dmVZblBLcGFNVzRxNkhDa0RmUm5EWDgwNjA3Q2hJZkRzWGtrNGtqYWFQVGRMeUlqWHpR?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C969" t="inlineStr">
+        <is>
+          <t>Semana.com</t>
+        </is>
+      </c>
+      <c r="D969" t="inlineStr"/>
+      <c r="E969" t="inlineStr"/>
+      <c r="F969" t="n">
+        <v>0</v>
+      </c>
+      <c r="G969" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H969" t="n">
+        <v>10</v>
+      </c>
+      <c r="I969" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J969" t="n">
+        <v>17</v>
+      </c>
+      <c r="K969" t="inlineStr">
+        <is>
+          <t>grande</t>
+        </is>
+      </c>
+      <c r="L969" t="inlineStr">
+        <is>
+          <t>Astrid Cáceres</t>
+        </is>
+      </c>
+      <c r="M969" t="n">
+        <v>1</v>
+      </c>
+      <c r="N969" t="inlineStr">
+        <is>
+          <t>big</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N969"/>
+  <dimension ref="A1:N970"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54284,6 +54284,60 @@
         </is>
       </c>
     </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>12 hogares infantiles del ICBF están a punto de suspender la atención por falta de pagos</t>
+        </is>
+      </c>
+      <c r="B970" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMifEFVX3lxTE9BaEZuZjFFQmd2eW9wYkNsck9wWl9pQnE2VW43S3dONHBKclhLZ2tpTzBtbzVaeENGRGN1TldvdXFlTnhPa1pRc094WVdnUEdUd2dicDczVnB3TGRrSTI5N1QxNkZaQ1lsMXY2QjlmTlJCMmJZSEp0UHNLWUw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C970" t="inlineStr">
+        <is>
+          <t>Telemedellín</t>
+        </is>
+      </c>
+      <c r="D970" t="inlineStr"/>
+      <c r="E970" t="inlineStr"/>
+      <c r="F970" t="n">
+        <v>0</v>
+      </c>
+      <c r="G970" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H970" t="n">
+        <v>3</v>
+      </c>
+      <c r="I970" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J970" t="n">
+        <v>11</v>
+      </c>
+      <c r="K970" t="inlineStr">
+        <is>
+          <t>suspender</t>
+        </is>
+      </c>
+      <c r="L970" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M970" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N970" t="inlineStr">
+        <is>
+          <t>suspend</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N970"/>
+  <dimension ref="A1:N971"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54338,6 +54338,64 @@
         </is>
       </c>
     </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>“Tenemos la esperanza...”, habla Astrid Cáceres, directora del ICBF, sobre el paradero de los niños desaparecidos en el Caquetá</t>
+        </is>
+      </c>
+      <c r="B971" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi-AFBVV95cUxOSnlMWkFHOURIYzRKMmVBcVdxSzZ3MldKTkhsWVVxQXl2ci02N252UEItdWlaVVNJS3NxU3pOZUR6cU81UFQ5Y21aT0dfTW9YdXlHejN6bU9jV0VhVThZYWlDbTE4al95LTltMGtCbEhHVmZLSm5Ga3VwNUtXWlpzX3I5c3dGcmhvNzZfbFRtSFBZSmhHY1dKVHl1T2p0NUxFMl9zNmJWb255ZEpZRHdnZV9MeEZJWFJaOU5DMmxES3hwQWdHVVFyTTBkZ1doYVlabHZDREdFZngzZk91RmlBWUp0c3FhbDVYN0dnZjhWOTNRYXRpZGJCd9IB_gFBVV95cUxNZmVTYmp3RVdzaTkzaWlaTEFiZnhVc2IwS1VMMW5IOWJ3dnY1aWdoWmlieGVwSmFmNDM1U3JqYjluTFh2SzJUVGtReGdIYUxuYTRqQlczZDdyNWFHcWV1SDlxY25wSkpNcGZxeGpFbk8yUmllRDctUWRfYnJwbnhNTUttUkc5QVlhYXo4d0tsb3ltMV8zSkctOWc1dmhwOFNjaTFjeGZpbl9YWnFVOUtfYVNNVzg0NmxpeXBtemJQZ29QVUowWmJQa0JTMHpIcFRlZnlqM2UyazNZWjNub081cmF0VmktSFc4VnNSQzJ2c2xCTlVSZDJJcFI4WnBrQQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C971" t="inlineStr">
+        <is>
+          <t>elpais.com.co</t>
+        </is>
+      </c>
+      <c r="D971" t="inlineStr"/>
+      <c r="E971" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="F971" t="n">
+        <v>0</v>
+      </c>
+      <c r="G971" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H971" t="n">
+        <v>5</v>
+      </c>
+      <c r="I971" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J971" t="n">
+        <v>18</v>
+      </c>
+      <c r="K971" t="inlineStr">
+        <is>
+          <t>esperanza</t>
+        </is>
+      </c>
+      <c r="L971" t="inlineStr">
+        <is>
+          <t>Astrid Cáceres</t>
+        </is>
+      </c>
+      <c r="M971" t="n">
+        <v>2</v>
+      </c>
+      <c r="N971" t="inlineStr">
+        <is>
+          <t>hope</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N971"/>
+  <dimension ref="A1:N972"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54396,6 +54396,60 @@
         </is>
       </c>
     </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>Directora del Bienestar Familiar llega al territorio arhuaco de Gunmaku tras ataques que dejaron niñas y niños heridos en la Sierra Nevada | Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="B972" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivgFBVV95cUxQWHc0LUlPZXVmNTJncjFoMllkTEI3a3JwYUxmTVRQdkdCWXF6TzhVeGUzeXJud1RlUWsyQjNIMVJwVlRLQXdlMkhMWnhRRkgzTHpPQ1FXb285X29SQU9pV0tFY3JUR0t3MHNUQnp1N3BUN3p5REpMQlFOQjVOM0hzODFQckdkc2F4TjAwQU1JRE1ROENoMk40bGw0OGhLNzJzVWd4ZERzVzloUkUxZ2ZWb0dpeUs1UnlvOE9EZVFn?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C972" t="inlineStr">
+        <is>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D972" t="inlineStr"/>
+      <c r="E972" t="inlineStr"/>
+      <c r="F972" t="n">
+        <v>0</v>
+      </c>
+      <c r="G972" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H972" t="n">
+        <v>3</v>
+      </c>
+      <c r="I972" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J972" t="n">
+        <v>12</v>
+      </c>
+      <c r="K972" t="inlineStr">
+        <is>
+          <t>ataques</t>
+        </is>
+      </c>
+      <c r="L972" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M972" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N972" t="inlineStr">
+        <is>
+          <t>attacks</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N972"/>
+  <dimension ref="A1:N977"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54450,6 +54450,280 @@
         </is>
       </c>
     </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>Crisis en hogares infantiles del Icbf en Medellín: 12 centros podrían suspender atención a más de 500 menores por falta de pagos</t>
+        </is>
+      </c>
+      <c r="B973" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiggJBVV95cUxNcmtwZk9SX2JyRVNkeTVHaGp0eUoyNG1LOG5TM1pDS3VPdXVhRFNIWVZaRHVQdGdJMHNyTmRNX3JhZVZXTnlrMk4yT24yU2VQN29nZmx2akcxMl9nazBuZ2hNVE84LVhwV0pQeFdNQ1NtVEhvNkhGSDVxRkxkMEF0cnFheW9IX1ZrMklmWUkzN3lvTG92NV9VMDdnMlE5R3BNa2I0aE1WSjROaVRGT0xyMy1wM0V5MUtKMm40cGl6S0NTX1JSNDMyM1Y1cnBydEd0bHJKRkZodGQtMDM3d1B3b3RSRWtoR2RZSjJRel9Oc1lWb0NFdXBSUmdIZUY5SEM0OEHSAZwCQVVfeXFMTkRTOTlYLUtyeDZZTFVCZUM5aXZMX2MzMnM3Zi1IaHVlTWM3WFBCQ2JvaEUyMWV2M0YxaHZ2UlVZT2dXMlVUeUhScHZhcEFwNVBsdWRLX1BuZ2VZaVZiRXBUVVlaeEVDNk1TNFNTRC1NYWZnVFIzRE1KeUxjS3FnOU5BZ1pKVmxtWllRa0dqajJnSWhQQnFVNXNOUnZVNk11dXZvdWJjaFRvY0RMczRmZmhGUjFIejlhR084WF9mZmtPbnNoRGFsbGQ4Ylp4a05ZeTd1MWFYRzVFejFTVEFoN3dvOVhqdXNjcHlPSFRGVW9zVUFYX081NHIxbDhEbEs4UEMyZ1IyM0l2cjhsTXAydzlhRFBGRzZpRWFHWWw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C973" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D973" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E973" t="inlineStr"/>
+      <c r="F973" t="n">
+        <v>0</v>
+      </c>
+      <c r="G973" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H973" t="n">
+        <v>3</v>
+      </c>
+      <c r="I973" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J973" t="n">
+        <v>12</v>
+      </c>
+      <c r="K973" t="inlineStr">
+        <is>
+          <t>suspender</t>
+        </is>
+      </c>
+      <c r="L973" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M973" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N973" t="inlineStr">
+        <is>
+          <t>suspend</t>
+        </is>
+      </c>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>Icbf lideró misión de emergencia en la Sierra Nevada tras ataques armados</t>
+        </is>
+      </c>
+      <c r="B974" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi5gFBVV95cUxPTGF1OWxYQkwxSHZJd3djZkpNS3IyR2VSNlFfSHIyNFJReGlrVXZKMWhyNHNCcEQwOVI1eDJKdWZ2UlNnclE0UkJ2UHoxTnN3aHlqYTlpQWEwWDhBd2FhaGZwdGp3eWc4WUhoLWlzTlVoNXp0LTh4ekhUS3FNa1R6cUxON05sakIxdDgtMFZhbWF6T2dLeVlYUmJGT3NMOFM1aThSdnJGdll4NVFNSzgxM0R1LVhyNzlZTVZTVm5DcU1uLWltcUYzV2wwZEhpYWV6NnB5eVBrLWdVSWpteTdTb2FHQmRnZw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C974" t="inlineStr">
+        <is>
+          <t>EL INFORMADOR - Santa Marta, Colombia</t>
+        </is>
+      </c>
+      <c r="D974" t="inlineStr"/>
+      <c r="E974" t="inlineStr"/>
+      <c r="F974" t="n">
+        <v>0</v>
+      </c>
+      <c r="G974" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H974" t="n">
+        <v>3</v>
+      </c>
+      <c r="I974" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J974" t="n">
+        <v>12</v>
+      </c>
+      <c r="K974" t="inlineStr">
+        <is>
+          <t>emergencia</t>
+        </is>
+      </c>
+      <c r="L974" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M974" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N974" t="inlineStr">
+        <is>
+          <t>emergency</t>
+        </is>
+      </c>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>Icbf lideró misión de emergencia en la Sierra Nevada tras ataques armados</t>
+        </is>
+      </c>
+      <c r="B975" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi5gFBVV95cUxPTGF1OWxYQkwxSHZJd3djZkpNS3IyR2VSNlFfSHIyNFJReGlrVXZKMWhyNHNCcEQwOVI1eDJKdWZ2UlNnclE0UkJ2UHoxTnN3aHlqYTlpQWEwWDhBd2FhaGZwdGp3eWc4WUhoLWlzTlVoNXp0LTh4ekhUS3FNa1R6cUxON05sakIxdDgtMFZhbWF6T2dLeVlYUmJGT3NMOFM1aThSdnJGdll4NVFNSzgxM0R1LVhyNzlZTVZTVm5DcU1uLWltcUYzV2wwZEhpYWV6NnB5eVBrLWdVSWpteTdTb2FHQmRnZw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C975" t="inlineStr">
+        <is>
+          <t>EL INFORMADOR - Santa Marta, Colombia</t>
+        </is>
+      </c>
+      <c r="D975" t="inlineStr"/>
+      <c r="E975" t="inlineStr"/>
+      <c r="F975" t="n">
+        <v>0</v>
+      </c>
+      <c r="G975" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H975" t="n">
+        <v>3</v>
+      </c>
+      <c r="I975" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J975" t="n">
+        <v>12</v>
+      </c>
+      <c r="K975" t="inlineStr">
+        <is>
+          <t>ataques</t>
+        </is>
+      </c>
+      <c r="L975" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M975" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N975" t="inlineStr">
+        <is>
+          <t>attacks</t>
+        </is>
+      </c>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>Directora del Bienestar Familiar llega al territorio arhuaco de Gunmaku tras ataques que dejaron niñas y niños heridos en la Sierra Nevada</t>
+        </is>
+      </c>
+      <c r="B976" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivgFBVV95cUxQWHc0LUlPZXVmNTJncjFoMllkTEI3a3JwYUxmTVRQdkdCWXF6TzhVeGUzeXJud1RlUWsyQjNIMVJwVlRLQXdlMkhMWnhRRkgzTHpPQ1FXb285X29SQU9pV0tFY3JUR0t3MHNUQnp1N3BUN3p5REpMQlFOQjVOM0hzODFQckdkc2F4TjAwQU1JRE1ROENoMk40bGw0OGhLNzJzVWd4ZERzVzloUkUxZ2ZWb0dpeUs1UnlvOE9EZVFn?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C976" t="inlineStr">
+        <is>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D976" t="inlineStr"/>
+      <c r="E976" t="inlineStr"/>
+      <c r="F976" t="n">
+        <v>0</v>
+      </c>
+      <c r="G976" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H976" t="n">
+        <v>3</v>
+      </c>
+      <c r="I976" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J976" t="n">
+        <v>12</v>
+      </c>
+      <c r="K976" t="inlineStr">
+        <is>
+          <t>ataques</t>
+        </is>
+      </c>
+      <c r="L976" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M976" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N976" t="inlineStr">
+        <is>
+          <t>attacks</t>
+        </is>
+      </c>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar refuerza acciones frente a la instrumentalización de menores de edad por estructuras criminales</t>
+        </is>
+      </c>
+      <c r="B977" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivwFBVV95cUxNRndqQUNfSFF0T0JnUEF1dFpQYjZLM1BqMGZuZ1BsMDZ3NnJGbXEtX014bHY0ZDVfTmF4SjVxSXJsYXZOQXRJUFh1bkxwNG5Ic1ZFcE5tNkE2TGVSN0QtNjRkcW9EWWR4M2pxLXRfeDBQd0hkT2hiNW9RUG9oY0pSNHU1aldpOHZZanhlbU1IbzVvN2N3MFNudVItc1VmX0tiWEV0UnhLZWtYelkzWkZmd2EyeVZreXg1WHB4czVmVQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C977" t="inlineStr">
+        <is>
+          <t>Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D977" t="inlineStr"/>
+      <c r="E977" t="inlineStr"/>
+      <c r="F977" t="n">
+        <v>0</v>
+      </c>
+      <c r="G977" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H977" t="n">
+        <v>3</v>
+      </c>
+      <c r="I977" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J977" t="n">
+        <v>12</v>
+      </c>
+      <c r="K977" t="inlineStr">
+        <is>
+          <t>criminales</t>
+        </is>
+      </c>
+      <c r="L977" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M977" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N977" t="inlineStr">
+        <is>
+          <t>criminals</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N977"/>
+  <dimension ref="A1:N979"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54724,6 +54724,118 @@
         </is>
       </c>
     </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>🚨 Más de 500 niños en riesgo por falta de pagos en hogares infantiles del ICBF Medellín. #Infancia #ICBF #Medellín #Crisis</t>
+        </is>
+      </c>
+      <c r="B978" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi6wFBVV95cUxNUHBENVRSNHE5ODlhS184U2tqemVBUFZuUlVKQ0hxdjJua1ZSYXBmSWg3LXpsUzZMWVVFNmt4YWNuRlFwdWJ0aFVEUGg0c3RGblBEd1dXbkwzc1V1d0dCTGFKRUVOMTNZNXFCd081eEdDbEJPaTF1OTV5a3lWQzFDMk55dkRQVnNSVnJrdkI1cFJ1MUZWZGJsVWxLLWpUZ1V5VV90YjlETFdlczc1RHg2NlE0TldjRlJTV0licUVETHJ5cTJ1aTBOemMta3hNd0hsOTFkTEVfTlFsalJoNHE5ODk5ZDhyaWpQQ2dJ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C978" t="inlineStr">
+        <is>
+          <t>facebook.com</t>
+        </is>
+      </c>
+      <c r="D978" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E978" t="inlineStr"/>
+      <c r="F978" t="n">
+        <v>0</v>
+      </c>
+      <c r="G978" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H978" t="n">
+        <v>3</v>
+      </c>
+      <c r="I978" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J978" t="n">
+        <v>13</v>
+      </c>
+      <c r="K978" t="inlineStr">
+        <is>
+          <t>riesgo</t>
+        </is>
+      </c>
+      <c r="L978" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M978" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N978" t="inlineStr">
+        <is>
+          <t>risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>ICBF llega al territorio arhuaco de Gunmaku tras ataques en la Sierra Nevada</t>
+        </is>
+      </c>
+      <c r="B979" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMisAFBVV95cUxNVU9WdEdPZ0ZSeW9JcVREZ0V2aGpJckllRjZMTzlROU53cHZsd21YS1BrNzVFTDNoSzlOaWx3SWlCMlBLN2xkM3dVZ0lIdnZLb3FVYW1GRElIVGxlRTM0TFpYSHY3QWpQRlBBRUNnWm0waHhfYjZIQmo2TVhKYm9CeHkzeG1QcW8zbDdNXzhqRlIyemFwamUwY0sySFc0ZF9zZ0lObkVsZGtZOVF6eVpESNIBxAFBVV95cUxPVFoydTlaS09WN3lZVTlLSzF3OW5BMjBvU3BsWndNWjNUQkVoZWhYYjJnLTBCOC15ZnBPQzdxUE9jM1paa0FCOWl1UjF6MW5YZTNyNkNoQi1FdDdtRTJuSGJzZThNMGl2bGdVczNQQnVaVWtQLUdRMVJaWC0wOFMwNGZTandpSjNaT19uRDB5dUo0VDJRV3hic0J4b2toY0IwRVJZd01LM0RWdWY0akI2VktTYUhfa3RtaDVwd3ZVclQzY2Vi?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C979" t="inlineStr">
+        <is>
+          <t>Caracol Radio</t>
+        </is>
+      </c>
+      <c r="D979" t="inlineStr"/>
+      <c r="E979" t="inlineStr"/>
+      <c r="F979" t="n">
+        <v>0</v>
+      </c>
+      <c r="G979" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H979" t="n">
+        <v>3</v>
+      </c>
+      <c r="I979" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J979" t="n">
+        <v>13</v>
+      </c>
+      <c r="K979" t="inlineStr">
+        <is>
+          <t>ataques</t>
+        </is>
+      </c>
+      <c r="L979" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M979" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N979" t="inlineStr">
+        <is>
+          <t>attacks</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N979"/>
+  <dimension ref="A1:N981"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54836,6 +54836,118 @@
         </is>
       </c>
     </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>Diputado Luis Lobo sostiene denuncia sobre ICBF mientras defensa de Arlithon Jaruffe exige retractación</t>
+        </is>
+      </c>
+      <c r="B980" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi2gFBVV95cUxOMmM4aGtZOUtjYWw5M0ltRmFUdl9jRlNUZ3ZwZDcwSzJkbThZMnFwVFhqTWxYa2ZfX2Y4SC1iSmxGNkFpQXc2alE3T284NkwxZDc4M2JqXzR1QXk3T2N6UVNpdUpudzFKX1V0TGIyRXVkaDdTUGVGRWVRVHZrOG0zcFc5ZHlGT21PZThzQkd2bTNaQ2ZGLTUtaDYyQXJBQU1tbWdIbG5BN1BNcWF4MER4d2tDMEdUc3hFbElPLWZJLVRZWVE2VjVlX05jenNvY3IxVk5wb0FYZkhYZw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C980" t="inlineStr">
+        <is>
+          <t>Diario del Norte</t>
+        </is>
+      </c>
+      <c r="D980" t="inlineStr"/>
+      <c r="E980" t="inlineStr"/>
+      <c r="F980" t="n">
+        <v>0</v>
+      </c>
+      <c r="G980" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H980" t="n">
+        <v>3</v>
+      </c>
+      <c r="I980" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J980" t="n">
+        <v>13</v>
+      </c>
+      <c r="K980" t="inlineStr">
+        <is>
+          <t>denuncia</t>
+        </is>
+      </c>
+      <c r="L980" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M980" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N980" t="inlineStr">
+        <is>
+          <t>denounces</t>
+        </is>
+      </c>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar advierte sobre falsas ofertas laborales que circulan en Caldas</t>
+        </is>
+      </c>
+      <c r="B981" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMitAFBVV95cUxOeWU0VkZWdHNFWUVlNTJmSDZvQVZ5Wl95ZFJyaU5sVHhRY1VqR19lWUJnc29TNXFIZFpiWkl5MG1ZMTZSVE9VanpYMDF3VG9xeFZQYTNOamNLVkRBdVE4WEJlbWJGR2RpYk9ESFhhODNpZ0hRMGNjdmQ0TU5lbUlkQVVIeVQzQTNXZ1RYS2NyODJKLVBjanVCVVhDYnM1bTQxeU9UcmgxS19qdDgwNTJORmJrQmU?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C981" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D981" t="inlineStr"/>
+      <c r="E981" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="F981" t="n">
+        <v>0</v>
+      </c>
+      <c r="G981" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H981" t="n">
+        <v>3</v>
+      </c>
+      <c r="I981" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J981" t="n">
+        <v>13</v>
+      </c>
+      <c r="K981" t="inlineStr">
+        <is>
+          <t>advierte</t>
+        </is>
+      </c>
+      <c r="L981" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M981" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N981" t="inlineStr">
+        <is>
+          <t>warns</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N981"/>
+  <dimension ref="A1:N982"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -54948,6 +54948,64 @@
         </is>
       </c>
     </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>Articulación institucional fortalece la protección de niños, niñas y adolescentes en Montería</t>
+        </is>
+      </c>
+      <c r="B982" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiuwFBVV95cUxOdmdXeW9reVhGN2VjUDNmNFNjNzBiVHIxb3FDV2laUUJ4RTRHdVlsc2pPZERHNGZKMDRqdHVnZkJHazBKdW5PX0x5SkZKRWxCbEpXR3h1R2dOQ1ducW9kM3BkQ2RFUHJkZ1JuVlZEeUVCMTViWU80OUR5YkhxLWwxcGlDcGlRaHJXc0xFdWR2cFpGTUw0ZXNlVXlTbTBEdVNWN3hMVHVCZDlhUGdHRC04b2pJUG5rR3lzTjNv?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C982" t="inlineStr">
+        <is>
+          <t>policia.gov.co</t>
+        </is>
+      </c>
+      <c r="D982" t="inlineStr">
+        <is>
+          <t>Montería</t>
+        </is>
+      </c>
+      <c r="E982" t="inlineStr"/>
+      <c r="F982" t="n">
+        <v>0</v>
+      </c>
+      <c r="G982" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H982" t="n">
+        <v>3</v>
+      </c>
+      <c r="I982" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J982" t="n">
+        <v>5</v>
+      </c>
+      <c r="K982" t="inlineStr">
+        <is>
+          <t>fortalece</t>
+        </is>
+      </c>
+      <c r="L982" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M982" t="n">
+        <v>2</v>
+      </c>
+      <c r="N982" t="inlineStr">
+        <is>
+          <t>strengthens</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N982"/>
+  <dimension ref="A1:N984"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55006,6 +55006,122 @@
         </is>
       </c>
     </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>El violador de jardín del ICBF en Bogotá, Freddy Castellanos, se disfrazó para escapar de la Policía: así lo hizo</t>
+        </is>
+      </c>
+      <c r="B983" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi-gFBVV95cUxQN01LMDQ2elpDM2R2VWY2VEJsQS1EVkxNeHlPOWtzWnZacUlCY1UzbVRmYkdkWjB1Z3I0eFQ2WTFLbGlSNDVhUURxQUxpRGtiYktRQ0U5ZXhYcXVCQVl3MGlBSE8xVEg5NVF5ZUJEVFVhY0pVcmYyT3hzYkZROVZrTVYwcVdmOE1SeWo4MDZoWUs1WjhJbUNKeHFYWWhkbEJ5cXBvYWxaaXRLZzdjTGVVRGc5N2xRZWNxVUJzbmkxTk1hdklhclMtOU1LVkFHb0xBVDFpN1J5YUh6SG1XcEVaQU9wNERfbUFFMlAxYmdkT2hfcWJ3RF94eWV30gH_AUFVX3lxTE5Tc3VSRl9BcWtfX1Y1ZlN3aENfdkJXdjNkb09ZbmoyNmt1cFpCWU9KZGV3TEhCOFV0RWdrOG1WMkZ1dGFENWsyV3VDV0Z0d0UySVdiQ20zNnRuV2ZFdU1udFdtM1daNmFPeHFremFXbVNrWlNCSTdZbGFYVi14ZE5sYlZzRjhYRVJ3WVFlNkFiT1BLMGJndkJIdGFSTGhwUU13T2haamJBbjJfMUxBdzBJRDBiQWtzSDViTzBrMUN6SElaS3FOSTRfeEIxc2dGVjdpZEs4cUo2U18zRjNmSVh1TU1ncVZ0T1VLc3BXN19Kam9pRUFicU0wQS1OYUpOQQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C983" t="inlineStr">
+        <is>
+          <t>ELTIEMPO.com</t>
+        </is>
+      </c>
+      <c r="D983" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E983" t="inlineStr"/>
+      <c r="F983" t="n">
+        <v>0</v>
+      </c>
+      <c r="G983" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H983" t="n">
+        <v>5</v>
+      </c>
+      <c r="I983" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J983" t="n">
+        <v>12</v>
+      </c>
+      <c r="K983" t="inlineStr">
+        <is>
+          <t>violador</t>
+        </is>
+      </c>
+      <c r="L983" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M983" t="n">
+        <v>-4</v>
+      </c>
+      <c r="N983" t="inlineStr">
+        <is>
+          <t>rapist</t>
+        </is>
+      </c>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>El violador de jardín del ICBF en Bogotá, Freddy Castellanos, se disfrazó para escapar de la Policía: así lo hizo</t>
+        </is>
+      </c>
+      <c r="B984" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi-gFBVV95cUxQN01LMDQ2elpDM2R2VWY2VEJsQS1EVkxNeHlPOWtzWnZacUlCY1UzbVRmYkdkWjB1Z3I0eFQ2WTFLbGlSNDVhUURxQUxpRGtiYktRQ0U5ZXhYcXVCQVl3MGlBSE8xVEg5NVF5ZUJEVFVhY0pVcmYyT3hzYkZROVZrTVYwcVdmOE1SeWo4MDZoWUs1WjhJbUNKeHFYWWhkbEJ5cXBvYWxaaXRLZzdjTGVVRGc5N2xRZWNxVUJzbmkxTk1hdklhclMtOU1LVkFHb0xBVDFpN1J5YUh6SG1XcEVaQU9wNERfbUFFMlAxYmdkT2hfcWJ3RF94eWV30gH_AUFVX3lxTE5Tc3VSRl9BcWtfX1Y1ZlN3aENfdkJXdjNkb09ZbmoyNmt1cFpCWU9KZGV3TEhCOFV0RWdrOG1WMkZ1dGFENWsyV3VDV0Z0d0UySVdiQ20zNnRuV2ZFdU1udFdtM1daNmFPeHFremFXbVNrWlNCSTdZbGFYVi14ZE5sYlZzRjhYRVJ3WVFlNkFiT1BLMGJndkJIdGFSTGhwUU13T2haamJBbjJfMUxBdzBJRDBiQWtzSDViTzBrMUN6SElaS3FOSTRfeEIxc2dGVjdpZEs4cUo2U18zRjNmSVh1TU1ncVZ0T1VLc3BXN19Kam9pRUFicU0wQS1OYUpOQQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C984" t="inlineStr">
+        <is>
+          <t>ELTIEMPO.com</t>
+        </is>
+      </c>
+      <c r="D984" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E984" t="inlineStr"/>
+      <c r="F984" t="n">
+        <v>0</v>
+      </c>
+      <c r="G984" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H984" t="n">
+        <v>5</v>
+      </c>
+      <c r="I984" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J984" t="n">
+        <v>12</v>
+      </c>
+      <c r="K984" t="inlineStr">
+        <is>
+          <t>escapar</t>
+        </is>
+      </c>
+      <c r="L984" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M984" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N984" t="inlineStr">
+        <is>
+          <t>escape</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N984"/>
+  <dimension ref="A1:N985"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55122,6 +55122,64 @@
         </is>
       </c>
     </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>Policía e ICBF refuerzan acciones para proteger a la niñez en el Mercado Público de Valledupar</t>
+        </is>
+      </c>
+      <c r="B985" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMigwFBVV95cUxPcFZSMk1iR2EyX3BYTWVNOFM4OElTWU9hTlJpM3Q3MVZHcGJ6M3VVdVlVTzFhXzMwN016TGZOcGRELTl3cFhZdjd2S05jLUx1blZSRHhXMm5oMHdZVFVIN1paWE5TdjlKMXMtM2FrbFlfSjhJQjJmS1Y0ZkZUMmJoNEZPVQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C985" t="inlineStr">
+        <is>
+          <t>Radio Guatapurí</t>
+        </is>
+      </c>
+      <c r="D985" t="inlineStr">
+        <is>
+          <t>Valledupar</t>
+        </is>
+      </c>
+      <c r="E985" t="inlineStr"/>
+      <c r="F985" t="n">
+        <v>0</v>
+      </c>
+      <c r="G985" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H985" t="n">
+        <v>3</v>
+      </c>
+      <c r="I985" t="inlineStr">
+        <is>
+          <t>domingo</t>
+        </is>
+      </c>
+      <c r="J985" t="n">
+        <v>15</v>
+      </c>
+      <c r="K985" t="inlineStr">
+        <is>
+          <t>proteger</t>
+        </is>
+      </c>
+      <c r="L985" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M985" t="n">
+        <v>1</v>
+      </c>
+      <c r="N985" t="inlineStr">
+        <is>
+          <t>protect</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N985"/>
+  <dimension ref="A1:N986"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55180,6 +55180,64 @@
         </is>
       </c>
     </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar participa en Consejo de Seguridad en Guaviare para fortalecer acciones contra el reclutamiento de niñas, niños y adolescentes | Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="B986" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivwFBVV95cUxNWUNIbEljOWpCVnBKODJWZmI1Y0pfaHJDREdlT1V2NzNFOFVDRmdSdVZHZlVLMDRWRVhwNzRmMzJwMWVKVkV5ODNJVnloU25aaTE1ZmxnRGE0SEV3YXk4ejNGY1RvYWdUaC1kQXo3eDBXOUVQNWZlNUNXcU5HNi1wbDlXVHNFZE9nbllYUnRJbzA5WG84MjRqaFJtaTZrTmhpZXJhbnFZRWowLXRvTXdJQTM4T0R4REhSbUtpdHZmVQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C986" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D986" t="inlineStr"/>
+      <c r="E986" t="inlineStr">
+        <is>
+          <t>Guaviare</t>
+        </is>
+      </c>
+      <c r="F986" t="n">
+        <v>0</v>
+      </c>
+      <c r="G986" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H986" t="n">
+        <v>3</v>
+      </c>
+      <c r="I986" t="inlineStr">
+        <is>
+          <t>domingo</t>
+        </is>
+      </c>
+      <c r="J986" t="n">
+        <v>15</v>
+      </c>
+      <c r="K986" t="inlineStr">
+        <is>
+          <t>fortalecer</t>
+        </is>
+      </c>
+      <c r="L986" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M986" t="n">
+        <v>2</v>
+      </c>
+      <c r="N986" t="inlineStr">
+        <is>
+          <t>strengthen</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N986"/>
+  <dimension ref="A1:N987"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55238,6 +55238,60 @@
         </is>
       </c>
     </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>Presión del conflicto armado limita acción del ICBF en el Catatumbo</t>
+        </is>
+      </c>
+      <c r="B987" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMioAFBVV95cUxObTJ4eTRJYnhzZ0lWR0wzSWgyc04zRTFHU09aSEc3QmJwbmhEMnBEVER0Ti01aEpRc19fbk5NbUNCSHNqc0tFNi1zei1PZ1B6WlZYVDRoYmlQOS1mc1dfUmMtUk8xeFFoYmNtZ3ZBeFhUX2FOVkdFZ25lT2VKYlVPai1nMS15dkxJV2NMYWZQT3hQOFJKM3pESncxdXAzX3Rf?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C987" t="inlineStr">
+        <is>
+          <t>laopinion.co</t>
+        </is>
+      </c>
+      <c r="D987" t="inlineStr"/>
+      <c r="E987" t="inlineStr"/>
+      <c r="F987" t="n">
+        <v>0</v>
+      </c>
+      <c r="G987" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H987" t="n">
+        <v>3</v>
+      </c>
+      <c r="I987" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J987" t="n">
+        <v>16</v>
+      </c>
+      <c r="K987" t="inlineStr">
+        <is>
+          <t>conflicto</t>
+        </is>
+      </c>
+      <c r="L987" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M987" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N987" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N987"/>
+  <dimension ref="A1:N988"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55292,6 +55292,64 @@
         </is>
       </c>
     </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>Congresista denuncia recorte del Icbf que afecta jardines infantiles en Bogotá</t>
+        </is>
+      </c>
+      <c r="B988" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMirAFBVV95cUxQZ2lVb0VQVDNRZUFMYVMwX2JDWW01WEowMWVnNGpfeGVkSjYtQno4YWZYY0Q1RFRESVZUTkdnaE1KMTdRTnVBRGNTQ3REX0NqbDg1cW9UNEFZUnctWkpXSFo2MWZRRVpkNnRsYTV5UDZYRzFJeURIZWZxNHpCM21EUXFJVldQeXlfbmJ2WElqTHUwT0R4d1RkQURLQnJHWjBvZnBFMGhhQ0VRMWh6?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C988" t="inlineStr">
+        <is>
+          <t>La Silla Vacía</t>
+        </is>
+      </c>
+      <c r="D988" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E988" t="inlineStr"/>
+      <c r="F988" t="n">
+        <v>0</v>
+      </c>
+      <c r="G988" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H988" t="n">
+        <v>5</v>
+      </c>
+      <c r="I988" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J988" t="n">
+        <v>20</v>
+      </c>
+      <c r="K988" t="inlineStr">
+        <is>
+          <t>denuncia</t>
+        </is>
+      </c>
+      <c r="L988" t="inlineStr">
+        <is>
+          <t>Astrid Cáceres</t>
+        </is>
+      </c>
+      <c r="M988" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N988" t="inlineStr">
+        <is>
+          <t>denounces</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N988"/>
+  <dimension ref="A1:N989"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55350,6 +55350,64 @@
         </is>
       </c>
     </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>Condenan a funcionario del ICBF en Cali por acoso sexual contra una compañera de trabajo</t>
+        </is>
+      </c>
+      <c r="B989" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMixgFBVV95cUxPekhuVExhTU9vYjVtb0FkdmNGTG83cDRLVjlKbmRzVU1jQU81YkNzbi1KUXZtSzQxbkI1ZU1IRWlLdlNqZGRtV2QxclNWcE44em1QdUJ1R0FjeDZDQmFZMTZ1Wl9zRmRYTzk3MnkyblBVRmFlcHdKMW5tX0FZNmpPRkhlcE5XQmRxMlVTaTZ0cWZENm45SFI3LWdXcnBwX2gwWjFGQWFReDFRajNUZEwwTWtsY1RZN285WVo4U0M2eFJJNGVNVkE?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C989" t="inlineStr">
+        <is>
+          <t>La Cuyabra Radio</t>
+        </is>
+      </c>
+      <c r="D989" t="inlineStr">
+        <is>
+          <t>Cali</t>
+        </is>
+      </c>
+      <c r="E989" t="inlineStr"/>
+      <c r="F989" t="n">
+        <v>0</v>
+      </c>
+      <c r="G989" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H989" t="n">
+        <v>3</v>
+      </c>
+      <c r="I989" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J989" t="n">
+        <v>17</v>
+      </c>
+      <c r="K989" t="inlineStr">
+        <is>
+          <t>acoso</t>
+        </is>
+      </c>
+      <c r="L989" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M989" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N989" t="inlineStr">
+        <is>
+          <t>bullying</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N989"/>
+  <dimension ref="A1:N990"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55408,6 +55408,64 @@
         </is>
       </c>
     </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>En Cartagena fortalecen alianza con el Icbf para mejorar la infraestructura de los CDI y Centros de Vida</t>
+        </is>
+      </c>
+      <c r="B990" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi7AFBVV95cUxPN3gybnQyaFc4XzVZUUdZWjNzd0hxQVFLRFd2OFR6MFZaSHd3TnlUeS1HUjIzWFVFLXpNMDFzdXNSQ014c0hWelRmUjY1VTJDSE9KWHl3WlZIdmRVZ2lvUTM3Rmc0cDR6Tm92Q2JtaDBFd2gydWlka194eEpSOFF5YjJWSUJReWFPUkpGVlhNTW9lRW5NczV0em9qaTUybm9NYVZiR3JpQ2gxVkVkN2RIUHFaTzc4YWpQckpScG9Tb1FheFV0MjVoSzR6ejd3RV9Fbmoxc3AwRVRmeHFyeW5STlJ5aHplRWJhTzQ2Q9IBhwJBVV95cUxPelZUY3lmOE00TXowRlMzbUhRT0tXUTk2VFJOa0N6MGJyenNFcVNCLTJuclRlS2hUU1JtN1kwcGFvakY4dmVLRXFncVdiQ1ZHWFV0QlV5MjRqRndlaXZVdmdna2EyNG1nMDZLT1pSMzROWlBLNllyUTFmR3hUYWZLS0tpRFJIakJxYVFjNFR6ek5sWlZRelR6QzA4UnRUaW1VcWt3M0cyQy14X1pkNzZ5VE56ZDhKeWhLZGIwWFZpb2lfbkxwbVdDQm5YN016Nkt5Zm5xdGZyLTA2RGJCdFExTTlWd3IwTmlGbGI0VHBUSzBMSVFmZHhKV291c09ieThYZHJNNFRKYw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C990" t="inlineStr">
+        <is>
+          <t>ELHERALDO.CO</t>
+        </is>
+      </c>
+      <c r="D990" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="E990" t="inlineStr"/>
+      <c r="F990" t="n">
+        <v>0</v>
+      </c>
+      <c r="G990" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H990" t="n">
+        <v>3</v>
+      </c>
+      <c r="I990" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J990" t="n">
+        <v>17</v>
+      </c>
+      <c r="K990" t="inlineStr">
+        <is>
+          <t>mejorar</t>
+        </is>
+      </c>
+      <c r="L990" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M990" t="n">
+        <v>2</v>
+      </c>
+      <c r="N990" t="inlineStr">
+        <is>
+          <t>improve</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N990"/>
+  <dimension ref="A1:N992"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55466,6 +55466,118 @@
         </is>
       </c>
     </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>Gobierno, a través del ICBF, atiende a las y los niños heridos en ataques en la Sierra Nevada</t>
+        </is>
+      </c>
+      <c r="B991" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiyAFBVV95cUxPWm1HZnBsYk5oZndRY0JmWHFuUEh0c1BHWDFERWZ0UUQtMml4UzJ4dF9JTFJSSlFkemlZR2Q2U0luOWdOaFpZNkh0TXBQRmlkMTBFdjlUS1dWcEdsVzVfUUoyVWNGd0Q2cU82b0pYRmFKaGxmTDFNaTF0ZTk4MTVPRklqMWdhSE90bk1yTFg3ajlmNWk0d1FXOXBickhuUDAtZnRDUG13VGd0eDVEakZPTHdNUjl2LU9mX3hXOENvMnIxX0t6OFJSQg?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C991" t="inlineStr">
+        <is>
+          <t>presidencia.gov.co</t>
+        </is>
+      </c>
+      <c r="D991" t="inlineStr"/>
+      <c r="E991" t="inlineStr"/>
+      <c r="F991" t="n">
+        <v>0</v>
+      </c>
+      <c r="G991" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H991" t="n">
+        <v>3</v>
+      </c>
+      <c r="I991" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J991" t="n">
+        <v>12</v>
+      </c>
+      <c r="K991" t="inlineStr">
+        <is>
+          <t>ataques</t>
+        </is>
+      </c>
+      <c r="L991" t="inlineStr">
+        <is>
+          <t>Astrid Cáceres</t>
+        </is>
+      </c>
+      <c r="M991" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N991" t="inlineStr">
+        <is>
+          <t>attacks</t>
+        </is>
+      </c>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>Alcalde Dumek Turbay e ICBF fortalecen alianza para mejorar infraestructura de CDI y Centros de Vida en Cartagena</t>
+        </is>
+      </c>
+      <c r="B992" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi1AFBVV95cUxOZ3E1R1djLUlEcHBEeEY2eG5ia0lTaG9ualhxUmZWZF9pNEM2NDdSc3pKdUZfanFrSmRxd3FxVVkybW85N05qR0dTeWUxdXlqZmczeHVhakpUR0E0cGRJeHNHWHFfZThTM3VSeXYwamZ2TS1pRE51UF9peW11RTdmTWVZM3lBcVNaMTFfZ1dVQUcwd2xGUkdhZ3MxdzVNWklYQS0yYjlVd1V3SUl6SjFOV1M4anE4dzZQaktEVzd0OXUwVVhPMDJrOGFXektJSTFsVnNFbg?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C992" t="inlineStr">
+        <is>
+          <t>cartagena.gov.co</t>
+        </is>
+      </c>
+      <c r="D992" t="inlineStr">
+        <is>
+          <t>Cartagena</t>
+        </is>
+      </c>
+      <c r="E992" t="inlineStr"/>
+      <c r="F992" t="n">
+        <v>0</v>
+      </c>
+      <c r="G992" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H992" t="n">
+        <v>3</v>
+      </c>
+      <c r="I992" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J992" t="n">
+        <v>17</v>
+      </c>
+      <c r="K992" t="inlineStr">
+        <is>
+          <t>mejorar</t>
+        </is>
+      </c>
+      <c r="L992" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M992" t="n">
+        <v>2</v>
+      </c>
+      <c r="N992" t="inlineStr">
+        <is>
+          <t>improve</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N992"/>
+  <dimension ref="A1:N995"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55578,6 +55578,168 @@
         </is>
       </c>
     </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>Personero de San Luis de Palenque explica acciones legales tras denuncia de agresión sexual infantil en CDI del ICBF.</t>
+        </is>
+      </c>
+      <c r="B993" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi2wFBVV95cUxQczRjM2lWRzE3MV9BQjhZbFRQTkp3elJyVTkyRU1JMmJUMzlqTE1BRm5RblJxWTExTVZhNWZOa2FMcVc4QTlCOXFMV3hnbnBFVHhLVFVLZE1vZ09YZEhlODNNMEVXLVI5N1RBaU85VEZRTThqdWVEX3BvYm9iQ0sxWVpUM21Fa3MyT3M1b1hoN2lveklPODJCc1FfSW56YXZDdjdQbXlUS3hDNzFOU1lDbkdWZGVlY3lKVkQ1RXI1UVE0Q1hxUzV5d2V1dU5RWDVZRGJqbDlaMnJ4VjA?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C993" t="inlineStr">
+        <is>
+          <t>Casanare online</t>
+        </is>
+      </c>
+      <c r="D993" t="inlineStr"/>
+      <c r="E993" t="inlineStr"/>
+      <c r="F993" t="n">
+        <v>0</v>
+      </c>
+      <c r="G993" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H993" t="n">
+        <v>3</v>
+      </c>
+      <c r="I993" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J993" t="n">
+        <v>18</v>
+      </c>
+      <c r="K993" t="inlineStr">
+        <is>
+          <t>denuncia</t>
+        </is>
+      </c>
+      <c r="L993" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M993" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N993" t="inlineStr">
+        <is>
+          <t>denounces</t>
+        </is>
+      </c>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>Personero de San Luis de Palenque explica acciones legales tras denuncia de agresión sexual infantil en CDI del ICBF.</t>
+        </is>
+      </c>
+      <c r="B994" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi2wFBVV95cUxQczRjM2lWRzE3MV9BQjhZbFRQTkp3elJyVTkyRU1JMmJUMzlqTE1BRm5RblJxWTExTVZhNWZOa2FMcVc4QTlCOXFMV3hnbnBFVHhLVFVLZE1vZ09YZEhlODNNMEVXLVI5N1RBaU85VEZRTThqdWVEX3BvYm9iQ0sxWVpUM21Fa3MyT3M1b1hoN2lveklPODJCc1FfSW56YXZDdjdQbXlUS3hDNzFOU1lDbkdWZGVlY3lKVkQ1RXI1UVE0Q1hxUzV5d2V1dU5RWDVZRGJqbDlaMnJ4VjA?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C994" t="inlineStr">
+        <is>
+          <t>Casanare online</t>
+        </is>
+      </c>
+      <c r="D994" t="inlineStr"/>
+      <c r="E994" t="inlineStr"/>
+      <c r="F994" t="n">
+        <v>0</v>
+      </c>
+      <c r="G994" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H994" t="n">
+        <v>3</v>
+      </c>
+      <c r="I994" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J994" t="n">
+        <v>18</v>
+      </c>
+      <c r="K994" t="inlineStr">
+        <is>
+          <t>agresión</t>
+        </is>
+      </c>
+      <c r="L994" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M994" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N994" t="inlineStr">
+        <is>
+          <t>aggression</t>
+        </is>
+      </c>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>Personero de San Luis de Palenque explica acciones legales tras denuncia de agresión sexual infantil en CDI del ICBF.</t>
+        </is>
+      </c>
+      <c r="B995" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi2wFBVV95cUxQczRjM2lWRzE3MV9BQjhZbFRQTkp3elJyVTkyRU1JMmJUMzlqTE1BRm5RblJxWTExTVZhNWZOa2FMcVc4QTlCOXFMV3hnbnBFVHhLVFVLZE1vZ09YZEhlODNNMEVXLVI5N1RBaU85VEZRTThqdWVEX3BvYm9iQ0sxWVpUM21Fa3MyT3M1b1hoN2lveklPODJCc1FfSW56YXZDdjdQbXlUS3hDNzFOU1lDbkdWZGVlY3lKVkQ1RXI1UVE0Q1hxUzV5d2V1dU5RWDVZRGJqbDlaMnJ4VjA?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C995" t="inlineStr">
+        <is>
+          <t>Casanare online</t>
+        </is>
+      </c>
+      <c r="D995" t="inlineStr"/>
+      <c r="E995" t="inlineStr"/>
+      <c r="F995" t="n">
+        <v>0</v>
+      </c>
+      <c r="G995" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H995" t="n">
+        <v>3</v>
+      </c>
+      <c r="I995" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J995" t="n">
+        <v>18</v>
+      </c>
+      <c r="K995" t="inlineStr">
+        <is>
+          <t>infantil</t>
+        </is>
+      </c>
+      <c r="L995" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M995" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N995" t="inlineStr">
+        <is>
+          <t>childish</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N995"/>
+  <dimension ref="A1:N996"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55740,6 +55740,60 @@
         </is>
       </c>
     </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar realiza jornada de sensibilización frente al trabajo infantil en Bahía Solano</t>
+        </is>
+      </c>
+      <c r="B996" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivAFBVV95cUxOcVlmWml6VmNPeXlxLXl1SVZEaUR6eVhjanZ1ZFZNVnh3NkZpZHJwMExZUWdETFJCN21uR0xRdUJoRXE5UUZzZzlZSThzSmxRLU1PYnpydElFR2w0LUQ2MGJJb0VWMjgyeS14Q2ZRSF83YzZsNDlsYmMwaEFGS1p1ajA1aGZQcTVLQjRKUWl0RnlYci1JenZScGJTUUU0YVF5dVI1Tlc2d1M4OFFmTEh3eXBPWDFELTRvZWl5SA?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C996" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D996" t="inlineStr"/>
+      <c r="E996" t="inlineStr"/>
+      <c r="F996" t="n">
+        <v>0</v>
+      </c>
+      <c r="G996" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H996" t="n">
+        <v>3</v>
+      </c>
+      <c r="I996" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J996" t="n">
+        <v>18</v>
+      </c>
+      <c r="K996" t="inlineStr">
+        <is>
+          <t>infantil</t>
+        </is>
+      </c>
+      <c r="L996" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M996" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N996" t="inlineStr">
+        <is>
+          <t>childish</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N996"/>
+  <dimension ref="A1:N997"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55794,6 +55794,64 @@
         </is>
       </c>
     </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>Diputado de La Guajira mantiene denuncia por presunta corrupción en contratación del Icbf</t>
+        </is>
+      </c>
+      <c r="B997" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMizAFBVV95cUxNaGFtUEx6TTI1ZW9xNUl3ai1TbWFMUjIxMm40c0Q4UEVBd1ByYWdqRVJyb1BuTzNFMGxQN0Y0Y2ZfVUNZRjQyeWZHaC1aazB6UnhucnZETkdFRW9ZYzN2cEpKc1BEZkJzT1pQUlo1Q0ViX0NDZzJYOUJ5aTZkS0taYlRqeHNlQ3gwWnpjVWpPd3dRbjRWTlUwN1VTOHhrT2s0S0k3eXlDZHhINGtOWE9DU1o5RWdaZXRJUmlMUWxZQ0VZR0pISDJObkpGejQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C997" t="inlineStr">
+        <is>
+          <t>La Guajira Hoy.com</t>
+        </is>
+      </c>
+      <c r="D997" t="inlineStr"/>
+      <c r="E997" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="F997" t="n">
+        <v>0</v>
+      </c>
+      <c r="G997" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H997" t="n">
+        <v>3</v>
+      </c>
+      <c r="I997" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J997" t="n">
+        <v>19</v>
+      </c>
+      <c r="K997" t="inlineStr">
+        <is>
+          <t>denuncia</t>
+        </is>
+      </c>
+      <c r="L997" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M997" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N997" t="inlineStr">
+        <is>
+          <t>denounces</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N997"/>
+  <dimension ref="A1:N999"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55852,6 +55852,114 @@
         </is>
       </c>
     </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>«Avanzamos hacia una planta temporal para fortalecer la operación directa»: Astrid Cáceres, directora del Bienestar Familiar.</t>
+        </is>
+      </c>
+      <c r="B998" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivAFBVV95cUxOZVdmdWtMR05kT3FCYmg4bDd0bUF5UnlNUEliQzNUNzJ5bjZEN216MGJEbjc2SUljUjI5NE1ZUzJrYU1CX0ZyODFfQzIyRlU3djUzRlcyZHQxVXZPM0NiN0ZUX0dOb2Z6WC05OWhrbUk2NzNJa1BucHNkUmZrUXNZWm9tWjE3TDlQVDdSRkxvVVptMGoxcWxvallCXy1FV1FhbWI1WGtBTUQ2bW56cGFLeE0yYUxLRkVTd3U2SQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C998" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D998" t="inlineStr"/>
+      <c r="E998" t="inlineStr"/>
+      <c r="F998" t="n">
+        <v>0</v>
+      </c>
+      <c r="G998" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H998" t="n">
+        <v>3</v>
+      </c>
+      <c r="I998" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J998" t="n">
+        <v>19</v>
+      </c>
+      <c r="K998" t="inlineStr">
+        <is>
+          <t>fortalecer</t>
+        </is>
+      </c>
+      <c r="L998" t="inlineStr">
+        <is>
+          <t>Astrid Cáceres</t>
+        </is>
+      </c>
+      <c r="M998" t="n">
+        <v>2</v>
+      </c>
+      <c r="N998" t="inlineStr">
+        <is>
+          <t>strengthen</t>
+        </is>
+      </c>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>ICBF emitió un comunicado tras denuncia de presunta vulneración de derechos de niña en CDI de San Luis de Palenque.</t>
+        </is>
+      </c>
+      <c r="B999" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi2AFBVV95cUxQbk1WSlZCSVdGX09oaFNGajk4QmZTbDF3MWhmQmIwMGFHek1WX242YS1RclJZVUdPRS0zaHJYdnNObWNyOXJBUGdSMnh0TUpmV25QX3hYeXpfTjZlUHAtZTZIOHlvNml1WUdqTkE4Q1BoYXI5NURpQWFxZkVMM1ZtOXhHTW1Qc3pQRE10eFo1REwwR1dJaG1xRV8ySlNKVFlOVkpRemM0UzN5Sm9abzB4Z0hxNjlYbzBmenRzb3lpUFhmNmlKY0F1WkxuTUZIWVJ1YUF2RHp0Wlg?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C999" t="inlineStr">
+        <is>
+          <t>Casanare online</t>
+        </is>
+      </c>
+      <c r="D999" t="inlineStr"/>
+      <c r="E999" t="inlineStr"/>
+      <c r="F999" t="n">
+        <v>0</v>
+      </c>
+      <c r="G999" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H999" t="n">
+        <v>3</v>
+      </c>
+      <c r="I999" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J999" t="n">
+        <v>19</v>
+      </c>
+      <c r="K999" t="inlineStr">
+        <is>
+          <t>denuncia</t>
+        </is>
+      </c>
+      <c r="L999" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M999" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N999" t="inlineStr">
+        <is>
+          <t>denounces</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N999"/>
+  <dimension ref="A1:N1000"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -55960,6 +55960,64 @@
         </is>
       </c>
     </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar fortalece capacidades en educación inclusiva de docentes y equipos psicosociales en Riohacha</t>
+        </is>
+      </c>
+      <c r="B1000" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiugFBVV95cUxObnZqNUpjdTJOb21JWHBoZ0J1dS1Zc1ZBclRKYy15VmcyWXlCRDdkNGthOWw3dXluX2Rham1JOEt4dE5qcTlCeUNqYUtyNjBtVXcwYXgySTl3V2lOVjNWUWRSd3czOW1FaTMtZVVMcEtwakk1TEpIa1FLcVVJZm1aVlJqaEg3Qm5yeVRfbWczaVk5R2tlUFBOa0FDOWNVUlZ5eUpoR1pPazg1TmtuQ1JidHh3ZkRrazROTWc?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1000" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1000" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="E1000" t="inlineStr"/>
+      <c r="F1000" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1000" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1000" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1000" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1000" t="n">
+        <v>19</v>
+      </c>
+      <c r="K1000" t="inlineStr">
+        <is>
+          <t>fortalece</t>
+        </is>
+      </c>
+      <c r="L1000" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1000" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1000" t="inlineStr">
+        <is>
+          <t>strengthens</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1000"/>
+  <dimension ref="A1:N1002"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56018,6 +56018,114 @@
         </is>
       </c>
     </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>ICBF llega a la Sierra y brinda atención a niños arhuacos en medio de conflicto</t>
+        </is>
+      </c>
+      <c r="B1001" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiugFBVV95cUxNNW5WdGg0V3NxcEc2Z0ROdERSTFZYTFFYemJfbzlRcW0yb3hNUkd5UmE5dDQxVlZvSWJ4WmJVMjVuX294TnNmZjVyRURvREJnNlhOUlh2TUJYc1A3MlpPNEt3eW44aUF5RDd0TS1RSGJicUZvZlFFamNCMllHLXZYVHpManBKeW9DdDVxNEFyNHVlUFdoSlBoUTFWWXJvSUNUa2JnUFpSWGoyZVVMcGZCTWQ3RnVUbmxYY1E?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1001" t="inlineStr">
+        <is>
+          <t>Seguimiento.co</t>
+        </is>
+      </c>
+      <c r="D1001" t="inlineStr"/>
+      <c r="E1001" t="inlineStr"/>
+      <c r="F1001" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1001" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1001" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1001" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1001" t="n">
+        <v>12</v>
+      </c>
+      <c r="K1001" t="inlineStr">
+        <is>
+          <t>conflicto</t>
+        </is>
+      </c>
+      <c r="L1001" t="inlineStr">
+        <is>
+          <t>Astrid Cáceres</t>
+        </is>
+      </c>
+      <c r="M1001" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1001" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>Procuraduría acusa que falta de impulso en procesos prolonga permanencia de menores de edad en protección del ICBF</t>
+        </is>
+      </c>
+      <c r="B1002" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiwAFBVV95cUxPakZSZDhXanRYOGFKaWtLakZaekZzLUpHZm5MVmVwRUxzUVFYY0pzMDlPY1podXVkV3dpYU9fcjNkZmk4RVFzTDU4ZVZTdU9HZHhJMDZDamJrWXpHbGJNdUZMRFRSbWJSSGxGc3BadUtMTGJhenZBYzhBMWd4TDNTMFdfU0d2NWZzVmdzSVRtNTBucUljbXNaMHpZRV9sSm9EZlV3S002S3FvZ0lrckhyQ09DQ2w3eTUwcHRSbll5NWU?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1002" t="inlineStr">
+        <is>
+          <t>Ecos del Combeima</t>
+        </is>
+      </c>
+      <c r="D1002" t="inlineStr"/>
+      <c r="E1002" t="inlineStr"/>
+      <c r="F1002" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1002" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1002" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1002" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1002" t="n">
+        <v>16</v>
+      </c>
+      <c r="K1002" t="inlineStr">
+        <is>
+          <t>acusa</t>
+        </is>
+      </c>
+      <c r="L1002" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1002" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1002" t="inlineStr">
+        <is>
+          <t>accuses</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1002"/>
+  <dimension ref="A1:N1003"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56126,6 +56126,64 @@
         </is>
       </c>
     </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>Rescatan a niño de 3 años abandonado en inquilinato de La Dorada, Caldas</t>
+        </is>
+      </c>
+      <c r="B1003" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMilgFBVV95cUxON21QZE5DTUROX2Iwd29rUExlZWJWMkRTQlh3SkhTZjJ6M05JemVkRy1aRGdaWVFia1pwYlVvQkVFTlNoYmZ3aGNMcUMyUGdpTlFjZzhyWjhzeWdGd3dqZ002dVFkek5OTExybml1SHdjNUNFUHRGTjd0WmIzWEFJbUlmSTdtdDJLcVRkYl9jLUFZTDJabmc?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1003" t="inlineStr">
+        <is>
+          <t>Crónica del Quindio</t>
+        </is>
+      </c>
+      <c r="D1003" t="inlineStr"/>
+      <c r="E1003" t="inlineStr">
+        <is>
+          <t>Caldas</t>
+        </is>
+      </c>
+      <c r="F1003" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1003" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1003" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1003" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J1003" t="n">
+        <v>20</v>
+      </c>
+      <c r="K1003" t="inlineStr">
+        <is>
+          <t>abandonado</t>
+        </is>
+      </c>
+      <c r="L1003" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1003" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1003" t="inlineStr">
+        <is>
+          <t>abandoned</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1003"/>
+  <dimension ref="A1:N1004"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56184,6 +56184,60 @@
         </is>
       </c>
     </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>Un niño de tres años fue rescatado tras denuncia ciudadana</t>
+        </is>
+      </c>
+      <c r="B1004" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMipwFBVV95cUxPU00wV19zTTUydzJyb3E5TXJVNlU5NkJza1ZWU2JkUGR4VzFVNy1KbC12bTM2NlMyeVdxNnB2OVpoX3Q4THJQV1hXRGRQNkQ3dXV4dURBeTU0djdHT21uWmhmbWQ4R0h2VHUzUkdqV21wRWg5eXc5OHFSTThCUnhHaVBRcGw1Ti02OS1YNlpzd1piNGVYQ0JqLXE2em02MnpLMGNXSUhrdw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1004" t="inlineStr">
+        <is>
+          <t>elnuevodia.com.co</t>
+        </is>
+      </c>
+      <c r="D1004" t="inlineStr"/>
+      <c r="E1004" t="inlineStr"/>
+      <c r="F1004" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1004" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1004" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1004" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="J1004" t="n">
+        <v>21</v>
+      </c>
+      <c r="K1004" t="inlineStr">
+        <is>
+          <t>denuncia</t>
+        </is>
+      </c>
+      <c r="L1004" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1004" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1004" t="inlineStr">
+        <is>
+          <t>denounces</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1004"/>
+  <dimension ref="A1:N1006"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56238,6 +56238,114 @@
         </is>
       </c>
     </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>Madre sustituta lucha por adoptar a una niña que le retiró el ICBF: esta es su historia</t>
+        </is>
+      </c>
+      <c r="B1005" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi4wFBVV95cUxPYTB1bjBiTjd1ZGZMWllpd2Y4cENCb2FIMHdmZ0VtVkpyNERKLUgyVm52UXUtbWdZU1dHR2NVc01WT3Y5clVCYXpLYV9iWkkyMV90S0FQcGF0TVdPd0l6NFhib21CYWZybFplZU1JMTRvS3RuM2pRaXBrYzdlZk5kbVZWcmo0U2FHem1LZFZtS0E2NElGV29ocjNIcGpjZDhUU0NhaEIwTE1qWmNqWFpfdGJvdlpaNXlKN1JOeUUyQmpDUnJaNFdNVjg0Q3YzS1VfeTBESC1xcFRfai04N3pCcDVrSQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1005" t="inlineStr">
+        <is>
+          <t>MSN</t>
+        </is>
+      </c>
+      <c r="D1005" t="inlineStr"/>
+      <c r="E1005" t="inlineStr"/>
+      <c r="F1005" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1005" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1005" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1005" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1005" t="n">
+        <v>23</v>
+      </c>
+      <c r="K1005" t="inlineStr">
+        <is>
+          <t>lucha</t>
+        </is>
+      </c>
+      <c r="L1005" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1005" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N1005" t="inlineStr">
+        <is>
+          <t>fight</t>
+        </is>
+      </c>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>Madre sustituta lucha por adoptar a una niña que le retiró el ICBF: esta es su historia</t>
+        </is>
+      </c>
+      <c r="B1006" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi4wFBVV95cUxPYTB1bjBiTjd1ZGZMWllpd2Y4cENCb2FIMHdmZ0VtVkpyNERKLUgyVm52UXUtbWdZU1dHR2NVc01WT3Y5clVCYXpLYV9iWkkyMV90S0FQcGF0TVdPd0l6NFhib21CYWZybFplZU1JMTRvS3RuM2pRaXBrYzdlZk5kbVZWcmo0U2FHem1LZFZtS0E2NElGV29ocjNIcGpjZDhUU0NhaEIwTE1qWmNqWFpfdGJvdlpaNXlKN1JOeUUyQmpDUnJaNFdNVjg0Q3YzS1VfeTBESC1xcFRfai04N3pCcDVrSQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1006" t="inlineStr">
+        <is>
+          <t>MSN</t>
+        </is>
+      </c>
+      <c r="D1006" t="inlineStr"/>
+      <c r="E1006" t="inlineStr"/>
+      <c r="F1006" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1006" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1006" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1006" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1006" t="n">
+        <v>23</v>
+      </c>
+      <c r="K1006" t="inlineStr">
+        <is>
+          <t>adoptar</t>
+        </is>
+      </c>
+      <c r="L1006" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1006" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1006" t="inlineStr">
+        <is>
+          <t>embrace</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1006"/>
+  <dimension ref="A1:N1007"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56346,6 +56346,60 @@
         </is>
       </c>
     </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>34 de los 570 menores del programa de reintegración quieren volver a la guerra: directora del ICBF</t>
+        </is>
+      </c>
+      <c r="B1007" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiuAFBVV95cUxPR1FmLXVwSjkyMFZ1Q0t4NEVaR3E0a1pSTkE2cWdjT0FFYURGX3kyUjM1RzB5dnRRaXJZUEpFc3RhQ3JNVkw3UC1TVncyaUpFbTRHYWttT3p3SUh4UE81RkdfUmQ2STlOVTdaSTJCWU44eG1yUi1GU1BVZ1Q4MGlrMUZzYjFIMlE0cG9ZMnB2OVRyOTEweUcwUXhPcUFCYmdrRkFxTkZWNTVqaUxGcVk3RTlqSnhfVTh4?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1007" t="inlineStr">
+        <is>
+          <t>larazon.co</t>
+        </is>
+      </c>
+      <c r="D1007" t="inlineStr"/>
+      <c r="E1007" t="inlineStr"/>
+      <c r="F1007" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1007" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H1007" t="n">
+        <v>11</v>
+      </c>
+      <c r="I1007" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1007" t="n">
+        <v>20</v>
+      </c>
+      <c r="K1007" t="inlineStr">
+        <is>
+          <t>guerra</t>
+        </is>
+      </c>
+      <c r="L1007" t="inlineStr">
+        <is>
+          <t>Astrid Cáceres</t>
+        </is>
+      </c>
+      <c r="M1007" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1007" t="inlineStr">
+        <is>
+          <t>war</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1007"/>
+  <dimension ref="A1:N1008"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56400,6 +56400,64 @@
         </is>
       </c>
     </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar fortalece la articulación institucional para prevenir y atender las violencias basadas en género en Cesar | Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="B1008" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiuwFBVV95cUxNVlBtXzdKMXpJWWdvSlJ0NUM4VWIwcEY2MkhLZndYMmVRQ25lbUhFaWdaWEtLRGlqa2N3SDlsV0hkcmYydmZBeUs2Vzk0OXFleTAtdTJnTDdHRUdLVTFpVS1rRU1YZ3ZxLWpXcDRBUXY1R0hDSjhvN2dmakpFejFvblFkR2lXNDBUM21jZnU3dFBDdjF5b0sxWHQ1ZHQ2d0Z1akxrN2JaNnpOaGlFaDFBVUpWOTFvZlcwV0s4?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1008" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1008" t="inlineStr"/>
+      <c r="E1008" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="F1008" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1008" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1008" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1008" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1008" t="n">
+        <v>24</v>
+      </c>
+      <c r="K1008" t="inlineStr">
+        <is>
+          <t>fortalece</t>
+        </is>
+      </c>
+      <c r="L1008" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1008" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1008" t="inlineStr">
+        <is>
+          <t>strengthens</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1008"/>
+  <dimension ref="A1:N1014"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56458,6 +56458,346 @@
         </is>
       </c>
     </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>Madre sustituta lucha por adoptar a una niña que le retiró el ICBF: esta es su historia | El Colombiano</t>
+        </is>
+      </c>
+      <c r="B1009" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMinwFBVV95cUxQZUdxaDlkWHNndG9VQWVDSXZnWDBFR1VZYkU4ZWJUeWM0QnRHVzB3ZDQ3UXNwQkNOTEpBRW9nNUhCUGI0bVhSakFyY3VmVk1mUHlaUHZhQ2VOSmNuVUVidDBtRnhHRm53WC16dGJ3ay1SRVFob05MSzl2WWNtbUVaR2xvcmdoVEM2RG93VnF5YTBPWm40YWZ1SkUtbWw1YXfSAaQBQVVfeXFMUE50eFV0LVBVUjNDMWNRbzdzQUY2WGtxWWR5cERrSEZnZ24yV1NwM0tCY2NnaXlpRThPS19pRUJDN3R1ZHZLaU9UVTFYZ1pUN2U5TW53REtfak9lRUluemNsNk5zdi1PWUhNWHdTcGpIVmFtNE9EaVZ4cFh0YzVCNi1VN2dYdU0wSGZHN1pYLU84d1dUUjBLZ2FfeVNsMm1tVEdfV2w?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1009" t="inlineStr">
+        <is>
+          <t>El Colombiano</t>
+        </is>
+      </c>
+      <c r="D1009" t="inlineStr"/>
+      <c r="E1009" t="inlineStr"/>
+      <c r="F1009" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1009" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1009" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1009" t="inlineStr">
+        <is>
+          <t>domingo</t>
+        </is>
+      </c>
+      <c r="J1009" t="n">
+        <v>22</v>
+      </c>
+      <c r="K1009" t="inlineStr">
+        <is>
+          <t>lucha</t>
+        </is>
+      </c>
+      <c r="L1009" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1009" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N1009" t="inlineStr">
+        <is>
+          <t>fight</t>
+        </is>
+      </c>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>Madre sustituta lucha por adoptar a una niña que le retiró el ICBF: esta es su historia | El Colombiano</t>
+        </is>
+      </c>
+      <c r="B1010" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMinwFBVV95cUxQZUdxaDlkWHNndG9VQWVDSXZnWDBFR1VZYkU4ZWJUeWM0QnRHVzB3ZDQ3UXNwQkNOTEpBRW9nNUhCUGI0bVhSakFyY3VmVk1mUHlaUHZhQ2VOSmNuVUVidDBtRnhHRm53WC16dGJ3ay1SRVFob05MSzl2WWNtbUVaR2xvcmdoVEM2RG93VnF5YTBPWm40YWZ1SkUtbWw1YXfSAaQBQVVfeXFMUE50eFV0LVBVUjNDMWNRbzdzQUY2WGtxWWR5cERrSEZnZ24yV1NwM0tCY2NnaXlpRThPS19pRUJDN3R1ZHZLaU9UVTFYZ1pUN2U5TW53REtfak9lRUluemNsNk5zdi1PWUhNWHdTcGpIVmFtNE9EaVZ4cFh0YzVCNi1VN2dYdU0wSGZHN1pYLU84d1dUUjBLZ2FfeVNsMm1tVEdfV2w?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1010" t="inlineStr">
+        <is>
+          <t>El Colombiano</t>
+        </is>
+      </c>
+      <c r="D1010" t="inlineStr"/>
+      <c r="E1010" t="inlineStr"/>
+      <c r="F1010" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1010" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1010" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1010" t="inlineStr">
+        <is>
+          <t>domingo</t>
+        </is>
+      </c>
+      <c r="J1010" t="n">
+        <v>22</v>
+      </c>
+      <c r="K1010" t="inlineStr">
+        <is>
+          <t>adoptar</t>
+        </is>
+      </c>
+      <c r="L1010" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1010" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1010" t="inlineStr">
+        <is>
+          <t>embrace</t>
+        </is>
+      </c>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar promueve la inclusión en jornada de movilización social en Ciudad Bolívar</t>
+        </is>
+      </c>
+      <c r="B1011" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiuAFBVV95cUxNeURiNXNUZi12aHpwSUg4N0s0UnZ3SkhwLVdjU0ZmUFhZaDJMVFhiZXdqQ3dVeXpyaTF4VnpDZVpYVlkxenludVc1d1dnUHVVMnJlS09MUzNFMWtZa01iaDFzV3JIMDJ6WGhtQXloRzJFeVA2VnZIOUctXzRZVVBpV1V2NWN1ZjJhSklNcHNYc2tkcWtQX1JCSXRXNTNIRUxlRkk1ZGdsV2tBcDhJdVlmZUg0c0dvQTZ4?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1011" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1011" t="inlineStr"/>
+      <c r="E1011" t="inlineStr">
+        <is>
+          <t>Bolívar</t>
+        </is>
+      </c>
+      <c r="F1011" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1011" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1011" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1011" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1011" t="n">
+        <v>24</v>
+      </c>
+      <c r="K1011" t="inlineStr">
+        <is>
+          <t>promueve</t>
+        </is>
+      </c>
+      <c r="L1011" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1011" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1011" t="inlineStr">
+        <is>
+          <t>promotes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>En Casanare, Bienestar Familiar fortalece la garantía de derechos de la niñez y adolescencia junto a entidades territoriales | Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="B1012" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMisAFBVV95cUxPZjNiRzNudzJYeDBSWTk0aXZpN3RIZzAzMkZENjk4TVFKbG1OTVhhUDZ6Wmh0cl9yQnZPYWlJU3U1V0dlcVZMOGlzNXBLZmRJX2xRLWVocnlWcWpETWNVWXpySlgwUWZ1VE10QUs3dklJZlBUclc5eEZic3JIZGFhZ1hlMXVPbl80aVFON1d4S1htbmxlOUtxdl9POU1MS0Q1VGFoRlgwemM5NEVrTEdPWQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1012" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1012" t="inlineStr"/>
+      <c r="E1012" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="F1012" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1012" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1012" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1012" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1012" t="n">
+        <v>24</v>
+      </c>
+      <c r="K1012" t="inlineStr">
+        <is>
+          <t>fortalece</t>
+        </is>
+      </c>
+      <c r="L1012" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1012" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1012" t="inlineStr">
+        <is>
+          <t>strengthens</t>
+        </is>
+      </c>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>En Casanare, Bienestar Familiar fortalece la garantía de derechos de la niñez y adolescencia junto a entidades territoriales | Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="B1013" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMisAFBVV95cUxPZjNiRzNudzJYeDBSWTk0aXZpN3RIZzAzMkZENjk4TVFKbG1OTVhhUDZ6Wmh0cl9yQnZPYWlJU3U1V0dlcVZMOGlzNXBLZmRJX2xRLWVocnlWcWpETWNVWXpySlgwUWZ1VE10QUs3dklJZlBUclc5eEZic3JIZGFhZ1hlMXVPbl80aVFON1d4S1htbmxlOUtxdl9POU1MS0Q1VGFoRlgwemM5NEVrTEdPWQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1013" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1013" t="inlineStr"/>
+      <c r="E1013" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="F1013" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1013" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1013" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1013" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1013" t="n">
+        <v>24</v>
+      </c>
+      <c r="K1013" t="inlineStr">
+        <is>
+          <t>garantía</t>
+        </is>
+      </c>
+      <c r="L1013" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1013" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1013" t="inlineStr">
+        <is>
+          <t>guarantee</t>
+        </is>
+      </c>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar fortalece la articulación institucional para prevenir y atender las violencias basadas en género en Cesar</t>
+        </is>
+      </c>
+      <c r="B1014" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiuwFBVV95cUxNVlBtXzdKMXpJWWdvSlJ0NUM4VWIwcEY2MkhLZndYMmVRQ25lbUhFaWdaWEtLRGlqa2N3SDlsV0hkcmYydmZBeUs2Vzk0OXFleTAtdTJnTDdHRUdLVTFpVS1rRU1YZ3ZxLWpXcDRBUXY1R0hDSjhvN2dmakpFejFvblFkR2lXNDBUM21jZnU3dFBDdjF5b0sxWHQ1ZHQ2d0Z1akxrN2JaNnpOaGlFaDFBVUpWOTFvZlcwV0s4?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1014" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1014" t="inlineStr"/>
+      <c r="E1014" t="inlineStr">
+        <is>
+          <t>Cesar</t>
+        </is>
+      </c>
+      <c r="F1014" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1014" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1014" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1014" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1014" t="n">
+        <v>24</v>
+      </c>
+      <c r="K1014" t="inlineStr">
+        <is>
+          <t>fortalece</t>
+        </is>
+      </c>
+      <c r="L1014" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1014" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1014" t="inlineStr">
+        <is>
+          <t>strengthens</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1014"/>
+  <dimension ref="A1:N1016"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56798,6 +56798,122 @@
         </is>
       </c>
     </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>En Casanare, Bienestar Familiar fortalece la garantía de derechos de la niñez y adolescencia junto a entidades territoriales</t>
+        </is>
+      </c>
+      <c r="B1015" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMisAFBVV95cUxPZjNiRzNudzJYeDBSWTk0aXZpN3RIZzAzMkZENjk4TVFKbG1OTVhhUDZ6Wmh0cl9yQnZPYWlJU3U1V0dlcVZMOGlzNXBLZmRJX2xRLWVocnlWcWpETWNVWXpySlgwUWZ1VE10QUs3dklJZlBUclc5eEZic3JIZGFhZ1hlMXVPbl80aVFON1d4S1htbmxlOUtxdl9POU1MS0Q1VGFoRlgwemM5NEVrTEdPWQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1015" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1015" t="inlineStr"/>
+      <c r="E1015" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="F1015" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1015" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1015" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1015" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1015" t="n">
+        <v>24</v>
+      </c>
+      <c r="K1015" t="inlineStr">
+        <is>
+          <t>fortalece</t>
+        </is>
+      </c>
+      <c r="L1015" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1015" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1015" t="inlineStr">
+        <is>
+          <t>strengthens</t>
+        </is>
+      </c>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>En Casanare, Bienestar Familiar fortalece la garantía de derechos de la niñez y adolescencia junto a entidades territoriales</t>
+        </is>
+      </c>
+      <c r="B1016" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMisAFBVV95cUxPZjNiRzNudzJYeDBSWTk0aXZpN3RIZzAzMkZENjk4TVFKbG1OTVhhUDZ6Wmh0cl9yQnZPYWlJU3U1V0dlcVZMOGlzNXBLZmRJX2xRLWVocnlWcWpETWNVWXpySlgwUWZ1VE10QUs3dklJZlBUclc5eEZic3JIZGFhZ1hlMXVPbl80aVFON1d4S1htbmxlOUtxdl9POU1MS0Q1VGFoRlgwemM5NEVrTEdPWQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1016" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1016" t="inlineStr"/>
+      <c r="E1016" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="F1016" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1016" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1016" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1016" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1016" t="n">
+        <v>24</v>
+      </c>
+      <c r="K1016" t="inlineStr">
+        <is>
+          <t>garantía</t>
+        </is>
+      </c>
+      <c r="L1016" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1016" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1016" t="inlineStr">
+        <is>
+          <t>guarantee</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1016"/>
+  <dimension ref="A1:N1017"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56914,6 +56914,64 @@
         </is>
       </c>
     </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>Alianza entre ICBF, Icetex y la Universidad Cooperativa impacta 193 espacios de atención infantil en Boyacá</t>
+        </is>
+      </c>
+      <c r="B1017" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi3gFBVV95cUxOVktsclF5VXJncGlMOExzR1YwYUg3RGVnTlBzeFd0OWpRWng5OHFyd0U5cnNoTFhDZjFtb01hVkxncVdhNXlHRzFzdFo0Xy0wQURFT3N2RWZyTndUMldKVS10YzJzUXNPb1JkUXZJdWhWdFgwVmkyY2tNT2VqMXdiZ3FzaEJYZ1AxVzRjU1l6T3JUUFBfdTQ3UkJaU1k0bVJ1RkY2d3I1RW9pUDFJSXdlRUJWR3JSN2d6UFZxRUhIeldKWTZEUmpSeG1QaU1jVzE3aGJCaWM0VjB6Wk0wVGc?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1017" t="inlineStr">
+        <is>
+          <t>Boyacá 7 Días</t>
+        </is>
+      </c>
+      <c r="D1017" t="inlineStr"/>
+      <c r="E1017" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="F1017" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1017" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1017" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1017" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J1017" t="n">
+        <v>25</v>
+      </c>
+      <c r="K1017" t="inlineStr">
+        <is>
+          <t>infantil</t>
+        </is>
+      </c>
+      <c r="L1017" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1017" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1017" t="inlineStr">
+        <is>
+          <t>childish</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1017"/>
+  <dimension ref="A1:N1019"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -56972,6 +56972,118 @@
         </is>
       </c>
     </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>Las infancias y adolescencias alzan la voz por la paz y sus derechos en el Foro de Alto Nivel CELAC–África 2026</t>
+        </is>
+      </c>
+      <c r="B1018" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivAFBVV95cUxOTi0tOXlwYnloLVpIMmRubXBIcURUM1MyalljZDRxYzZILWJzRXZqWlZKcjl5VDdyMk1aLTJ1REVKSnVMNzBzTE56dmxTS2xCWlV5eUk5OHBXLWpncnlTN1R5M3Vtbm1xZzZ1ckdqNWpXU1E4MDVpRnR5ZjAwRHg3UHBMbF9YQVFDMDFKZFJTSkNHWEdFdHBLVXRpcEhpUWdJVXZhbS15TmpmWmFOM3QwU2FoLTFfcnQwakg2Vg?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1018" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1018" t="inlineStr"/>
+      <c r="E1018" t="inlineStr"/>
+      <c r="F1018" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1018" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1018" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1018" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1018" t="n">
+        <v>26</v>
+      </c>
+      <c r="K1018" t="inlineStr">
+        <is>
+          <t>paz</t>
+        </is>
+      </c>
+      <c r="L1018" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1018" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1018" t="inlineStr">
+        <is>
+          <t>peace</t>
+        </is>
+      </c>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>Entre raíces y saberes, el Bienestar Familiar fortalece la primera infancia en el Tolima</t>
+        </is>
+      </c>
+      <c r="B1019" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivAFBVV95cUxPaUU1R3NUVFQ2NnZndFRjU2swUFkyY1lsbmVKTXRuQmttZ21QRjFhT09udUZadkFaNVMzbi1ZTjdDMzRNcF96Zmh4dXFqZFFqMVF1WHBORGMtS1RTTkxzbzZ2T25nSEVTVXBXckcwWUtGa0NfLVNOa1U4cUc3dUdJX0tvOGZ2UDZQanJmWmRNMks0c2xZOWxGZXpxWVJickRiME16dEgxZERtcW54b0oxellnWGtiT3RRS1c2eA?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1019" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1019" t="inlineStr"/>
+      <c r="E1019" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="F1019" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1019" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1019" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1019" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1019" t="n">
+        <v>26</v>
+      </c>
+      <c r="K1019" t="inlineStr">
+        <is>
+          <t>fortalece</t>
+        </is>
+      </c>
+      <c r="L1019" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1019" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1019" t="inlineStr">
+        <is>
+          <t>strengthens</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1019"/>
+  <dimension ref="A1:N1020"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57084,6 +57084,64 @@
         </is>
       </c>
     </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>Adolescentes del Sistema de Responsabilidad Penal construyen nuevas oportunidades de vida en Yopal</t>
+        </is>
+      </c>
+      <c r="B1020" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivwFBVV95cUxQWll4eGoxd2hKaXdMOUJESU1wUkR0MG5zNGcwWDNkd3lDVHhuTkJDdkE1Z3dDemd1MjJraTBMbkZlZ0hRS1hLNjVXSXBjazVmQUp5NUlydmtFNmlqRFJrY2FIMDRkX2JpR0dWNkFtZDFfVU9WZnY4cFNQOEhZaWVUV2J3dEoyc2FyX1NjdTZHdTZsZzh1MExDeWtIYW5sWklibDBkUkY5VDN3YmV5R1ZzZ0xjUGlCVFRESC1HT1U1dw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1020" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1020" t="inlineStr">
+        <is>
+          <t>Yopal</t>
+        </is>
+      </c>
+      <c r="E1020" t="inlineStr"/>
+      <c r="F1020" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1020" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1020" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1020" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1020" t="n">
+        <v>26</v>
+      </c>
+      <c r="K1020" t="inlineStr">
+        <is>
+          <t>oportunidades</t>
+        </is>
+      </c>
+      <c r="L1020" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1020" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1020" t="inlineStr">
+        <is>
+          <t>opportunities</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1020"/>
+  <dimension ref="A1:N1021"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57142,6 +57142,60 @@
         </is>
       </c>
     </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>“Es como si hubiésemos nombrado a Garavito director del ICBF”: escándalo por nombramiento de Sandra Ramírez, expareja de ‘Tirofijo’</t>
+        </is>
+      </c>
+      <c r="B1021" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMinAJBVV95cUxNbC0xZlh5VmxUVkE3MFpvTkJlWm5ra1JLS19EdGg2RkFHcTBoczM2VlB1Z3E4VTlfc0h3U0lpb3hKNWFwZndwZ1RXWXpKdUc0RjJaakhURXZnMUoxZzVnMFhjNUotVmdVNEUyclFqTmJRbEdnNXFOdU9qSlFka1lTdXlrS01xUUpYcGRnUWtJMkh2RHZkdXZJRFhTSUtCcTZ4M3dScTJDbWFOYmcwR211T3FKNHJ6NUdadXVOMVR6N19zQVkyaF9HQ1FaVDFLV0haVGhYWTNkSnNKVExxS3J1NXFVeXZkbnh2OF9QXzR1ZFlZSGNsX3lQNjVkMkZGZVFqTzBkMWU3akpuLU5wU1N5eXplbU04TzhXRGozatIBogJBVV95cUxQbDVKWTFJdEdsZVV6YU1wMF9PODdxM0FUQ2R1WkhkaWJWYjJIeTVsVzRVWGl6VXMyR0duOVBQM3F2dmthLVBoN1hBQVkwQUN3WGszTktOT3hOV01lNkNMQmc1dUN2MUM3a2pXTUFkN2FQNnVXMWd0THhfbE92R1VmR2FxYkp6N3ZYdHBSX19NUjctMEhnM2EzR0VpeTlpYjdvdXVUMG1uMmQ5QWU1S0FPODNUTDg4MG5jeEVKT2ltLVZQUk5TdENvZXV3NUgyM0FOM2tVNThwRmYyNW9DcERmT2NzLVpBMWN5MlNiOTFOc0V0bWRraDRWWFhMWmtrOVRHTG43MF9JSVdpc0Z5TmJVTkJibFJWb2hrM3IzTnJJRFBLQQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1021" t="inlineStr">
+        <is>
+          <t>Revista Semana</t>
+        </is>
+      </c>
+      <c r="D1021" t="inlineStr"/>
+      <c r="E1021" t="inlineStr"/>
+      <c r="F1021" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1021" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1021" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1021" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J1021" t="n">
+        <v>27</v>
+      </c>
+      <c r="K1021" t="inlineStr">
+        <is>
+          <t>escándalo</t>
+        </is>
+      </c>
+      <c r="L1021" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1021" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1021" t="inlineStr">
+        <is>
+          <t>scandal</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1021"/>
+  <dimension ref="A1:N1022"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57196,6 +57196,64 @@
         </is>
       </c>
     </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>ICBF rompe el silencio frente al caso de presunto abuso de una estudiante en Ibagué</t>
+        </is>
+      </c>
+      <c r="B1022" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiywFBVV95cUxNQmJVYUJCelBidXZzUmFrQzl1bnlfampxMzFQdVE5cGdCRmEtNm15U2lKZklScTkxY2J1NkpUZTJ6NW1PQVhMcjVmclI1X3F2T0phX292cEN1cGtyOE56cWlqRy1UQmhMN2Z1d2pqNVMtRUJxMnFBSElHMFI0V0hpekxRaWlmOTBhR0phWnAtQmNoaF90bk9YaHhjTm9vbUx5WmwtU2x3NDROMUVYaG5fb19waURwbGtORG1QbWFVZU5EUlQ3bVBWN1E1bw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1022" t="inlineStr">
+        <is>
+          <t>El Irreverente Ibagué</t>
+        </is>
+      </c>
+      <c r="D1022" t="inlineStr">
+        <is>
+          <t>Ibagué</t>
+        </is>
+      </c>
+      <c r="E1022" t="inlineStr"/>
+      <c r="F1022" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1022" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1022" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1022" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="J1022" t="n">
+        <v>28</v>
+      </c>
+      <c r="K1022" t="inlineStr">
+        <is>
+          <t>abuso</t>
+        </is>
+      </c>
+      <c r="L1022" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1022" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1022" t="inlineStr">
+        <is>
+          <t>abuse</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1022"/>
+  <dimension ref="A1:N1025"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57254,6 +57254,180 @@
         </is>
       </c>
     </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>ICBF pide celeridad en caso de presunto abuso en jardín de Ibagué</t>
+        </is>
+      </c>
+      <c r="B1023" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMimAFBVV95cUxOTU1iVnJrd2RGb3lScXY2aFB3dUpiTkk5YXp5M3VwUzRSRmE5bUV0TjB4bkM3MGVCSkE0ckY4MENwS01aRlFVRW95UUEwNnJGTjdLLXFWeDBMR0piQk5ub2h4Y0l6ZEtMLWZ2YlQ3TFFkOE1sMF9wb0ZPY3Zta1U2TDRQNk1yMjdYSlRCQk0zYVRfa0N3TjI1eQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1023" t="inlineStr">
+        <is>
+          <t>El Olfato</t>
+        </is>
+      </c>
+      <c r="D1023" t="inlineStr">
+        <is>
+          <t>Ibagué</t>
+        </is>
+      </c>
+      <c r="E1023" t="inlineStr"/>
+      <c r="F1023" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1023" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1023" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1023" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="J1023" t="n">
+        <v>28</v>
+      </c>
+      <c r="K1023" t="inlineStr">
+        <is>
+          <t>abuso</t>
+        </is>
+      </c>
+      <c r="L1023" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1023" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1023" t="inlineStr">
+        <is>
+          <t>abuse</t>
+        </is>
+      </c>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>Cancelan licencia a jardín infantil de Ibagué tras presunto abuso sexual a una niña</t>
+        </is>
+      </c>
+      <c r="B1024" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiugFBVV95cUxQYmdlRHBhN1FJOGl5cWNpamFLaFl5QW5NMEtGNzlyalJ5eUowSEt4cDd6NU9pNVhnOEYxY2lRcVJNRXdROE81dEVBTTFOSzY2UHd2QTd0a204aTc0MWYxZjh2STNYTFdxUHEzb2NOeU5sbmxiTFFxR2hNa2N0R2RfTWJOSk9sM2pSWlE4U2lkZ09pMTVIUUotazFfeVJtT0JwX1E1dVVlbDR6azdIcVQ2REVfSmhKNEdldGfSAc4BQVVfeXFMTUJoRkdkZ2lESUpIdjJ6OUx3UmJENWRfMUNZTDV3bFpORGYyV0JvTFM4bGkwQ0VYcEFtR1JUdnlOWWtJcXJfZDY0QV8yeW1IV0g2MDRIeG5KRVRSVXdlZW5rb1Z1aWhHUU5aMU1qaFcxR3Q4dmZuYVFEdkhkS2V1Q1VDX082M3VIdW9CalhvM3E4V3NOdXFzNGdNaE1TRTVGUDZVbEVfbXEwRFVUclNZNVVacjNwdU14RW5XaWw0Z0hFeEhsN1RmcVQ0OGZNNGc?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1024" t="inlineStr">
+        <is>
+          <t>Caracol Radio</t>
+        </is>
+      </c>
+      <c r="D1024" t="inlineStr">
+        <is>
+          <t>Ibagué</t>
+        </is>
+      </c>
+      <c r="E1024" t="inlineStr"/>
+      <c r="F1024" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1024" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1024" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1024" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="J1024" t="n">
+        <v>28</v>
+      </c>
+      <c r="K1024" t="inlineStr">
+        <is>
+          <t>infantil</t>
+        </is>
+      </c>
+      <c r="L1024" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1024" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1024" t="inlineStr">
+        <is>
+          <t>childish</t>
+        </is>
+      </c>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>Cancelan licencia a jardín infantil de Ibagué tras presunto abuso sexual a una niña</t>
+        </is>
+      </c>
+      <c r="B1025" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiugFBVV95cUxQYmdlRHBhN1FJOGl5cWNpamFLaFl5QW5NMEtGNzlyalJ5eUowSEt4cDd6NU9pNVhnOEYxY2lRcVJNRXdROE81dEVBTTFOSzY2UHd2QTd0a204aTc0MWYxZjh2STNYTFdxUHEzb2NOeU5sbmxiTFFxR2hNa2N0R2RfTWJOSk9sM2pSWlE4U2lkZ09pMTVIUUotazFfeVJtT0JwX1E1dVVlbDR6azdIcVQ2REVfSmhKNEdldGfSAc4BQVVfeXFMTUJoRkdkZ2lESUpIdjJ6OUx3UmJENWRfMUNZTDV3bFpORGYyV0JvTFM4bGkwQ0VYcEFtR1JUdnlOWWtJcXJfZDY0QV8yeW1IV0g2MDRIeG5KRVRSVXdlZW5rb1Z1aWhHUU5aMU1qaFcxR3Q4dmZuYVFEdkhkS2V1Q1VDX082M3VIdW9CalhvM3E4V3NOdXFzNGdNaE1TRTVGUDZVbEVfbXEwRFVUclNZNVVacjNwdU14RW5XaWw0Z0hFeEhsN1RmcVQ0OGZNNGc?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1025" t="inlineStr">
+        <is>
+          <t>Caracol Radio</t>
+        </is>
+      </c>
+      <c r="D1025" t="inlineStr">
+        <is>
+          <t>Ibagué</t>
+        </is>
+      </c>
+      <c r="E1025" t="inlineStr"/>
+      <c r="F1025" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1025" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1025" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1025" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="J1025" t="n">
+        <v>28</v>
+      </c>
+      <c r="K1025" t="inlineStr">
+        <is>
+          <t>abuso</t>
+        </is>
+      </c>
+      <c r="L1025" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1025" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1025" t="inlineStr">
+        <is>
+          <t>abuse</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1025"/>
+  <dimension ref="A1:N1026"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57428,6 +57428,60 @@
         </is>
       </c>
     </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>ICBF aclara versiones sobre el menor fugado y relacionado con el atentado que acabó con la vida de Miguel Uribe Turbay</t>
+        </is>
+      </c>
+      <c r="B1026" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi-AFBVV95cUxPa3dXZ3ZVSXdyc05vR3d4T1RCSnNXek1ic3dQbW1JTVBPbDFZNEVJM2N4anEzMUZSY2RSa19GV1JCNjhxMENFb0FnX2hvcGZlNFlmV2ZlVE1wOGNCU0ZwTFhSa21WNW5iNVpuTkVMMTJEWVhVV1A5R2FxcEFDQUh1Z3lTTk1MUEM4a0kwb0NpOW1qWXZlanpCWVdHTU0tal9iXzEtZjNuSWVPazU5U2M1R0hZUXlYQUJYckw3ZngyVzgxMW5GWU02ekxPODcwYUNZZEcxaGdLRWI2SElYdEt6MjY5RW9SdDNwcmEzd1Y4TExmZDBmNVYteNIB_gFBVV95cUxQNktBUDV5VWtFc1ZOUEtaNG9OX2xmQzVwMVJiZFpZZU9jNHhNTm42LTNVU1p3OVFfdnhFZFU4Vkh5MUdVc0lSNVcwQmRCX3NRelp3cV8yU3RwZHBIVF8yNDdCQ25qbEtuTTVDZTRpV01YaHZRYm1kOUE0SFlmemFFYmdfS2g1RHk2eXQyM2puS0tzY2xldmpoczVXVjliN0JrNy1vZ1FhMG1nSmtkX2VQTFJhelRXX3FrNzFiN0t4dmJZcXk0aDVXdHpSREdNTFZ0eWxMSUpqZGV6LVNMcjUxTTVsR2pHM0N0N0V6bWFuLUJtVk5MUzYxOFRHQnhqQQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1026" t="inlineStr">
+        <is>
+          <t>semana.com</t>
+        </is>
+      </c>
+      <c r="D1026" t="inlineStr"/>
+      <c r="E1026" t="inlineStr"/>
+      <c r="F1026" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1026" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H1026" t="n">
+        <v>8</v>
+      </c>
+      <c r="I1026" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J1026" t="n">
+        <v>29</v>
+      </c>
+      <c r="K1026" t="inlineStr">
+        <is>
+          <t>aclara</t>
+        </is>
+      </c>
+      <c r="L1026" t="inlineStr">
+        <is>
+          <t>Astrid Cáceres</t>
+        </is>
+      </c>
+      <c r="M1026" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1026" t="inlineStr">
+        <is>
+          <t>clarifies</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1026"/>
+  <dimension ref="A1:N1028"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57482,6 +57482,114 @@
         </is>
       </c>
     </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar continúa atendiendo a las comunidades afectadas por la grave crisis humanitaria en el Catatumbo</t>
+        </is>
+      </c>
+      <c r="B1027" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiuAFBVV95cUxQMjJVRUl3cTlLTEdpY0hjaG5IaTJuX1Q1UE9FaWktckVBbmhjUFI4amVQVnM4RFhwcEpHNS1fQU5TUlBzX3hkN2FpNkpEYUFtT0tVS0FNTC1Ebm5sNTRJS3ZsM2k5d0QtdGRkeFE5dUV2LTdKdDJtNjh3VTVvd25ULS1WaVpTSE1KNEdUQ1U0aEVFeFJNOGpxdWtXbFl0RkowY3NKLUE2aG9QZkxzeXlab0lZR2Q5WV82?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1027" t="inlineStr">
+        <is>
+          <t>icbf.gov.co</t>
+        </is>
+      </c>
+      <c r="D1027" t="inlineStr"/>
+      <c r="E1027" t="inlineStr"/>
+      <c r="F1027" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1027" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1027" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1027" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1027" t="n">
+        <v>30</v>
+      </c>
+      <c r="K1027" t="inlineStr">
+        <is>
+          <t>grave</t>
+        </is>
+      </c>
+      <c r="L1027" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1027" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1027" t="inlineStr">
+        <is>
+          <t>severe</t>
+        </is>
+      </c>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar continúa atendiendo a las comunidades afectadas por la grave crisis humanitaria en el Catatumbo</t>
+        </is>
+      </c>
+      <c r="B1028" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiuAFBVV95cUxQMjJVRUl3cTlLTEdpY0hjaG5IaTJuX1Q1UE9FaWktckVBbmhjUFI4amVQVnM4RFhwcEpHNS1fQU5TUlBzX3hkN2FpNkpEYUFtT0tVS0FNTC1Ebm5sNTRJS3ZsM2k5d0QtdGRkeFE5dUV2LTdKdDJtNjh3VTVvd25ULS1WaVpTSE1KNEdUQ1U0aEVFeFJNOGpxdWtXbFl0RkowY3NKLUE2aG9QZkxzeXlab0lZR2Q5WV82?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1028" t="inlineStr">
+        <is>
+          <t>icbf.gov.co</t>
+        </is>
+      </c>
+      <c r="D1028" t="inlineStr"/>
+      <c r="E1028" t="inlineStr"/>
+      <c r="F1028" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1028" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1028" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1028" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1028" t="n">
+        <v>30</v>
+      </c>
+      <c r="K1028" t="inlineStr">
+        <is>
+          <t>crisis</t>
+        </is>
+      </c>
+      <c r="L1028" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1028" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1028" t="inlineStr">
+        <is>
+          <t>crisis</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1028"/>
+  <dimension ref="A1:N1029"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57590,6 +57590,64 @@
         </is>
       </c>
     </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>Kevin Escorcia «K 27 Rap Real»: una historia de justicia restaurativa en Quindío</t>
+        </is>
+      </c>
+      <c r="B1029" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMirwFBVV95cUxPRUFuLXFXMjVZMG5aNlBCUmgyMVlrSjNCNzdJSmpEcW5HVlVtVXhzeHFFWDBRYVdJVVZ0Ymd5eVUtSjl2SERqZkZxcE93N085QkZHbTNZcThucmR5VmJZcXg1VVhCM0FfdVB4SDRfV0w4b3B1enpYRG45YUhXX1BQanhoVTFwWWI0YktTNHg2eVlDaVVDNWdjT2JYNUZMN1ZOd09LR3poajJUcUxqajBj?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1029" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1029" t="inlineStr"/>
+      <c r="E1029" t="inlineStr">
+        <is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="F1029" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1029" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1029" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1029" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1029" t="n">
+        <v>31</v>
+      </c>
+      <c r="K1029" t="inlineStr">
+        <is>
+          <t>justicia</t>
+        </is>
+      </c>
+      <c r="L1029" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1029" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1029" t="inlineStr">
+        <is>
+          <t>justice</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1029"/>
+  <dimension ref="A1:N1035"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57648,6 +57648,354 @@
         </is>
       </c>
     </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>Así se habrían robado 860 millones de pesos del ICBF destinados a alimentar niños y mujeres gestantes en La Guajira</t>
+        </is>
+      </c>
+      <c r="B1030" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi9wFBVV95cUxQUmI3S2RqdWo0NVFsY3o0NU5OOHZ3RkVrajltakpzaG11Q19xbGJ4clR3V29pWjFyU25VZ0dUck1YQ2lDZGU1aTZQOThOb2VPTjRRY2pVcHp3eVRINWk4a0JTTzZlM1N1NXUzNmJvcnFjWWpnWFpyVUVaSkJCVGtmWXRDdkkxbUNHV3lMWXRiQTZQZ1NFV2poc3JpMnI1ZnZ4YUg5TnZvMzBOWEJCS3FFejVZTU1rZ2hRVHhScjczOTVaZ0IxSUFvb05aYnBSYUZhRzhPUUFyTGJ2WnZBS21kc3NvZGpOSy1YaWx6dFVvb2pveUU3WWlR?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1030" t="inlineStr">
+        <is>
+          <t>CAMBIO Colombia</t>
+        </is>
+      </c>
+      <c r="D1030" t="inlineStr"/>
+      <c r="E1030" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="F1030" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1030" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1030" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1030" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1030" t="n">
+        <v>31</v>
+      </c>
+      <c r="K1030" t="inlineStr">
+        <is>
+          <t>robado</t>
+        </is>
+      </c>
+      <c r="L1030" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1030" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1030" t="inlineStr">
+        <is>
+          <t>stolen</t>
+        </is>
+      </c>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>Su familiar detalló su incapacidad para protegerla y solicitó ayuda del personal médico, mientras la adolescente recibe atención bajo la custodia del Icbf</t>
+        </is>
+      </c>
+      <c r="B1031" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi6wFBVV95cUxNcUFWbWI0Vktvd3NpRTJycmdIU3I4cFVKNnA3TWdUdDlQQy1sUkNQTDFjVEU4cW1nMTgtWm5IdkdaMkphVGdFRGN5TnJFYzFLakV1NzBVT3A0SFFOQm9IN0xtSG03elo0SkZVdktSVmNFa0x5M0tQSHQ4VkNlN3JHaGJ5STFEZVBqcGF3eURhdWk4c0pLQkI1NkE5WHY2QjVuZVp3VTRzY1pXMmQ2b09CWkg3b1JyZ2hQNmRKeVI2QVRPVTQ5NEFfRVl1SlFxUFR3SkYxNWl3TXVGcVdmM3phY05VYkI4bFJkbkg4?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1031" t="inlineStr">
+        <is>
+          <t>facebook.com</t>
+        </is>
+      </c>
+      <c r="D1031" t="inlineStr"/>
+      <c r="E1031" t="inlineStr"/>
+      <c r="F1031" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1031" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1031" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1031" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1031" t="n">
+        <v>31</v>
+      </c>
+      <c r="K1031" t="inlineStr">
+        <is>
+          <t>incapacidad</t>
+        </is>
+      </c>
+      <c r="L1031" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1031" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1031" t="inlineStr">
+        <is>
+          <t>inability</t>
+        </is>
+      </c>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>Su familiar detalló su incapacidad para protegerla y solicitó ayuda del personal médico, mientras la adolescente recibe atención bajo la custodia del Icbf</t>
+        </is>
+      </c>
+      <c r="B1032" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi6wFBVV95cUxNcUFWbWI0Vktvd3NpRTJycmdIU3I4cFVKNnA3TWdUdDlQQy1sUkNQTDFjVEU4cW1nMTgtWm5IdkdaMkphVGdFRGN5TnJFYzFLakV1NzBVT3A0SFFOQm9IN0xtSG03elo0SkZVdktSVmNFa0x5M0tQSHQ4VkNlN3JHaGJ5STFEZVBqcGF3eURhdWk4c0pLQkI1NkE5WHY2QjVuZVp3VTRzY1pXMmQ2b09CWkg3b1JyZ2hQNmRKeVI2QVRPVTQ5NEFfRVl1SlFxUFR3SkYxNWl3TXVGcVdmM3phY05VYkI4bFJkbkg4?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1032" t="inlineStr">
+        <is>
+          <t>facebook.com</t>
+        </is>
+      </c>
+      <c r="D1032" t="inlineStr"/>
+      <c r="E1032" t="inlineStr"/>
+      <c r="F1032" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1032" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1032" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1032" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1032" t="n">
+        <v>31</v>
+      </c>
+      <c r="K1032" t="inlineStr">
+        <is>
+          <t>ayuda</t>
+        </is>
+      </c>
+      <c r="L1032" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1032" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1032" t="inlineStr">
+        <is>
+          <t>help</t>
+        </is>
+      </c>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>Arauca fortalece acciones para proteger a la niñez y las familias frente a la trata de personas</t>
+        </is>
+      </c>
+      <c r="B1033" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMitgFBVV95cUxOalZTd2hLdlFrR0NoNTFEdXlFbDEyc1FsbWUtTlBzbGZTUUs5aHNZbmRuLUMtdkVfcWVhajZILUVKRW4zRE4xSE1JMXpTZ2hERmNXVTl3VHdTRnVSRkJBNWR6WHpGOEw2bmtUSUJlNGFZa3VHeG8tNjdJbmQ2RmZVMHNQU0VvWDJEWnAyUTZMZWVmb1hId2F6dmo5dzR3UWFCazgta3lRN0hja19sQ2N1alp6QU5Ldw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1033" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1033" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="E1033" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="F1033" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1033" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1033" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1033" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1033" t="n">
+        <v>31</v>
+      </c>
+      <c r="K1033" t="inlineStr">
+        <is>
+          <t>fortalece</t>
+        </is>
+      </c>
+      <c r="L1033" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1033" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1033" t="inlineStr">
+        <is>
+          <t>strengthens</t>
+        </is>
+      </c>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>Arauca fortalece acciones para proteger a la niñez y las familias frente a la trata de personas</t>
+        </is>
+      </c>
+      <c r="B1034" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMitgFBVV95cUxOalZTd2hLdlFrR0NoNTFEdXlFbDEyc1FsbWUtTlBzbGZTUUs5aHNZbmRuLUMtdkVfcWVhajZILUVKRW4zRE4xSE1JMXpTZ2hERmNXVTl3VHdTRnVSRkJBNWR6WHpGOEw2bmtUSUJlNGFZa3VHeG8tNjdJbmQ2RmZVMHNQU0VvWDJEWnAyUTZMZWVmb1hId2F6dmo5dzR3UWFCazgta3lRN0hja19sQ2N1alp6QU5Ldw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1034" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1034" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="E1034" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="F1034" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1034" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1034" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1034" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1034" t="n">
+        <v>31</v>
+      </c>
+      <c r="K1034" t="inlineStr">
+        <is>
+          <t>proteger</t>
+        </is>
+      </c>
+      <c r="L1034" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1034" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1034" t="inlineStr">
+        <is>
+          <t>protect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>«Yo les doy el amor que ellos necesitan; eso es lo que más les hace falta» - Entrevista a Yaqueline Fernandez, madre sustituta en Vaupés</t>
+        </is>
+      </c>
+      <c r="B1035" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMitgFBVV95cUxPZ3RSc01OYjNEQ043dlIxUnF0Zzk2UHlMYjhXVFVwQ1B4WEJ0ajM4ckpYMUhNOHBDaXNqOU1LV2MwWEllbEFVU01pQkY5RXA5LUhYd0RkUWYwLTVhLVVPandvdWFIQkVkY28wdzRNZEZMTGo5dVBZM0owNkxmc0NTTGVUQ0R3bW9xM1hOU2hVeUZhZ29XTmRDVzRVTlNocDJoeEw1amp3dkdGRExpaEJWMl80b3BIQQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1035" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1035" t="inlineStr"/>
+      <c r="E1035" t="inlineStr">
+        <is>
+          <t>Vaupés</t>
+        </is>
+      </c>
+      <c r="F1035" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1035" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1035" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1035" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1035" t="n">
+        <v>31</v>
+      </c>
+      <c r="K1035" t="inlineStr">
+        <is>
+          <t>amor</t>
+        </is>
+      </c>
+      <c r="L1035" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1035" t="n">
+        <v>3</v>
+      </c>
+      <c r="N1035" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1035"/>
+  <dimension ref="A1:N1037"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -57996,6 +57996,114 @@
         </is>
       </c>
     </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar protege a 5 niñas, niños y adolescentes rescatados del riesgo de reclutamiento</t>
+        </is>
+      </c>
+      <c r="B1036" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiswFBVV95cUxOS08wTmtuWmNnRE5SR2lVUGlwMmV2Z0tCUGxfMWJnb192bk1NemdRTFA5SHB1ZHdSZ3NZWHFkQkk0VHM3V3BNV1ZkQUtSTWxlc05mVnpvLWJyNTNkQWYzWFk5bGJiZFFvTk9KQ0k1UFBkaHQ1MVpCYmJfNEkzMmdEc3kzQVZGai1GMno0endaek44WHhmUVdUU1lkanRJSmhJZGhMc0xPcGo3UFhMa3R6SWxOaw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1036" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1036" t="inlineStr"/>
+      <c r="E1036" t="inlineStr"/>
+      <c r="F1036" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1036" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1036" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1036" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J1036" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1036" t="inlineStr">
+        <is>
+          <t>protege</t>
+        </is>
+      </c>
+      <c r="L1036" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1036" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1036" t="inlineStr">
+        <is>
+          <t>protects</t>
+        </is>
+      </c>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar protege a 5 niñas, niños y adolescentes rescatados del riesgo de reclutamiento</t>
+        </is>
+      </c>
+      <c r="B1037" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiswFBVV95cUxOS08wTmtuWmNnRE5SR2lVUGlwMmV2Z0tCUGxfMWJnb192bk1NemdRTFA5SHB1ZHdSZ3NZWHFkQkk0VHM3V3BNV1ZkQUtSTWxlc05mVnpvLWJyNTNkQWYzWFk5bGJiZFFvTk9KQ0k1UFBkaHQ1MVpCYmJfNEkzMmdEc3kzQVZGai1GMno0endaek44WHhmUVdUU1lkanRJSmhJZGhMc0xPcGo3UFhMa3R6SWxOaw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1037" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1037" t="inlineStr"/>
+      <c r="E1037" t="inlineStr"/>
+      <c r="F1037" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1037" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1037" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1037" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J1037" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1037" t="inlineStr">
+        <is>
+          <t>riesgo</t>
+        </is>
+      </c>
+      <c r="L1037" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1037" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1037" t="inlineStr">
+        <is>
+          <t>risk</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1037"/>
+  <dimension ref="A1:N1039"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58104,6 +58104,122 @@
         </is>
       </c>
     </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar fortalece la prevención del delito y la salud mental en La Guajira con proceso formativo territorial</t>
+        </is>
+      </c>
+      <c r="B1038" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivgFBVV95cUxNbDQwYUN6UFFkc0RaVEVXYktLX0djem5xa1BqM19wV1VMYm5BYlM2cjVJcGNCWlpOcHpLSXNMTmJVcVBHN0gzZHotYzM1SjJIbW1JeFk1d05GcWFFWEhwUEtCSTZVLW1JZVB5b0MxQmdMNnd2Y3M1STRjbk1aSktuaER0WEpVUEt3Z2NkRVA5YkdnNHIwTU0zaHhVRXdZVjNCbFpNNEhHNko2LXh2S3dfNDZGdXZ3U2d2aWhCeWJ3?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1038" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1038" t="inlineStr"/>
+      <c r="E1038" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="F1038" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1038" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1038" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1038" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1038" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1038" t="inlineStr">
+        <is>
+          <t>fortalece</t>
+        </is>
+      </c>
+      <c r="L1038" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1038" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1038" t="inlineStr">
+        <is>
+          <t>strengthens</t>
+        </is>
+      </c>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar fortalece la prevención del delito y la salud mental en La Guajira con proceso formativo territorial</t>
+        </is>
+      </c>
+      <c r="B1039" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivgFBVV95cUxNbDQwYUN6UFFkc0RaVEVXYktLX0djem5xa1BqM19wV1VMYm5BYlM2cjVJcGNCWlpOcHpLSXNMTmJVcVBHN0gzZHotYzM1SjJIbW1JeFk1d05GcWFFWEhwUEtCSTZVLW1JZVB5b0MxQmdMNnd2Y3M1STRjbk1aSktuaER0WEpVUEt3Z2NkRVA5YkdnNHIwTU0zaHhVRXdZVjNCbFpNNEhHNko2LXh2S3dfNDZGdXZ3U2d2aWhCeWJ3?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1039" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1039" t="inlineStr"/>
+      <c r="E1039" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="F1039" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1039" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1039" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1039" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1039" t="n">
+        <v>2</v>
+      </c>
+      <c r="K1039" t="inlineStr">
+        <is>
+          <t>delito</t>
+        </is>
+      </c>
+      <c r="L1039" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1039" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1039" t="inlineStr">
+        <is>
+          <t>felony</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1039"/>
+  <dimension ref="A1:N1040"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58220,6 +58220,60 @@
         </is>
       </c>
     </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar asume protección de seis niños y niñas en La Dorada tras presunto maltrato físico y negligencia</t>
+        </is>
+      </c>
+      <c r="B1040" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiuAFBVV95cUxPYjBnZDFPam9MTGVXc0dXUXpKbEl4RXVwYUNhUWRtNy1FXzNaYnZzM2tua2lEMEkzRmh1X3VlQ2c1VHJ6NGZDRVd4Q0R4dkJFMVJlYWFwdlpreVJzaDVRTHUtQ1hyTkVENkdBZTRkVGVVaEp5SWJFQXZ2WXVJNzV1Qm5sa2lhdzNEWnNsazNPd2d3cnlab3M2a3NnRU54bmREZHFNRmxXWGRybDhESEFudXM2VGRVSW1s?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1040" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1040" t="inlineStr"/>
+      <c r="E1040" t="inlineStr"/>
+      <c r="F1040" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1040" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1040" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1040" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J1040" t="n">
+        <v>3</v>
+      </c>
+      <c r="K1040" t="inlineStr">
+        <is>
+          <t>negligencia</t>
+        </is>
+      </c>
+      <c r="L1040" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1040" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1040" t="inlineStr">
+        <is>
+          <t>neglect</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1040"/>
+  <dimension ref="A1:N1042"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58274,6 +58274,122 @@
         </is>
       </c>
     </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>ICBF anunció medidas tras denuncias de abuso en jardín infantil de Bogotá</t>
+        </is>
+      </c>
+      <c r="B1041" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMisAFBVV95cUxNYndBYWFTNGZtUkFnUy14WGFhMFNlSUN3Mk1acWU3N1lUTllZVVZTTTFvVW5LUmVXY0dhT1NEdm82VTJrQWdJMjd0ZERyN0RsZ3lkZ1FVOWVCMmpYVjJBUnpmWkp2Y0ZsSkY2VnpPbjlqR2J2OF9ycnFMWWYxb0dsNUxGbmc3b3pCTWxoamZUckt6NTFXNGhNS3JWenVndnZndkpWU2FqcGN4RE1OVHMzUNIBxAFBVV95cUxPN1p6STFWNHdOSDJqdjJydTBZcndIMWllR1NjeVNLRFB6SW8wekE1eVVSdkl2MmNoV29rNE1yNHJrTzBNdGdmWjRBR05OY3RFNVg4TlRseDM2b3praDBVYW12Y3pDbVpwV3ZnZDdPQnd6S1ZXVzN0Wkwwc1lmM3VCLWNla0ZzWWo0d0NkanBkT2phNWtOZVV0TDhHYmxxaVJaSWJiUnU3bnJMU2ZWVnA4R1pXUUFBemZvUlg2aVlud3lOUUUy?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1041" t="inlineStr">
+        <is>
+          <t>WRadio</t>
+        </is>
+      </c>
+      <c r="D1041" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E1041" t="inlineStr"/>
+      <c r="F1041" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1041" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H1041" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1041" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J1041" t="n">
+        <v>7</v>
+      </c>
+      <c r="K1041" t="inlineStr">
+        <is>
+          <t>abuso</t>
+        </is>
+      </c>
+      <c r="L1041" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1041" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1041" t="inlineStr">
+        <is>
+          <t>abuse</t>
+        </is>
+      </c>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>ICBF anunció medidas tras denuncias de abuso en jardín infantil de Bogotá</t>
+        </is>
+      </c>
+      <c r="B1042" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMisAFBVV95cUxNYndBYWFTNGZtUkFnUy14WGFhMFNlSUN3Mk1acWU3N1lUTllZVVZTTTFvVW5LUmVXY0dhT1NEdm82VTJrQWdJMjd0ZERyN0RsZ3lkZ1FVOWVCMmpYVjJBUnpmWkp2Y0ZsSkY2VnpPbjlqR2J2OF9ycnFMWWYxb0dsNUxGbmc3b3pCTWxoamZUckt6NTFXNGhNS3JWenVndnZndkpWU2FqcGN4RE1OVHMzUNIBxAFBVV95cUxPN1p6STFWNHdOSDJqdjJydTBZcndIMWllR1NjeVNLRFB6SW8wekE1eVVSdkl2MmNoV29rNE1yNHJrTzBNdGdmWjRBR05OY3RFNVg4TlRseDM2b3praDBVYW12Y3pDbVpwV3ZnZDdPQnd6S1ZXVzN0Wkwwc1lmM3VCLWNla0ZzWWo0d0NkanBkT2phNWtOZVV0TDhHYmxxaVJaSWJiUnU3bnJMU2ZWVnA4R1pXUUFBemZvUlg2aVlud3lOUUUy?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1042" t="inlineStr">
+        <is>
+          <t>WRadio</t>
+        </is>
+      </c>
+      <c r="D1042" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E1042" t="inlineStr"/>
+      <c r="F1042" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1042" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H1042" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1042" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J1042" t="n">
+        <v>7</v>
+      </c>
+      <c r="K1042" t="inlineStr">
+        <is>
+          <t>infantil</t>
+        </is>
+      </c>
+      <c r="L1042" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1042" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1042" t="inlineStr">
+        <is>
+          <t>childish</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1042"/>
+  <dimension ref="A1:N1043"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58390,6 +58390,60 @@
         </is>
       </c>
     </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>Nuevos detalles de la captura de Freddy Castellanos, presunto abusador del ICBF: estaba disfrazado</t>
+        </is>
+      </c>
+      <c r="B1043" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi4wFBVV95cUxQQ2FBb2ttVGhVaHZjd1M4MXQ3SnIyOEYycWdSdlpva3JqalJXcXRydTVQVW1mQ25LeG9jeldBYXVzSTc0emlkSHRRdGFqT3V5UVVlTjIydUZlNzJsZEdmWXg3R0NWWWRGd09aRG4wRmlYVTNaVFdFVnVjdTBDOG9uVlVTQ0t6YnpRamlOd3ZSZ2lXLUg3dzNsOEVyLWgxSzBBaktJWXVFS05aU2FUNnRzbnFuVE81RVhBZ3I1QlBNem9mZjk2X0kzakg1MTNTNFdwMDNGV2EwczktTWZMYVFnamJnY9IB8AFBVV95cUxPTzZUNFVZTDFRZDAya2dWdS1UTE4ybFFrQ0NTdVlRZVZyeF9SQXNtMjZ5LXBWaUlaVkFpaEJFX2VSNzNvR2lwcGNuRjNoOHVaSlZ5MVN4V01hU2cyeTdBbTNlR3hKSk5ZUTl0UmZxek55ZGhVUnhNWHgzWHBJT0VLbEs1Z3FxY2dMSVRJOWRuOHpwSjZPVjJNdjNFdmo2aVRZSkkyYnhaNUs4MDlYODNBR1RSQVFVa3lyc2N2U1VUTzRULXAyUHVMbHFVTDVPekx0ODhHS19sSmM5ZGc1UjlReGs1SzZTVnlzRGtrT2RRZ0c?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1043" t="inlineStr">
+        <is>
+          <t>Noticias Caracol</t>
+        </is>
+      </c>
+      <c r="D1043" t="inlineStr"/>
+      <c r="E1043" t="inlineStr"/>
+      <c r="F1043" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1043" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H1043" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1043" t="inlineStr">
+        <is>
+          <t>domingo</t>
+        </is>
+      </c>
+      <c r="J1043" t="n">
+        <v>11</v>
+      </c>
+      <c r="K1043" t="inlineStr">
+        <is>
+          <t>disfrazado</t>
+        </is>
+      </c>
+      <c r="L1043" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1043" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N1043" t="inlineStr">
+        <is>
+          <t>disguised</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1043"/>
+  <dimension ref="A1:N1044"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58444,6 +58444,64 @@
         </is>
       </c>
     </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>Amazonas se conecta con la vida: Bienestar Familiar fortalece la atención integral a pueblos indígenas en La Pedrera</t>
+        </is>
+      </c>
+      <c r="B1044" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiwAFBVV95cUxNbFdTa2Jja2JlamZIc1NrenBtbDdFRzY5NzM4ME9YaHZmSnpSc0w2Z0k3bDgzeDZLMFo2d3VEQkpQal9zTVlROWJOOTJOY1ZfOWRsYWd3UlNpelEyRWdNVXRCRHlxanR1YS1TMVFuam5KVUM4YmJZYTBDamxyNTZLN0R4Y2c4bDV2a1BoT21lTTFmejVOOE1HUTlTdE5HWkZ5ZzZ3NTlDR0NTREFOcEhaV3B6Y0JDMzJjelFZY2NsSkQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1044" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1044" t="inlineStr"/>
+      <c r="E1044" t="inlineStr">
+        <is>
+          <t>Amazonas</t>
+        </is>
+      </c>
+      <c r="F1044" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1044" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H1044" t="n">
+        <v>8</v>
+      </c>
+      <c r="I1044" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="J1044" t="n">
+        <v>9</v>
+      </c>
+      <c r="K1044" t="inlineStr">
+        <is>
+          <t>fortalece</t>
+        </is>
+      </c>
+      <c r="L1044" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1044" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1044" t="inlineStr">
+        <is>
+          <t>strengthens</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1044"/>
+  <dimension ref="A1:N1045"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58502,6 +58502,60 @@
         </is>
       </c>
     </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>Procuraduría formuló cargos a defensora del ICBF por presuntas irregularidades en restitución de derechos de una menor</t>
+        </is>
+      </c>
+      <c r="B1045" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi1AFBVV95cUxPRUlEUjBqa1lGSEc5SGlmUWZQZExBV2pWWGN2QjBDaFlUX0R6WU5fNkhOQ29IUzFRM1hmeGFaT1U3VGREYVZoSlBUbmppSGFJcHRiaG5jTjdwSGkwVUVZek5CRFBSWFFEWjFvYm9XLU0xcW5UQmtSRlozOXN1ZkVtUDAwS1dhcWpWT25UWmdIQWtQaktSMF9XOEF1VVJJM3BfY1hoZTNGMDUwdjQ5OTJjdW0tVUt1VWd3OUFreUk5TnRtaVFXeWJxX3NyRUZQa21DS0V5cA?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1045" t="inlineStr">
+        <is>
+          <t>procuraduria.gov.co</t>
+        </is>
+      </c>
+      <c r="D1045" t="inlineStr"/>
+      <c r="E1045" t="inlineStr"/>
+      <c r="F1045" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1045" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H1045" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1045" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="J1045" t="n">
+        <v>10</v>
+      </c>
+      <c r="K1045" t="inlineStr">
+        <is>
+          <t>cargos</t>
+        </is>
+      </c>
+      <c r="L1045" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1045" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1045" t="inlineStr">
+        <is>
+          <t>charges</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1045"/>
+  <dimension ref="A1:N1048"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58556,6 +58556,168 @@
         </is>
       </c>
     </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar hace un llamado urgente a proteger los alimentos destinados a la niñez wayuu y rechaza su comercialización | Portal ICBF - Instituto Colombiano de Bienestar</t>
+        </is>
+      </c>
+      <c r="B1046" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiugFBVV95cUxPOU9KdWZDaTZHT0RUbVJBTzhRNHp6T0RGbE1kN3AwdHhJQ2xQa29oWGIxWGozaG9MSEJ4MXMtYXVCM3dvWFQ1UkVWd1hYYmlwUHJESW81VEN0dGdib0FreE9EdFJLWkd6V2JZN0MzanluMlByWDJoN2Y5Mk5YVDhQWWtGbDRNUHNGMWFEbmhzaWstSkExZFlaRzR1R0syX2IwZ1RKVGJqVy1NS3ZQUWFmZmZZQnR3UkVyOEE?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1046" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1046" t="inlineStr"/>
+      <c r="E1046" t="inlineStr"/>
+      <c r="F1046" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1046" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1046" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1046" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1046" t="n">
+        <v>6</v>
+      </c>
+      <c r="K1046" t="inlineStr">
+        <is>
+          <t>urgente</t>
+        </is>
+      </c>
+      <c r="L1046" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1046" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N1046" t="inlineStr">
+        <is>
+          <t>urgent</t>
+        </is>
+      </c>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar hace un llamado urgente a proteger los alimentos destinados a la niñez wayuu y rechaza su comercialización | Portal ICBF - Instituto Colombiano de Bienestar</t>
+        </is>
+      </c>
+      <c r="B1047" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiugFBVV95cUxPOU9KdWZDaTZHT0RUbVJBTzhRNHp6T0RGbE1kN3AwdHhJQ2xQa29oWGIxWGozaG9MSEJ4MXMtYXVCM3dvWFQ1UkVWd1hYYmlwUHJESW81VEN0dGdib0FreE9EdFJLWkd6V2JZN0MzanluMlByWDJoN2Y5Mk5YVDhQWWtGbDRNUHNGMWFEbmhzaWstSkExZFlaRzR1R0syX2IwZ1RKVGJqVy1NS3ZQUWFmZmZZQnR3UkVyOEE?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1047" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1047" t="inlineStr"/>
+      <c r="E1047" t="inlineStr"/>
+      <c r="F1047" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1047" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1047" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1047" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1047" t="n">
+        <v>6</v>
+      </c>
+      <c r="K1047" t="inlineStr">
+        <is>
+          <t>proteger</t>
+        </is>
+      </c>
+      <c r="L1047" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1047" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1047" t="inlineStr">
+        <is>
+          <t>protect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar hace un llamado urgente a proteger los alimentos destinados a la niñez wayuu y rechaza su comercialización | Portal ICBF - Instituto Colombiano de Bienestar</t>
+        </is>
+      </c>
+      <c r="B1048" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiugFBVV95cUxPOU9KdWZDaTZHT0RUbVJBTzhRNHp6T0RGbE1kN3AwdHhJQ2xQa29oWGIxWGozaG9MSEJ4MXMtYXVCM3dvWFQ1UkVWd1hYYmlwUHJESW81VEN0dGdib0FreE9EdFJLWkd6V2JZN0MzanluMlByWDJoN2Y5Mk5YVDhQWWtGbDRNUHNGMWFEbmhzaWstSkExZFlaRzR1R0syX2IwZ1RKVGJqVy1NS3ZQUWFmZmZZQnR3UkVyOEE?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1048" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1048" t="inlineStr"/>
+      <c r="E1048" t="inlineStr"/>
+      <c r="F1048" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1048" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1048" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1048" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1048" t="n">
+        <v>6</v>
+      </c>
+      <c r="K1048" t="inlineStr">
+        <is>
+          <t>rechaza</t>
+        </is>
+      </c>
+      <c r="L1048" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1048" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N1048" t="inlineStr">
+        <is>
+          <t>rejects</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1048"/>
+  <dimension ref="A1:N1052"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58718,6 +58718,226 @@
         </is>
       </c>
     </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar hace un llamado urgente a proteger los alimentos destinados a la niñez wayuu y rechaza su comercialización</t>
+        </is>
+      </c>
+      <c r="B1049" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiugFBVV95cUxPOU9KdWZDaTZHT0RUbVJBTzhRNHp6T0RGbE1kN3AwdHhJQ2xQa29oWGIxWGozaG9MSEJ4MXMtYXVCM3dvWFQ1UkVWd1hYYmlwUHJESW81VEN0dGdib0FreE9EdFJLWkd6V2JZN0MzanluMlByWDJoN2Y5Mk5YVDhQWWtGbDRNUHNGMWFEbmhzaWstSkExZFlaRzR1R0syX2IwZ1RKVGJqVy1NS3ZQUWFmZmZZQnR3UkVyOEE?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1049" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1049" t="inlineStr"/>
+      <c r="E1049" t="inlineStr"/>
+      <c r="F1049" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1049" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1049" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1049" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1049" t="n">
+        <v>6</v>
+      </c>
+      <c r="K1049" t="inlineStr">
+        <is>
+          <t>urgente</t>
+        </is>
+      </c>
+      <c r="L1049" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1049" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N1049" t="inlineStr">
+        <is>
+          <t>urgent</t>
+        </is>
+      </c>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar hace un llamado urgente a proteger los alimentos destinados a la niñez wayuu y rechaza su comercialización</t>
+        </is>
+      </c>
+      <c r="B1050" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiugFBVV95cUxPOU9KdWZDaTZHT0RUbVJBTzhRNHp6T0RGbE1kN3AwdHhJQ2xQa29oWGIxWGozaG9MSEJ4MXMtYXVCM3dvWFQ1UkVWd1hYYmlwUHJESW81VEN0dGdib0FreE9EdFJLWkd6V2JZN0MzanluMlByWDJoN2Y5Mk5YVDhQWWtGbDRNUHNGMWFEbmhzaWstSkExZFlaRzR1R0syX2IwZ1RKVGJqVy1NS3ZQUWFmZmZZQnR3UkVyOEE?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1050" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1050" t="inlineStr"/>
+      <c r="E1050" t="inlineStr"/>
+      <c r="F1050" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1050" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1050" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1050" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1050" t="n">
+        <v>6</v>
+      </c>
+      <c r="K1050" t="inlineStr">
+        <is>
+          <t>proteger</t>
+        </is>
+      </c>
+      <c r="L1050" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1050" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1050" t="inlineStr">
+        <is>
+          <t>protect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar hace un llamado urgente a proteger los alimentos destinados a la niñez wayuu y rechaza su comercialización</t>
+        </is>
+      </c>
+      <c r="B1051" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiugFBVV95cUxPOU9KdWZDaTZHT0RUbVJBTzhRNHp6T0RGbE1kN3AwdHhJQ2xQa29oWGIxWGozaG9MSEJ4MXMtYXVCM3dvWFQ1UkVWd1hYYmlwUHJESW81VEN0dGdib0FreE9EdFJLWkd6V2JZN0MzanluMlByWDJoN2Y5Mk5YVDhQWWtGbDRNUHNGMWFEbmhzaWstSkExZFlaRzR1R0syX2IwZ1RKVGJqVy1NS3ZQUWFmZmZZQnR3UkVyOEE?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1051" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1051" t="inlineStr"/>
+      <c r="E1051" t="inlineStr"/>
+      <c r="F1051" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1051" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1051" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1051" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1051" t="n">
+        <v>6</v>
+      </c>
+      <c r="K1051" t="inlineStr">
+        <is>
+          <t>rechaza</t>
+        </is>
+      </c>
+      <c r="L1051" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1051" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N1051" t="inlineStr">
+        <is>
+          <t>rejects</t>
+        </is>
+      </c>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>Judicializadas siete personas por desfalco de alimentación infantil en La Guajira</t>
+        </is>
+      </c>
+      <c r="B1052" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMitAFBVV95cUxOUzY5LWlwV2E4Wmgyb2xxYzJjTnZMbUFqLXdKVzVmZXpleFM5aDhib0F0bTJMNkFiS084NFRnS2NwZFNGZjdTd2NhRTE2dUpKVHhvVHRaMU1taEp0Tk84QzlZNks4alJ2ZElaM3FsQkZoczI0MDhfaTVxT0Vsd2xpYktPMjNtSm9UWC1DSlpySmQzRnQxVmxFZ01qbWtDNEpKY0hFeGt1NGdDbHY2UTNHVUFRb2w?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1052" t="inlineStr">
+        <is>
+          <t>elcronista.co</t>
+        </is>
+      </c>
+      <c r="D1052" t="inlineStr"/>
+      <c r="E1052" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="F1052" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1052" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1052" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1052" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1052" t="n">
+        <v>31</v>
+      </c>
+      <c r="K1052" t="inlineStr">
+        <is>
+          <t>infantil</t>
+        </is>
+      </c>
+      <c r="L1052" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1052" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1052" t="inlineStr">
+        <is>
+          <t>childish</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1052"/>
+  <dimension ref="A1:N1054"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -58938,6 +58938,114 @@
         </is>
       </c>
     </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>Comunidades étnicas y el ICBF acuerdan hoja de ruta para el cuidado de la niñez</t>
+        </is>
+      </c>
+      <c r="B1053" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMisgFBVV95cUxOUFNZRUJScnBYSjRraWowZEVPNWxrMDZQV0pWQnBfOEs3WVZwbWZ3ZEdvOHlDRS1sY3V1d2dtTWdNVnVmaDhHMXkwLVhfNTZCQVpXNE9pUEUxSGNkTHlwVExVVmwwSnU4aENuMEVDczZqUXJqMWpvaFZCQmhPSU56LWxiTElDMkh0R0U5YjItX3BCdTFFZm13VHhENm1SX1B2TjF5MGxTbmtQWENST3otMG93?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1053" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1053" t="inlineStr"/>
+      <c r="E1053" t="inlineStr"/>
+      <c r="F1053" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1053" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H1053" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1053" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1053" t="n">
+        <v>25</v>
+      </c>
+      <c r="K1053" t="inlineStr">
+        <is>
+          <t>cuidado</t>
+        </is>
+      </c>
+      <c r="L1053" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1053" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1053" t="inlineStr">
+        <is>
+          <t>care</t>
+        </is>
+      </c>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>El ICBF enfrenta la corrupción y denuncia irregularidades dentro de la entidad</t>
+        </is>
+      </c>
+      <c r="B1054" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMisAFBVV95cUxNdWhjRjhIQUtmb0djWTVlT01DeFhiUTNDQnprLUxjNmFFaTNXUlptMHZKbVJnR3dKMVlNZkxiV3VLdkVjZlFBZ0dWbC1Ed0hoNV9fVnFSckdxVnN2QjRmU0M4VGNpMGZqQ1JNSnc2VDFaREEtVTEwQkk5YzdNal9VUFR0SktUa0Y1WURlMGVUbkp2TDFhV0ZZdThmQ2tVTjE5eDlnckhKNENYNGJ5SGw4dw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1054" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1054" t="inlineStr"/>
+      <c r="E1054" t="inlineStr"/>
+      <c r="F1054" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1054" t="n">
+        <v>2024</v>
+      </c>
+      <c r="H1054" t="n">
+        <v>3</v>
+      </c>
+      <c r="I1054" t="inlineStr">
+        <is>
+          <t>domingo</t>
+        </is>
+      </c>
+      <c r="J1054" t="n">
+        <v>3</v>
+      </c>
+      <c r="K1054" t="inlineStr">
+        <is>
+          <t>denuncia</t>
+        </is>
+      </c>
+      <c r="L1054" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1054" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1054" t="inlineStr">
+        <is>
+          <t>denounces</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1054"/>
+  <dimension ref="A1:N1055"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59046,6 +59046,64 @@
         </is>
       </c>
     </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>Con diálogos comunitarios, Unidades Móviles de ICBF restablecen la confianza de la población en Suárez, Cauca</t>
+        </is>
+      </c>
+      <c r="B1055" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMitAFBVV95cUxPTEZjZFE3dHZxajdtVmR6N1ZNT1pZenoxZ3BMby1EdmYzYXNMOHVLNTZNanlQYTAtWVRYZzZiV3U4UW9Xa3lzUE4yM1gtZDBWM0IwVE5udVRmaXRab3UySGxubmNuOTY1X2lETnVLQlUxYTNneHotTVp6X0swSmtGZmRhaTlFVS0tdFMxQjZENnNBQWVZcjBoR1RVNTg3c2l6dWxCVXgwWjBqQlMyTk5ZUGdOMk0?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1055" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1055" t="inlineStr"/>
+      <c r="E1055" t="inlineStr">
+        <is>
+          <t>Cauca</t>
+        </is>
+      </c>
+      <c r="F1055" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1055" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H1055" t="n">
+        <v>10</v>
+      </c>
+      <c r="I1055" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="J1055" t="n">
+        <v>25</v>
+      </c>
+      <c r="K1055" t="inlineStr">
+        <is>
+          <t>confianza</t>
+        </is>
+      </c>
+      <c r="L1055" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1055" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1055" t="inlineStr">
+        <is>
+          <t>confidence</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1055"/>
+  <dimension ref="A1:N1056"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59104,6 +59104,64 @@
         </is>
       </c>
     </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>Tres entidades del Estado investigan al ICBF al mismo tiempo: contratos irregulares, cartel de contratistas y un desfalco de $860 millones en alimentos para niños de La Guajira</t>
+        </is>
+      </c>
+      <c r="B1056" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMipAJBVV95cUxOYV82eUp2WnZtRUtMRjhxeDJfZHVFNFpFZmpyN0NkeXhhNTNUdmluQWp2SldxODZRUC00NklmVC10RldtTGZ5SDlMemZ2ZHBFZ2pqMW85SmVWX1Z6WXItLW1JZmt5OGNESFh1VDQ2M3BJaWVUeUtmdlJFM01ib0ZxMzQyem1hSHpjTFRteEJERUI2VzNxRUVPUFBiT0RaTVZRVV9UUzhzSEJ2QUZBbGJzMGFhbzBvdFhvYUl2aGdzeGtiU1B0THp5ZkQxbXd0VFQydG8xY3JPbUVjQ2pXeUxTMWkwX0dXQUV2SnlscHMwbmhUaHdkc1p0RnNSbU0yUU5NZnRsa0s2dW5MX21sT2ZIWlpzdTlZd2JZXzhQeDhUa04wTjYw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1056" t="inlineStr">
+        <is>
+          <t>El Expediente</t>
+        </is>
+      </c>
+      <c r="D1056" t="inlineStr"/>
+      <c r="E1056" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="F1056" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1056" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1056" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1056" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1056" t="n">
+        <v>9</v>
+      </c>
+      <c r="K1056" t="inlineStr">
+        <is>
+          <t>tiempo</t>
+        </is>
+      </c>
+      <c r="L1056" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1056" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1056" t="inlineStr">
+        <is>
+          <t>tense</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1056"/>
+  <dimension ref="A1:N1058"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59162,6 +59162,114 @@
         </is>
       </c>
     </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>En Colombia crece la Generación para la Paz: Bienestar Familiar refuerza la protección de la niñez víctima del conflicto</t>
+        </is>
+      </c>
+      <c r="B1057" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivgFBVV95cUxNSy10S3Y4SnhQdTcyb2h0dUVMaVNqMEpzWUUyUFFJOFZVQ0hMNkJuWW81SzJoMjB4SGduRkxPNHlrQzAyU2paTXpMcElDTU8zd3l6Y3pCdl80X3V3eDBpZ0JEbXJFZ3oxTnZOdHNEd2xMNmZEc1Q5X0pkU3NiMi1SV1N3dE0xX05YVVg4d1BQM1VEZW81VWNXdXJQQ1dobGEwMDg4RFFZdWplMUkxQ1hWMmJMVjBlNW9yZzYxNDBB?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1057" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1057" t="inlineStr"/>
+      <c r="E1057" t="inlineStr"/>
+      <c r="F1057" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1057" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1057" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1057" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1057" t="n">
+        <v>9</v>
+      </c>
+      <c r="K1057" t="inlineStr">
+        <is>
+          <t>víctima</t>
+        </is>
+      </c>
+      <c r="L1057" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1057" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1057" t="inlineStr">
+        <is>
+          <t>casualty</t>
+        </is>
+      </c>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>En Colombia crece la Generación para la Paz: Bienestar Familiar refuerza la protección de la niñez víctima del conflicto</t>
+        </is>
+      </c>
+      <c r="B1058" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivgFBVV95cUxNSy10S3Y4SnhQdTcyb2h0dUVMaVNqMEpzWUUyUFFJOFZVQ0hMNkJuWW81SzJoMjB4SGduRkxPNHlrQzAyU2paTXpMcElDTU8zd3l6Y3pCdl80X3V3eDBpZ0JEbXJFZ3oxTnZOdHNEd2xMNmZEc1Q5X0pkU3NiMi1SV1N3dE0xX05YVVg4d1BQM1VEZW81VWNXdXJQQ1dobGEwMDg4RFFZdWplMUkxQ1hWMmJMVjBlNW9yZzYxNDBB?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1058" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1058" t="inlineStr"/>
+      <c r="E1058" t="inlineStr"/>
+      <c r="F1058" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1058" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1058" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1058" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1058" t="n">
+        <v>9</v>
+      </c>
+      <c r="K1058" t="inlineStr">
+        <is>
+          <t>conflicto</t>
+        </is>
+      </c>
+      <c r="L1058" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1058" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1058" t="inlineStr">
+        <is>
+          <t>conflict</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1058"/>
+  <dimension ref="A1:N1061"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59270,6 +59270,168 @@
         </is>
       </c>
     </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>"Solo intentaba resocializarlos": menores infractores son señalados de darle muerte a su cuidadora en hogar del ICBF</t>
+        </is>
+      </c>
+      <c r="B1059" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi0wFBVV95cUxQLUdxRHEwdG5NcjI0YzkycEVVa0tQcHctZDZJWEpQU2lFSXJGTUozMnZhcTlsUGpuOUFUdkRpZDFMN1lJRkJCRm9SbzZMampqSmRmM09vTGYxU2tGdXVGVmR1TjNacmxudzhoTUszWHBLcEtNd2g3aTlVdnlpa245RlVza0duSW9mZUlpNWFnTDlTWnFLclZ5c09CS2RHTm9zSHFuZkg2RmhVblBzRjVPcGUya3FMTkRPeXZtQ0t3d2VPS2NpdjFpcGROd1NBd1RvbXhB?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1059" t="inlineStr">
+        <is>
+          <t>impactonews.co</t>
+        </is>
+      </c>
+      <c r="D1059" t="inlineStr"/>
+      <c r="E1059" t="inlineStr"/>
+      <c r="F1059" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1059" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1059" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1059" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J1059" t="n">
+        <v>10</v>
+      </c>
+      <c r="K1059" t="inlineStr">
+        <is>
+          <t>muerte</t>
+        </is>
+      </c>
+      <c r="L1059" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1059" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1059" t="inlineStr">
+        <is>
+          <t>death</t>
+        </is>
+      </c>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>La alertó antes de morir: investigan crimen de cuidadora en el ICBF de Barrancabermeja</t>
+        </is>
+      </c>
+      <c r="B1060" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiygFBVV95cUxPc1hULXg5Q2hiUmpxMDBDd081MXNvV2hCWmRYc0pyVV9EZ0ppV3BkZVc4d2ViTDkzaUg3d3VYdi1ZcXJ5eGhWTmttT2tVa1FDUnFiZWpfN2tBREtrdkV2a0x3ZG16cjlzSFR3UWdYRHE1Y3Y5bTUxMUx3ZTdTamlkc2V0Wms5R25WX0VKMUtCQW5ZaHNnTGFLR09hQ2t0RmlEZGVvZlFsZjAyVG5MNUtFcFM5MjlUZEJVVUQ2YzI2T21nelNVd1FTSnhn?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1060" t="inlineStr">
+        <is>
+          <t>Oro Noticias</t>
+        </is>
+      </c>
+      <c r="D1060" t="inlineStr"/>
+      <c r="E1060" t="inlineStr"/>
+      <c r="F1060" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1060" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1060" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1060" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J1060" t="n">
+        <v>10</v>
+      </c>
+      <c r="K1060" t="inlineStr">
+        <is>
+          <t>morir</t>
+        </is>
+      </c>
+      <c r="L1060" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1060" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1060" t="inlineStr">
+        <is>
+          <t>die</t>
+        </is>
+      </c>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>La alertó antes de morir: investigan crimen de cuidadora en el ICBF de Barrancabermeja</t>
+        </is>
+      </c>
+      <c r="B1061" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiygFBVV95cUxPc1hULXg5Q2hiUmpxMDBDd081MXNvV2hCWmRYc0pyVV9EZ0ppV3BkZVc4d2ViTDkzaUg3d3VYdi1ZcXJ5eGhWTmttT2tVa1FDUnFiZWpfN2tBREtrdkV2a0x3ZG16cjlzSFR3UWdYRHE1Y3Y5bTUxMUx3ZTdTamlkc2V0Wms5R25WX0VKMUtCQW5ZaHNnTGFLR09hQ2t0RmlEZGVvZlFsZjAyVG5MNUtFcFM5MjlUZEJVVUQ2YzI2T21nelNVd1FTSnhn?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1061" t="inlineStr">
+        <is>
+          <t>Oro Noticias</t>
+        </is>
+      </c>
+      <c r="D1061" t="inlineStr"/>
+      <c r="E1061" t="inlineStr"/>
+      <c r="F1061" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1061" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1061" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1061" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J1061" t="n">
+        <v>10</v>
+      </c>
+      <c r="K1061" t="inlineStr">
+        <is>
+          <t>crimen</t>
+        </is>
+      </c>
+      <c r="L1061" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1061" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1061" t="inlineStr">
+        <is>
+          <t>crime</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1061"/>
+  <dimension ref="A1:N1062"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59432,6 +59432,60 @@
         </is>
       </c>
     </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>ICBF había otorgado la custodia de la niña abusada en Montelíbano apenas cuatro meses antes del ataque</t>
+        </is>
+      </c>
+      <c r="B1062" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivwFBVV95cUxPajJrUDhTTXZYTGIyeEJ5SmY0eVV0TWVXYkZhTTdCTkVwRjFvNG9kdi13QVBRQlctdjc1Y19XbFU0cHo2ZFI0THYzaFYxTDIwdVhVb212NzIzOE1CT0hUSEZQU1VfcHhTbjFSU2JUNkt1TmpQZXk4NEV2MW9ub3lINHNuTUlEanB4NUFQUVRSYnZ5cDUwOXZ1UWxSVjNxQmtuWDRsajZkeGdwaHE2WThWam4xcVBPR3ZrT3dRaHpBWQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1062" t="inlineStr">
+        <is>
+          <t>larazon.co</t>
+        </is>
+      </c>
+      <c r="D1062" t="inlineStr"/>
+      <c r="E1062" t="inlineStr"/>
+      <c r="F1062" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1062" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1062" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1062" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J1062" t="n">
+        <v>10</v>
+      </c>
+      <c r="K1062" t="inlineStr">
+        <is>
+          <t>ataque</t>
+        </is>
+      </c>
+      <c r="L1062" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1062" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N1062" t="inlineStr">
+        <is>
+          <t>attack</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1062"/>
+  <dimension ref="A1:N1067"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59486,6 +59486,284 @@
         </is>
       </c>
     </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>El Icbf se las entregó, ahora a la cárcel por presunto abuso</t>
+        </is>
+      </c>
+      <c r="B1063" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiqgFBVV95cUxQT0N6d29Bclg1dkVoV3ZYNFJBUGpMY010OGJMRmJmUk1RVXFVbkdWS1VHcnRVRTlOYTRQanUtYjEyS2dyZWF5MkJrLVBkcVFJbkZya0REQ2tlSmRIcExOSW0tdGNQQVhhUkFnbnlnTDRUcGc4N1RLUC1aNFlqeTVkWFJYc04yMEhmcEpNNDJNQW9Ub0xkRG8xVENrOEFKZkdZSkFmYjFCa0E4dw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1063" t="inlineStr">
+        <is>
+          <t>El Meridiano</t>
+        </is>
+      </c>
+      <c r="D1063" t="inlineStr"/>
+      <c r="E1063" t="inlineStr"/>
+      <c r="F1063" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1063" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1063" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1063" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="J1063" t="n">
+        <v>11</v>
+      </c>
+      <c r="K1063" t="inlineStr">
+        <is>
+          <t>abuso</t>
+        </is>
+      </c>
+      <c r="L1063" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1063" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1063" t="inlineStr">
+        <is>
+          <t>abuse</t>
+        </is>
+      </c>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>Esta es la hipótesis sobre el presunto asesinato a psicóloga del Icbf en Barrancabermeja: cuatro adolescentes, ya capturados, la habrían ahorcado</t>
+        </is>
+      </c>
+      <c r="B1064" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMilgJBVV95cUxPcWJkR1gyVTZLZkZPaVpsNDlxQXowQl9tXzBZQ3QyaGZYcnphZnhKY0djWHR4MzNaNjVZLWZ2MGZObV8zT0M0blRxdWYxbmtHTUZXMGZJMV9OXzBjTFBxYnpQaEdVM09vdkROdDdJbXNjLTdiT2cxYVhCXzltM0ZsUmh2N042bTJQZGpZWUp0NHJNbk40eGlaMzFsZ2ROQTRZbmxVT2ZuRXF2TW5YaWRud240UEs3QmZERTBuUWhVUXkxR1BvWHFlak1CMFlvSzJUTGpuWnJ3cml6MnBDSVJzTUx4bFZPU0NKYjg2TU5nSS1oTjNoZkl0S2ZvVUo0eEtIZlZmVlZEMU12dVVldkk5QUQ2UHV4d9IBsAJBVV95cUxQR1VZU2NtT0ZHQTBNQl9yZWk2d1lOZHhnV19ydzRZTGZuek53MF9RcVJOYVJTSS1qbE8xaXBjcE5mWDV3dmtzTk1yYjF4YlA0TGpoZVB0R3FGR0JKcUxNRHZGajUwZDc3eEFLdmZ0OGtydjc5ay1RLVUwNG5fWW5yZ0VKbE5RRVJXaGZXUGVNWm1iNFl0ZXJlRDhaZmpkdlBxZGM5elhWVkljRXdieVV1Q1NmbENmWW9ocm90ZDluVDlZbE5iblkyeEdyRVgzb0g4bVJYUDU1RTRhdVV2Q3FHazBCVzlaM3J0Mks5bXA2TDhoRzRXUnoyckFnMENYVkg4VHQ4c1FZVzVFTGU1WUJDdzZ2RkxfZVhqWDQ5blhOMVZRVDk4cWFCZFNKZGREUm5W?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1064" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D1064" t="inlineStr"/>
+      <c r="E1064" t="inlineStr"/>
+      <c r="F1064" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1064" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1064" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1064" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="J1064" t="n">
+        <v>11</v>
+      </c>
+      <c r="K1064" t="inlineStr">
+        <is>
+          <t>asesinato</t>
+        </is>
+      </c>
+      <c r="L1064" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1064" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1064" t="inlineStr">
+        <is>
+          <t>assassination</t>
+        </is>
+      </c>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>Historia tras crimen de la psicóloga del ICBF, asesinada por menores a los que ayudaba</t>
+        </is>
+      </c>
+      <c r="B1065" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMizwFBVV95cUxNeGV4NVR4LU1EMU9HaC16Q2luRENNenB0S2RVbl9BRGJxb25oalAtXzNtbUNOZllkaElmN2Y3b0ZDVnRGX0d2Rk1hU1JteURHVEZxV1k5NW5lV3NVVlhQWWxMNzVfQUlqZnY1Zmp2UTU2R0xZbFhJZHlFdkJ3NmVwQmtGQ2laaFoweERidTV0WDZFSHV4elFQNTY1YmkyMzlyTmk3SHp2OWVsRThrNTl0bFdKdHdSS3ZnMnIxYi1jMXlqbklzdVhaczUwNERmRXfSAc8BQVVfeXFMTTZRME9Qd2dSVGhnNHp2bjN3LWNyNFJoYzlZUU14NFZaSlZOS2NoTzNrelVXRlZrU0dUWGMxOWVYLUpoNTN6T1NrdVg1R3FlWTluV28wbG9raUZoNjVGVzNUWnNKcDEwOFFnNUpJeFdiOGZ6SWk2R2drNW9hcWwzVHc5Z0ZXLXViWEEtejVCdzFybEw2WnhEVFlTSHpEalk5ZFU4dnV1UlFCMl9jaGNNM0hnSWdCNkk3X2pRX3NQeWhveFJfamxka25WMzc0S2dn?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1065" t="inlineStr">
+        <is>
+          <t>La FM</t>
+        </is>
+      </c>
+      <c r="D1065" t="inlineStr"/>
+      <c r="E1065" t="inlineStr"/>
+      <c r="F1065" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1065" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1065" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1065" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="J1065" t="n">
+        <v>11</v>
+      </c>
+      <c r="K1065" t="inlineStr">
+        <is>
+          <t>crimen</t>
+        </is>
+      </c>
+      <c r="L1065" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1065" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1065" t="inlineStr">
+        <is>
+          <t>crime</t>
+        </is>
+      </c>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar despliega unidades móviles para proteger a la niñez afectada por la emergencia invernal en Córdoba</t>
+        </is>
+      </c>
+      <c r="B1066" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiuAFBVV95cUxNM1B0QnFaRHhwYklIOEZqV0tkVkNudmxQcDNJdmVKVXE0eW5qeUVnbV9scy1DZHdXbEFpdmV1S1cxOWJSd2J0NmtkNVNqTEVFQ010eFV2cm1EbUZsd2FQTWNrOU9JZ0dVV1A5V0NreVRyck1rNDRNNWozSHZ6eVZvaGRncVFveklaWWc5OXpGc0NaeDZYWWMtVGVyTkdWU0dMYUNjcGZOcXdTZEJnYXZTZGdJTHRnRmg1?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1066" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1066" t="inlineStr"/>
+      <c r="E1066" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="F1066" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1066" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1066" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1066" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="J1066" t="n">
+        <v>7</v>
+      </c>
+      <c r="K1066" t="inlineStr">
+        <is>
+          <t>proteger</t>
+        </is>
+      </c>
+      <c r="L1066" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1066" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1066" t="inlineStr">
+        <is>
+          <t>protect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar despliega unidades móviles para proteger a la niñez afectada por la emergencia invernal en Córdoba</t>
+        </is>
+      </c>
+      <c r="B1067" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiuAFBVV95cUxNM1B0QnFaRHhwYklIOEZqV0tkVkNudmxQcDNJdmVKVXE0eW5qeUVnbV9scy1DZHdXbEFpdmV1S1cxOWJSd2J0NmtkNVNqTEVFQ010eFV2cm1EbUZsd2FQTWNrOU9JZ0dVV1A5V0NreVRyck1rNDRNNWozSHZ6eVZvaGRncVFveklaWWc5OXpGc0NaeDZYWWMtVGVyTkdWU0dMYUNjcGZOcXdTZEJnYXZTZGdJTHRnRmg1?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1067" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1067" t="inlineStr"/>
+      <c r="E1067" t="inlineStr">
+        <is>
+          <t>Córdoba</t>
+        </is>
+      </c>
+      <c r="F1067" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1067" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1067" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1067" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="J1067" t="n">
+        <v>7</v>
+      </c>
+      <c r="K1067" t="inlineStr">
+        <is>
+          <t>emergencia</t>
+        </is>
+      </c>
+      <c r="L1067" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1067" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1067" t="inlineStr">
+        <is>
+          <t>emergency</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1067"/>
+  <dimension ref="A1:N1069"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59764,6 +59764,114 @@
         </is>
       </c>
     </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>“Con sevicia”: así fue el asesinato de menores de edad a psicóloga de hogar de paso del ICBF</t>
+        </is>
+      </c>
+      <c r="B1068" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi0gFBVV95cUxPcnZRR0dFUW00WUxhTUd0ZXc3R0EtQmZmdlpuMHJYck01XzF6QjYxYU8wSmNya0dzWVhiUHluV2g1SjVTbHA4YXI5cE1kU3RZUHd2WWJKU0RMTlZneVd3cEZHVG5uU3Z1UTFJa0M5WGlCZ1hMVUU0YzM1eFdKZ3FiTHZQNzJYaDlCRjlnWmlEaUxzcEQ5VE1tZ0RYSzV6bVQtM1VETU1UeS1aY2VEZTlwSlFUZnpCem9fYy1UTWZ0U0otSURCM1U4eEF1aUJhcEhKSkHSAdcBQVVfeXFMTUF0V1hzUkkyQTBQbVpuNllOYnZ3TkdnZjRtc3JfZ1RnSjFWUzF6bm81cFZMd1BWTnZETzJ0VndEd0RQbjZPb19NcFRPYW02Y0VJWWRxbGF5VFlCWk9LSW1iTE9vMkd1c2pkM01LekxyVG81RXRyWlZGUWhkbkFneU1DQVQ5Vm81ak5nN2pmYUhVdFlKX2lhSEZkOG5Ub2RBMnZUOWdSd1hMNE0wTlV2VDVkc2R1dGpkcy1aamZmRkdBV1JRYnVVWnRVb05iaU0zZFllRzltVVk?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1068" t="inlineStr">
+        <is>
+          <t>Revista Semana</t>
+        </is>
+      </c>
+      <c r="D1068" t="inlineStr"/>
+      <c r="E1068" t="inlineStr"/>
+      <c r="F1068" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1068" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1068" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1068" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="J1068" t="n">
+        <v>11</v>
+      </c>
+      <c r="K1068" t="inlineStr">
+        <is>
+          <t>asesinato</t>
+        </is>
+      </c>
+      <c r="L1068" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1068" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1068" t="inlineStr">
+        <is>
+          <t>assassination</t>
+        </is>
+      </c>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>Pareja que tenía custodia del ICBF, a la cárcel por presunto abuso y maltrato a niña de dos años</t>
+        </is>
+      </c>
+      <c r="B1069" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiygFBVV95cUxPRm15WHR5S2ZUNlpRODV1ek43MUZ5a2hTSXI0T2VNNjM0UWRvZHU3cC1FZlV6UWJIcnhGendjV3lObkZYa2VTbDlOa1NTdmVTaEtKZ1lZWW4xTFdmYTUybkVPZld0NlU3cE9UTmNUMWlxbjRfS2tFcHA4S0FJTm40X2RXajh5bmRocE9kS0tFdmZ1N0NOMF9zbzEtNWtDRFlrVUtPMXlEamUyX3FpaVVHV0tlWGRIOTJSMUU5ZXRZdkVWMWFIMXh6UG1B0gHeAUFVX3lxTE5ZeTRHNmp1WEZHM29oQi1uRVRxX0pfYkljbmdUTmRpV1ZlWXNfMEo2djdwX0JnX1NqZGI1S1JMSDV6bllYREVHd3l3NTdFaHZ1TDM3VTUyRlY5VEQ5OVlhUmlZaDNFbUJYTnlDM3pveGFYYURvQzQzRmVWOHM0UWI0V1MyWFQ4Wk1vU19nWUNFWlViVW5iQ2plOW1HelBGVnNRbWRPcTI1TEdienNOTTRZcml5WXlKc1RXS1lvMHl4dTNJTTdpYnpwQk1fOTVRcVpXY1AzbUFXR21GeEc4dw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1069" t="inlineStr">
+        <is>
+          <t>Caracol Radio</t>
+        </is>
+      </c>
+      <c r="D1069" t="inlineStr"/>
+      <c r="E1069" t="inlineStr"/>
+      <c r="F1069" t="n">
+        <v>1</v>
+      </c>
+      <c r="G1069" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1069" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1069" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="J1069" t="n">
+        <v>11</v>
+      </c>
+      <c r="K1069" t="inlineStr">
+        <is>
+          <t>abuso</t>
+        </is>
+      </c>
+      <c r="L1069" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1069" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1069" t="inlineStr">
+        <is>
+          <t>abuse</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1069"/>
+  <dimension ref="A1:N1072"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -59872,6 +59872,176 @@
         </is>
       </c>
     </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>¿Cuál es el salario de un profesor infantil del ICBF en Colombia para el 2026?</t>
+        </is>
+      </c>
+      <c r="B1070" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMitgFBVV95cUxNektCU0MyZ0ZiM1ZPTkpRRE11T2RsR3h4cHgxZFhHVDRjaUtrSHMzLWhqT0Njcl9zNGdFbzZFdWhoaEQ0UFNwdmVpaGtOZjlYTjBrTE9BaHBPcksyUGFkSFk0b19xZlBrZ1hLeFpOUEQtVXlxOEVKRzVtT1Z1TXhabm04YVZLeFpqMDQ3M1FKRTMzYUNoUFRMd1ZJS0FHZmNCVmhTYU5QaUJUSnRFMVJtcTZDV3hNdw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1070" t="inlineStr">
+        <is>
+          <t>RCN Radio</t>
+        </is>
+      </c>
+      <c r="D1070" t="inlineStr"/>
+      <c r="E1070" t="inlineStr"/>
+      <c r="F1070" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1070" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1070" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1070" t="inlineStr">
+        <is>
+          <t>domingo</t>
+        </is>
+      </c>
+      <c r="J1070" t="n">
+        <v>12</v>
+      </c>
+      <c r="K1070" t="inlineStr">
+        <is>
+          <t>infantil</t>
+        </is>
+      </c>
+      <c r="L1070" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1070" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1070" t="inlineStr">
+        <is>
+          <t>childish</t>
+        </is>
+      </c>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar protege a adolescentes del Sistema de Responsabilidad Penal ante emergencia sanitaria en el CAE de Villavicencio</t>
+        </is>
+      </c>
+      <c r="B1071" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMitwFBVV95cUxPZkVuV2xCekkxSzN4Ujd2SmRpZ2t5RW40c3p4a3hVNi16S0RGWGI2N25vUWdLcFdVVl9lOXNiMENYV1JEajN2dVVJeV81R0dXQ3NpQjVCa3pyWEFBSzJENXZUVmNEcmhCSzlma1BJNlRwSzlEZFpiWWVaTGFmcWV0YjZuQV9Ja0NvaUF6dDh6NFJIU21hTGFORFpSQTFHYXRuZndMSk5Sd1BtYWplVktPTnZGQm5QQzg?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1071" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1071" t="inlineStr">
+        <is>
+          <t>Villavicencio</t>
+        </is>
+      </c>
+      <c r="E1071" t="inlineStr"/>
+      <c r="F1071" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1071" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1071" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1071" t="inlineStr">
+        <is>
+          <t>domingo</t>
+        </is>
+      </c>
+      <c r="J1071" t="n">
+        <v>12</v>
+      </c>
+      <c r="K1071" t="inlineStr">
+        <is>
+          <t>protege</t>
+        </is>
+      </c>
+      <c r="L1071" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1071" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1071" t="inlineStr">
+        <is>
+          <t>protects</t>
+        </is>
+      </c>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar protege a adolescentes del Sistema de Responsabilidad Penal ante emergencia sanitaria en el CAE de Villavicencio</t>
+        </is>
+      </c>
+      <c r="B1072" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMitwFBVV95cUxPZkVuV2xCekkxSzN4Ujd2SmRpZ2t5RW40c3p4a3hVNi16S0RGWGI2N25vUWdLcFdVVl9lOXNiMENYV1JEajN2dVVJeV81R0dXQ3NpQjVCa3pyWEFBSzJENXZUVmNEcmhCSzlma1BJNlRwSzlEZFpiWWVaTGFmcWV0YjZuQV9Ja0NvaUF6dDh6NFJIU21hTGFORFpSQTFHYXRuZndMSk5Sd1BtYWplVktPTnZGQm5QQzg?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1072" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1072" t="inlineStr">
+        <is>
+          <t>Villavicencio</t>
+        </is>
+      </c>
+      <c r="E1072" t="inlineStr"/>
+      <c r="F1072" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1072" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1072" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1072" t="inlineStr">
+        <is>
+          <t>domingo</t>
+        </is>
+      </c>
+      <c r="J1072" t="n">
+        <v>12</v>
+      </c>
+      <c r="K1072" t="inlineStr">
+        <is>
+          <t>emergencia</t>
+        </is>
+      </c>
+      <c r="L1072" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1072" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1072" t="inlineStr">
+        <is>
+          <t>emergency</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1072"/>
+  <dimension ref="A1:N1074"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60042,6 +60042,118 @@
         </is>
       </c>
     </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>Cuatro menores bajo protección del ICBF habrían asesinado a una psicóloga para escapar del hogar de paso</t>
+        </is>
+      </c>
+      <c r="B1073" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi_wFBVV95cUxObjF1ZFBtVnRMWGJ6UHJnZUpyYlFtSTJRSUtqcWdfVU5UbDgxTGJjMS05emNtRE1DZjM5NXdGT3ZDMW8zeWxKdUZ2a1M0bjVRcjIyQ09Ud1NZSjNybVhURDV2OUs2THh5YlhOZ21VYnVldkNEWEZ3SmxhS0M1RUF5dUV4TUdjZlVDM3JnVzNuYVZZT2FkZ3JGUGVoSWR2QmhkVFJpaEl2QUluTnhRbjh3UDRwMV9hTzB0QXYxNmVzMksxaEZWdHJHTXFkVHQ4MWV6Z3B2YWlHSWpINGNVMEgzMXM1SE1TV2k2OTVSX1JybUY1RVZQVE1UX211ZkpFZlnSAZoCQVVfeXFMTWRLUVpTcDNsSjVONTd2Q0RLQWZIdWdjVGhMN0xhbkdqMlhMeU5kbmV5YjBJQmF6eVY2UzFBOXYwOENZQVFscFV6Q2c2QkFSd1JmRWk2WVFmU1VUTEdFU3c1bGx3ZHhjQ3JYY0xNV1RoSmxBdDdPVFlUSzRhS3g2SnhDc19Ybm9Ydks4cjlWRlppdlZFS09JaGk4RUtvdUR6QWp3Y1FZaEExeVZ1UlFjTEh3ZWt6SmtzTkU1OHNybHlEYTRtSFJ0aTVjYThteW9qUEtENGJVcWlSS203blBaQ3VKQ2JkZXdXdmRBQkJMWVRxX1NrdjhDY1A0SDdaLVVpVVhPX2VFcms3aFZlWXVYWGxIM2lyUzBaMkVB?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1073" t="inlineStr">
+        <is>
+          <t>ELHERALDO.CO</t>
+        </is>
+      </c>
+      <c r="D1073" t="inlineStr"/>
+      <c r="E1073" t="inlineStr"/>
+      <c r="F1073" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1073" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1073" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1073" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1073" t="n">
+        <v>13</v>
+      </c>
+      <c r="K1073" t="inlineStr">
+        <is>
+          <t>escapar</t>
+        </is>
+      </c>
+      <c r="L1073" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1073" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N1073" t="inlineStr">
+        <is>
+          <t>escape</t>
+        </is>
+      </c>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>Riohacha, escenario de reunificación familiar que devuelve la esperanza a padre e hijo tras separación</t>
+        </is>
+      </c>
+      <c r="B1074" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivgFBVV95cUxPOVVXcUFYa29oMGZyTzF0RG5uejh2TnA0bml0WC11Z3lyaHZlY2tOMUpqNEMtdzRCNTdaekE4aHlSMGJ3LTlIXzdiSWJSTlRJMDF2SmxhcXRHSldmNWpOTEp3UzNkR1k1MkVWNmVneWRtS2I3WUxjbXZmU3RKT0ZmNk55ZHFkY2ZwYkQ5Y0QxdDFWSTZrTnpxdFBBV1NWc2NPRHF1TXFZdlFMM1hiZXRTejgzdEEzczdaRm5mWDNB?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1074" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1074" t="inlineStr">
+        <is>
+          <t>Riohacha</t>
+        </is>
+      </c>
+      <c r="E1074" t="inlineStr"/>
+      <c r="F1074" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1074" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1074" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1074" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1074" t="n">
+        <v>13</v>
+      </c>
+      <c r="K1074" t="inlineStr">
+        <is>
+          <t>esperanza</t>
+        </is>
+      </c>
+      <c r="L1074" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1074" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1074" t="inlineStr">
+        <is>
+          <t>hope</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1074"/>
+  <dimension ref="A1:N1077"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60154,6 +60154,176 @@
         </is>
       </c>
     </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>Cuatro menores habrían asesinado a psicóloga en hogar del ICBF durante intento de fuga</t>
+        </is>
+      </c>
+      <c r="B1075" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivwFBVV95cUxOeGxiOVBPd19FZ3NMS3Q4cnhIdVFuOUtVOXJOZ1UwSXptNU9hMkRhS3plMUhWeUJobnIxT3VxbXc2YlZRRmMwRDN1cWJnVGlvdXA1U2EwRVlvXzh3RFp6b3Z2OEdxNHdCcEdfdklfRnNSRldncXJ6S1pJU2wwV3o5dGVuUEF1b2c5aU01TGtDMEMyR3JnOHdCaWExYmhpSmwyQk92WmloTUJrdTROYmRINmt6dmdpcTAtLXh4T0pkbw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1075" t="inlineStr">
+        <is>
+          <t>Seguimiento.co</t>
+        </is>
+      </c>
+      <c r="D1075" t="inlineStr"/>
+      <c r="E1075" t="inlineStr"/>
+      <c r="F1075" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1075" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1075" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1075" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1075" t="n">
+        <v>13</v>
+      </c>
+      <c r="K1075" t="inlineStr">
+        <is>
+          <t>fuga</t>
+        </is>
+      </c>
+      <c r="L1075" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1075" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N1075" t="inlineStr">
+        <is>
+          <t>leak</t>
+        </is>
+      </c>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar intensifica acciones para prevenir el trabajo infantil y proteger a la niñez en Casanare</t>
+        </is>
+      </c>
+      <c r="B1076" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivAFBVV95cUxNWFB3TU1wbUloT2ZYR3o0eWFEM2hxMG9UeGdocUotU3d4bWJqRERhSDFMcERBMmc4aWkwQkxGQXZGZld4c1NlV2hvLTlrYlhsRGRncnZCMGpCNjRaakxrNV9Wa1ZwcTB6V1lrazVPQ1YzYkRkT21KWGFHOVVFOWktTW84bWRBanNDdVJneUt2bzBzV0VSMjBZcEZzQ2lvQ1BHeFd4ZUUxbFhFWnN3S29Vd1hsQnNMcDNwLXZDTQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1076" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1076" t="inlineStr"/>
+      <c r="E1076" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="F1076" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1076" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1076" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1076" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1076" t="n">
+        <v>13</v>
+      </c>
+      <c r="K1076" t="inlineStr">
+        <is>
+          <t>infantil</t>
+        </is>
+      </c>
+      <c r="L1076" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1076" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1076" t="inlineStr">
+        <is>
+          <t>childish</t>
+        </is>
+      </c>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar intensifica acciones para prevenir el trabajo infantil y proteger a la niñez en Casanare</t>
+        </is>
+      </c>
+      <c r="B1077" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivAFBVV95cUxNWFB3TU1wbUloT2ZYR3o0eWFEM2hxMG9UeGdocUotU3d4bWJqRERhSDFMcERBMmc4aWkwQkxGQXZGZld4c1NlV2hvLTlrYlhsRGRncnZCMGpCNjRaakxrNV9Wa1ZwcTB6V1lrazVPQ1YzYkRkT21KWGFHOVVFOWktTW84bWRBanNDdVJneUt2bzBzV0VSMjBZcEZzQ2lvQ1BHeFd4ZUUxbFhFWnN3S29Vd1hsQnNMcDNwLXZDTQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1077" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1077" t="inlineStr"/>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>Casanare</t>
+        </is>
+      </c>
+      <c r="F1077" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1077" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1077" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1077" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1077" t="n">
+        <v>13</v>
+      </c>
+      <c r="K1077" t="inlineStr">
+        <is>
+          <t>proteger</t>
+        </is>
+      </c>
+      <c r="L1077" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1077" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1077" t="inlineStr">
+        <is>
+          <t>protect</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1077"/>
+  <dimension ref="A1:N1078"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60324,6 +60324,60 @@
         </is>
       </c>
     </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>Video revela qué pasó después del asesinato de psicóloga en hogar del ICBF; aparecen 4 menores</t>
+        </is>
+      </c>
+      <c r="B1078" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiogFBVV95cUxQVHBHTUF5Nml4a0p6dkd0bVBWdnZUb2R3ZzJuTFU4aVhHZjBwZjJja2pOVTd1SWMxZFlQTWZQR1g4NUFIbHloQ05Za1RJZVpHUWJzTG1TcWNYcGx6T3dSQXUtTzlhY0hwMHpoV0VGeDk3MjRoa3UwWG5seDVFU3EybUhPWmNnQkxZakRtbFRXcDNzUFNtekNBZkEyWDJsaUNOWEE?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1078" t="inlineStr">
+        <is>
+          <t>Pulzo</t>
+        </is>
+      </c>
+      <c r="D1078" t="inlineStr"/>
+      <c r="E1078" t="inlineStr"/>
+      <c r="F1078" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1078" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1078" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1078" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1078" t="n">
+        <v>14</v>
+      </c>
+      <c r="K1078" t="inlineStr">
+        <is>
+          <t>asesinato</t>
+        </is>
+      </c>
+      <c r="L1078" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1078" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1078" t="inlineStr">
+        <is>
+          <t>assassination</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1078"/>
+  <dimension ref="A1:N1079"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60378,6 +60378,64 @@
         </is>
       </c>
     </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>Nueva Casa Universitaria en Pasto impulsa proyectos de vida de jóvenes en educación superior</t>
+        </is>
+      </c>
+      <c r="B1079" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMitwFBVV95cUxQY3N5QlNmN3NQUkFXUGw2ckVEaklXalM5aGk4VzIyQVVrRWlMTmUybF9WVUtoY3R1eWh4RGVwSHYtUVRxT0ZLckRZdk5EUlNKVk5wV21fdHVlXzlMU25mMkFTdTl2MGJBbFF0SFpWdktnNVN1N25aQjBQQURQOXE3bUlpMWhFTHgwbkVmaFNFb1Y1UmhyTUJWMVQ3dFMwbGNxTTJVb2pNejZva0h1UWZORGtYNnFsck0?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1079" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1079" t="inlineStr">
+        <is>
+          <t>Pasto</t>
+        </is>
+      </c>
+      <c r="E1079" t="inlineStr"/>
+      <c r="F1079" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1079" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1079" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1079" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J1079" t="n">
+        <v>15</v>
+      </c>
+      <c r="K1079" t="inlineStr">
+        <is>
+          <t>superior</t>
+        </is>
+      </c>
+      <c r="L1079" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1079" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1079" t="inlineStr">
+        <is>
+          <t>superior</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1079"/>
+  <dimension ref="A1:N1083"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60436,6 +60436,230 @@
         </is>
       </c>
     </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>Cayó Concha Baracaldo, directora del ICBF. Tras polémica gestión, renunció y el presidente Gustavo Petro anunció reemplazo</t>
+        </is>
+      </c>
+      <c r="B1080" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi3gFBVV95cUxNRTRoMjJFN0ROQlZnaGZHOEJxU2dVNDRYWlNMT1otME9fY3RTeWRRSm1ZcndwdnB3a0c0VV9zUHJzTlYyQVJvTlFIU0loRkJFQng1T0xEUWs2RW5CdVRxYXpmNW1nR3BBMmIxTHZsRUEtSDlkVlF3NElMLTNoU1BUQTlPMW1mNnJHakcwN1RGVFl0OE8yTDhIc0xvaXV5NFBnMVJlcGxqdWdaTGF6TnZKbExSemlWaElCckJORFJFU3NxamFhclE2YVF6b1pXMTEyNldvcEU1MFFXWmZKakHSAeMBQVVfeXFMTXc4dTNZbkhQU1NHTDN3X1dRQlFrSHloU3FJNTZTYkNnOFdUcjhJQ2NoX25mZ3dBb2xNUHFINFVXTExGQVM3R1hCVDQzZWpBUTV1a0JkNGFfcWZ3a3F0QVVWRC1wd1NhRExKMDdmMkIteDEtV2xSdFFTZzRuREhfdDdIWmx4WlRSZXJyck1xUWxRTE5zaEFUdF9mOTdmLVEtSU1EamJ2OVByaVBmRkdXNlo3UTQ5NjB2bmY2a3NmSDRsZ2hCNlllVDV1d0JvN3FYTEIzbTZKMlpFdW9DT0dxTWFJb2c?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1080" t="inlineStr">
+        <is>
+          <t>Revista Semana</t>
+        </is>
+      </c>
+      <c r="D1080" t="inlineStr"/>
+      <c r="E1080" t="inlineStr"/>
+      <c r="F1080" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1080" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H1080" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1080" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J1080" t="n">
+        <v>8</v>
+      </c>
+      <c r="K1080" t="inlineStr">
+        <is>
+          <t>polémica</t>
+        </is>
+      </c>
+      <c r="L1080" t="inlineStr">
+        <is>
+          <t>Astrid Cáceres</t>
+        </is>
+      </c>
+      <c r="M1080" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1080" t="inlineStr">
+        <is>
+          <t>controversially</t>
+        </is>
+      </c>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>Gobierno anunció renuncia de directora del ICBF, Concepción Baracaldo</t>
+        </is>
+      </c>
+      <c r="B1081" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMirwFBVV95cUxQVklYZm45MHE0d0xTYWw2MGZOOW5fTnhHckhzbE9heDE0VDM5M05CT1lqU2FnRHVfWjVOX054NjNoV2M5ZWdrWjNHbHFLcHRCWjdtbTdtb0w4Yks5ZzU5MTQ2SlphbXJySlhLMEE4a1hGay15RE1CcnJUTlFrVmM3UVEtS0lGREd3QlQxdE5mb0IwczRSbEwyYXdtbTMwS1h2Z3BMNzJLbjRZVFd0RE9j?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1081" t="inlineStr">
+        <is>
+          <t>Opinion Caribe</t>
+        </is>
+      </c>
+      <c r="D1081" t="inlineStr"/>
+      <c r="E1081" t="inlineStr"/>
+      <c r="F1081" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1081" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H1081" t="n">
+        <v>2</v>
+      </c>
+      <c r="I1081" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1081" t="n">
+        <v>9</v>
+      </c>
+      <c r="K1081" t="inlineStr">
+        <is>
+          <t>renuncia</t>
+        </is>
+      </c>
+      <c r="L1081" t="inlineStr">
+        <is>
+          <t>Astrid Cáceres</t>
+        </is>
+      </c>
+      <c r="M1081" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N1081" t="inlineStr">
+        <is>
+          <t>resigns</t>
+        </is>
+      </c>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar impulsa oportunidades para jóvenes del SRPA con modelo de reindustrialización</t>
+        </is>
+      </c>
+      <c r="B1082" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMirgFBVV95cUxNTThLcWNac2RJVXg3R0JxaFdLZEJ4UktkSDBodlZ4SkVCWFVGN0VwUDBIUjJ5U196c2xyc3o2X0RORmlQcnhISndONlNjZXhKQl9sN2VoNnFYZmRUTmJieWZGSXpqTEJnTGZ0cm91bXhZelVyT0tjOEJOcml3Y3dBcWpreG8yaFVDeWxLeFBrNU1LN243ZDRVZHNqSy1PbG9xMWlCRlJReHRIYkFaN3c?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1082" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1082" t="inlineStr"/>
+      <c r="E1082" t="inlineStr"/>
+      <c r="F1082" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1082" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1082" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1082" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1082" t="n">
+        <v>16</v>
+      </c>
+      <c r="K1082" t="inlineStr">
+        <is>
+          <t>oportunidades</t>
+        </is>
+      </c>
+      <c r="L1082" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1082" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1082" t="inlineStr">
+        <is>
+          <t>opportunities</t>
+        </is>
+      </c>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar fortalece acciones por la protección de la niñez y las familias en Arauca</t>
+        </is>
+      </c>
+      <c r="B1083" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiugFBVV95cUxPdDZHWFFYSkhYQTBlVDU1eDJ1X1ZBOUVLX2RFVEhEeFp3MWtXckc0MVAtNDMtQ2ZJSnZwWnRJTWpCdEJSQkdpaUg2eDFBNmJsdUdMMk9wOE5aOExQR1lCWU1pVnk2dlB4NTh2c08zUXctOEJFd3VIOXVkNFFTWHNMcTBtOXpHSjlJdkhxODBZR1RjLXJaUVRKMFNrNVBtbkZST25wbWpLcWtsM2Fnblh0NEF5eFRfbUZmOHc?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1083" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1083" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="E1083" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="F1083" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1083" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1083" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1083" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J1083" t="n">
+        <v>15</v>
+      </c>
+      <c r="K1083" t="inlineStr">
+        <is>
+          <t>fortalece</t>
+        </is>
+      </c>
+      <c r="L1083" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1083" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1083" t="inlineStr">
+        <is>
+          <t>strengthens</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1083"/>
+  <dimension ref="A1:N1084"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60660,6 +60660,60 @@
         </is>
       </c>
     </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>Habla testigo clave en el homicidio a la cuidadora del ICBF en Barrancabermeja: habría sido atacada por adolescentes por impedir violación de una niña</t>
+        </is>
+      </c>
+      <c r="B1084" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMimwJBVV95cUxNOFZxSlpYcENpQTBHVFk2WFo3ZUs0elIwX1NhcVpaNFpoYmJud0lYZ0pxMjdlT0hxNzBzb29GeTVqRVFFYUltV0VzNzJ5YkNZWEo4azBlVVVhVUh4N2dXN2xlTHBqMV9xM0hZaUJpaDBFVTB5eHpNTy1sZ3ZXelhhcTR4cU9LNzBkWGNyaU9GY3VLR0ZhVi03VWU4dFFkU0RhN0dtMWFyNXB0NmdKRlViRmNsQmY5S05NR2xmMTN1bTNyT2lpTFI5bEl5b1hZVHZhMFlyQnVTZEhkVXVGU0QtWFlGM1ZqQ0h2eHRacnhFVXZTclRZZDlDTm1uaHp3dlp4SzN3bG5xbEpXLXdWMFFNOWZ2RnRkMkUxQU93?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1084" t="inlineStr">
+        <is>
+          <t>ELTIEMPO.COM</t>
+        </is>
+      </c>
+      <c r="D1084" t="inlineStr"/>
+      <c r="E1084" t="inlineStr"/>
+      <c r="F1084" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1084" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1084" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1084" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1084" t="n">
+        <v>16</v>
+      </c>
+      <c r="K1084" t="inlineStr">
+        <is>
+          <t>violación</t>
+        </is>
+      </c>
+      <c r="L1084" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1084" t="n">
+        <v>-4</v>
+      </c>
+      <c r="N1084" t="inlineStr">
+        <is>
+          <t>rape</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1084"/>
+  <dimension ref="A1:N1086"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60714,6 +60714,118 @@
         </is>
       </c>
     </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>Tres niñas fueron protegidas por el ICBF tras riesgo de reclutamiento en Nariño</t>
+        </is>
+      </c>
+      <c r="B1085" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMitAFBVV95cUxPUWt1VUgtYUJVR184aW1feTU3M0s0d0tkZjNPaW1GQXgxdmxaMk9RN0c0WktPcE43S0ZlbC1CbTZpSUpVSkEzbkdJc0RjSUt1dUdXVS1SU19FTUNCTW9IZEtHUkloWG1NblZteDhoQVBuNDFYV08zQ01rMkpDMjl4UVRjZ2pjeFdiV2Q2Q21ZdjM4bUJfSWFSeWt2NS1FOGI4TlM5NEFaZTJxZzBEbVJGNDdVLTHSAcgBQVVfeXFMT2x0eFZhZDR0T2dYN1BWV2JSY2Rsa0txaURTSWFkY25NXzJyWEhDUzNYR2NHRG5MdDB4ZF9QQzlVTXdUZFdtSmhYVmpsTXZUQ3pvRzJTR0g4aEpoRXFtbzRqQUItTTN3UEJIbUpKLUlDWHBlZUFKbGRBa3ZkNXFVa0FiYUN4elBWMEltRW5DMy1saTl0dWZ2Sm5kNUc0YTQxV2t1OVFFMlhKUTdWdFRCOUlkTHRObnNjZTYzX0k5UV9wdGVIM3hKWDc?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1085" t="inlineStr">
+        <is>
+          <t>Caracol Radio</t>
+        </is>
+      </c>
+      <c r="D1085" t="inlineStr"/>
+      <c r="E1085" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="F1085" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1085" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1085" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1085" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J1085" t="n">
+        <v>17</v>
+      </c>
+      <c r="K1085" t="inlineStr">
+        <is>
+          <t>riesgo</t>
+        </is>
+      </c>
+      <c r="L1085" t="inlineStr">
+        <is>
+          <t>Astrid Cáceres</t>
+        </is>
+      </c>
+      <c r="M1085" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1085" t="inlineStr">
+        <is>
+          <t>risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>Testigo revela que cuidadora del Icbf fue asesinada por impedir el abuso de una menor</t>
+        </is>
+      </c>
+      <c r="B1086" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiygFBVV95cUxOZEllTFpJaV9Gcm9fM19EMUoycEdjTENnaTJISldjSTcxVl9XdmdjbHRBTXVfX0lLNGdKS0wtYzhhSUtYNmUtVDNPaUFyTFFHeUxLLVNqMnoxcTAyZEwySWZXUEVHYXhoSkwyd2U0VEhrSjFhcjhWT3FCMHZrLUQzUzNpLXNlU3NOcjhwZ0otbnpMZlFQUmFib2JlVTE1VXFKZHJKNllGNTdicHczVE9ERE44VGhPVVZ0VEEwWEJDVkU4WmFLcUxVeVFn0gHPAUFVX3lxTFB5OTB3ZTF5QXdHdUZsREpiaUVZSW85MDRpa3Z3R0VYUjhzdFAtUWJVbVlqX2NxLVBLcUI0dWFhNjE2ZVI1QzJmdFlZWmpJZ0ZHZmNHSjNyMnhLYUpscDl4YnNDd2Z5VFJEU2VlMDh0R29RSFRXWXk4Wjl6Nk1HaUJ0X2JISTdFZHYtNk51LTB0c2JqbW9vQ3dxTWRhRkJqTFZQRk1Iak5hTEh3VGFnUWZwd2tDbFJWU2R6Q3hFb2JpNkVOTWF1bDhRMEQ4WUYtZw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1086" t="inlineStr">
+        <is>
+          <t>elpais.com.co</t>
+        </is>
+      </c>
+      <c r="D1086" t="inlineStr"/>
+      <c r="E1086" t="inlineStr"/>
+      <c r="F1086" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1086" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1086" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1086" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J1086" t="n">
+        <v>17</v>
+      </c>
+      <c r="K1086" t="inlineStr">
+        <is>
+          <t>abuso</t>
+        </is>
+      </c>
+      <c r="L1086" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1086" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1086" t="inlineStr">
+        <is>
+          <t>abuse</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1086"/>
+  <dimension ref="A1:N1089"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60826,6 +60826,172 @@
         </is>
       </c>
     </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>ICBF evita el reclutamiento de tres niñas en Nariño y refuerza acciones de prevención</t>
+        </is>
+      </c>
+      <c r="B1087" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiuwFBVV95cUxNdlV6UW9Tclh3dUY3N1hLb3dydWJqb0NEMHN3WWZJb21UWWpISUwxVzhsTmEwUUl0SkgyUDNQUmQ5UUtTajNsWTh1SXhhR0FIcEFYeTV6eGVPUEJNMDY3TGwwamI5NkhJX1hRQUw0aWkwbGVXOUVsZXgyaXFpOTFvMXlxM3BIUzdxajdUWHV5M1dxZHlCN2l1MC04d1FCSVN5MHFKNTlpVV9QMVRLbC0wMjJ6MjJBMHJNSVpZ0gHDAUFVX3lxTFBOeWRSWEJQeWdMbnp0V1MyTmZZUDZOREhneU1tVHQxYVNOU2RvX29UMFZsQkhMVXJueXFpVjJrUEllZmhoZGtPNVVISGtFdndndmhUbTRvc2llUnFwT092QWhoZ2o0YVJ4NW9aaUlTRV9TQVcyZ2tmbldPXzJjcWdWbW40RzVncHJmWldTX0lRM0NmLTBJMG9mUHlzM1Rtc0ZqaTRNd3hDby1HNmt1UWsyVWtyWlZxNEVsTENOdEk3aHlvQQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1087" t="inlineStr">
+        <is>
+          <t>informativo del guaico</t>
+        </is>
+      </c>
+      <c r="D1087" t="inlineStr"/>
+      <c r="E1087" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="F1087" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1087" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1087" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1087" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J1087" t="n">
+        <v>17</v>
+      </c>
+      <c r="K1087" t="inlineStr">
+        <is>
+          <t>evita</t>
+        </is>
+      </c>
+      <c r="L1087" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1087" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N1087" t="inlineStr">
+        <is>
+          <t>averts</t>
+        </is>
+      </c>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar fortalece el reconocimiento del campesinado como sujeto de derechos con atención a más de 200 mil participantes. | Portal ICBF - Instituto Colombiano de Bienestar</t>
+        </is>
+      </c>
+      <c r="B1088" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiwAFBVV95cUxQVjNIWFlQeW9pQmhMUDFMQXpZczgzUTRIZ1puZ3lqODBSX2YzLVVyYUtoWmd1UWhTSHVBOVlsRVhCZGNoU1VvclU5RDR5VkFjVUx5bEYteWRaZlFvT3hXVmNvMUt1WlFCVzAwbl9La2d4azZtU3hpMUduWjZscF9RcnhmeGZ1a3hTaFIzcVJlWHozdlhnbWdBMHdFV2ZyWmM0aldwYkl1VzYzU3lJdUsyMGhlbjA5Yld6YjZzYVM3VFQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1088" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1088" t="inlineStr"/>
+      <c r="E1088" t="inlineStr"/>
+      <c r="F1088" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1088" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1088" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1088" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J1088" t="n">
+        <v>17</v>
+      </c>
+      <c r="K1088" t="inlineStr">
+        <is>
+          <t>fortalece</t>
+        </is>
+      </c>
+      <c r="L1088" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1088" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1088" t="inlineStr">
+        <is>
+          <t>strengthens</t>
+        </is>
+      </c>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar resalta la importancia del respeto a los entornos escolares como espacios de especial protección para la niñez | Portal ICBF - Instituto Colombiano de Bienestar</t>
+        </is>
+      </c>
+      <c r="B1089" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiwAFBVV95cUxPZzgyUV8zQXdNZnRPR0pKSEp2SUF4YUVTRnA3SFh4cTZFRV9jTWI0OTlCbDlfb3VYZ1BteDVXeExpd3BWbWxkeGt1N1BlazlabTViT0s2bms0MDJoOEdYS2loeUkxakZmMmdtX1M4d3Rfbmp4UzBUVkFvdEVtVWR4aHV4V0VFN2trUVZBaUt5WHc3cFJvU3gzSHVoWFlqSWVycEpTSTYzemdNaTZmb2JMT0pHenBKSTE0TGJvVlQ1NTQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1089" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1089" t="inlineStr"/>
+      <c r="E1089" t="inlineStr"/>
+      <c r="F1089" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1089" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1089" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1089" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J1089" t="n">
+        <v>17</v>
+      </c>
+      <c r="K1089" t="inlineStr">
+        <is>
+          <t>importancia</t>
+        </is>
+      </c>
+      <c r="L1089" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1089" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1089" t="inlineStr">
+        <is>
+          <t>importance</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1089"/>
+  <dimension ref="A1:N1090"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -60992,6 +60992,60 @@
         </is>
       </c>
     </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar resalta la importancia del respeto a los entornos escolares como espacios de especial protección para la niñez | Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="B1090" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiwAFBVV95cUxPZzgyUV8zQXdNZnRPR0pKSEp2SUF4YUVTRnA3SFh4cTZFRV9jTWI0OTlCbDlfb3VYZ1BteDVXeExpd3BWbWxkeGt1N1BlazlabTViT0s2bms0MDJoOEdYS2loeUkxakZmMmdtX1M4d3Rfbmp4UzBUVkFvdEVtVWR4aHV4V0VFN2trUVZBaUt5WHc3cFJvU3gzSHVoWFlqSWVycEpTSTYzemdNaTZmb2JMT0pHenBKSTE0TGJvVlQ1NTQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1090" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1090" t="inlineStr"/>
+      <c r="E1090" t="inlineStr"/>
+      <c r="F1090" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1090" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1090" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1090" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J1090" t="n">
+        <v>17</v>
+      </c>
+      <c r="K1090" t="inlineStr">
+        <is>
+          <t>importancia</t>
+        </is>
+      </c>
+      <c r="L1090" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1090" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1090" t="inlineStr">
+        <is>
+          <t>importance</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1090"/>
+  <dimension ref="A1:N1091"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61046,6 +61046,64 @@
         </is>
       </c>
     </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar aporta a la reivindicación de una lucha histórica con la implementación de modelo propio en Putumayo</t>
+        </is>
+      </c>
+      <c r="B1091" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivgFBVV95cUxPVVEzYmkwR0s0aFVQNFVBNlBoQ1d0NFV5OXlqRFJFUWRtUURQbVZYbTNSZnJnTGlGSE52cDBrYzZyWmU2aGd0N2U1WVlpbHpLdHM3cUw2SWpBei1HYXRYN2llcjF0UE5sMkhaQ01TQXVISW5Fc21yYzUzdHUtTk9sQXdJMHVKbFVhMTZyLWhpeHJrSFdwc1VFRlFXaFVMUnZMc3dlT2hfa0F0YUhyVWo2dXJ3dmp6MEdMUnc1dHpB?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1091" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1091" t="inlineStr"/>
+      <c r="E1091" t="inlineStr">
+        <is>
+          <t>Putumayo</t>
+        </is>
+      </c>
+      <c r="F1091" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1091" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1091" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1091" t="inlineStr">
+        <is>
+          <t>domingo</t>
+        </is>
+      </c>
+      <c r="J1091" t="n">
+        <v>19</v>
+      </c>
+      <c r="K1091" t="inlineStr">
+        <is>
+          <t>lucha</t>
+        </is>
+      </c>
+      <c r="L1091" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1091" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N1091" t="inlineStr">
+        <is>
+          <t>fight</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1091"/>
+  <dimension ref="A1:N1092"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61104,6 +61104,68 @@
         </is>
       </c>
     </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar fortalece la atención a la niñez del pueblo Hitnú en Arauca</t>
+        </is>
+      </c>
+      <c r="B1092" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMirgFBVV95cUxQSWpENGtla2hhd2otX29wWXFjSFRDSWpCNnB0R3lEY3VZZmRqTXhCMjdEbTlTSkNEbncyQXZoMDRNVUhPaC1RNHlIZzVUYmE0c1lmVGZiYTdoVGstc2VtbWdKX2V6WWF5OTBITWJOZ2JFWlI5N0MxaG9ydFhXLVI3Nlc3blltckZPQ053TlFvTnZSMEM5WF9RU2NjYnF6SkFVNVFrM1ZxU0p5R3hrM1E?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1092" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1092" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="E1092" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="F1092" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1092" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1092" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1092" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1092" t="n">
+        <v>20</v>
+      </c>
+      <c r="K1092" t="inlineStr">
+        <is>
+          <t>fortalece</t>
+        </is>
+      </c>
+      <c r="L1092" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1092" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1092" t="inlineStr">
+        <is>
+          <t>strengthens</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1092"/>
+  <dimension ref="A1:N1096"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61166,6 +61166,222 @@
         </is>
       </c>
     </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>“Fue escalofriante”: revelan amenazas previas y fallas en caso de psicóloga asesinada en hogar del ICBF</t>
+        </is>
+      </c>
+      <c r="B1093" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi3gFBVV95cUxPUkJPU1dpdjJsYURTN2djYUVMTWJ0REtGN1VRRF9ZVzdicmRBdTVlanBaNTljZzhzMHo2RlIwRUxnQ2NxUnB5ZWFFMEUtSGZkTHdKSE0ycHNvZ0IyclJPb21NTG9BZUhOZmJVYnh1NWJ6eWVqZEpoblVabWx5LXBoc1lvZ3Q0dklWWFIzV2NKVTNocEF2YnQxQU9VOGIwbm1oRVZHOVRyQkwwb2FYUmVQd2lEXzJHU1hzN05uUHhxUmhZZ1VuQUVubWxtR0ZqWko2VE9RLVBsQ3dnTFJLZ3fSAfgBQVVfeXFMTzJhVWRneU9sXzNFdVJlSXRmeG9Za1BtOGpETzZCRWVlSzNwc0tsdGczdXRGYjBDcTZtMnI5RlF1YWNiaElOaDdmYzhLT1RyeTJ3RERMeWU3SHpabDI4RzZ4aFh5WUY1SnpDc2VDR2pyU2FxUWZMSG1yZ1NSS3NNV0lBZ2l0Wmo2ZXN0bHIwV2RHVEw1U0Vsc3JnQjFxVTdsQWhRell3WkRWZDFWUHNLZHJVRjZCNklGZlVaalNxdy1OaVRTQTBKVXZlZEVGYmVHeDlMNS13Ulk4RG1ic2ZuQlNOV2dkajBIVUpGck0tQWF3cWczRlRKa18?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1093" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D1093" t="inlineStr"/>
+      <c r="E1093" t="inlineStr"/>
+      <c r="F1093" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1093" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1093" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1093" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1093" t="n">
+        <v>21</v>
+      </c>
+      <c r="K1093" t="inlineStr">
+        <is>
+          <t>escalofriante</t>
+        </is>
+      </c>
+      <c r="L1093" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1093" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N1093" t="inlineStr">
+        <is>
+          <t>chilling</t>
+        </is>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>“Fue escalofriante”: revelan amenazas previas y fallas en caso de psicóloga asesinada en hogar del ICBF</t>
+        </is>
+      </c>
+      <c r="B1094" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi3gFBVV95cUxPUkJPU1dpdjJsYURTN2djYUVMTWJ0REtGN1VRRF9ZVzdicmRBdTVlanBaNTljZzhzMHo2RlIwRUxnQ2NxUnB5ZWFFMEUtSGZkTHdKSE0ycHNvZ0IyclJPb21NTG9BZUhOZmJVYnh1NWJ6eWVqZEpoblVabWx5LXBoc1lvZ3Q0dklWWFIzV2NKVTNocEF2YnQxQU9VOGIwbm1oRVZHOVRyQkwwb2FYUmVQd2lEXzJHU1hzN05uUHhxUmhZZ1VuQUVubWxtR0ZqWko2VE9RLVBsQ3dnTFJLZ3fSAfgBQVVfeXFMTzJhVWRneU9sXzNFdVJlSXRmeG9Za1BtOGpETzZCRWVlSzNwc0tsdGczdXRGYjBDcTZtMnI5RlF1YWNiaElOaDdmYzhLT1RyeTJ3RERMeWU3SHpabDI4RzZ4aFh5WUY1SnpDc2VDR2pyU2FxUWZMSG1yZ1NSS3NNV0lBZ2l0Wmo2ZXN0bHIwV2RHVEw1U0Vsc3JnQjFxVTdsQWhRell3WkRWZDFWUHNLZHJVRjZCNklGZlVaalNxdy1OaVRTQTBKVXZlZEVGYmVHeDlMNS13Ulk4RG1ic2ZuQlNOV2dkajBIVUpGck0tQWF3cWczRlRKa18?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1094" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D1094" t="inlineStr"/>
+      <c r="E1094" t="inlineStr"/>
+      <c r="F1094" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1094" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1094" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1094" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1094" t="n">
+        <v>21</v>
+      </c>
+      <c r="K1094" t="inlineStr">
+        <is>
+          <t>amenazas</t>
+        </is>
+      </c>
+      <c r="L1094" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1094" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1094" t="inlineStr">
+        <is>
+          <t>threats</t>
+        </is>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>“Fue escalofriante”: Nuevos detalles del asesinato de menores de edad a psicóloga de hogar de paso del ICBF</t>
+        </is>
+      </c>
+      <c r="B1095" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi5gFBVV95cUxOUkFSbkZVQnM3NmFMd0J5WjFvaHc0b2xpMFRnMF83QW5jZThja01GTEZZZEM0OE56aUh1QzhaRHZTNDVQVU4xQTh2RkpkclM2VDhjZVNoNHVpNFRaOFE0TldwWERrVGFYMUYtN002eXNjVjJfY3ZoSnAyWi1Qem15ODFLSzAtN2ZjR3p4akRoMFJwMjdzdGZGbFFOaWtmT3FGVjFtbkZncTVVbWJIRmlDT3k5RnptZHM1ZGJLUk5HV2ZKZ2U0TWRzamM4aWQ4dGloRHVxcTVLZklyemZjWXlSMlRUYlhDZ9IB6wFBVV95cUxOTEx2NzBlMlJ4VDJ3ZElHY21xaEJNcXpPWEs1bWN0Rk51RDJUSWZra2V0QUh3SFYzQ091VUl1Mlh2ajhwNG14RkVCXzBnWkptRzlzM05iSzEwZ3FUR19rYWtGWXBDNGZqb3B0Q2c3WDk0THF5Uk9aNXhfNlZWTDB6VEc3clI4REtnelhFb3B1TTdVT0JPSkhTeWV2ZWoyNnlSUWlZWVowbWpTa1pDdVFpSkpudzIxZXdTM01qWWUtdzNQQnhGZHE3RC0xUVpqbU1SZkxoalFKVmN0MVgyZXpqQWtUcFBkMUlIM0ZN?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1095" t="inlineStr">
+        <is>
+          <t>Revista Semana</t>
+        </is>
+      </c>
+      <c r="D1095" t="inlineStr"/>
+      <c r="E1095" t="inlineStr"/>
+      <c r="F1095" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1095" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1095" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1095" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1095" t="n">
+        <v>21</v>
+      </c>
+      <c r="K1095" t="inlineStr">
+        <is>
+          <t>escalofriante</t>
+        </is>
+      </c>
+      <c r="L1095" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1095" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N1095" t="inlineStr">
+        <is>
+          <t>chilling</t>
+        </is>
+      </c>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>“Fue escalofriante”: Nuevos detalles del asesinato de menores de edad a psicóloga de hogar de paso del ICBF</t>
+        </is>
+      </c>
+      <c r="B1096" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi5gFBVV95cUxOUkFSbkZVQnM3NmFMd0J5WjFvaHc0b2xpMFRnMF83QW5jZThja01GTEZZZEM0OE56aUh1QzhaRHZTNDVQVU4xQTh2RkpkclM2VDhjZVNoNHVpNFRaOFE0TldwWERrVGFYMUYtN002eXNjVjJfY3ZoSnAyWi1Qem15ODFLSzAtN2ZjR3p4akRoMFJwMjdzdGZGbFFOaWtmT3FGVjFtbkZncTVVbWJIRmlDT3k5RnptZHM1ZGJLUk5HV2ZKZ2U0TWRzamM4aWQ4dGloRHVxcTVLZklyemZjWXlSMlRUYlhDZ9IB6wFBVV95cUxOTEx2NzBlMlJ4VDJ3ZElHY21xaEJNcXpPWEs1bWN0Rk51RDJUSWZra2V0QUh3SFYzQ091VUl1Mlh2ajhwNG14RkVCXzBnWkptRzlzM05iSzEwZ3FUR19rYWtGWXBDNGZqb3B0Q2c3WDk0THF5Uk9aNXhfNlZWTDB6VEc3clI4REtnelhFb3B1TTdVT0JPSkhTeWV2ZWoyNnlSUWlZWVowbWpTa1pDdVFpSkpudzIxZXdTM01qWWUtdzNQQnhGZHE3RC0xUVpqbU1SZkxoalFKVmN0MVgyZXpqQWtUcFBkMUlIM0ZN?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1096" t="inlineStr">
+        <is>
+          <t>Revista Semana</t>
+        </is>
+      </c>
+      <c r="D1096" t="inlineStr"/>
+      <c r="E1096" t="inlineStr"/>
+      <c r="F1096" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1096" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1096" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1096" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1096" t="n">
+        <v>21</v>
+      </c>
+      <c r="K1096" t="inlineStr">
+        <is>
+          <t>asesinato</t>
+        </is>
+      </c>
+      <c r="L1096" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1096" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1096" t="inlineStr">
+        <is>
+          <t>assassination</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1096"/>
+  <dimension ref="A1:N1098"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61382,6 +61382,114 @@
         </is>
       </c>
     </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>Nuevos detalles del crimen de trabajadora del ICBF, Karelis Merlano en Barrancabermeja a manos de cuatro adolescentes: 'Ya era una noche de terror'</t>
+        </is>
+      </c>
+      <c r="B1097" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMikwJBVV95cUxNZmk3YlR4czdXSXZnckdBSkVNZUNuMEg0NlltVG05WDRTVXBQX0NVUVF2OTBwUmdzbnZrSVFLOEZNRHhYOGpBbnEzOUR3bVVsa0tUSUN5QnY0SU1VQjZKZmxTRjNsa1hEOERZS0NOb0JLVUhBZFpJTTllYVRCSFl5UWd5YU5SMmhKNVc2c1JjWjI2TWNWOC1GLU1tMmZLQWxuV3ZQc3htOFJMOTdoS0lnYXJrQ0Q3ZWRXd2xiYkthNlVhbnpHeUhwdWxmRGRpRnRQdUt3dWg3TG1jNFFlQVVUd1NnQXRMb3VsYTdqREVWaDduNXpJTW1uVG1KdmdZMVQ4a3NHU2FOcUtaM1o4ejVXenZnZ9IBmAJBVV95cUxONDA1NE9nWi12SkMxc25IRFNrbllTYlNiV2ZaNUUxbXpWdVYyS19FZFJVdWlSWmF3NkU5SVpiZGtzRHdNVFpyblRnU09EajVWMHd3OHBLTTVfWl9zLXJhOXpYRXhkUi1hajdBalNhZ3djdDJCcU10UVU0eUNwX3Y4TmpTMjllT2ltWWE4NVpVVkxVTU53YV8wN1lOaC1NN1I4c2JXVWl2ME4zVmNobmdzV3FvQTgtdUdYYm1DcDVoNzhIQU1oUjluYnVDN1NyVjZBVmMxUjhZZXUySnhRc0dBWFctTi11SXNmVjNvUW1SeFo0MkpHTW56V0dFWjdHQmx2MDBhVTZtTC1Lc2R1U0IxMU8yd25HbnJn?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1097" t="inlineStr">
+        <is>
+          <t>ELTIEMPO.com</t>
+        </is>
+      </c>
+      <c r="D1097" t="inlineStr"/>
+      <c r="E1097" t="inlineStr"/>
+      <c r="F1097" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1097" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1097" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1097" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1097" t="n">
+        <v>21</v>
+      </c>
+      <c r="K1097" t="inlineStr">
+        <is>
+          <t>crimen</t>
+        </is>
+      </c>
+      <c r="L1097" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1097" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1097" t="inlineStr">
+        <is>
+          <t>crime</t>
+        </is>
+      </c>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>Nuevos detalles del crimen de trabajadora del ICBF, Karelis Merlano en Barrancabermeja a manos de cuatro adolescentes: 'Ya era una noche de terror'</t>
+        </is>
+      </c>
+      <c r="B1098" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMikwJBVV95cUxNZmk3YlR4czdXSXZnckdBSkVNZUNuMEg0NlltVG05WDRTVXBQX0NVUVF2OTBwUmdzbnZrSVFLOEZNRHhYOGpBbnEzOUR3bVVsa0tUSUN5QnY0SU1VQjZKZmxTRjNsa1hEOERZS0NOb0JLVUhBZFpJTTllYVRCSFl5UWd5YU5SMmhKNVc2c1JjWjI2TWNWOC1GLU1tMmZLQWxuV3ZQc3htOFJMOTdoS0lnYXJrQ0Q3ZWRXd2xiYkthNlVhbnpHeUhwdWxmRGRpRnRQdUt3dWg3TG1jNFFlQVVUd1NnQXRMb3VsYTdqREVWaDduNXpJTW1uVG1KdmdZMVQ4a3NHU2FOcUtaM1o4ejVXenZnZ9IBmAJBVV95cUxONDA1NE9nWi12SkMxc25IRFNrbllTYlNiV2ZaNUUxbXpWdVYyS19FZFJVdWlSWmF3NkU5SVpiZGtzRHdNVFpyblRnU09EajVWMHd3OHBLTTVfWl9zLXJhOXpYRXhkUi1hajdBalNhZ3djdDJCcU10UVU0eUNwX3Y4TmpTMjllT2ltWWE4NVpVVkxVTU53YV8wN1lOaC1NN1I4c2JXVWl2ME4zVmNobmdzV3FvQTgtdUdYYm1DcDVoNzhIQU1oUjluYnVDN1NyVjZBVmMxUjhZZXUySnhRc0dBWFctTi11SXNmVjNvUW1SeFo0MkpHTW56V0dFWjdHQmx2MDBhVTZtTC1Lc2R1U0IxMU8yd25HbnJn?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1098" t="inlineStr">
+        <is>
+          <t>ELTIEMPO.com</t>
+        </is>
+      </c>
+      <c r="D1098" t="inlineStr"/>
+      <c r="E1098" t="inlineStr"/>
+      <c r="F1098" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1098" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1098" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1098" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1098" t="n">
+        <v>21</v>
+      </c>
+      <c r="K1098" t="inlineStr">
+        <is>
+          <t>terror</t>
+        </is>
+      </c>
+      <c r="L1098" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1098" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1098" t="inlineStr">
+        <is>
+          <t>terror</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1098"/>
+  <dimension ref="A1:N1101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61490,6 +61490,172 @@
         </is>
       </c>
     </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>Nuevos detalles del crimen de Karelis Merlano en Barrancabermeja: trabajadora de fundación vinculada al ICBF; 'ya era una noche de terror'</t>
+        </is>
+      </c>
+      <c r="B1099" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMikwJBVV95cUxNZmk3YlR4czdXSXZnckdBSkVNZUNuMEg0NlltVG05WDRTVXBQX0NVUVF2OTBwUmdzbnZrSVFLOEZNRHhYOGpBbnEzOUR3bVVsa0tUSUN5QnY0SU1VQjZKZmxTRjNsa1hEOERZS0NOb0JLVUhBZFpJTTllYVRCSFl5UWd5YU5SMmhKNVc2c1JjWjI2TWNWOC1GLU1tMmZLQWxuV3ZQc3htOFJMOTdoS0lnYXJrQ0Q3ZWRXd2xiYkthNlVhbnpHeUhwdWxmRGRpRnRQdUt3dWg3TG1jNFFlQVVUd1NnQXRMb3VsYTdqREVWaDduNXpJTW1uVG1KdmdZMVQ4a3NHU2FOcUtaM1o4ejVXenZnZ9IBmAJBVV95cUxONDA1NE9nWi12SkMxc25IRFNrbllTYlNiV2ZaNUUxbXpWdVYyS19FZFJVdWlSWmF3NkU5SVpiZGtzRHdNVFpyblRnU09EajVWMHd3OHBLTTVfWl9zLXJhOXpYRXhkUi1hajdBalNhZ3djdDJCcU10UVU0eUNwX3Y4TmpTMjllT2ltWWE4NVpVVkxVTU53YV8wN1lOaC1NN1I4c2JXVWl2ME4zVmNobmdzV3FvQTgtdUdYYm1DcDVoNzhIQU1oUjluYnVDN1NyVjZBVmMxUjhZZXUySnhRc0dBWFctTi11SXNmVjNvUW1SeFo0MkpHTW56V0dFWjdHQmx2MDBhVTZtTC1Lc2R1U0IxMU8yd25HbnJn?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1099" t="inlineStr">
+        <is>
+          <t>ELTIEMPO.COM</t>
+        </is>
+      </c>
+      <c r="D1099" t="inlineStr"/>
+      <c r="E1099" t="inlineStr"/>
+      <c r="F1099" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1099" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1099" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1099" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1099" t="n">
+        <v>21</v>
+      </c>
+      <c r="K1099" t="inlineStr">
+        <is>
+          <t>crimen</t>
+        </is>
+      </c>
+      <c r="L1099" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1099" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1099" t="inlineStr">
+        <is>
+          <t>crime</t>
+        </is>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>Nuevos detalles del crimen de Karelis Merlano en Barrancabermeja: trabajadora de fundación vinculada al ICBF; 'ya era una noche de terror'</t>
+        </is>
+      </c>
+      <c r="B1100" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMikwJBVV95cUxNZmk3YlR4czdXSXZnckdBSkVNZUNuMEg0NlltVG05WDRTVXBQX0NVUVF2OTBwUmdzbnZrSVFLOEZNRHhYOGpBbnEzOUR3bVVsa0tUSUN5QnY0SU1VQjZKZmxTRjNsa1hEOERZS0NOb0JLVUhBZFpJTTllYVRCSFl5UWd5YU5SMmhKNVc2c1JjWjI2TWNWOC1GLU1tMmZLQWxuV3ZQc3htOFJMOTdoS0lnYXJrQ0Q3ZWRXd2xiYkthNlVhbnpHeUhwdWxmRGRpRnRQdUt3dWg3TG1jNFFlQVVUd1NnQXRMb3VsYTdqREVWaDduNXpJTW1uVG1KdmdZMVQ4a3NHU2FOcUtaM1o4ejVXenZnZ9IBmAJBVV95cUxONDA1NE9nWi12SkMxc25IRFNrbllTYlNiV2ZaNUUxbXpWdVYyS19FZFJVdWlSWmF3NkU5SVpiZGtzRHdNVFpyblRnU09EajVWMHd3OHBLTTVfWl9zLXJhOXpYRXhkUi1hajdBalNhZ3djdDJCcU10UVU0eUNwX3Y4TmpTMjllT2ltWWE4NVpVVkxVTU53YV8wN1lOaC1NN1I4c2JXVWl2ME4zVmNobmdzV3FvQTgtdUdYYm1DcDVoNzhIQU1oUjluYnVDN1NyVjZBVmMxUjhZZXUySnhRc0dBWFctTi11SXNmVjNvUW1SeFo0MkpHTW56V0dFWjdHQmx2MDBhVTZtTC1Lc2R1U0IxMU8yd25HbnJn?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1100" t="inlineStr">
+        <is>
+          <t>ELTIEMPO.COM</t>
+        </is>
+      </c>
+      <c r="D1100" t="inlineStr"/>
+      <c r="E1100" t="inlineStr"/>
+      <c r="F1100" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1100" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1100" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1100" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1100" t="n">
+        <v>21</v>
+      </c>
+      <c r="K1100" t="inlineStr">
+        <is>
+          <t>terror</t>
+        </is>
+      </c>
+      <c r="L1100" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1100" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1100" t="inlineStr">
+        <is>
+          <t>terror</t>
+        </is>
+      </c>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar rechaza hechos que dejaron niños heridos por explosivo en Nariño</t>
+        </is>
+      </c>
+      <c r="B1101" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMitwFBVV95cUxPY3FmZzk3dl9waGFQVHlubXpUazRWc1lZd1l2d3hMUm4tTERXRHZBaGlZbndnYmRWMTItS0daTlhpUHVTRVNidFpPeGFYc3d5ZFhkeUdYT1JyeDFwTk41QjRmLTdzTTVxRU9Pd3hHTzRXaElVUkJtbENaQkl5WDFQS2RlU2owNUg3T0ZaRnMzVzRTNHEwZF95ZFQ2T2FXaDVrWDNaVHBUcUhGazNKYmZOUnNtVGQ0bGc?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1101" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1101" t="inlineStr"/>
+      <c r="E1101" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="F1101" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1101" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1101" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1101" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1101" t="n">
+        <v>21</v>
+      </c>
+      <c r="K1101" t="inlineStr">
+        <is>
+          <t>rechaza</t>
+        </is>
+      </c>
+      <c r="L1101" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1101" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N1101" t="inlineStr">
+        <is>
+          <t>rejects</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1101"/>
+  <dimension ref="A1:N1102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61656,6 +61656,64 @@
         </is>
       </c>
     </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar promueve la participación de niñas, niños y adolescentes en La Guajira con la primera Mesa de Participación 2026 | Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="B1102" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivgFBVV95cUxPX1YyN1NnclNWOWpQT0E2dmYybDFLWjlUbV9LX0oyYXN6WDQ1ZElITlFBZEFSakUyT3pVd3k5Z29aVTVSQmthY2tEeTdHSG9MS01za0FGYy13bWVHR3locXFTX2ZwRU54ZFlmbVo2ekd5akxtTC13VEt4Q3JEZDk4cnAtc3FEY1NkSmI5aHlxX0pacl94OWN0a3FFTHdQWkNUWHdtUkN4WWpVOUxjQUs3SWxGdDJWenlIdEZxaUN3?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1102" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1102" t="inlineStr"/>
+      <c r="E1102" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="F1102" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1102" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1102" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1102" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J1102" t="n">
+        <v>22</v>
+      </c>
+      <c r="K1102" t="inlineStr">
+        <is>
+          <t>promueve</t>
+        </is>
+      </c>
+      <c r="L1102" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1102" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1102" t="inlineStr">
+        <is>
+          <t>promotes</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1102"/>
+  <dimension ref="A1:N1104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61714,6 +61714,126 @@
         </is>
       </c>
     </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar promueve la participación de niñas, niños y adolescentes en La Guajira con la primera Mesa de Participación 2026</t>
+        </is>
+      </c>
+      <c r="B1103" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivgFBVV95cUxPX1YyN1NnclNWOWpQT0E2dmYybDFLWjlUbV9LX0oyYXN6WDQ1ZElITlFBZEFSakUyT3pVd3k5Z29aVTVSQmthY2tEeTdHSG9MS01za0FGYy13bWVHR3locXFTX2ZwRU54ZFlmbVo2ekd5akxtTC13VEt4Q3JEZDk4cnAtc3FEY1NkSmI5aHlxX0pacl94OWN0a3FFTHdQWkNUWHdtUkN4WWpVOUxjQUs3SWxGdDJWenlIdEZxaUN3?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1103" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1103" t="inlineStr"/>
+      <c r="E1103" t="inlineStr">
+        <is>
+          <t>La Guajira</t>
+        </is>
+      </c>
+      <c r="F1103" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1103" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1103" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1103" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J1103" t="n">
+        <v>22</v>
+      </c>
+      <c r="K1103" t="inlineStr">
+        <is>
+          <t>promueve</t>
+        </is>
+      </c>
+      <c r="L1103" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1103" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1103" t="inlineStr">
+        <is>
+          <t>promotes</t>
+        </is>
+      </c>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>En Arauca se fortalece la atención y protección de la niñez y adolescencia</t>
+        </is>
+      </c>
+      <c r="B1104" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiqwFBVV95cUxQTjBkZHFwVFVVb3lHazh6ZmxHN3lHUDlWYVpsYkFkaDdXaHBDTDBHbDYzQ0tXQkFxT2pSUDVYLTROUS1FTTFGcnlVSGxscEk4bDBuZDlzR1pCY0RUeDNGVUZnVWkyZ0VVWk5hWlkwSVFwbVhWTklqUUljaHE5QkdMQ0pSczZianFFS3N6cGUwLUYwZmxIUUY3OVN6N21ZUkJpeENFZG5XaDlhVFE?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1104" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1104" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="E1104" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="F1104" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1104" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1104" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1104" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J1104" t="n">
+        <v>22</v>
+      </c>
+      <c r="K1104" t="inlineStr">
+        <is>
+          <t>fortalece</t>
+        </is>
+      </c>
+      <c r="L1104" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1104" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1104" t="inlineStr">
+        <is>
+          <t>strengthens</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1104"/>
+  <dimension ref="A1:N1107"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61834,6 +61834,168 @@
         </is>
       </c>
     </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>Revelan amenazas previas al crimen de Karelis Merlano, cuidadora del ICBF en Barrancabermeja que habría sido asesinada por menores: 'Noche de terror'</t>
+        </is>
+      </c>
+      <c r="B1105" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMilgJBVV95cUxQai0xdTJ6amV5ZjJVR29STmdUM3YxdU4tR3ByVWM4NGQyX3EzR1pZbU9EdC1VcTZSSm5za0gwZ2kyd3pFbU1OVDMxeWViQUhXd3lXMEdWMVpUc2JzdUt5M3RCZUZIbTEwc09OVW1LUE1mQkVydHpaUFViYy1VcEM4VUtVSHFuNndGTE5tV2szQ0ZSalJPQmdOWmpFUHl1b29tNklRa3hpLXRfOXh3TWVpSnRfT0FuZldaYWM4d29jcUx2b0F2YTdBX1Z5N29uTUpNVXFsd0Y4OWJpSExIRHBuczFyYTBEM0p6aWcyS2RmcG4zSUo1eWYtc3Awcm8wVzI5WGYtUmNoNUhEd2NMN0wyU1hMYkdLZ9IBmwJBVV95cUxPSC1aV2taMG5Yc0RvSE01Tlh1SnNCUGFZblF1X1FhWnRWNFRhYTZ5bExKTk5yNVNYeFNlQTVHcm9NX1h5ZDZRcTVBVnozZnVkdHFjbnBLcDF6YmEtdGpGNkNnWmd1MlJsNVZUOVdxSG8yTVpMS1llSU1lSnZVMENnbGRmSUVTWFdFWWFRdWFxYUZPYm9JZjQyX2pnTEppY1k3YnhTT3VDeEQ3bnFYUHptYjBwUnJfdjdCUEhOSFV3Qzl4c0Y4OFJpV3d4cks2cUk0bHlRbl9UWm14MnV3VFFaVGRzOEhzelBkUTByV09ndG1sLXo2X0dTYmpENmZOdGJLcldEbHFvMlpLM2UxR2k4RUVhUGtLa0JCa2tR?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1105" t="inlineStr">
+        <is>
+          <t>ELTIEMPO.COM</t>
+        </is>
+      </c>
+      <c r="D1105" t="inlineStr"/>
+      <c r="E1105" t="inlineStr"/>
+      <c r="F1105" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1105" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1105" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1105" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1105" t="n">
+        <v>21</v>
+      </c>
+      <c r="K1105" t="inlineStr">
+        <is>
+          <t>amenazas</t>
+        </is>
+      </c>
+      <c r="L1105" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1105" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1105" t="inlineStr">
+        <is>
+          <t>threats</t>
+        </is>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>Revelan amenazas previas al crimen de Karelis Merlano, cuidadora del ICBF en Barrancabermeja que habría sido asesinada por menores: 'Noche de terror'</t>
+        </is>
+      </c>
+      <c r="B1106" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMilgJBVV95cUxQai0xdTJ6amV5ZjJVR29STmdUM3YxdU4tR3ByVWM4NGQyX3EzR1pZbU9EdC1VcTZSSm5za0gwZ2kyd3pFbU1OVDMxeWViQUhXd3lXMEdWMVpUc2JzdUt5M3RCZUZIbTEwc09OVW1LUE1mQkVydHpaUFViYy1VcEM4VUtVSHFuNndGTE5tV2szQ0ZSalJPQmdOWmpFUHl1b29tNklRa3hpLXRfOXh3TWVpSnRfT0FuZldaYWM4d29jcUx2b0F2YTdBX1Z5N29uTUpNVXFsd0Y4OWJpSExIRHBuczFyYTBEM0p6aWcyS2RmcG4zSUo1eWYtc3Awcm8wVzI5WGYtUmNoNUhEd2NMN0wyU1hMYkdLZ9IBmwJBVV95cUxPSC1aV2taMG5Yc0RvSE01Tlh1SnNCUGFZblF1X1FhWnRWNFRhYTZ5bExKTk5yNVNYeFNlQTVHcm9NX1h5ZDZRcTVBVnozZnVkdHFjbnBLcDF6YmEtdGpGNkNnWmd1MlJsNVZUOVdxSG8yTVpMS1llSU1lSnZVMENnbGRmSUVTWFdFWWFRdWFxYUZPYm9JZjQyX2pnTEppY1k3YnhTT3VDeEQ3bnFYUHptYjBwUnJfdjdCUEhOSFV3Qzl4c0Y4OFJpV3d4cks2cUk0bHlRbl9UWm14MnV3VFFaVGRzOEhzelBkUTByV09ndG1sLXo2X0dTYmpENmZOdGJLcldEbHFvMlpLM2UxR2k4RUVhUGtLa0JCa2tR?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1106" t="inlineStr">
+        <is>
+          <t>ELTIEMPO.COM</t>
+        </is>
+      </c>
+      <c r="D1106" t="inlineStr"/>
+      <c r="E1106" t="inlineStr"/>
+      <c r="F1106" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1106" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1106" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1106" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1106" t="n">
+        <v>21</v>
+      </c>
+      <c r="K1106" t="inlineStr">
+        <is>
+          <t>crimen</t>
+        </is>
+      </c>
+      <c r="L1106" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1106" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1106" t="inlineStr">
+        <is>
+          <t>crime</t>
+        </is>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>Revelan amenazas previas al crimen de Karelis Merlano, cuidadora del ICBF en Barrancabermeja que habría sido asesinada por menores: 'Noche de terror'</t>
+        </is>
+      </c>
+      <c r="B1107" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMilgJBVV95cUxQai0xdTJ6amV5ZjJVR29STmdUM3YxdU4tR3ByVWM4NGQyX3EzR1pZbU9EdC1VcTZSSm5za0gwZ2kyd3pFbU1OVDMxeWViQUhXd3lXMEdWMVpUc2JzdUt5M3RCZUZIbTEwc09OVW1LUE1mQkVydHpaUFViYy1VcEM4VUtVSHFuNndGTE5tV2szQ0ZSalJPQmdOWmpFUHl1b29tNklRa3hpLXRfOXh3TWVpSnRfT0FuZldaYWM4d29jcUx2b0F2YTdBX1Z5N29uTUpNVXFsd0Y4OWJpSExIRHBuczFyYTBEM0p6aWcyS2RmcG4zSUo1eWYtc3Awcm8wVzI5WGYtUmNoNUhEd2NMN0wyU1hMYkdLZ9IBmwJBVV95cUxPSC1aV2taMG5Yc0RvSE01Tlh1SnNCUGFZblF1X1FhWnRWNFRhYTZ5bExKTk5yNVNYeFNlQTVHcm9NX1h5ZDZRcTVBVnozZnVkdHFjbnBLcDF6YmEtdGpGNkNnWmd1MlJsNVZUOVdxSG8yTVpMS1llSU1lSnZVMENnbGRmSUVTWFdFWWFRdWFxYUZPYm9JZjQyX2pnTEppY1k3YnhTT3VDeEQ3bnFYUHptYjBwUnJfdjdCUEhOSFV3Qzl4c0Y4OFJpV3d4cks2cUk0bHlRbl9UWm14MnV3VFFaVGRzOEhzelBkUTByV09ndG1sLXo2X0dTYmpENmZOdGJLcldEbHFvMlpLM2UxR2k4RUVhUGtLa0JCa2tR?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1107" t="inlineStr">
+        <is>
+          <t>ELTIEMPO.COM</t>
+        </is>
+      </c>
+      <c r="D1107" t="inlineStr"/>
+      <c r="E1107" t="inlineStr"/>
+      <c r="F1107" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1107" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1107" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1107" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1107" t="n">
+        <v>21</v>
+      </c>
+      <c r="K1107" t="inlineStr">
+        <is>
+          <t>terror</t>
+        </is>
+      </c>
+      <c r="L1107" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1107" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1107" t="inlineStr">
+        <is>
+          <t>terror</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1107"/>
+  <dimension ref="A1:N1108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -61996,6 +61996,60 @@
         </is>
       </c>
     </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>MinHacienda propone aumentar el presupuesto de 2026 en medio billón de pesos por cuenta de mayores ingresos</t>
+        </is>
+      </c>
+      <c r="B1108" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi1gFBVV95cUxNQnBMQkhWbkhBcEhCRVdiOV9DQTZKYmVTY25GOEsyZ01OTTRRYnNSZUNVZkoyT2ZhUHVjWlNSazZMVlRIQ1NBUVpsOVdOd0xPaTJ1VzRtY1E1cTM4N2RoZm9QXzZiRTE4TkFnT1lXZ1Z1alJ0N0FVSEdHVlZjaEJoRmlqSmM1ZTZBTGg0R0djTE1fMDQwVzF6UjQ0VmVDMEQ4RXNEZ0c1WjdEdUthdDdyZFRiZHlucHBYUy0waFJST09MRXN2YjJlODJqdDI3UzZldmd3ZUlR0gHbAUFVX3lxTFBKQ0ZNX3dKZjhWM2xBSmlNMEM4NE5rTTZCajc2cnJXMVR1Nk9IaVlFcHpZZk9jM1lPVUUyRTlZcWNpMUNPbDcwbEpBVmM4UC1neHU4M205YWhhZ0hiX3FIektsc3BrZE9KY1NXa1lIcEdGZmJlSGpCZDNpSHVPX0RGRjFKZGVwc0o1cjhvamd0aW5CRGtNdDVLM0puOFA3MGdYYVJHaGFkVTI4d1J3Ty1vQXVMYmRfenl1Q2RzTlhRZjM2aHExdjc1TTRSOW95OTRPTzlXRWVFWVNSUQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1108" t="inlineStr">
+        <is>
+          <t>Valora Analitik</t>
+        </is>
+      </c>
+      <c r="D1108" t="inlineStr"/>
+      <c r="E1108" t="inlineStr"/>
+      <c r="F1108" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1108" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1108" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1108" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1108" t="n">
+        <v>27</v>
+      </c>
+      <c r="K1108" t="inlineStr">
+        <is>
+          <t>aumentar</t>
+        </is>
+      </c>
+      <c r="L1108" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1108" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1108" t="inlineStr">
+        <is>
+          <t>boost</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1108"/>
+  <dimension ref="A1:N1109"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62050,6 +62050,68 @@
         </is>
       </c>
     </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>48 niñas, niños y adolescentes fueron focalizados en Arauca en acciones de prevención del trabajo infantil</t>
+        </is>
+      </c>
+      <c r="B1109" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivgFBVV95cUxOS281X05TU2pEc1E5dHNlSlN3QXA5ZXRSLU5nVjJwUXN0Y2dnWHE3VUdZUkFkd1JFNTFYNWZzdjltTm1qR1hYbEpRZFNnOXVWdkhmeVBCSFZ2cGN0U2RZVmhneEpvT0NucC1GdXdNOWhHd0ZQNGFCaUtCVjZoU0lydjRZX2VaUFRxakNzdGtEcHVFcDk0TXI5VWhQVG5tMzRWbjlqYVNNdmYybTZJcWFfcmZRT185M0VWNkVhb2pR?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1109" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1109" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="E1109" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="F1109" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1109" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1109" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1109" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1109" t="n">
+        <v>27</v>
+      </c>
+      <c r="K1109" t="inlineStr">
+        <is>
+          <t>infantil</t>
+        </is>
+      </c>
+      <c r="L1109" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1109" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1109" t="inlineStr">
+        <is>
+          <t>childish</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1109"/>
+  <dimension ref="A1:N1110"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62112,6 +62112,64 @@
         </is>
       </c>
     </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>Tolima ya tiene un modelo propio que rescata sus raíces indígenas gracias al Bienestar Familiar</t>
+        </is>
+      </c>
+      <c r="B1110" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiuwFBVV95cUxPWVZqUzFwbThUMVc1UDRPNDhoRUJRNmFrSk1RRXZyOXNhbXkwWUNuUVZ2b21vTWZGcG51clVLNXVaaTBWQmU5TW9yMk1FWjRsMTJMbXVqNk1QLTVjbmhxUEhUS1hGNExucDlLQzhYUU16ejJJRVRqbWF2XzhwaDhDckhHLWhSYmpHUEExdFc0QWloTFlXT0dFNzlRUWlPMjhPbENIZVNndTVBQkpKaTQwVzV5R2ZGeU4yMi1N?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1110" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1110" t="inlineStr"/>
+      <c r="E1110" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="F1110" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1110" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1110" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1110" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1110" t="n">
+        <v>28</v>
+      </c>
+      <c r="K1110" t="inlineStr">
+        <is>
+          <t>gracias</t>
+        </is>
+      </c>
+      <c r="L1110" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1110" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1110" t="inlineStr">
+        <is>
+          <t>thank</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1110"/>
+  <dimension ref="A1:N1111"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62170,6 +62170,64 @@
         </is>
       </c>
     </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar avanza en la garantía de la alimentación de la niñez en Quindío a través de compras locales</t>
+        </is>
+      </c>
+      <c r="B1111" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivwFBVV95cUxOZlRFUGRXeU1KNGEtdW14Ti1Bc1hQNGdYd09BNlJ2dDNyUHBiQ0J4VWVCOHItd3h4WmprbEJsZ0xTSUhTajNRY2Q4YzRaOUxCNm5NWTRscDd0STlxajQxSWNLakZpWWVjYTNqaHhWV3hLN05LTzNJVnhTM1VwY3d3ZFhKNjhlTHQ0ZVhlcmVJZG9HNnlKTmZlVWZMc21wampSOFV6ZHkxU2tpa0lDNXd1SmRLb0VibUQ2SXhpQVpNNA?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1111" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1111" t="inlineStr"/>
+      <c r="E1111" t="inlineStr">
+        <is>
+          <t>Quindío</t>
+        </is>
+      </c>
+      <c r="F1111" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1111" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1111" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1111" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1111" t="n">
+        <v>28</v>
+      </c>
+      <c r="K1111" t="inlineStr">
+        <is>
+          <t>garantía</t>
+        </is>
+      </c>
+      <c r="L1111" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1111" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1111" t="inlineStr">
+        <is>
+          <t>guarantee</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1111"/>
+  <dimension ref="A1:N1113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62228,6 +62228,114 @@
         </is>
       </c>
     </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>ICBF asegura que han recibido 7 menores desvinculados de filas del Clan del Golfo</t>
+        </is>
+      </c>
+      <c r="B1112" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiugFBVV95cUxPcVc4NkFOYW9nS2dKVnBPcWlNYnpSMjZ6dVdLemlmaXRsZElnMU8yUGxGOUhqV1hpa3NmU0Fsempoa0dHUnN3STc0d0NiT1ktRDRiTHNZZkxFZmlYY3BncTZNSGVwZmJ2ODFRek50QjNkcjB4UmkwZy05V21uM1hiVnlnR0tOc3RWcGYtNkJlQ0V3MXNrRUVMZ055NUdua1dOT05VSl9XaW1lOHR2QkNqVkE0U2F1cVhwU0E?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1112" t="inlineStr">
+        <is>
+          <t>Blu Radio</t>
+        </is>
+      </c>
+      <c r="D1112" t="inlineStr"/>
+      <c r="E1112" t="inlineStr"/>
+      <c r="F1112" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1112" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1112" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1112" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J1112" t="n">
+        <v>29</v>
+      </c>
+      <c r="K1112" t="inlineStr">
+        <is>
+          <t>asegura</t>
+        </is>
+      </c>
+      <c r="L1112" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1112" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1112" t="inlineStr">
+        <is>
+          <t>secures</t>
+        </is>
+      </c>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar llevó a la FILBo espacios para hablar de paz, prevención y protección de la niñez</t>
+        </is>
+      </c>
+      <c r="B1113" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivgFBVV95cUxPZ0JqeEJuNFJrWGx0YkQyemJVdWdQaXoxR1hPekVXcGpUY2I0ZmRYUGc0Ti15d3VQZk9vNWpvZ0daWUEtVVQydW51eHFWaFYyXzNDNzI5TjhyR1VqUTdUaVlwd2tNT01FTGdPZms1NUJSZVZ4OWNBVnk5QlZ4RjQ4VG9uY2htc1BhUkRqemJUVVd3dGRIUXcxaThJNlJsRTl4TkF1TWJIY1RtM0t0SzhkUU9pQ0VWTGp6UVktZE1B?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1113" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1113" t="inlineStr"/>
+      <c r="E1113" t="inlineStr"/>
+      <c r="F1113" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1113" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1113" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1113" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J1113" t="n">
+        <v>29</v>
+      </c>
+      <c r="K1113" t="inlineStr">
+        <is>
+          <t>paz</t>
+        </is>
+      </c>
+      <c r="L1113" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1113" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1113" t="inlineStr">
+        <is>
+          <t>peace</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1113"/>
+  <dimension ref="A1:N1115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62336,6 +62336,118 @@
         </is>
       </c>
     </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>Más de 600 madres y ex madres comunitarias avanzan hacia su pensión en Bogotá gracias a jornada del Bienestar Familiar y Colpensiones | Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="B1114" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiugFBVV95cUxOMXBRUlZrb2NBYmlZeVlBUmgyX1A0ZVVXbGtzVU9lXzNEc1pNNTVEQ3dJb0dVOWQzM29aU2hMRjFRNy03TU5QeXdBNk9fTzRrb0JLOVNZOVJERnhMYTZLeDBYNUMtbi11UXhpQm9pTEVtQTdrQVYzSE5fX1lWS05oTGwxTUpyZUpSSGRBQy1IZ2ZYSW9UdWNseVYxSGpRUmt0ZTdXLVJCdG5uNzVKUk5MUGhmVWl2dDg2OXc?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1114" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1114" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E1114" t="inlineStr"/>
+      <c r="F1114" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1114" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1114" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1114" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J1114" t="n">
+        <v>29</v>
+      </c>
+      <c r="K1114" t="inlineStr">
+        <is>
+          <t>gracias</t>
+        </is>
+      </c>
+      <c r="L1114" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1114" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1114" t="inlineStr">
+        <is>
+          <t>thank</t>
+        </is>
+      </c>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>ICBF refuerza monitoreo del pacto por la paz en Buenaventura</t>
+        </is>
+      </c>
+      <c r="B1115" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMinwFBVV95cUxPeTZFWnZoM1U5dnRwY2ZGYWRRM0RlM0FoWXBkQ2Z0aTlwa0NzNFlvcnA5OTFQWWRXQ201WkRnTFU4cTNFOE5HelpHMk05VDAyUnVYWi1VZzQzQWNZREhvZXRsZk83ajVId0wtdk1kM0J4eXBSUDNwOUZSNmY5cmg3LTRZdzMwVVBQZ0FKSU44Skh1bjFwaUdUbFQxcE1IbnPSAbMBQVVfeXFMTUVzOW9MRDh4NUdQblRqejVlMDlkWko2eDZQT0JBOC1VWFRfUHFOMmZyOV8tSHlHemJyNVVuMXRCVU0wam1PZ0tPcDRNVE9DWkpxMGx2VXdyc3kwTndkNHJFVlhoenk3eXk5S3FDLUNPY09uOHhTdWZoaVJNTlg2dkhiZHY4SEQtZFc5cnJUWGpUR1hwdEdSdW4yeXYxRXRBX05VcVFHeEpxUFhLNmhIcEN6VmM?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1115" t="inlineStr">
+        <is>
+          <t>WRadio</t>
+        </is>
+      </c>
+      <c r="D1115" t="inlineStr"/>
+      <c r="E1115" t="inlineStr"/>
+      <c r="F1115" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1115" t="n">
+        <v>2025</v>
+      </c>
+      <c r="H1115" t="n">
+        <v>7</v>
+      </c>
+      <c r="I1115" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J1115" t="n">
+        <v>25</v>
+      </c>
+      <c r="K1115" t="inlineStr">
+        <is>
+          <t>paz</t>
+        </is>
+      </c>
+      <c r="L1115" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1115" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1115" t="inlineStr">
+        <is>
+          <t>peace</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1115"/>
+  <dimension ref="A1:N1119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62448,6 +62448,234 @@
         </is>
       </c>
     </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>Indígenas embera usaron a sus niños como ‘escudos humanos’ en Bogotá y la directora del Icbf anunció acciones legales: “Es un delito”</t>
+        </is>
+      </c>
+      <c r="B1116" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMigwJBVV95cUxOYmVxaVJmYW93WGFfWl93eGszbmlpY1R4b2ZwLVBjT2IwZnBZYmFYbWVVV3FBNkFZSEs0anFWM0pXOVVkU2lBX2xYcFR1bTZUTFZqUDN3Q2VIMHNqalkxbU9WQzhkeWMtTGtJYmRhTU81b25WLVpicWxRb2xDQVZjb2lGR0NaalllMUQ5NTlPZUVmM2pSUXgtRWZIR1lOR2I5NVpMdG5QSC12dXdOd0pYLVgtWF9HRDEwbFllUVBxZHdvT2VoaGFMWEExSzFmYjJZcm9OajdFWUdMZnRNbWNGdjN4SWh1d2JKRWVqQmFBSDIyOFdTcUZIekFFdFI4RTh2NG840gGeAkFVX3lxTE5JYmFaRHJVenkzc1VZSEZqWmM3M0dyVWJNMENYNXcyekZ0ZkltcnhvUjJmVGJHZ1FwMnN3Z1djcGdSckpDT0l5Um1rR1Z1cmJ1WE10dTlKSEljeXZrQ1kzWXdYYmZtRG5JU3Myak9oNnBHUGxmcWlKVk4xVUQ4akZDNkRESlRXNWFJZjhGaU9TZUZMVnptdV9ySVN5S29jMFVjNmE3cm81T0l3ZFJfTmpMUlh0d3I1NHVyTDZ0WmlsVTJfc1RjQkFmcl9SRHJSWC1HWDRqeDhJWUFYLUZzZEh6NTltbVBoQVo0SnNsTWRjb1ZVU3ZNM2RLSE1EcC1NZ2ctZVhoWVZCX1VzNVpIWmZlOVRQZkppSTVUUGN1OWc?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1116" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D1116" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E1116" t="inlineStr"/>
+      <c r="F1116" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1116" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1116" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1116" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1116" t="n">
+        <v>30</v>
+      </c>
+      <c r="K1116" t="inlineStr">
+        <is>
+          <t>delito</t>
+        </is>
+      </c>
+      <c r="L1116" t="inlineStr">
+        <is>
+          <t>Astrid Cáceres</t>
+        </is>
+      </c>
+      <c r="M1116" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1116" t="inlineStr">
+        <is>
+          <t>felony</t>
+        </is>
+      </c>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>Presidente Gustavo Petro y directora del ICBF rechazan uso de niños embera como escudos humanos en protestas en sede del MinInterior: 'No lo admito'</t>
+        </is>
+      </c>
+      <c r="B1117" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiogJBVV95cUxNd1NpYkpJZlNoTlVfQmVwN1k4TVlRR2ZYV3YtSFlXTEc1SDNZNjZpbXVvOHFQb0NYenZFNjR1Y0NMN1hwRjdVeS12X3h4UG5aWlFPMVAzbk02Nk9Cc2RkYlNNSTJKal9PTHJkWUptdThIWW53S2ZtZlVCNFpQbU5YTkQ2bUxjR0U5eG9wSWFvVHdZa0o4WEFabUhPU0RVUGZYWnUySjNLUUJhYWNiOHdJMWx3YjlfRXdIbmFNVEl6UVRVbVFidUZKWTNBWnlSaUJxS28yLTk3RFZGY042TjNMLTJrTXBuR3U0ckxKdWRLNnR4SkM1ei04NENqeDgtaDlING9QNU1iYURXUUs5WVJyUTVSNFZPTTdIRUlHQl9fd1dHUdIBpwJBVV95cUxPakdnMmN1Rk9Zc0owRnB0aG1qa3pYMUNzZVF5amRNS3gzUEdmNkJFODFKalZ0LWRnNm5xZm5EdHVRblB1ejlxajYxd1NXWDlXbUZwZ3VNeHB3YmZadnNmQTUtQ0lRSDJwQVFnaEFOT1dkdWotV29XcmtjUnZsQmc0NW1jNm5ZTjllUjVLTHJ4LUh5STdFQW0tSDJTSDQ0cnl6VGMxdnB1a0JSYS1yVHJzZzhaMWNvSUp3bEFwLWg1TlNNQUtwdGJGdmxTOXd5SmQ0eUdVUGhyVDdrYlFYVkdTeVV5cHFoWlVQTnItZmM3clcxS2U1Qjk4SkNLclJIZWJTc3ZReVJTcThTZFhnblA4MGpYdWh5dTFKY1BHZXVBV2NTVm5QYklr?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1117" t="inlineStr">
+        <is>
+          <t>ELTIEMPO.COM</t>
+        </is>
+      </c>
+      <c r="D1117" t="inlineStr"/>
+      <c r="E1117" t="inlineStr"/>
+      <c r="F1117" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1117" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1117" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1117" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1117" t="n">
+        <v>30</v>
+      </c>
+      <c r="K1117" t="inlineStr">
+        <is>
+          <t>protestas</t>
+        </is>
+      </c>
+      <c r="L1117" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1117" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1117" t="inlineStr">
+        <is>
+          <t>protests</t>
+        </is>
+      </c>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>Uso de menores en protestas en Bogotá desata rechazo y acciones legales del ICBF; Petro se pronunció</t>
+        </is>
+      </c>
+      <c r="B1118" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi3AFBVV95cUxQRS16VF9leElTV2JQUFR6cE9BMTF0MXpCOFhIMzZkQ1puOHpIMkwwMWJDVmhnUWNZSEJUMVZJMGVlbmVrSzFKLUNZZ25xUUlheUUzdkRRZzQ0Y01qMG5EYlJNamRyYzUzbm1maHFSdXY5cVZaeTd3VjlCNWNHbTNuU0hucmpGTWFuSkgzSnUwWTFlSmVZVnN0ajh2M3k4UkEtSXZLLWFwZnRKeWkyT2tONzd1OXlscmRaekdxQVhSS1pOR21EckJBTDZpa0twbWlVVEx5VFA2c2xtdU5W0gHiAUFVX3lxTE9SWWYxbFZ4aWhJUE9RMGR1czc4WXZDX1pxdjdEc1gtcW55RzRjMkVwWU1yWm1mN3B1Vml1S3lyNzFqVVYwWThqdmpfWVplT0N2NjVTd0lkRHE4NnJOMk1XNG5uRWdWZ1V4RTlHN0xvQVl2dmRZcUtydVk2aFROc01ZSlotQXM5ZmhtSVJZWDF4NFBJTl9remZ2Qjlha2NqdFZhWlA5SjZtZmZNbnlFSDNQcmtZR3YxQko1VklRaklCTkRBUVdiX1VIaHcxeG50eEM5ZW1kWU03aWFJT21QTlBZWnc?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1118" t="inlineStr">
+        <is>
+          <t>elpais.com.co</t>
+        </is>
+      </c>
+      <c r="D1118" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E1118" t="inlineStr"/>
+      <c r="F1118" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1118" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1118" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1118" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1118" t="n">
+        <v>30</v>
+      </c>
+      <c r="K1118" t="inlineStr">
+        <is>
+          <t>protestas</t>
+        </is>
+      </c>
+      <c r="L1118" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1118" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1118" t="inlineStr">
+        <is>
+          <t>protests</t>
+        </is>
+      </c>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>Más de 600 madres y ex madres comunitarias avanzan hacia su pensión en Bogotá gracias a jornada del Bienestar Familiar y Colpensiones</t>
+        </is>
+      </c>
+      <c r="B1119" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiugFBVV95cUxOMXBRUlZrb2NBYmlZeVlBUmgyX1A0ZVVXbGtzVU9lXzNEc1pNNTVEQ3dJb0dVOWQzM29aU2hMRjFRNy03TU5QeXdBNk9fTzRrb0JLOVNZOVJERnhMYTZLeDBYNUMtbi11UXhpQm9pTEVtQTdrQVYzSE5fX1lWS05oTGwxTUpyZUpSSGRBQy1IZ2ZYSW9UdWNseVYxSGpRUmt0ZTdXLVJCdG5uNzVKUk5MUGhmVWl2dDg2OXc?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1119" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1119" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E1119" t="inlineStr"/>
+      <c r="F1119" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1119" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1119" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1119" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J1119" t="n">
+        <v>29</v>
+      </c>
+      <c r="K1119" t="inlineStr">
+        <is>
+          <t>gracias</t>
+        </is>
+      </c>
+      <c r="L1119" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1119" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1119" t="inlineStr">
+        <is>
+          <t>thank</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1119"/>
+  <dimension ref="A1:N1126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -62676,6 +62676,412 @@
         </is>
       </c>
     </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar rechaza la exposición de niñas y niños en situaciones de riesgo y confrontación, y denuncia penalmente los hechos ocurridos en Bogotá | Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="B1120" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiuAFBVV95cUxObGJROE5UalBCYl95bUhoOFcyWG1EYm9DdDgzc05uUXNXY2k1SnpNcVVtVHdyMzJsdE9XaG9BSVpKcmNYcEV2SEJpTFNyRVg4c1pGYU4yWkV5WDQ1ZGhmOENZa3JRZGRQYlFKRm51WC0xSzV2QzVyeVZub0RTUVJ0NjRpNG84dkU0TDhoSEJ3OHYzT3psSWRRZGZHVmZoZG40UW1TeXVPR0Ffd1NDdm1PRVhmc2E2Z1dD?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1120" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1120" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E1120" t="inlineStr"/>
+      <c r="F1120" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1120" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1120" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1120" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1120" t="n">
+        <v>30</v>
+      </c>
+      <c r="K1120" t="inlineStr">
+        <is>
+          <t>rechaza</t>
+        </is>
+      </c>
+      <c r="L1120" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1120" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N1120" t="inlineStr">
+        <is>
+          <t>rejects</t>
+        </is>
+      </c>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar rechaza la exposición de niñas y niños en situaciones de riesgo y confrontación, y denuncia penalmente los hechos ocurridos en Bogotá | Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="B1121" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiuAFBVV95cUxObGJROE5UalBCYl95bUhoOFcyWG1EYm9DdDgzc05uUXNXY2k1SnpNcVVtVHdyMzJsdE9XaG9BSVpKcmNYcEV2SEJpTFNyRVg4c1pGYU4yWkV5WDQ1ZGhmOENZa3JRZGRQYlFKRm51WC0xSzV2QzVyeVZub0RTUVJ0NjRpNG84dkU0TDhoSEJ3OHYzT3psSWRRZGZHVmZoZG40UW1TeXVPR0Ffd1NDdm1PRVhmc2E2Z1dD?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1121" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1121" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E1121" t="inlineStr"/>
+      <c r="F1121" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1121" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1121" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1121" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1121" t="n">
+        <v>30</v>
+      </c>
+      <c r="K1121" t="inlineStr">
+        <is>
+          <t>exposición</t>
+        </is>
+      </c>
+      <c r="L1121" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1121" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N1121" t="inlineStr">
+        <is>
+          <t>exposing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar rechaza la exposición de niñas y niños en situaciones de riesgo y confrontación, y denuncia penalmente los hechos ocurridos en Bogotá | Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="B1122" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiuAFBVV95cUxObGJROE5UalBCYl95bUhoOFcyWG1EYm9DdDgzc05uUXNXY2k1SnpNcVVtVHdyMzJsdE9XaG9BSVpKcmNYcEV2SEJpTFNyRVg4c1pGYU4yWkV5WDQ1ZGhmOENZa3JRZGRQYlFKRm51WC0xSzV2QzVyeVZub0RTUVJ0NjRpNG84dkU0TDhoSEJ3OHYzT3psSWRRZGZHVmZoZG40UW1TeXVPR0Ffd1NDdm1PRVhmc2E2Z1dD?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1122" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1122" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E1122" t="inlineStr"/>
+      <c r="F1122" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1122" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1122" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1122" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1122" t="n">
+        <v>30</v>
+      </c>
+      <c r="K1122" t="inlineStr">
+        <is>
+          <t>riesgo</t>
+        </is>
+      </c>
+      <c r="L1122" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1122" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1122" t="inlineStr">
+        <is>
+          <t>risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar rechaza la exposición de niñas y niños en situaciones de riesgo y confrontación, y denuncia penalmente los hechos ocurridos en Bogotá | Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="B1123" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiuAFBVV95cUxObGJROE5UalBCYl95bUhoOFcyWG1EYm9DdDgzc05uUXNXY2k1SnpNcVVtVHdyMzJsdE9XaG9BSVpKcmNYcEV2SEJpTFNyRVg4c1pGYU4yWkV5WDQ1ZGhmOENZa3JRZGRQYlFKRm51WC0xSzV2QzVyeVZub0RTUVJ0NjRpNG84dkU0TDhoSEJ3OHYzT3psSWRRZGZHVmZoZG40UW1TeXVPR0Ffd1NDdm1PRVhmc2E2Z1dD?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1123" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1123" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E1123" t="inlineStr"/>
+      <c r="F1123" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1123" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1123" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1123" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1123" t="n">
+        <v>30</v>
+      </c>
+      <c r="K1123" t="inlineStr">
+        <is>
+          <t>denuncia</t>
+        </is>
+      </c>
+      <c r="L1123" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1123" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1123" t="inlineStr">
+        <is>
+          <t>denounces</t>
+        </is>
+      </c>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>Atlántico refuerza estrategias para prevenir criminalidad juvenil en el territorio</t>
+        </is>
+      </c>
+      <c r="B1124" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiyAFBVV95cUxQQjhkOVdjd0g5SE12RnVfWmZKeVY3WE9XTXJqQzZmLVh3TXlTN0VoUDdtTXpMVXN1ek0tVUpRVWFxY2JlMnZobGhuNHRjVC0xVWJxYVNmeDlTUDRHSThua3VVeUhtZlRjYm5vakVZTGM1SFp4OFJ5QnVBS3YzX2o2VTFqOWIwSjhPcjAzSzlick04ZDZIUGZXbTFveDVJQU1tbWlYOFlEMFc0NUdxT3FYZThQNVFsWUJid1F4anhwdW1OUjZYa3A1StIB4wFBVV95cUxQbl9RUHdzcmFlQ0daVVpKODdmQ201Zjd5ZEZPeXFTLWJxbUNTNm51UHBRLUpiV3owLW9XYXhsZm04OEZjbmJNbFJtdUk3Xzd2TUZ5NDlKRThISWlSNzNTTDlmc1FxMmNUSFY0YVZZLXVYS1daMXkyU3RfY2xOQmJvUlJkRXNnamVaQW1QWEpWMHY1ZUE0MUl4SXlXaDlTUGpjWVQxZmJWeE5zZm5RX2RjQk83RjUtZTBrVlBZZTZwMEowajd0Y0dYcDZEdXpDSFdQVGdNM2N0eEc1eWllOWhJUG1sNA?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1124" t="inlineStr">
+        <is>
+          <t>ELHERALDO.CO</t>
+        </is>
+      </c>
+      <c r="D1124" t="inlineStr"/>
+      <c r="E1124" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="F1124" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1124" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1124" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1124" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1124" t="n">
+        <v>30</v>
+      </c>
+      <c r="K1124" t="inlineStr">
+        <is>
+          <t>juvenil</t>
+        </is>
+      </c>
+      <c r="L1124" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1124" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1124" t="inlineStr">
+        <is>
+          <t>youthful</t>
+        </is>
+      </c>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>Gracias a operativo de fuerza pública y al ICBF, cinco menores son protegidos de reclutamiento en Caquetá</t>
+        </is>
+      </c>
+      <c r="B1125" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMizwFBVV95cUxPYll0ZVV1a2F1dU1acW80cFZsN3poOFJvTWVTUGFOWXlqQmFESm9YTVV4R3NFcUVpakN5MGRJWFZMbXQzTEhzMEF3Ukt6R0YycGFwX2tzSXRoeEdLRUJKcW5nbnJZOE5ZM2l0XzhsU3dINUZIS2FXMWg0d2pBTTYxeWxNNE1ocjREbGhjaUpxN3BmZVlRQkpnUThtQlU5aGx4ZzUyMGVzbjdzOTFDRmpCYTZDYjg4UXYxOVdvQ0JlZXpibUhxWW5OMWZwb3g5bjQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1125" t="inlineStr">
+        <is>
+          <t>presidencia.gov.co</t>
+        </is>
+      </c>
+      <c r="D1125" t="inlineStr"/>
+      <c r="E1125" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="F1125" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1125" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1125" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1125" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J1125" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1125" t="inlineStr">
+        <is>
+          <t>Gracias</t>
+        </is>
+      </c>
+      <c r="L1125" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1125" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1125" t="inlineStr">
+        <is>
+          <t>thanks</t>
+        </is>
+      </c>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>Gracias a operativo de fuerza pública y al ICBF, cinco menores son protegidos de reclutamiento en Caquetá</t>
+        </is>
+      </c>
+      <c r="B1126" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMizwFBVV95cUxPYll0ZVV1a2F1dU1acW80cFZsN3poOFJvTWVTUGFOWXlqQmFESm9YTVV4R3NFcUVpakN5MGRJWFZMbXQzTEhzMEF3Ukt6R0YycGFwX2tzSXRoeEdLRUJKcW5nbnJZOE5ZM2l0XzhsU3dINUZIS2FXMWg0d2pBTTYxeWxNNE1ocjREbGhjaUpxN3BmZVlRQkpnUThtQlU5aGx4ZzUyMGVzbjdzOTFDRmpCYTZDYjg4UXYxOVdvQ0JlZXpibUhxWW5OMWZwb3g5bjQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1126" t="inlineStr">
+        <is>
+          <t>presidencia.gov.co</t>
+        </is>
+      </c>
+      <c r="D1126" t="inlineStr"/>
+      <c r="E1126" t="inlineStr">
+        <is>
+          <t>Caquetá</t>
+        </is>
+      </c>
+      <c r="F1126" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1126" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1126" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1126" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J1126" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1126" t="inlineStr">
+        <is>
+          <t>fuerza</t>
+        </is>
+      </c>
+      <c r="L1126" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1126" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1126" t="inlineStr">
+        <is>
+          <t>strength</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1126"/>
+  <dimension ref="A1:N1133"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63082,6 +63082,408 @@
         </is>
       </c>
     </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>Astrid Cáceres aseguró que ya se interpusieron las denuncias para que las autoridades individualicen a los indígenas que expusieron a los menores durante una protesta en el Ministerio del Interior en Bogotá</t>
+        </is>
+      </c>
+      <c r="B1127" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi6wFBVV95cUxNN09aOVN3Q3o0YXVfUGJIWDZnT1VxNjhLaGVZMU9YWDEzT0Rxc0tGTzE4V05UVVBkOTY5OVRsbGpZaVI0MldDRDh0bFI1d2NjdWJyREI4d2hGX3ZmdFlXbjVaNGtmcGl3QkJVVkd6X2NPSk1uYTU3U1lGSElleG9DNGFuRGxFbHVKQ1Z0eXBqRWMzaWR2aURTcHBMNnpOZ0dpZFlia1F2SzRLamNhVENwc24tLVNWLVkyWnIwUkVTVDE0SjJ2eDJXU2t0ZGVYN0l4Z2I0TG1jekZraHo2c0JwSzk1X19GLWZINWdn?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1127" t="inlineStr">
+        <is>
+          <t>facebook.com</t>
+        </is>
+      </c>
+      <c r="D1127" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E1127" t="inlineStr"/>
+      <c r="F1127" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1127" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1127" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1127" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1127" t="n">
+        <v>30</v>
+      </c>
+      <c r="K1127" t="inlineStr">
+        <is>
+          <t>protesta</t>
+        </is>
+      </c>
+      <c r="L1127" t="inlineStr">
+        <is>
+          <t>Astrid Cáceres</t>
+        </is>
+      </c>
+      <c r="M1127" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1127" t="inlineStr">
+        <is>
+          <t>protest</t>
+        </is>
+      </c>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar rechaza la exposición de niñas y niños en situaciones de riesgo y confrontación, y denuncia penalmente los hechos ocurridos en Bogotá</t>
+        </is>
+      </c>
+      <c r="B1128" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiuAFBVV95cUxObGJROE5UalBCYl95bUhoOFcyWG1EYm9DdDgzc05uUXNXY2k1SnpNcVVtVHdyMzJsdE9XaG9BSVpKcmNYcEV2SEJpTFNyRVg4c1pGYU4yWkV5WDQ1ZGhmOENZa3JRZGRQYlFKRm51WC0xSzV2QzVyeVZub0RTUVJ0NjRpNG84dkU0TDhoSEJ3OHYzT3psSWRRZGZHVmZoZG40UW1TeXVPR0Ffd1NDdm1PRVhmc2E2Z1dD?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1128" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1128" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E1128" t="inlineStr"/>
+      <c r="F1128" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1128" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1128" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1128" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1128" t="n">
+        <v>30</v>
+      </c>
+      <c r="K1128" t="inlineStr">
+        <is>
+          <t>rechaza</t>
+        </is>
+      </c>
+      <c r="L1128" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N1128" t="inlineStr">
+        <is>
+          <t>rejects</t>
+        </is>
+      </c>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar rechaza la exposición de niñas y niños en situaciones de riesgo y confrontación, y denuncia penalmente los hechos ocurridos en Bogotá</t>
+        </is>
+      </c>
+      <c r="B1129" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiuAFBVV95cUxObGJROE5UalBCYl95bUhoOFcyWG1EYm9DdDgzc05uUXNXY2k1SnpNcVVtVHdyMzJsdE9XaG9BSVpKcmNYcEV2SEJpTFNyRVg4c1pGYU4yWkV5WDQ1ZGhmOENZa3JRZGRQYlFKRm51WC0xSzV2QzVyeVZub0RTUVJ0NjRpNG84dkU0TDhoSEJ3OHYzT3psSWRRZGZHVmZoZG40UW1TeXVPR0Ffd1NDdm1PRVhmc2E2Z1dD?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1129" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1129" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E1129" t="inlineStr"/>
+      <c r="F1129" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1129" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1129" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1129" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1129" t="n">
+        <v>30</v>
+      </c>
+      <c r="K1129" t="inlineStr">
+        <is>
+          <t>exposición</t>
+        </is>
+      </c>
+      <c r="L1129" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N1129" t="inlineStr">
+        <is>
+          <t>exposing</t>
+        </is>
+      </c>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar rechaza la exposición de niñas y niños en situaciones de riesgo y confrontación, y denuncia penalmente los hechos ocurridos en Bogotá</t>
+        </is>
+      </c>
+      <c r="B1130" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiuAFBVV95cUxObGJROE5UalBCYl95bUhoOFcyWG1EYm9DdDgzc05uUXNXY2k1SnpNcVVtVHdyMzJsdE9XaG9BSVpKcmNYcEV2SEJpTFNyRVg4c1pGYU4yWkV5WDQ1ZGhmOENZa3JRZGRQYlFKRm51WC0xSzV2QzVyeVZub0RTUVJ0NjRpNG84dkU0TDhoSEJ3OHYzT3psSWRRZGZHVmZoZG40UW1TeXVPR0Ffd1NDdm1PRVhmc2E2Z1dD?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1130" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1130" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E1130" t="inlineStr"/>
+      <c r="F1130" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1130" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1130" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1130" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1130" t="n">
+        <v>30</v>
+      </c>
+      <c r="K1130" t="inlineStr">
+        <is>
+          <t>riesgo</t>
+        </is>
+      </c>
+      <c r="L1130" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1130" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1130" t="inlineStr">
+        <is>
+          <t>risk</t>
+        </is>
+      </c>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar rechaza la exposición de niñas y niños en situaciones de riesgo y confrontación, y denuncia penalmente los hechos ocurridos en Bogotá</t>
+        </is>
+      </c>
+      <c r="B1131" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiuAFBVV95cUxObGJROE5UalBCYl95bUhoOFcyWG1EYm9DdDgzc05uUXNXY2k1SnpNcVVtVHdyMzJsdE9XaG9BSVpKcmNYcEV2SEJpTFNyRVg4c1pGYU4yWkV5WDQ1ZGhmOENZa3JRZGRQYlFKRm51WC0xSzV2QzVyeVZub0RTUVJ0NjRpNG84dkU0TDhoSEJ3OHYzT3psSWRRZGZHVmZoZG40UW1TeXVPR0Ffd1NDdm1PRVhmc2E2Z1dD?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1131" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1131" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E1131" t="inlineStr"/>
+      <c r="F1131" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1131" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1131" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1131" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1131" t="n">
+        <v>30</v>
+      </c>
+      <c r="K1131" t="inlineStr">
+        <is>
+          <t>denuncia</t>
+        </is>
+      </c>
+      <c r="L1131" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1131" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1131" t="inlineStr">
+        <is>
+          <t>denounces</t>
+        </is>
+      </c>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>ICBF denunciará el uso de niños y niñas emberá como escudos en disturbios de Bogotá</t>
+        </is>
+      </c>
+      <c r="B1132" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMipgFBVV95cUxQbTFHalMzWEgzczBWM19BVEN0YU0xa3JrSExUU0VtSEplNVgtQUw1SlVXSGpDdEpQbkdCVVJzSzFjSVRjNUdqQXFCYnNCMWstckROTmZVNGFnVzY1aUZkVF84QmRTdkhRa0Yya0Y4UU1KejlITnRwa1FEYUVJZkRlZ3JMUnRLWW9wTHhidEhMbnJ6eU4xdkczT0dwOGJlcTRwTURfZWFR?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1132" t="inlineStr">
+        <is>
+          <t>larazon.co</t>
+        </is>
+      </c>
+      <c r="D1132" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E1132" t="inlineStr"/>
+      <c r="F1132" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1132" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1132" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1132" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1132" t="n">
+        <v>30</v>
+      </c>
+      <c r="K1132" t="inlineStr">
+        <is>
+          <t>disturbios</t>
+        </is>
+      </c>
+      <c r="L1132" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1132" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1132" t="inlineStr">
+        <is>
+          <t>riots</t>
+        </is>
+      </c>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>Indignación de Petro por video de comunidad Emberá usando niños como escudos en protestas: ICBF tomó medidas</t>
+        </is>
+      </c>
+      <c r="B1133" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi6gFBVV95cUxOY1I1UjhtbWpyWUdMQ045eWViSjFpZk9yOTl1eUcxTGRXQjkzMEM5TU13MnVKdnJoaXFHOFpheG1vWFhqRmhYcTZxQkdqS0NzVVRPcWVtRFIwOEhCWFhoYllCVmZOSnBNMS1PQUllX2drc3ZDWmhEem1hZWtoTWJiMF9UbGZXWVBKSVVoNTNZYXY0d3FHb1B6eGhwNGJ6eHVkTGtJZmxWZVNqbk0xdlItdUpFT3JvNTJWQ1ViYjBfZmtidlhqbjJzekxzV1RBdDc4clkwaHlSOEdTVE80OU9KTDl2MThBQnFvbnc?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1133" t="inlineStr">
+        <is>
+          <t>Publimetro Colombia</t>
+        </is>
+      </c>
+      <c r="D1133" t="inlineStr"/>
+      <c r="E1133" t="inlineStr"/>
+      <c r="F1133" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1133" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1133" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1133" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1133" t="n">
+        <v>30</v>
+      </c>
+      <c r="K1133" t="inlineStr">
+        <is>
+          <t>protestas</t>
+        </is>
+      </c>
+      <c r="L1133" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1133" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1133" t="inlineStr">
+        <is>
+          <t>protests</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1133"/>
+  <dimension ref="A1:N1134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63484,6 +63484,64 @@
         </is>
       </c>
     </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>Icbf denunció el uso de niños como escudos en protesta indígena | Q´HUBO Medellín</t>
+        </is>
+      </c>
+      <c r="B1134" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMitgFBVV95cUxOX05uTC1fQkpKMmtoUEU2R012Y2hPZXhobmo4d2g5QVZUMEFFd3FjRHc1RnlmMU9sNmJYSUhhV0pidjNXOFpaYzBxYmozM3hIWlhNcUNlQ05QTWp1cXJxVVNLT082cGxpbzB3WFVEdmpSaC1zQkl6aWExUmpVajBUdXhIT3FtT0MyRWs5VTNzbTlMV0daa0ZjVFRvQW1sZEEyTG9TRXFNX3Q5eV83bWxoNnpzaTNIUdIBwAFBVV95cUxOWF9XNmRFY0s3eEFrTlZhb01IUDEyaElWTk94Q2JKc2VqejZKS3pGa2VORGY4b1NfRnc2WUtxYlZpMzNpc3Q5MFVkb1ZYSG1QX0VtMWwtbGVxWTRVNVF1aXJzNkZtVndZVVlXTTB0di05cXRzUzhQMkVZWDRkaEhObW1wY1AyTWQ4TEpycVc4dkhLeVkzQ2I4RDNwZ2ZjWTdzc0NRdkRuUDJub2RybzZhN1puT1ViajFQWjMyaEFBd08?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1134" t="inlineStr">
+        <is>
+          <t>Qhubo Medellín</t>
+        </is>
+      </c>
+      <c r="D1134" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E1134" t="inlineStr"/>
+      <c r="F1134" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1134" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1134" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1134" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J1134" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1134" t="inlineStr">
+        <is>
+          <t>protesta</t>
+        </is>
+      </c>
+      <c r="L1134" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1134" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1134" t="inlineStr">
+        <is>
+          <t>protest</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1134"/>
+  <dimension ref="A1:N1137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63542,6 +63542,172 @@
         </is>
       </c>
     </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>ICBF denuncia uso de niños indígenas como escudos en protesta Embera</t>
+        </is>
+      </c>
+      <c r="B1135" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiuwFBVV95cUxOZ1h1dkE4NWRsMVVac2UyOHhCTjY1TVlzajRGZjRNTEFOM0hZWjF2aEd1OTMtbmlyWDNQQkQ4cEhEeEE0R0poTzhiSDFHRFBHM2gwVWtMNm5STDdhNDZnbXpya2o3alBOQTlVUEhZT19CcEV5YzdPUTZiVTEyWmtoaUV5VWwyUldVU0kyRE4xUEIwRlF2aWxHS0UyMkp0WmsyWXJoa2xjVzJZWVRvM0V6SHk2cUxmUDBnV0U0?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1135" t="inlineStr">
+        <is>
+          <t>Crónica del Quindio</t>
+        </is>
+      </c>
+      <c r="D1135" t="inlineStr"/>
+      <c r="E1135" t="inlineStr"/>
+      <c r="F1135" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1135" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1135" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1135" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J1135" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1135" t="inlineStr">
+        <is>
+          <t>denuncia</t>
+        </is>
+      </c>
+      <c r="L1135" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1135" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1135" t="inlineStr">
+        <is>
+          <t>denounces</t>
+        </is>
+      </c>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>ICBF denuncia uso de niños indígenas como escudos en protesta Embera</t>
+        </is>
+      </c>
+      <c r="B1136" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiuwFBVV95cUxOZ1h1dkE4NWRsMVVac2UyOHhCTjY1TVlzajRGZjRNTEFOM0hZWjF2aEd1OTMtbmlyWDNQQkQ4cEhEeEE0R0poTzhiSDFHRFBHM2gwVWtMNm5STDdhNDZnbXpya2o3alBOQTlVUEhZT19CcEV5YzdPUTZiVTEyWmtoaUV5VWwyUldVU0kyRE4xUEIwRlF2aWxHS0UyMkp0WmsyWXJoa2xjVzJZWVRvM0V6SHk2cUxmUDBnV0U0?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1136" t="inlineStr">
+        <is>
+          <t>Crónica del Quindio</t>
+        </is>
+      </c>
+      <c r="D1136" t="inlineStr"/>
+      <c r="E1136" t="inlineStr"/>
+      <c r="F1136" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1136" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1136" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1136" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J1136" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1136" t="inlineStr">
+        <is>
+          <t>protesta</t>
+        </is>
+      </c>
+      <c r="L1136" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1136" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1136" t="inlineStr">
+        <is>
+          <t>protest</t>
+        </is>
+      </c>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>Atlántico activa mesa intersectorial para frenar uso de menores por bandas y fortalecer a las familias -</t>
+        </is>
+      </c>
+      <c r="B1137" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi2AFBVV95cUxQTmFTNm1OX2oxSFhuOTNiaG9HRDJsVDhRWi1pY0kwRHVXbDUzVHVWMVNQQzY0d3IxRlpHZFdPUng1ZkZZaE5FZzRNaWNTRjdFb0VheHhFZENKZUpNQnBkY2tlUm1rSDh1TmdhYi1zN2VpblhESHNxaW85Vm0wb0RfSU9OMVI2RjBPclhkNmVQYzhKYW1XT0tkb3NJTElCTlBGTGlqTTJycVp5LXk3YzJrZy12VThSQzIySUxUX04yQ3d0Q2t0X2ltZlV0N3Z1RkRDeXlUN2FoaE3SAeABQVVfeXFMTW5EOU4yTDdtblpyRmxFZlJpQms1TVNaQTE0SDBFS0FqUXJ3T2I5d19lVUVVdmxLaTlPODBJN1p4T1VLTmg5N1o1cmR0VjhJaGtGVS1OV3pqWjNFT0hSWFRZcXhwSTdvaVhqSWFYM25Jakg1UTdHU1EzMTlwcU9ZMFpPWElYYWo5aDhfeXM2VFRmaHJVTEV0cDRHajRpaEpzeVhCbUt6WVdBWkNVeVBHREc0M3dHTDJISUNrclJhRG50R1dCc1BkWTJidGRPUzdpemlTbHdRNjVmZFF6eHh3Q2E?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1137" t="inlineStr">
+        <is>
+          <t>emisoraatlantico.com.co</t>
+        </is>
+      </c>
+      <c r="D1137" t="inlineStr"/>
+      <c r="E1137" t="inlineStr">
+        <is>
+          <t>Atlántico</t>
+        </is>
+      </c>
+      <c r="F1137" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1137" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1137" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1137" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1137" t="n">
+        <v>30</v>
+      </c>
+      <c r="K1137" t="inlineStr">
+        <is>
+          <t>fortalecer</t>
+        </is>
+      </c>
+      <c r="L1137" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1137" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1137" t="inlineStr">
+        <is>
+          <t>strengthen</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1137"/>
+  <dimension ref="A1:N1138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63708,6 +63708,60 @@
         </is>
       </c>
     </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>Presidente Gustavo Petro y directora del ICBF rechazan uso de niños Embera como escudos humanos en protestas en sede del MinInterior: 'No lo admito'</t>
+        </is>
+      </c>
+      <c r="B1138" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiogJBVV95cUxNd1NpYkpJZlNoTlVfQmVwN1k4TVlRR2ZYV3YtSFlXTEc1SDNZNjZpbXVvOHFQb0NYenZFNjR1Y0NMN1hwRjdVeS12X3h4UG5aWlFPMVAzbk02Nk9Cc2RkYlNNSTJKal9PTHJkWUptdThIWW53S2ZtZlVCNFpQbU5YTkQ2bUxjR0U5eG9wSWFvVHdZa0o4WEFabUhPU0RVUGZYWnUySjNLUUJhYWNiOHdJMWx3YjlfRXdIbmFNVEl6UVRVbVFidUZKWTNBWnlSaUJxS28yLTk3RFZGY042TjNMLTJrTXBuR3U0ckxKdWRLNnR4SkM1ei04NENqeDgtaDlING9QNU1iYURXUUs5WVJyUTVSNFZPTTdIRUlHQl9fd1dHUdIBpwJBVV95cUxPakdnMmN1Rk9Zc0owRnB0aG1qa3pYMUNzZVF5amRNS3gzUEdmNkJFODFKalZ0LWRnNm5xZm5EdHVRblB1ejlxajYxd1NXWDlXbUZwZ3VNeHB3YmZadnNmQTUtQ0lRSDJwQVFnaEFOT1dkdWotV29XcmtjUnZsQmc0NW1jNm5ZTjllUjVLTHJ4LUh5STdFQW0tSDJTSDQ0cnl6VGMxdnB1a0JSYS1yVHJzZzhaMWNvSUp3bEFwLWg1TlNNQUtwdGJGdmxTOXd5SmQ0eUdVUGhyVDdrYlFYVkdTeVV5cHFoWlVQTnItZmM3clcxS2U1Qjk4SkNLclJIZWJTc3ZReVJTcThTZFhnblA4MGpYdWh5dTFKY1BHZXVBV2NTVm5QYklr?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1138" t="inlineStr">
+        <is>
+          <t>ELTIEMPO.COM</t>
+        </is>
+      </c>
+      <c r="D1138" t="inlineStr"/>
+      <c r="E1138" t="inlineStr"/>
+      <c r="F1138" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1138" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1138" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1138" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1138" t="n">
+        <v>30</v>
+      </c>
+      <c r="K1138" t="inlineStr">
+        <is>
+          <t>protestas</t>
+        </is>
+      </c>
+      <c r="L1138" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1138" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1138" t="inlineStr">
+        <is>
+          <t>protests</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1138"/>
+  <dimension ref="A1:N1139"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63762,6 +63762,60 @@
         </is>
       </c>
     </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>Niñez wayuu aprendió sobre la sal marina con el apoyo del Museo de la Sal ICHI</t>
+        </is>
+      </c>
+      <c r="B1139" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMipAFBVV95cUxNcjFCWS1pTmVHWGZFVGl5YlhvM1p2MzUxS3l4VkZjdkFVMkFLSnZNbmRMdVRUSjA4bmgwb3pLU2RJZHREUkZVR3dqZmZhWlNWUUJlZ0IyQmhzNV9JajBLM1ZseFJGUkM1V2h3YWJQOGZVYnNYTUtpVFozcTVFUFRrRUlybDF2Q0U3OEdnNHBjZmtrNnRmWW5NbFJ5ZGJ1U1FQYkkxOA?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1139" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1139" t="inlineStr"/>
+      <c r="E1139" t="inlineStr"/>
+      <c r="F1139" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1139" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1139" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1139" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1139" t="n">
+        <v>4</v>
+      </c>
+      <c r="K1139" t="inlineStr">
+        <is>
+          <t>apoyo</t>
+        </is>
+      </c>
+      <c r="L1139" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1139" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1139" t="inlineStr">
+        <is>
+          <t>backing</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1139"/>
+  <dimension ref="A1:N1142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63816,6 +63816,180 @@
         </is>
       </c>
     </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>ICBF Boyacá llama a celebrar el Día de las Madres con amor, corresponsabilidad y cero tolerancia a la violencia</t>
+        </is>
+      </c>
+      <c r="B1140" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi1gFBVV95cUxQNlBOU0hRMFQwQXprbFRsSkJGR1lpaDZvYXgxRjczUmp5V0FUMm5VMzJwcVJsVWNzNTlxNjZ6alBMb3FqX3hPbm9QaTMtTVp0T0oxSW54QnlRTS11OHBMRzhuNkx2TmhsbmZBM1dUN0hfSElTcl9yTHlGREpDdDlHNnVEMVpEMDFUNEt4VEVIU3dsTGRPQ1ZSYU1YS21YdU96NjlxSTFYWjl0bk5Mek5LRWl1aV9hNTRtR2dsOWczM3I5X0tuRDZ4T1MteG1lUmp4V3d2bU13?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1140" t="inlineStr">
+        <is>
+          <t>Boyacá 95.6 fm</t>
+        </is>
+      </c>
+      <c r="D1140" t="inlineStr"/>
+      <c r="E1140" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="F1140" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1140" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1140" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1140" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1140" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1140" t="inlineStr">
+        <is>
+          <t>celebrar</t>
+        </is>
+      </c>
+      <c r="L1140" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1140" t="n">
+        <v>3</v>
+      </c>
+      <c r="N1140" t="inlineStr">
+        <is>
+          <t>celebrate</t>
+        </is>
+      </c>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>ICBF Boyacá llama a celebrar el Día de las Madres con amor, corresponsabilidad y cero tolerancia a la violencia</t>
+        </is>
+      </c>
+      <c r="B1141" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi1gFBVV95cUxQNlBOU0hRMFQwQXprbFRsSkJGR1lpaDZvYXgxRjczUmp5V0FUMm5VMzJwcVJsVWNzNTlxNjZ6alBMb3FqX3hPbm9QaTMtTVp0T0oxSW54QnlRTS11OHBMRzhuNkx2TmhsbmZBM1dUN0hfSElTcl9yTHlGREpDdDlHNnVEMVpEMDFUNEt4VEVIU3dsTGRPQ1ZSYU1YS21YdU96NjlxSTFYWjl0bk5Mek5LRWl1aV9hNTRtR2dsOWczM3I5X0tuRDZ4T1MteG1lUmp4V3d2bU13?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1141" t="inlineStr">
+        <is>
+          <t>Boyacá 95.6 fm</t>
+        </is>
+      </c>
+      <c r="D1141" t="inlineStr"/>
+      <c r="E1141" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="F1141" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1141" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1141" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1141" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1141" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1141" t="inlineStr">
+        <is>
+          <t>amor</t>
+        </is>
+      </c>
+      <c r="L1141" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1141" t="n">
+        <v>3</v>
+      </c>
+      <c r="N1141" t="inlineStr">
+        <is>
+          <t>love</t>
+        </is>
+      </c>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>ICBF Boyacá llama a celebrar el Día de las Madres con amor, corresponsabilidad y cero tolerancia a la violencia</t>
+        </is>
+      </c>
+      <c r="B1142" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi1gFBVV95cUxQNlBOU0hRMFQwQXprbFRsSkJGR1lpaDZvYXgxRjczUmp5V0FUMm5VMzJwcVJsVWNzNTlxNjZ6alBMb3FqX3hPbm9QaTMtTVp0T0oxSW54QnlRTS11OHBMRzhuNkx2TmhsbmZBM1dUN0hfSElTcl9yTHlGREpDdDlHNnVEMVpEMDFUNEt4VEVIU3dsTGRPQ1ZSYU1YS21YdU96NjlxSTFYWjl0bk5Mek5LRWl1aV9hNTRtR2dsOWczM3I5X0tuRDZ4T1MteG1lUmp4V3d2bU13?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1142" t="inlineStr">
+        <is>
+          <t>Boyacá 95.6 fm</t>
+        </is>
+      </c>
+      <c r="D1142" t="inlineStr"/>
+      <c r="E1142" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="F1142" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1142" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1142" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1142" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1142" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1142" t="inlineStr">
+        <is>
+          <t>violencia</t>
+        </is>
+      </c>
+      <c r="L1142" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1142" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1142" t="inlineStr">
+        <is>
+          <t>violence</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1142"/>
+  <dimension ref="A1:N1143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63990,6 +63990,64 @@
         </is>
       </c>
     </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>Cae presunta red de pornografía infantil en Medellín: operativo de la Fiscalía, la Policía y los EE. UU.</t>
+        </is>
+      </c>
+      <c r="B1143" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi3wFBVV95cUxOSzgyZDZ4NWN5dW1RdzhMNnlWZnpBZFdOUnBsa083czlqNVFGM0dOYk45RnNMOGl1WkppVTJTNWgxcTMwOHR5RUtXUnpsYnZENGVHTFdmSG5YemNCejREclMyNzhKVjJpOGdXeGlOMmtGamVseDM0WDY0OGpoc2V0UGZkWmt3VWxZVGZMaHhVLXd3QnFJUG9wenFFS3V6a1hodUF2bTh0OWVlM3VBbzNIWTBROFNHUktUZ0NyMWg5REVTZ3ZhaGg1TGIzOVRIb0hwbFF6V0x2eTg1WF9ERi1V0gH6AUFVX3lxTE82Sl9vX2hJTHdScWk3LXNRdG9lN3I5RVNLSU9IV0RIOEtYRnBqa2ZfdDBEWi1hZzlDa1prWGN2NUZWZU5yZW94UjFhVnVqeUk2WEtZRkZVNmV1VnFTa0Q0TGhaVVlnUURsN282SWVqTFkwWEFUY0VyeDQyVzcyUmNmQkZhR2xFbnBaejZoRVRYZTR0VVNjY0poNHEwV3Ezd01DaFVqY1dPQV92YkpxSjBWdjlha3ZxeEhpaW1jUWRqLXlsWnllcDhvN3VGdlozMUdFYTB4Y3pnVDd3ZGlsbnlpSFIteUVTUWdCU1M5SGJ4aVNIWjF2aFZZWFE?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1143" t="inlineStr">
+        <is>
+          <t>ELHERALDO.CO</t>
+        </is>
+      </c>
+      <c r="D1143" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E1143" t="inlineStr"/>
+      <c r="F1143" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1143" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1143" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1143" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1143" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1143" t="inlineStr">
+        <is>
+          <t>infantil</t>
+        </is>
+      </c>
+      <c r="L1143" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1143" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1143" t="inlineStr">
+        <is>
+          <t>childish</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1143"/>
+  <dimension ref="A1:N1146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64048,6 +64048,188 @@
         </is>
       </c>
     </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar fortalece acciones para prevenir el reclutamiento y la violencia contra la niñez en Arauca</t>
+        </is>
+      </c>
+      <c r="B1144" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiwAFBVV95cUxOT1hNNHVlWnAxWnF0SWlXRzNQNHlqUFZ1ZnZFR3J2bXo5MWc5SEwxQ2NReUtONVJKSGpSQV9Oa1dITlFTSmY2b2M1TVFkbzhaYXNFS0JuZnRrUlhJMmtjRGN2RXNmMHprc1pJTlBNQVhCcG1WSEF3MEd1RWdmYlJXbjRDRzFOa2tiOHZDX2Q1RWttLU9FT2xTYUNJcFhTTmMwd2JQejh3X0J1VWw0YXB2bm1wc1JmSHR6M3ZORFlueG8?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1144" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1144" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="E1144" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="F1144" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1144" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1144" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1144" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J1144" t="n">
+        <v>6</v>
+      </c>
+      <c r="K1144" t="inlineStr">
+        <is>
+          <t>fortalece</t>
+        </is>
+      </c>
+      <c r="L1144" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1144" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1144" t="inlineStr">
+        <is>
+          <t>strengthens</t>
+        </is>
+      </c>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar fortalece acciones para prevenir el reclutamiento y la violencia contra la niñez en Arauca</t>
+        </is>
+      </c>
+      <c r="B1145" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiwAFBVV95cUxOT1hNNHVlWnAxWnF0SWlXRzNQNHlqUFZ1ZnZFR3J2bXo5MWc5SEwxQ2NReUtONVJKSGpSQV9Oa1dITlFTSmY2b2M1TVFkbzhaYXNFS0JuZnRrUlhJMmtjRGN2RXNmMHprc1pJTlBNQVhCcG1WSEF3MEd1RWdmYlJXbjRDRzFOa2tiOHZDX2Q1RWttLU9FT2xTYUNJcFhTTmMwd2JQejh3X0J1VWw0YXB2bm1wc1JmSHR6M3ZORFlueG8?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1145" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1145" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="E1145" t="inlineStr">
+        <is>
+          <t>Arauca</t>
+        </is>
+      </c>
+      <c r="F1145" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1145" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1145" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1145" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J1145" t="n">
+        <v>6</v>
+      </c>
+      <c r="K1145" t="inlineStr">
+        <is>
+          <t>violencia</t>
+        </is>
+      </c>
+      <c r="L1145" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1145" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1145" t="inlineStr">
+        <is>
+          <t>violence</t>
+        </is>
+      </c>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>Adolescentes del Sistema de Responsabilidad Penal fortalecen habilidades para la vida en Yopal</t>
+        </is>
+      </c>
+      <c r="B1146" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivgFBVV95cUxQeHhiNTl5dktPdl9HWXNuU0ZrbXRNUkJPdURQTUwtaDVtdEJYeTBzYVJEdkVvd2JSLXRheUw0NHNrdVlNdFBGVlZEZ19ocTMwbHFsNW1pYWZKWUs5YXBpR3hBR0gycHZud0ZFM2gydkhiVjZxRGhEYjd3cW5jYThuMXB1MEcyT05uVndTdFZjdkEweVk2b09aMXVvd0lCZnJ0Nm1zczF3bUlubnJ0MjJnWXJoMXVUYkdodUJtTHh3?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1146" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1146" t="inlineStr">
+        <is>
+          <t>Yopal</t>
+        </is>
+      </c>
+      <c r="E1146" t="inlineStr"/>
+      <c r="F1146" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1146" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1146" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1146" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1146" t="n">
+        <v>5</v>
+      </c>
+      <c r="K1146" t="inlineStr">
+        <is>
+          <t>habilidades</t>
+        </is>
+      </c>
+      <c r="L1146" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1146" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1146" t="inlineStr">
+        <is>
+          <t>abilities</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1146"/>
+  <dimension ref="A1:N1149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64230,6 +64230,176 @@
         </is>
       </c>
     </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>Violencia sexual, la principal causa de los procesos del ICBF para proteger a niños y niñas: 3.773 casos en 2026</t>
+        </is>
+      </c>
+      <c r="B1147" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMigAJBVV95cUxOWVB0ZEtxNUQ1ZWV0NS11QVA2c1QxSDRCc2laRHZxd1ZERkc2V2FXVUtzS3BQbDA3bS1Bc2NPajA3SjRhVlJqX1dYS2hWcFFmRmRpclFDY2oxMF91VVBhQkVIN3hyWl9BTGpQX1M0NEhWYUZtMjRCWVRIeWs0Z0pXbnlJZnBQb0JpVE5WMjhYbld5aGNiZzJKelo4NWVuVmFrNktuTW91WFo5U29DQmZPRkpMRlRFdTRxSFIwNDYwU0JOSE1WeG56U0FBc3VqMC1lNTBOVk9lbU5ySHZHWVZod2kwVm5IbHZWT1M2Smo0OHJxWktYa2J3RnpiNDFNek5B?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1147" t="inlineStr">
+        <is>
+          <t>ELTIEMPO.COM</t>
+        </is>
+      </c>
+      <c r="D1147" t="inlineStr"/>
+      <c r="E1147" t="inlineStr"/>
+      <c r="F1147" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1147" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1147" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1147" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J1147" t="n">
+        <v>6</v>
+      </c>
+      <c r="K1147" t="inlineStr">
+        <is>
+          <t>proteger</t>
+        </is>
+      </c>
+      <c r="L1147" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1147" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1147" t="inlineStr">
+        <is>
+          <t>protect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>ICBF denuncia uso de menores como escudos humanos en disturbios en Bogotá</t>
+        </is>
+      </c>
+      <c r="B1148" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiZ0FVX3lxTE5TazQxTmJwZzhrd2tUTWg0OG5WbFgtZklpZmJBa1E1cVRYUnpjMUpzQndLOVZiV1M5OGhTNTdSMUxqaHE2eTh1VDdueXQ5Y3g4OVFBNmJUdXZHWWpnOFgtZWdwN2t2bUk?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1148" t="inlineStr">
+        <is>
+          <t>Canal TRO</t>
+        </is>
+      </c>
+      <c r="D1148" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E1148" t="inlineStr"/>
+      <c r="F1148" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1148" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1148" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1148" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J1148" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1148" t="inlineStr">
+        <is>
+          <t>denuncia</t>
+        </is>
+      </c>
+      <c r="L1148" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1148" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1148" t="inlineStr">
+        <is>
+          <t>denounces</t>
+        </is>
+      </c>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>ICBF denuncia uso de menores como escudos humanos en disturbios en Bogotá</t>
+        </is>
+      </c>
+      <c r="B1149" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiZ0FVX3lxTE5TazQxTmJwZzhrd2tUTWg0OG5WbFgtZklpZmJBa1E1cVRYUnpjMUpzQndLOVZiV1M5OGhTNTdSMUxqaHE2eTh1VDdueXQ5Y3g4OVFBNmJUdXZHWWpnOFgtZWdwN2t2bUk?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1149" t="inlineStr">
+        <is>
+          <t>Canal TRO</t>
+        </is>
+      </c>
+      <c r="D1149" t="inlineStr">
+        <is>
+          <t>Bogotá</t>
+        </is>
+      </c>
+      <c r="E1149" t="inlineStr"/>
+      <c r="F1149" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1149" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1149" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1149" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J1149" t="n">
+        <v>1</v>
+      </c>
+      <c r="K1149" t="inlineStr">
+        <is>
+          <t>disturbios</t>
+        </is>
+      </c>
+      <c r="L1149" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1149" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1149" t="inlineStr">
+        <is>
+          <t>riots</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1149"/>
+  <dimension ref="A1:N1152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64400,6 +64400,168 @@
         </is>
       </c>
     </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>Más de 3.700 menores de edad han sido víctimas de violencia sexual en 2026 | El Colombiano</t>
+        </is>
+      </c>
+      <c r="B1150" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivAFBVV95cUxNUXhaYkU2ZUVpNnV5THFYQ0ZPYzZ3RHZBQmZrRTdrSnhzSGJ4WU5vcU5tU1I0OWRYeVVJdTZBeEdQY1BfMHV1LU9uNU9YcklDSEpQS0J6OHJkQ09icUFiMXYtWHNiZElsbU5UU01kN2ZDUThSVmtGSzMxemtlbHpuWl9SM0k2d3l3X25hZjRReFBQUUt5YjVUS0tWSnNWQmFCY3NQcEdjZlA5WWxaNlFFeXFyY2prckZfX2VpMtIBwgFBVV95cUxPRVNSOVBUMmtIeGFmOHhYdGdtQm1mMkdzRXFXWU5TWU10M3ZKQjVnRWNGY0xoQ0MwVXdweF91Nmw2NkZmUDV6NGJZblM2ZXFWdmIzczdJMlZTTk96T25vVVJEVWlxbjRMeWhuQl9QREt6eUVsQ1FRd3ppdFJoZXg5MG1mM1RlaGlCcDdCLUFlQW9fOEVxZzhaTTlQRVVDSWpzVFN5bThTUlFnMHp4YlZrQ2gybDM1ZG5fS0VYalQxMWthdw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1150" t="inlineStr">
+        <is>
+          <t>El Colombiano</t>
+        </is>
+      </c>
+      <c r="D1150" t="inlineStr"/>
+      <c r="E1150" t="inlineStr"/>
+      <c r="F1150" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1150" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1150" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1150" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1150" t="n">
+        <v>7</v>
+      </c>
+      <c r="K1150" t="inlineStr">
+        <is>
+          <t>víctimas</t>
+        </is>
+      </c>
+      <c r="L1150" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1150" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1150" t="inlineStr">
+        <is>
+          <t>victimized</t>
+        </is>
+      </c>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>Más de 3.700 menores de edad han sido víctimas de violencia sexual en 2026 | El Colombiano</t>
+        </is>
+      </c>
+      <c r="B1151" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivAFBVV95cUxNUXhaYkU2ZUVpNnV5THFYQ0ZPYzZ3RHZBQmZrRTdrSnhzSGJ4WU5vcU5tU1I0OWRYeVVJdTZBeEdQY1BfMHV1LU9uNU9YcklDSEpQS0J6OHJkQ09icUFiMXYtWHNiZElsbU5UU01kN2ZDUThSVmtGSzMxemtlbHpuWl9SM0k2d3l3X25hZjRReFBQUUt5YjVUS0tWSnNWQmFCY3NQcEdjZlA5WWxaNlFFeXFyY2prckZfX2VpMtIBwgFBVV95cUxPRVNSOVBUMmtIeGFmOHhYdGdtQm1mMkdzRXFXWU5TWU10M3ZKQjVnRWNGY0xoQ0MwVXdweF91Nmw2NkZmUDV6NGJZblM2ZXFWdmIzczdJMlZTTk96T25vVVJEVWlxbjRMeWhuQl9QREt6eUVsQ1FRd3ppdFJoZXg5MG1mM1RlaGlCcDdCLUFlQW9fOEVxZzhaTTlQRVVDSWpzVFN5bThTUlFnMHp4YlZrQ2gybDM1ZG5fS0VYalQxMWthdw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1151" t="inlineStr">
+        <is>
+          <t>El Colombiano</t>
+        </is>
+      </c>
+      <c r="D1151" t="inlineStr"/>
+      <c r="E1151" t="inlineStr"/>
+      <c r="F1151" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1151" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1151" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1151" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1151" t="n">
+        <v>7</v>
+      </c>
+      <c r="K1151" t="inlineStr">
+        <is>
+          <t>violencia</t>
+        </is>
+      </c>
+      <c r="L1151" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1151" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1151" t="inlineStr">
+        <is>
+          <t>violence</t>
+        </is>
+      </c>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>Directora de Bienestar Familiar advierte sobre cómo las plataformas y algoritmos facilitan la explotación de niñas, niños y adolescentes</t>
+        </is>
+      </c>
+      <c r="B1152" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiwAFBVV95cUxQRHhyWkRseEhEeTBmNEJ5MHY0dGlTbDhSNGU1ejA1UXh0dkVUb3ZYa1dNY1Zudmx3T1VtOXBHQkNtaldiT3c0ejhvZkhIbHJjMjdOcmFaOC0zQjdNdHlGVWR5YlhBQi1MN09OTnVvLWpGTFA0UDVENVRfV3dRdnd5TmJ4aVZSUExfckJqUHlQNnZERnhLWUpHOUg1RHJpMURPQmw5UkV3bUtHZndTTFlIeE85RldwWjNkQmdXZER0dUQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1152" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1152" t="inlineStr"/>
+      <c r="E1152" t="inlineStr"/>
+      <c r="F1152" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1152" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1152" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1152" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1152" t="n">
+        <v>7</v>
+      </c>
+      <c r="K1152" t="inlineStr">
+        <is>
+          <t>advierte</t>
+        </is>
+      </c>
+      <c r="L1152" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1152" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1152" t="inlineStr">
+        <is>
+          <t>warns</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1152"/>
+  <dimension ref="A1:N1153"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64562,6 +64562,64 @@
         </is>
       </c>
     </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>"Que el Tigre llegue a la Casa de Nariño es como haber puesto a Garavito a manejar el ICBF": Sondra Macollins</t>
+        </is>
+      </c>
+      <c r="B1153" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMinwFBVV95cUxPdEMyblVqMWxfQ2lqTnhQWXhfZVJ2VEZVd1lCZC12VHFBUWxpVWREb0NRUEVrY0htQUtTY19laWdEd0NOYllFRWpMNzF2TTJSSEFsbGctOUNuTWVCdG5KR2tEYy1DZ0wxc0dyVzJINjd1WFhocG00eGxJSDBjdzQ5cEIwOUticlEtMzhBdENiM3FNeGlucEpnMHZ1c3VBX0XSAaMBQVVfeXFMTjN3bldZeXdEZFJOQ3JTbmo5THFWTkotT0FVZmpYaFU1TmgxbndLbC1vOHZ0WllEWFE3UU92MXNWZ3NwaXVUd1hCbGFGaGFNNWtjRU91ZHV5X1d2Ynd1NWRZTjdhcHYzMXc1WHB0RnZhVmZsb2daOHZIY2xHUkI0UkdNVGZEZWVvbzMwRm5Jam1YQk93Y1pRbVVvQ20yWGhxR2NuVQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1153" t="inlineStr">
+        <is>
+          <t>bogota.alerta.com.co</t>
+        </is>
+      </c>
+      <c r="D1153" t="inlineStr"/>
+      <c r="E1153" t="inlineStr">
+        <is>
+          <t>Nariño</t>
+        </is>
+      </c>
+      <c r="F1153" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1153" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1153" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1153" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1153" t="n">
+        <v>7</v>
+      </c>
+      <c r="K1153" t="inlineStr">
+        <is>
+          <t>puesto</t>
+        </is>
+      </c>
+      <c r="L1153" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1153" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1153" t="inlineStr">
+        <is>
+          <t>stall</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1153"/>
+  <dimension ref="A1:N1154"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64620,6 +64620,60 @@
         </is>
       </c>
     </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>Cuentas para la Vida: el día en el que el país se conectó desde los territorios para hablar de la niñez y la paz</t>
+        </is>
+      </c>
+      <c r="B1154" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiwAFBVV95cUxNeXFIRDFTbDB5OUZTNmtjUFRONTVmOG1YSEdEdmtaaGExSmNJRlBtSXU4dTJZcVR2U1dSU29GMTM1R1RPV1E1dC15a2VTbGIyaV9nX2c5MVMyTC16d2poanBUMmk0RG9ZUmJoVGhyMWk1bkxsOFVDZFNRdkdxbjFOLWNXYzk5LWhhSHBaWktIenVVZ2p5UldYamdoOXZQSFNMRl9oSmQ2aG5uWXIwdS04U0ktRWVKX2V2TjdxeVhVdmQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1154" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1154" t="inlineStr"/>
+      <c r="E1154" t="inlineStr"/>
+      <c r="F1154" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1154" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1154" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1154" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J1154" t="n">
+        <v>8</v>
+      </c>
+      <c r="K1154" t="inlineStr">
+        <is>
+          <t>paz</t>
+        </is>
+      </c>
+      <c r="L1154" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1154" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1154" t="inlineStr">
+        <is>
+          <t>peace</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1154"/>
+  <dimension ref="A1:N1155"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64674,6 +64674,60 @@
         </is>
       </c>
     </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>«La lucha es contra los mitos que existen sobre las personas con discapacidad»: directora general de Bienestar Familiar</t>
+        </is>
+      </c>
+      <c r="B1155" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiuwFBVV95cUxQTFdBQ0o2TllpX1BkZ3R5QTJvZXk4WDNCS2RySTJERTdrc0ZIX3loTlhsYUJkbnNRUmtYSGxKRXpJWlpoY1VTZmlHbXZIRkExR2VhbF8zX3RqLTlUMGtnNUE3cllsLVpMdkV4YklaWEdXRkItTG90SVJkR2VnbUcwdnk5cG9VbmhfREhTb3RCTXBMRGpfdUdsanhzWEdXWlhCZWZQdFhhS1owWGQ0M1dFYWNkVDFGU0NIUzMw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1155" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1155" t="inlineStr"/>
+      <c r="E1155" t="inlineStr"/>
+      <c r="F1155" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1155" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1155" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1155" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1155" t="n">
+        <v>7</v>
+      </c>
+      <c r="K1155" t="inlineStr">
+        <is>
+          <t>lucha</t>
+        </is>
+      </c>
+      <c r="L1155" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1155" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N1155" t="inlineStr">
+        <is>
+          <t>fight</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1155"/>
+  <dimension ref="A1:N1158"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64728,6 +64728,176 @@
         </is>
       </c>
     </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>Niño de dos años cae desde un cuarto piso en Suba y sobrevive tras ser auxiliado por vecinos que improvisaron una red con cobijas; ICBF investiga posible negligencia</t>
+        </is>
+      </c>
+      <c r="B1156" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMisAJBVV95cUxQVW1XQ09XYkZjUVgzOW8yRW5qN3EzWGdRSThXYVlzSTFmSUxZZnlQWXpPaXlvNjJlMHFIRHktSjlPYncxdTl5M2swQmd0SzEwNGF4Z2dTNlRBdS16WTN5dkliQUVWZi14azNoOUdNRUItbEdqWnZidEZDX3Zwa1Q2Zm5ZU1RQLWVoRXMxb3dMejJVQ2w4RTBHSUJQaGlyRjhmejc0Z3NuWUp6R3Y4NGFfZ1FsNjJLaDZiZ3JseURlUG5lWERxLWR1TEl5STZBeTZMOGNZaGVNV2Y2RU0tbjV6RzRFOVlOTlpENUgyUGRHSVRhbnlkVEctcVV6d3VlWDBabFh5Y3lxUThzRk84TUwwQTNtdy1pZEM0WVNMSHJzQ3dsN2lYZENza2xUZFpvX1pO?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1156" t="inlineStr">
+        <is>
+          <t>Emisora Nueva Epoca</t>
+        </is>
+      </c>
+      <c r="D1156" t="inlineStr"/>
+      <c r="E1156" t="inlineStr"/>
+      <c r="F1156" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1156" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1156" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1156" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="J1156" t="n">
+        <v>9</v>
+      </c>
+      <c r="K1156" t="inlineStr">
+        <is>
+          <t>negligencia</t>
+        </is>
+      </c>
+      <c r="L1156" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1156" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1156" t="inlineStr">
+        <is>
+          <t>neglect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar rechaza graves hechos de explotación sexual infantil en Medellín</t>
+        </is>
+      </c>
+      <c r="B1157" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMitwFBVV95cUxOZ2xjeVJXcmlOX2F3cFlRRnAzNm1fcmpFVFZ4eTBLRmVHQXFiRTFiN1dJbDBWWElfZEY3Vm1aeDRfT2ZvbDZGVnhmZ2llRHkzekZEWE5vbmtTakZLaUhiTEZZLTRvdkZHLW5EV2lKMGJDWG9rS1MzV3NwWXNKLW5wQjVJVWQ5Rnh4NGdwb0RhTjU0YzdpZVpvSk45S3Z1TTY3UXk4SERjZWJCWThxZ0hpRU5BcW5FbFk?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1157" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1157" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E1157" t="inlineStr"/>
+      <c r="F1157" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1157" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1157" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1157" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J1157" t="n">
+        <v>8</v>
+      </c>
+      <c r="K1157" t="inlineStr">
+        <is>
+          <t>rechaza</t>
+        </is>
+      </c>
+      <c r="L1157" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1157" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N1157" t="inlineStr">
+        <is>
+          <t>rejects</t>
+        </is>
+      </c>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar rechaza graves hechos de explotación sexual infantil en Medellín</t>
+        </is>
+      </c>
+      <c r="B1158" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMitwFBVV95cUxOZ2xjeVJXcmlOX2F3cFlRRnAzNm1fcmpFVFZ4eTBLRmVHQXFiRTFiN1dJbDBWWElfZEY3Vm1aeDRfT2ZvbDZGVnhmZ2llRHkzekZEWE5vbmtTakZLaUhiTEZZLTRvdkZHLW5EV2lKMGJDWG9rS1MzV3NwWXNKLW5wQjVJVWQ5Rnh4NGdwb0RhTjU0YzdpZVpvSk45S3Z1TTY3UXk4SERjZWJCWThxZ0hpRU5BcW5FbFk?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1158" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1158" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E1158" t="inlineStr"/>
+      <c r="F1158" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1158" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1158" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1158" t="inlineStr">
+        <is>
+          <t>viernes</t>
+        </is>
+      </c>
+      <c r="J1158" t="n">
+        <v>8</v>
+      </c>
+      <c r="K1158" t="inlineStr">
+        <is>
+          <t>infantil</t>
+        </is>
+      </c>
+      <c r="L1158" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1158" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1158" t="inlineStr">
+        <is>
+          <t>childish</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1158"/>
+  <dimension ref="A1:N1159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64898,6 +64898,60 @@
         </is>
       </c>
     </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>Dramático rescate en Suba: vecinos salvaron a niño de dos años que cayó de una terraza</t>
+        </is>
+      </c>
+      <c r="B1159" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi7wFBVV95cUxOUW53OG1xUV9QODNMLWF4Ti1BRmlKbkZ4b2hiNnhXTmoxNkdpSC1PX3Z6QkZ5alNXb3JTQ0dxQ3JOUkxIVXJsLXAtQ2RIWkVjTTBUeEVXLVd6U01Fa1FBTEFmRWg1Ql9LNXd6SUFYbURZQldrTmdGLVE1d3ZKLXo2YWUzWjdudkxKY280elZtVm5MeHVZVTRRUTRYdlhfSllpOEpGcnhPVjMtM1JmaGh4N1g2NWlkcE9SZkRnNHNjR2x6WHhnWjBJZEhHWXRqSkhQclNvNF8ycTUySmVtdkZtc0VCQkJaMldtX1Y5VzNrTQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1159" t="inlineStr">
+        <is>
+          <t>MSN</t>
+        </is>
+      </c>
+      <c r="D1159" t="inlineStr"/>
+      <c r="E1159" t="inlineStr"/>
+      <c r="F1159" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1159" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1159" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1159" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="J1159" t="n">
+        <v>9</v>
+      </c>
+      <c r="K1159" t="inlineStr">
+        <is>
+          <t>rescate</t>
+        </is>
+      </c>
+      <c r="L1159" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1159" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1159" t="inlineStr">
+        <is>
+          <t>bailout</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1159"/>
+  <dimension ref="A1:N1161"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -64952,6 +64952,122 @@
         </is>
       </c>
     </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>Niños de Ataco, Tolima, están en peligro: Gobernación pide presencia permanente del ICBF</t>
+        </is>
+      </c>
+      <c r="B1160" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMioAFBVV95cUxPX3RGVUxxWkxmRTY0aERFOUdaWTF0VjBOWFVqM21IbWU3VzEtcnBXaXdrOTNfcUlzdFRPMUR5U1pHejZFb0NTcno0dVVLdHRqcjFtQ205a2lfN2RXaGcweUZHMlR6NjBXU0ZjOHhVQ3VPUDYwY0NONld6UHZaNVRZb1B1Zmc0ejNjbFdfQ2xORXdaMk44MjExa1RlUUpyQVZT0gGkAUFVX3lxTE5aZ181R2h4ZGQwS2ZDOTFyTjlDWU1tTG1peVBCbllNNHd1ZzRhdG14S21ZcEUyeThyZWhMNUVIV3pKbUtGalpveGtjZmdzS3cwcnhVTXQzTktzdnA5UkZzZVNreG1UT21oYUtDS0pxQmY2d1BBdGdDX25fVG5pVVFfNDRSS2VUa21zMzRiZ1JoVlo5aWxhM2xLYWwzazU0ODNaYUIw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1160" t="inlineStr">
+        <is>
+          <t>tolima.alerta.com.co</t>
+        </is>
+      </c>
+      <c r="D1160" t="inlineStr"/>
+      <c r="E1160" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="F1160" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1160" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1160" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1160" t="inlineStr">
+        <is>
+          <t>sábado</t>
+        </is>
+      </c>
+      <c r="J1160" t="n">
+        <v>9</v>
+      </c>
+      <c r="K1160" t="inlineStr">
+        <is>
+          <t>peligro</t>
+        </is>
+      </c>
+      <c r="L1160" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1160" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1160" t="inlineStr">
+        <is>
+          <t>danger</t>
+        </is>
+      </c>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar activó acompañamiento psicosocial tras hecho de violencia ocurrido cerca de una unidad de servicio en Valledupar | Portal ICBF - Instituto Colombiano de Bienestar</t>
+        </is>
+      </c>
+      <c r="B1161" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiugFBVV95cUxNRUhhcV8tZkxQRkpqLXRQTzBIQUlUTVRKMko5VW5WclU2Nld5YUlSRENVcXM5c29INXFON2FGbVNXZkEzSFRnbWloeWJkNGUwTXAycUY3WWJCRFVRN0RreHNBMHFZOHBMSkNGRjEzU2lGbkdJdHd2NUN3NENJWmotWmotRlN6T29sSXlnRy1UTEVNSTlBa2lIcXh1OHBLV0t4SGp4VGp4NHZjc05MejM4OUZFZ2Q4Yjk4QlE?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1161" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1161" t="inlineStr">
+        <is>
+          <t>Valledupar</t>
+        </is>
+      </c>
+      <c r="E1161" t="inlineStr"/>
+      <c r="F1161" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1161" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1161" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1161" t="inlineStr">
+        <is>
+          <t>domingo</t>
+        </is>
+      </c>
+      <c r="J1161" t="n">
+        <v>10</v>
+      </c>
+      <c r="K1161" t="inlineStr">
+        <is>
+          <t>violencia</t>
+        </is>
+      </c>
+      <c r="L1161" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1161" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1161" t="inlineStr">
+        <is>
+          <t>violence</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1161"/>
+  <dimension ref="A1:N1163"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65068,6 +65068,122 @@
         </is>
       </c>
     </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar activó acompañamiento psicosocial tras hecho de violencia ocurrido cerca de una unidad de servicio en Valledupar | Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="B1162" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiugFBVV95cUxNRUhhcV8tZkxQRkpqLXRQTzBIQUlUTVRKMko5VW5WclU2Nld5YUlSRENVcXM5c29INXFON2FGbVNXZkEzSFRnbWloeWJkNGUwTXAycUY3WWJCRFVRN0RreHNBMHFZOHBMSkNGRjEzU2lGbkdJdHd2NUN3NENJWmotWmotRlN6T29sSXlnRy1UTEVNSTlBa2lIcXh1OHBLV0t4SGp4VGp4NHZjc05MejM4OUZFZ2Q4Yjk4QlE?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1162" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1162" t="inlineStr">
+        <is>
+          <t>Valledupar</t>
+        </is>
+      </c>
+      <c r="E1162" t="inlineStr"/>
+      <c r="F1162" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1162" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1162" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1162" t="inlineStr">
+        <is>
+          <t>domingo</t>
+        </is>
+      </c>
+      <c r="J1162" t="n">
+        <v>10</v>
+      </c>
+      <c r="K1162" t="inlineStr">
+        <is>
+          <t>violencia</t>
+        </is>
+      </c>
+      <c r="L1162" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1162" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1162" t="inlineStr">
+        <is>
+          <t>violence</t>
+        </is>
+      </c>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar activó rutas de protección tras desarticulación de red de explotación sexual comercial infantil en Medellín</t>
+        </is>
+      </c>
+      <c r="B1163" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivgFBVV95cUxNVGo3Q0ZSRUdLQmg3bjhRZUxrWWNjekpoVmNUWk5ObFQ2WUlhTWtPZGpNZl9iZW1kN1hqRm1mcDF2bVFVV3hyUmsyVWx5X2ZWNmVCXzRZalVFRmFMSlRaOFNvOHFqcEFlRkdsS05SSUxSYnpGaW1kYjljOGtqLVdNdElfRU4waG01M05DQUVvNVFUcGpfd2trb1I3cHRucVBGaGhQZWtFM3pmbHh6eG9kNXY1dldqcC1kQkFDWXhn?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1163" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1163" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E1163" t="inlineStr"/>
+      <c r="F1163" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1163" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1163" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1163" t="inlineStr">
+        <is>
+          <t>domingo</t>
+        </is>
+      </c>
+      <c r="J1163" t="n">
+        <v>10</v>
+      </c>
+      <c r="K1163" t="inlineStr">
+        <is>
+          <t>infantil</t>
+        </is>
+      </c>
+      <c r="L1163" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1163" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1163" t="inlineStr">
+        <is>
+          <t>childish</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1163"/>
+  <dimension ref="A1:N1164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65184,6 +65184,60 @@
         </is>
       </c>
     </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>Ejército Nacional e ICBF unidos a favor de la niñez</t>
+        </is>
+      </c>
+      <c r="B1164" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMihgFBVV95cUxOQ3JNcUo1cWt0RjAweGZhTDdfempHMm5YaUNkMWxOMHlmamNSZ21CVnJ0Y2wxRGdTY293TnVFbU44LW5Bdlh0QmxnUmhINnl3U1VJeVJjUDJMNk50QWJLMkhoZVQ2SGRMVTJ4ZDVjdmVJZUlCelVtajVrWkFXVXVxV3NUTUVUUQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1164" t="inlineStr">
+        <is>
+          <t>Ejército Nacional de Colombia</t>
+        </is>
+      </c>
+      <c r="D1164" t="inlineStr"/>
+      <c r="E1164" t="inlineStr"/>
+      <c r="F1164" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1164" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1164" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1164" t="inlineStr">
+        <is>
+          <t>domingo</t>
+        </is>
+      </c>
+      <c r="J1164" t="n">
+        <v>10</v>
+      </c>
+      <c r="K1164" t="inlineStr">
+        <is>
+          <t>favor</t>
+        </is>
+      </c>
+      <c r="L1164" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1164" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1164" t="inlineStr">
+        <is>
+          <t>favor</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1164"/>
+  <dimension ref="A1:N1173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65238,6 +65238,496 @@
         </is>
       </c>
     </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>Al menos 400 menores bajo protección del ICBF terminaron respondiendo ante la justicia: Procuraduría</t>
+        </is>
+      </c>
+      <c r="B1165" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi3wFBVV95cUxQUVc3RUNNbmdXSHVDem1mS0ZwendidFd3Vi1wMmtfa01OWExabHRDRUI0X29PVHZQSHZDa1ZRWEZWR2tlM0o0dXkwLUViNE5OSDFyM0NHbGdNdEJBazdpakF4TjRoMlg4Z3FXcUF5WkJncDhDMktWa0NkY0tUb2VVcTk3LTEtVVNpU2pfcWE2U2tHZVVRX21XblhUM3lrcGhJX0txcm5RdkVFWFMwQ1dLVDhDN0ZCWEFrTS1rei1qYUhLSVBoUmNvWm90N0FJV2YzY0liQ2JLTlNYdDBBb1RJ0gHkAUFVX3lxTFA5TkJ3ekpzY19OTXVxeHQzcTRnaWFRNXdCaUlCb1MtOW9peURaUm1Yb0ZqRmw4ZEQwcVFIX2dTUXFuRFN3eWQ2X1hTVEZVUTdocnhpUmhIQXVkX2pQTWpFMlkyZXpnWVRPcjRRREk0X09nc2I5SmkxaGl3TTBVNE9wVU5QSTgxdWtUcDhuRDU3TE5ZeFBkV3lyY2ZSekdDZjRVcjBPV1ZLWFMxOTFKR0RqbTNBc19xQlZZNkxrbVVjM1hITHlEaWlCaXVBaWVsNG9xWFk5UGNtVFZUTmdYd3dKTXc5Sw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1165" t="inlineStr">
+        <is>
+          <t>Revista Semana</t>
+        </is>
+      </c>
+      <c r="D1165" t="inlineStr"/>
+      <c r="E1165" t="inlineStr"/>
+      <c r="F1165" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1165" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1165" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1165" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1165" t="n">
+        <v>11</v>
+      </c>
+      <c r="K1165" t="inlineStr">
+        <is>
+          <t>justicia</t>
+        </is>
+      </c>
+      <c r="L1165" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1165" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1165" t="inlineStr">
+        <is>
+          <t>justice</t>
+        </is>
+      </c>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>Crisis institucional: denuncian grave falla para atender menores víctimas de violencia que quedan a cargo del ICBF</t>
+        </is>
+      </c>
+      <c r="B1166" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi8gFBVV95cUxPV2JaS1pVR1M1WXlvaFF5Mms5QUNlMXVkSjFZSDBtQUhiOHpKZzRIXzdlVlJmNzhYUlJPS29ETGZUQS1lVFJ3ZngxMi1MMkR1RGtkWE1mbFpIVXQzdVVTcnczbGhXdHZQNERzTi1vWW9NWDhTVFBmY181Z3RjY1Q5czRySm9qSDRfZ0NWUVdZazdnZ0ZQVldBdXpaMUJXaHFLc3hKM3BYLUJaTWVKd0NuRVBXbHlJZjNEajdsQ2VacTZ5c2ZCSXpjc3o2NGpGdkl0RFNlbnhsbU5YQ2J5SDNhTHRfdi1BVEZrMHJKa25qaTNnZ9IB9wFBVV95cUxOVW5FSU03bm1JSXdIVHdmVWtKRld1cWIyVXdDQ2dYQkxzQTlmMjNfLXpFel9VVGI1OU9XTjlqMjlmVzQtbnVqa2ZKX1A3eGJtQVZzMjUwblkzQkVHcE8zNlRtOVF6MG9wN1VIRlgzUi1oYXZoeEdKU0xMUU92STd1RHk3S2NrMGhJeXdCSk5zS21TN0tsYUJmMnN1RFBNay1yXzhoMlFKbXVwdnBzemo5QTluZnZqZ3o3ZUIzZHhOdDdkTWVyNzhOVmQ5Wk1IanlLaTVrLUZYWTloREI2a1FIZk1iMnc5ZC1aOENZaExialFDOFJ1dG9B?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1166" t="inlineStr">
+        <is>
+          <t>Revista Semana</t>
+        </is>
+      </c>
+      <c r="D1166" t="inlineStr"/>
+      <c r="E1166" t="inlineStr"/>
+      <c r="F1166" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1166" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1166" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1166" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1166" t="n">
+        <v>11</v>
+      </c>
+      <c r="K1166" t="inlineStr">
+        <is>
+          <t>grave</t>
+        </is>
+      </c>
+      <c r="L1166" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1166" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1166" t="inlineStr">
+        <is>
+          <t>severe</t>
+        </is>
+      </c>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>Crisis institucional: denuncian grave falla para atender menores víctimas de violencia que quedan a cargo del ICBF</t>
+        </is>
+      </c>
+      <c r="B1167" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi8gFBVV95cUxPV2JaS1pVR1M1WXlvaFF5Mms5QUNlMXVkSjFZSDBtQUhiOHpKZzRIXzdlVlJmNzhYUlJPS29ETGZUQS1lVFJ3ZngxMi1MMkR1RGtkWE1mbFpIVXQzdVVTcnczbGhXdHZQNERzTi1vWW9NWDhTVFBmY181Z3RjY1Q5czRySm9qSDRfZ0NWUVdZazdnZ0ZQVldBdXpaMUJXaHFLc3hKM3BYLUJaTWVKd0NuRVBXbHlJZjNEajdsQ2VacTZ5c2ZCSXpjc3o2NGpGdkl0RFNlbnhsbU5YQ2J5SDNhTHRfdi1BVEZrMHJKa25qaTNnZ9IB9wFBVV95cUxOVW5FSU03bm1JSXdIVHdmVWtKRld1cWIyVXdDQ2dYQkxzQTlmMjNfLXpFel9VVGI1OU9XTjlqMjlmVzQtbnVqa2ZKX1A3eGJtQVZzMjUwblkzQkVHcE8zNlRtOVF6MG9wN1VIRlgzUi1oYXZoeEdKU0xMUU92STd1RHk3S2NrMGhJeXdCSk5zS21TN0tsYUJmMnN1RFBNay1yXzhoMlFKbXVwdnBzemo5QTluZnZqZ3o3ZUIzZHhOdDdkTWVyNzhOVmQ5Wk1IanlLaTVrLUZYWTloREI2a1FIZk1iMnc5ZC1aOENZaExialFDOFJ1dG9B?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1167" t="inlineStr">
+        <is>
+          <t>Revista Semana</t>
+        </is>
+      </c>
+      <c r="D1167" t="inlineStr"/>
+      <c r="E1167" t="inlineStr"/>
+      <c r="F1167" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1167" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1167" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1167" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1167" t="n">
+        <v>11</v>
+      </c>
+      <c r="K1167" t="inlineStr">
+        <is>
+          <t>falla</t>
+        </is>
+      </c>
+      <c r="L1167" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1167" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1167" t="inlineStr">
+        <is>
+          <t>fails</t>
+        </is>
+      </c>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>Crisis institucional: denuncian grave falla para atender menores víctimas de violencia que quedan a cargo del ICBF</t>
+        </is>
+      </c>
+      <c r="B1168" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi8gFBVV95cUxPV2JaS1pVR1M1WXlvaFF5Mms5QUNlMXVkSjFZSDBtQUhiOHpKZzRIXzdlVlJmNzhYUlJPS29ETGZUQS1lVFJ3ZngxMi1MMkR1RGtkWE1mbFpIVXQzdVVTcnczbGhXdHZQNERzTi1vWW9NWDhTVFBmY181Z3RjY1Q5czRySm9qSDRfZ0NWUVdZazdnZ0ZQVldBdXpaMUJXaHFLc3hKM3BYLUJaTWVKd0NuRVBXbHlJZjNEajdsQ2VacTZ5c2ZCSXpjc3o2NGpGdkl0RFNlbnhsbU5YQ2J5SDNhTHRfdi1BVEZrMHJKa25qaTNnZ9IB9wFBVV95cUxOVW5FSU03bm1JSXdIVHdmVWtKRld1cWIyVXdDQ2dYQkxzQTlmMjNfLXpFel9VVGI1OU9XTjlqMjlmVzQtbnVqa2ZKX1A3eGJtQVZzMjUwblkzQkVHcE8zNlRtOVF6MG9wN1VIRlgzUi1oYXZoeEdKU0xMUU92STd1RHk3S2NrMGhJeXdCSk5zS21TN0tsYUJmMnN1RFBNay1yXzhoMlFKbXVwdnBzemo5QTluZnZqZ3o3ZUIzZHhOdDdkTWVyNzhOVmQ5Wk1IanlLaTVrLUZYWTloREI2a1FIZk1iMnc5ZC1aOENZaExialFDOFJ1dG9B?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1168" t="inlineStr">
+        <is>
+          <t>Revista Semana</t>
+        </is>
+      </c>
+      <c r="D1168" t="inlineStr"/>
+      <c r="E1168" t="inlineStr"/>
+      <c r="F1168" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1168" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1168" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1168" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1168" t="n">
+        <v>11</v>
+      </c>
+      <c r="K1168" t="inlineStr">
+        <is>
+          <t>víctimas</t>
+        </is>
+      </c>
+      <c r="L1168" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1168" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1168" t="inlineStr">
+        <is>
+          <t>victimized</t>
+        </is>
+      </c>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>Crisis institucional: denuncian grave falla para atender menores víctimas de violencia que quedan a cargo del ICBF</t>
+        </is>
+      </c>
+      <c r="B1169" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi8gFBVV95cUxPV2JaS1pVR1M1WXlvaFF5Mms5QUNlMXVkSjFZSDBtQUhiOHpKZzRIXzdlVlJmNzhYUlJPS29ETGZUQS1lVFJ3ZngxMi1MMkR1RGtkWE1mbFpIVXQzdVVTcnczbGhXdHZQNERzTi1vWW9NWDhTVFBmY181Z3RjY1Q5czRySm9qSDRfZ0NWUVdZazdnZ0ZQVldBdXpaMUJXaHFLc3hKM3BYLUJaTWVKd0NuRVBXbHlJZjNEajdsQ2VacTZ5c2ZCSXpjc3o2NGpGdkl0RFNlbnhsbU5YQ2J5SDNhTHRfdi1BVEZrMHJKa25qaTNnZ9IB9wFBVV95cUxOVW5FSU03bm1JSXdIVHdmVWtKRld1cWIyVXdDQ2dYQkxzQTlmMjNfLXpFel9VVGI1OU9XTjlqMjlmVzQtbnVqa2ZKX1A3eGJtQVZzMjUwblkzQkVHcE8zNlRtOVF6MG9wN1VIRlgzUi1oYXZoeEdKU0xMUU92STd1RHk3S2NrMGhJeXdCSk5zS21TN0tsYUJmMnN1RFBNay1yXzhoMlFKbXVwdnBzemo5QTluZnZqZ3o3ZUIzZHhOdDdkTWVyNzhOVmQ5Wk1IanlLaTVrLUZYWTloREI2a1FIZk1iMnc5ZC1aOENZaExialFDOFJ1dG9B?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1169" t="inlineStr">
+        <is>
+          <t>Revista Semana</t>
+        </is>
+      </c>
+      <c r="D1169" t="inlineStr"/>
+      <c r="E1169" t="inlineStr"/>
+      <c r="F1169" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1169" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1169" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1169" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1169" t="n">
+        <v>11</v>
+      </c>
+      <c r="K1169" t="inlineStr">
+        <is>
+          <t>violencia</t>
+        </is>
+      </c>
+      <c r="L1169" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1169" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1169" t="inlineStr">
+        <is>
+          <t>violence</t>
+        </is>
+      </c>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>“Niños estarían siendo instrumentalizados”: alerta del ICBF por grave crisis de orden público en Ataco</t>
+        </is>
+      </c>
+      <c r="B1170" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiygFBVV95cUxOdk9jRVlQcVBtTG9tQkVlVEFvZVA1bEZ3Ykg1THIya1RHQlhLMklhSVZXYUVKWFhrRXk4eUo0Z3VhZUFya0dkYjRDTHBNZDBEN09RQXd5a0U3eklrWlBuak9hTnRuM2o1bHBnRzJQM0Q5SDBkZy0taUM0MzBCdXMwTFpqS1ZYSjB1VmpUdmp6Q29yMUw0VTFGVVdlZ1NRNXNZMmtrVkxIWGNPYlBTd3loMkEyS3N3dDNmbXY2V2hnZnJxQWJhOGxXUDhn?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1170" t="inlineStr">
+        <is>
+          <t>vozdelpueblo920am.com</t>
+        </is>
+      </c>
+      <c r="D1170" t="inlineStr"/>
+      <c r="E1170" t="inlineStr"/>
+      <c r="F1170" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1170" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1170" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1170" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1170" t="n">
+        <v>11</v>
+      </c>
+      <c r="K1170" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="L1170" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1170" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N1170" t="inlineStr">
+        <is>
+          <t>alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>“Niños estarían siendo instrumentalizados”: alerta del ICBF por grave crisis de orden público en Ataco</t>
+        </is>
+      </c>
+      <c r="B1171" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiygFBVV95cUxOdk9jRVlQcVBtTG9tQkVlVEFvZVA1bEZ3Ykg1THIya1RHQlhLMklhSVZXYUVKWFhrRXk4eUo0Z3VhZUFya0dkYjRDTHBNZDBEN09RQXd5a0U3eklrWlBuak9hTnRuM2o1bHBnRzJQM0Q5SDBkZy0taUM0MzBCdXMwTFpqS1ZYSjB1VmpUdmp6Q29yMUw0VTFGVVdlZ1NRNXNZMmtrVkxIWGNPYlBTd3loMkEyS3N3dDNmbXY2V2hnZnJxQWJhOGxXUDhn?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1171" t="inlineStr">
+        <is>
+          <t>vozdelpueblo920am.com</t>
+        </is>
+      </c>
+      <c r="D1171" t="inlineStr"/>
+      <c r="E1171" t="inlineStr"/>
+      <c r="F1171" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1171" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1171" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1171" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1171" t="n">
+        <v>11</v>
+      </c>
+      <c r="K1171" t="inlineStr">
+        <is>
+          <t>grave</t>
+        </is>
+      </c>
+      <c r="L1171" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1171" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1171" t="inlineStr">
+        <is>
+          <t>severe</t>
+        </is>
+      </c>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>“Niños estarían siendo instrumentalizados”: alerta del ICBF por grave crisis de orden público en Ataco</t>
+        </is>
+      </c>
+      <c r="B1172" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiygFBVV95cUxOdk9jRVlQcVBtTG9tQkVlVEFvZVA1bEZ3Ykg1THIya1RHQlhLMklhSVZXYUVKWFhrRXk4eUo0Z3VhZUFya0dkYjRDTHBNZDBEN09RQXd5a0U3eklrWlBuak9hTnRuM2o1bHBnRzJQM0Q5SDBkZy0taUM0MzBCdXMwTFpqS1ZYSjB1VmpUdmp6Q29yMUw0VTFGVVdlZ1NRNXNZMmtrVkxIWGNPYlBTd3loMkEyS3N3dDNmbXY2V2hnZnJxQWJhOGxXUDhn?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1172" t="inlineStr">
+        <is>
+          <t>vozdelpueblo920am.com</t>
+        </is>
+      </c>
+      <c r="D1172" t="inlineStr"/>
+      <c r="E1172" t="inlineStr"/>
+      <c r="F1172" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1172" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1172" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1172" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1172" t="n">
+        <v>11</v>
+      </c>
+      <c r="K1172" t="inlineStr">
+        <is>
+          <t>crisis</t>
+        </is>
+      </c>
+      <c r="L1172" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1172" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1172" t="inlineStr">
+        <is>
+          <t>crisis</t>
+        </is>
+      </c>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>Bienestar Familiar activó rutas de protección tras desarticulación de red de explotación sexual comercial infantil en Medellín | Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="B1173" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivgFBVV95cUxNVGo3Q0ZSRUdLQmg3bjhRZUxrWWNjekpoVmNUWk5ObFQ2WUlhTWtPZGpNZl9iZW1kN1hqRm1mcDF2bVFVV3hyUmsyVWx5X2ZWNmVCXzRZalVFRmFMSlRaOFNvOHFqcEFlRkdsS05SSUxSYnpGaW1kYjljOGtqLVdNdElfRU4waG01M05DQUVvNVFUcGpfd2trb1I3cHRucVBGaGhQZWtFM3pmbHh6eG9kNXY1dldqcC1kQkFDWXhn?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1173" t="inlineStr">
+        <is>
+          <t>Portal ICBF - Instituto Colombiano de Bienestar Familiar ICBF</t>
+        </is>
+      </c>
+      <c r="D1173" t="inlineStr">
+        <is>
+          <t>Medellín</t>
+        </is>
+      </c>
+      <c r="E1173" t="inlineStr"/>
+      <c r="F1173" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1173" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1173" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1173" t="inlineStr">
+        <is>
+          <t>domingo</t>
+        </is>
+      </c>
+      <c r="J1173" t="n">
+        <v>10</v>
+      </c>
+      <c r="K1173" t="inlineStr">
+        <is>
+          <t>infantil</t>
+        </is>
+      </c>
+      <c r="L1173" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1173" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1173" t="inlineStr">
+        <is>
+          <t>childish</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1173"/>
+  <dimension ref="A1:N1175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65728,6 +65728,118 @@
         </is>
       </c>
     </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>ICBF pide medidas urgentes para proteger a niños usados en asonadas contra la Fuerza Pública en Ataco</t>
+        </is>
+      </c>
+      <c r="B1174" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMixAFBVV95cUxPN1NYb1VwN3ItVnN6Zm9qX3dZZGlNVEJRYzhFZWppbkJ4UVRoNzRza3M2a1VWTnJ1X09ZaUZWZzZJNU03dGNfdjUzWEE0VWpEVFk1UHlOLU5Nekhsa0p1UmxuQTZQMUhsUjFqZkc3MFJuX0hNNE1JMUVMVUFTckphSTloZkFiV0U2VTVtU21mSndHVE9wa21peFBOS05VRW9MR29CQlRDbHZPV3BWZjlUb2hNODktamh5OWJyQ2gyWXd5bWIw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1174" t="inlineStr">
+        <is>
+          <t>Ecos del Combeima</t>
+        </is>
+      </c>
+      <c r="D1174" t="inlineStr"/>
+      <c r="E1174" t="inlineStr"/>
+      <c r="F1174" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1174" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1174" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1174" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1174" t="n">
+        <v>11</v>
+      </c>
+      <c r="K1174" t="inlineStr">
+        <is>
+          <t>proteger</t>
+        </is>
+      </c>
+      <c r="L1174" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1174" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1174" t="inlineStr">
+        <is>
+          <t>protect</t>
+        </is>
+      </c>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>ICBF pide medidas urgentes para proteger a niños tras asonada en Ataco, Tolima</t>
+        </is>
+      </c>
+      <c r="B1175" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMisgFBVV95cUxPR2h2S0ZUYklKWENPeTlwdEltVjJ2X1Bzc0FGVjBQQjRBNmFEWW9sd1hjU29UZ3RHUjc2MXNLcGN5b1gxYVJwbzh4S056WFI5RFJ3TlhEaVJ0Q2RxbENxQkRLWk9DYlE0T1RXT3hvU1BUcUlDbkVud0lfczlOYnM4SENyY0V1bDRsZFJXa2xOQWdYbVB3VHpmekk3MHdDcEtSaWdoSGhGb253ODBPaUk2X2dn0gHGAUFVX3lxTE52clVtRnBiSmhRR09Udm5rdU1YLUtGNm80V29TZE9pdnViaXp3R1JfY2dRVEpwZTZQRnNqb1E1a2Fmbko5ZFJHRzhuRUdZd2syTzJ0Z0R4VU1sRkJiaFJqRkZiWE9hOFpEZXJ6dXBkc3FjeEU5UG5PTmdnN0RWSlJmNEhBTUZCbVQwb2NHakZab2hwYkpoTnpwY0Z4M0hYZWpsZkQxR3NKLW1BTDRBMnh2SVhDMkFSQVIxd0tnMzZmbXZkUnprdw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1175" t="inlineStr">
+        <is>
+          <t>Caracol Radio</t>
+        </is>
+      </c>
+      <c r="D1175" t="inlineStr"/>
+      <c r="E1175" t="inlineStr">
+        <is>
+          <t>Tolima</t>
+        </is>
+      </c>
+      <c r="F1175" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1175" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1175" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1175" t="inlineStr">
+        <is>
+          <t>lunes</t>
+        </is>
+      </c>
+      <c r="J1175" t="n">
+        <v>11</v>
+      </c>
+      <c r="K1175" t="inlineStr">
+        <is>
+          <t>proteger</t>
+        </is>
+      </c>
+      <c r="L1175" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1175" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1175" t="inlineStr">
+        <is>
+          <t>protect</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1175"/>
+  <dimension ref="A1:N1180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -65840,6 +65840,276 @@
         </is>
       </c>
     </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>“No podemos esperar otra tragedia”: Personería de Nuquí alerta crisis alimentaria tras muerte de niño vinculado a programa del ICBF</t>
+        </is>
+      </c>
+      <c r="B1176" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi5wFBVV95cUxNQ2N3X1NaMkV1QnY2X3JNRzhzQjhFQ1F5RjRlQzBuTTVjNnBWTVl5YnJBT1hJckpEVHBHUmluNTJjNXJHQjVzRVU1WEVBQ0ZfemVzeUI2TmlfaWNRRVd0TmhLejVQTVNCakpCdThPby12LXkzc3JtVno3YlBPd0ZjMkEweDhRLWFmTTJwd1FMbmozeVpqTHNid2pyMHpWbjVEaFJVOUJPTWlKbHVFV0hWeWpMMWthYWREQWN5V19DUjBxd0VIMW9Pb0ptWktNOUYtNG1uaFYycTRnVEhRZXJSWjVxT2pYa2c?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1176" t="inlineStr">
+        <is>
+          <t>Chocó 7 días</t>
+        </is>
+      </c>
+      <c r="D1176" t="inlineStr"/>
+      <c r="E1176" t="inlineStr"/>
+      <c r="F1176" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1176" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1176" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1176" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1176" t="n">
+        <v>12</v>
+      </c>
+      <c r="K1176" t="inlineStr">
+        <is>
+          <t>esperar</t>
+        </is>
+      </c>
+      <c r="L1176" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1176" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N1176" t="inlineStr">
+        <is>
+          <t>await</t>
+        </is>
+      </c>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>“No podemos esperar otra tragedia”: Personería de Nuquí alerta crisis alimentaria tras muerte de niño vinculado a programa del ICBF</t>
+        </is>
+      </c>
+      <c r="B1177" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi5wFBVV95cUxNQ2N3X1NaMkV1QnY2X3JNRzhzQjhFQ1F5RjRlQzBuTTVjNnBWTVl5YnJBT1hJckpEVHBHUmluNTJjNXJHQjVzRVU1WEVBQ0ZfemVzeUI2TmlfaWNRRVd0TmhLejVQTVNCakpCdThPby12LXkzc3JtVno3YlBPd0ZjMkEweDhRLWFmTTJwd1FMbmozeVpqTHNid2pyMHpWbjVEaFJVOUJPTWlKbHVFV0hWeWpMMWthYWREQWN5V19DUjBxd0VIMW9Pb0ptWktNOUYtNG1uaFYycTRnVEhRZXJSWjVxT2pYa2c?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1177" t="inlineStr">
+        <is>
+          <t>Chocó 7 días</t>
+        </is>
+      </c>
+      <c r="D1177" t="inlineStr"/>
+      <c r="E1177" t="inlineStr"/>
+      <c r="F1177" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1177" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1177" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1177" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1177" t="n">
+        <v>12</v>
+      </c>
+      <c r="K1177" t="inlineStr">
+        <is>
+          <t>tragedia</t>
+        </is>
+      </c>
+      <c r="L1177" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1177" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1177" t="inlineStr">
+        <is>
+          <t>tragedy</t>
+        </is>
+      </c>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>“No podemos esperar otra tragedia”: Personería de Nuquí alerta crisis alimentaria tras muerte de niño vinculado a programa del ICBF</t>
+        </is>
+      </c>
+      <c r="B1178" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi5wFBVV95cUxNQ2N3X1NaMkV1QnY2X3JNRzhzQjhFQ1F5RjRlQzBuTTVjNnBWTVl5YnJBT1hJckpEVHBHUmluNTJjNXJHQjVzRVU1WEVBQ0ZfemVzeUI2TmlfaWNRRVd0TmhLejVQTVNCakpCdThPby12LXkzc3JtVno3YlBPd0ZjMkEweDhRLWFmTTJwd1FMbmozeVpqTHNid2pyMHpWbjVEaFJVOUJPTWlKbHVFV0hWeWpMMWthYWREQWN5V19DUjBxd0VIMW9Pb0ptWktNOUYtNG1uaFYycTRnVEhRZXJSWjVxT2pYa2c?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1178" t="inlineStr">
+        <is>
+          <t>Chocó 7 días</t>
+        </is>
+      </c>
+      <c r="D1178" t="inlineStr"/>
+      <c r="E1178" t="inlineStr"/>
+      <c r="F1178" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1178" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1178" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1178" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1178" t="n">
+        <v>12</v>
+      </c>
+      <c r="K1178" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="L1178" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1178" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N1178" t="inlineStr">
+        <is>
+          <t>alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>“No podemos esperar otra tragedia”: Personería de Nuquí alerta crisis alimentaria tras muerte de niño vinculado a programa del ICBF</t>
+        </is>
+      </c>
+      <c r="B1179" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi5wFBVV95cUxNQ2N3X1NaMkV1QnY2X3JNRzhzQjhFQ1F5RjRlQzBuTTVjNnBWTVl5YnJBT1hJckpEVHBHUmluNTJjNXJHQjVzRVU1WEVBQ0ZfemVzeUI2TmlfaWNRRVd0TmhLejVQTVNCakpCdThPby12LXkzc3JtVno3YlBPd0ZjMkEweDhRLWFmTTJwd1FMbmozeVpqTHNid2pyMHpWbjVEaFJVOUJPTWlKbHVFV0hWeWpMMWthYWREQWN5V19DUjBxd0VIMW9Pb0ptWktNOUYtNG1uaFYycTRnVEhRZXJSWjVxT2pYa2c?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1179" t="inlineStr">
+        <is>
+          <t>Chocó 7 días</t>
+        </is>
+      </c>
+      <c r="D1179" t="inlineStr"/>
+      <c r="E1179" t="inlineStr"/>
+      <c r="F1179" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1179" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1179" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1179" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1179" t="n">
+        <v>12</v>
+      </c>
+      <c r="K1179" t="inlineStr">
+        <is>
+          <t>crisis</t>
+        </is>
+      </c>
+      <c r="L1179" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1179" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1179" t="inlineStr">
+        <is>
+          <t>crisis</t>
+        </is>
+      </c>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>“No podemos esperar otra tragedia”: Personería de Nuquí alerta crisis alimentaria tras muerte de niño vinculado a programa del ICBF</t>
+        </is>
+      </c>
+      <c r="B1180" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi5wFBVV95cUxNQ2N3X1NaMkV1QnY2X3JNRzhzQjhFQ1F5RjRlQzBuTTVjNnBWTVl5YnJBT1hJckpEVHBHUmluNTJjNXJHQjVzRVU1WEVBQ0ZfemVzeUI2TmlfaWNRRVd0TmhLejVQTVNCakpCdThPby12LXkzc3JtVno3YlBPd0ZjMkEweDhRLWFmTTJwd1FMbmozeVpqTHNid2pyMHpWbjVEaFJVOUJPTWlKbHVFV0hWeWpMMWthYWREQWN5V19DUjBxd0VIMW9Pb0ptWktNOUYtNG1uaFYycTRnVEhRZXJSWjVxT2pYa2c?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1180" t="inlineStr">
+        <is>
+          <t>Chocó 7 días</t>
+        </is>
+      </c>
+      <c r="D1180" t="inlineStr"/>
+      <c r="E1180" t="inlineStr"/>
+      <c r="F1180" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1180" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1180" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1180" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1180" t="n">
+        <v>12</v>
+      </c>
+      <c r="K1180" t="inlineStr">
+        <is>
+          <t>muerte</t>
+        </is>
+      </c>
+      <c r="L1180" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1180" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1180" t="inlineStr">
+        <is>
+          <t>death</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1180"/>
+  <dimension ref="A1:N1182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66110,6 +66110,114 @@
         </is>
       </c>
     </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>ICBF apoya el proyecto de la reforma a la salud: podría salvar vidas de más niños</t>
+        </is>
+      </c>
+      <c r="B1181" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiqwFBVV95cUxQTHRZQzc0TlhRVjE0ZXNaQlk2a0tTcWJ0WDlxZEVCNFNBYi1keW05RHhPZHlVbkRyZFhqamtPOUY5S0xIWHpTTTFBeVlIeGdoeUxJMFFPUGlrQ29rNGFvajhMcDRTRy16UlNvXy1aaVZSODRKQU5aQ1B6aTAzMjJGODhYMFNXYjhQczVMVi1MTGVMc0diRWtXV2tpd0NHRm5QMUNjWXZVNDlPVlXSAasBQVVfeXFMTzMxcS1POGRHLWstOWo1amVrMFdNS3JGOW5GeHVzdzVEaFZCcmJVQVYwVVVkYkJGeFE5RTliUUtieExYU3JyZ3VINUYzdUsyRXNmU3pwTGlHeFdjaGZFS29oSmM0TEhmV2ZxLUhvWnRtTi1XdlZQM1VfYlZkQlhZcEd6QkE4d1RTOF8xRnpGM1dUMWhmNXRBUXNLemtwWlFiNXh4WEZDVTNGT09Z?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1181" t="inlineStr">
+        <is>
+          <t>La FM</t>
+        </is>
+      </c>
+      <c r="D1181" t="inlineStr"/>
+      <c r="E1181" t="inlineStr"/>
+      <c r="F1181" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1181" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H1181" t="n">
+        <v>4</v>
+      </c>
+      <c r="I1181" t="inlineStr">
+        <is>
+          <t>martes</t>
+        </is>
+      </c>
+      <c r="J1181" t="n">
+        <v>18</v>
+      </c>
+      <c r="K1181" t="inlineStr">
+        <is>
+          <t>salvar</t>
+        </is>
+      </c>
+      <c r="L1181" t="inlineStr">
+        <is>
+          <t>Astrid Cáceres</t>
+        </is>
+      </c>
+      <c r="M1181" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1181" t="inlineStr">
+        <is>
+          <t>save</t>
+        </is>
+      </c>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>MinHacienda llevó al Congreso proyecto de ley para incrementar presupuesto del Icbf</t>
+        </is>
+      </c>
+      <c r="B1182" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMixgFBVV95cUxPZU1wSldBQVB4MXZOOWJGR1hWSGdCcktPQTE2THFUYlNwZUVmN0IzZ21SdnI3WDB3Y3FvTWVmTUZHZkUtMTBVWXRreXBLeFN6WC01akpOWWhfYTBoYUJUeWVYbTJNMzh3UzNYQ3ZCTUhSM1pOVUl0TU5DMV8tVUIwQWRSQ2FLT29WRE9YbFVCNTY2dWx6M3BjTFhUaUJnX3lWREZIWjd6c0UzcXF0MklOWm1VNU5FMHp1TWJmNjRRcE5aN1JoaGfSAcYBQVVfeXFMUEVmWFJBdlBLNFU1VFFCVTVCV3FuSVViYWtvdlhfcVZGRkZpTU4tdllMNnJoNm1iNGUydW90M2lTaGZRYnM4bk1qSWdnRnNVMVRHUGtOY2c2RnVHQjNrUW9DcUZtenBPeHl0N04waWYzcTd1TGZPZ1VTQ3QxNlZOc2p1N1A2M1JzWW9vOS1Kb3V4YTVDVk8zblJmRUdleXJ4c1dzdlRGdHl6REx5QnBSRkdLaGhqWUNNNmVYN3Z1cGhsSE9UXzBR?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1182" t="inlineStr">
+        <is>
+          <t>LaRepublica.co</t>
+        </is>
+      </c>
+      <c r="D1182" t="inlineStr"/>
+      <c r="E1182" t="inlineStr"/>
+      <c r="F1182" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1182" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1182" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1182" t="inlineStr">
+        <is>
+          <t>miércoles</t>
+        </is>
+      </c>
+      <c r="J1182" t="n">
+        <v>13</v>
+      </c>
+      <c r="K1182" t="inlineStr">
+        <is>
+          <t>incrementar</t>
+        </is>
+      </c>
+      <c r="L1182" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1182" t="n">
+        <v>1</v>
+      </c>
+      <c r="N1182" t="inlineStr">
+        <is>
+          <t>increase</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1182"/>
+  <dimension ref="A1:N1184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66218,6 +66218,114 @@
         </is>
       </c>
     </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>Casos de violencia sexual lideran las atenciones de protección infantil del Icbf en 2026</t>
+        </is>
+      </c>
+      <c r="B1183" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMizgFBVV95cUxNaHlybXFPQTlyLXphVGlJZ1U0UmI1ODVsOXBJZEZhUmFPdlhDVnMxbXk0UVBBNklFMG9nZEV6TVVtdFJJRHo1dTVjUDZBZ19lbl8xY3o4OVlfNU1VOEVBa1FzOTA5b0JtUzJ4NlhJbkp3OG9Nb2luNXRTcE1lWTA4SHItTURSX0pralRvelRBY1NFTDhvbTRDem4zUjJZZ25QWV83TXBQNVBGeUJyaE9RdGhtcm9pVmwxOThSTnY2cHk2YlZ6dlFSYlN2ZFFVQdIB6AFBVV95cUxQZUNwYVd0TjlmOUxjX0xKUzROOExibkZab2FSemYybzk5NnllTEJEWWdEQXl3QjVmdXVHaDdyUTZCVnBodHFRWVh6Qk1GSFFuZzA2cTdiT1lYZEZ2SlQ0NkFiMk1Gdjc2UEptNExXRjBleVVKSVhuNnpqYmxBb3BNZlQ3eXdPbVRPcDkyRXl3aTlFTk4xbkgydWd4SURpQy1SdXkwVkVXN3E1UkZva1hBbkdCTl9nMHI2V3lGaFBRYUV3VndObjBTVndxMFdGZUl6RmwtR3ZSdzF1RFJTS2RoYjRFLW5OMWVX?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1183" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D1183" t="inlineStr"/>
+      <c r="E1183" t="inlineStr"/>
+      <c r="F1183" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1183" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1183" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1183" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1183" t="n">
+        <v>14</v>
+      </c>
+      <c r="K1183" t="inlineStr">
+        <is>
+          <t>violencia</t>
+        </is>
+      </c>
+      <c r="L1183" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1183" t="n">
+        <v>-3</v>
+      </c>
+      <c r="N1183" t="inlineStr">
+        <is>
+          <t>violence</t>
+        </is>
+      </c>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>Casos de violencia sexual lideran las atenciones de protección infantil del Icbf en 2026</t>
+        </is>
+      </c>
+      <c r="B1184" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMizgFBVV95cUxNaHlybXFPQTlyLXphVGlJZ1U0UmI1ODVsOXBJZEZhUmFPdlhDVnMxbXk0UVBBNklFMG9nZEV6TVVtdFJJRHo1dTVjUDZBZ19lbl8xY3o4OVlfNU1VOEVBa1FzOTA5b0JtUzJ4NlhJbkp3OG9Nb2luNXRTcE1lWTA4SHItTURSX0pralRvelRBY1NFTDhvbTRDem4zUjJZZ25QWV83TXBQNVBGeUJyaE9RdGhtcm9pVmwxOThSTnY2cHk2YlZ6dlFSYlN2ZFFVQdIB6AFBVV95cUxQZUNwYVd0TjlmOUxjX0xKUzROOExibkZab2FSemYybzk5NnllTEJEWWdEQXl3QjVmdXVHaDdyUTZCVnBodHFRWVh6Qk1GSFFuZzA2cTdiT1lYZEZ2SlQ0NkFiMk1Gdjc2UEptNExXRjBleVVKSVhuNnpqYmxBb3BNZlQ3eXdPbVRPcDkyRXl3aTlFTk4xbkgydWd4SURpQy1SdXkwVkVXN3E1UkZva1hBbkdCTl9nMHI2V3lGaFBRYUV3VndObjBTVndxMFdGZUl6RmwtR3ZSdzF1RFJTS2RoYjRFLW5OMWVX?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1184" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D1184" t="inlineStr"/>
+      <c r="E1184" t="inlineStr"/>
+      <c r="F1184" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1184" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1184" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1184" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1184" t="n">
+        <v>14</v>
+      </c>
+      <c r="K1184" t="inlineStr">
+        <is>
+          <t>infantil</t>
+        </is>
+      </c>
+      <c r="L1184" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1184" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1184" t="inlineStr">
+        <is>
+          <t>childish</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1184"/>
+  <dimension ref="A1:N1190"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66326,6 +66326,334 @@
         </is>
       </c>
     </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>ICBF visitó la casa de Aida Victoria Merlano; recibieron alerta de Juan David Tejada</t>
+        </is>
+      </c>
+      <c r="B1185" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiyAFBVV95cUxNSkx3TWpic0xpUEtyUC11RDNQbHMwUjJJUmV3UVVjbHVTM1F2eE02RDJTaWhJcWdzUHdJaTlqaktrRm5TNGhQUlJpN29BNVJrbmFQZ0M4WDRSOExyd0tNSEtidHpBQUJfU1p0Z2s1UEVrdkNvMUhPc2lZTzNiSUwybk1rX3VxZkhYSFpHSFhRckUzby1aV3pVeDV3S2NxUFlEN0Fnb09kdUl4bmxRR2tPWW1HUEMySzNKRGo2VmlfUUxNcWxwODJZTNIBzgFBVV95cUxOdlNReVY5NlZlbkNEZ2FPMzdBcWY5TklXR2RxTm8tZ1lSVVk5MlY5Mi1neHA2OV9Rd1N0S2pPWjBaeEZWU09NUmFHb0h4M1k0S1hUU3IySFA2cERMZ0w2UDl6blFqb3BpbGNxRll5d0FNRVVIMFVfR3FYRU1MNDU1NkZ3Tl9KamZ2clRmTHhqY1ljQTQ4Q0tyZzJsWjJtYVk3bk5rNzJPc1lhUUdkR0FOa3hnSjhXVk9QVzJtWU16VE5NM2xQWFd3YnlEczhXdw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1185" t="inlineStr">
+        <is>
+          <t>Revista Semana</t>
+        </is>
+      </c>
+      <c r="D1185" t="inlineStr"/>
+      <c r="E1185" t="inlineStr"/>
+      <c r="F1185" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1185" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1185" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1185" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1185" t="n">
+        <v>14</v>
+      </c>
+      <c r="K1185" t="inlineStr">
+        <is>
+          <t>alerta</t>
+        </is>
+      </c>
+      <c r="L1185" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1185" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N1185" t="inlineStr">
+        <is>
+          <t>alert</t>
+        </is>
+      </c>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>Aida Victoria Merlano fue denunciada ante el Bienestar Familiar por ‘El Agropecuario’: la acusó de abandonar a su hijo para participar en ‘La mansión VIP’</t>
+        </is>
+      </c>
+      <c r="B1186" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMipwJBVV95cUxORkw2bkhiMHRFUVR6SUZtaG1BcWpnLW9ZUFhoa3JGZTNBYXR1YTFsZ3M0clUzVlB0V0pQWnlZcHdOSGw1bmtxTVVza0o1R1VIMUphblRXVlNKc1l2Q0pvV0lJZzJ1X190eWdwVTZRODRJQmcwNmhHOFRVd1RrRnc4OEpmaUp5ekpjTnhqX0RGaHRKY1loT0lib1ZCSjl3NEx5c1VwX3V3NlNoX1BYTEFrMC1GQTlWQzJhLWdubktrRHQwRm9LSFRVMVQ0LUxLd0M0UlFDRjdnZlVvbC1TSC0zUlR0TUZvd25yMXlKNFJwRGJ6NGFFQ3YxTGxVOVJLTWp1bDdaY3BpNzE2bndGcnlWNXExUEIyU3lvN0tVT2RYYTNoVjNVbVcw0gHCAkFVX3lxTFBZeVV4bG9OYjNtX2JxWVA1UzIxZzNpNjUzdkpuN0dJWnF4RFI0eDBCOUpsRm1fVjhwSWltWUdfcE5HY1llbU5zZ21KSXhoc3REdUNWQkJENl9yYlRxaVR5UG85NGZsLThmdFpzaFJNSzBOd21tTzJOWWlqc3drS3lnLWktS040NTJxZ0ZVLVVjc1hmRTRfQ041OU91Y2hFTUNHQ3NRbGtFUkVqdTFaWGU0X3NIdTg5dkdaYzJ4WGoyMnpldFhqdXJaUjhLRkFGVURCY1g2TnZKR3EzekhRaUJIYU8ybTJMeTVGVldwOFI0ejhZV1dVTFBJMmpKS1NodUVQenY4R3hibUQ1LUktZEVLcWN6OWozc0RwSk5fQ2pWekF4YTVWdzR2cFlWOTFZTndabGdJbV9SamRqaVEzRHBJcmc?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1186" t="inlineStr">
+        <is>
+          <t>Infobae</t>
+        </is>
+      </c>
+      <c r="D1186" t="inlineStr"/>
+      <c r="E1186" t="inlineStr"/>
+      <c r="F1186" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1186" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1186" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1186" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1186" t="n">
+        <v>14</v>
+      </c>
+      <c r="K1186" t="inlineStr">
+        <is>
+          <t>abandonar</t>
+        </is>
+      </c>
+      <c r="L1186" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1186" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1186" t="inlineStr">
+        <is>
+          <t>abandon</t>
+        </is>
+      </c>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>Madres comunitarias del ICBF en Boyacá denuncian malas condiciones laborales y sobrecarga de trabajo</t>
+        </is>
+      </c>
+      <c r="B1187" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi1wFBVV95cUxNcjdZVjQtVHFfMmtlRFoxalZaVWZGWHJQUl9FUy1ZUnoyR2otWkRzR1U1UXM4dHZFMkM2OWt6bUZnc2x5UU9WTUVyUHBsTHhMR2dlOVFyTTJKR2NWRS14V2VjT2pDdldFNTdlX3piWjVmeHNxMF8wOXF2WkJPOUdvcUJuQkx1VzM2S0JuanYzQTY4djAxUlRfSUR3a19pcG51RVJMSlliU19yYjJlSS1tNjJSVWFEVDNCYXZaWktyRUpIbThjemdYeG5xVnF3QUtnRmV3ZFBoYw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1187" t="inlineStr">
+        <is>
+          <t>Matinal Noticias</t>
+        </is>
+      </c>
+      <c r="D1187" t="inlineStr"/>
+      <c r="E1187" t="inlineStr">
+        <is>
+          <t>Boyacá</t>
+        </is>
+      </c>
+      <c r="F1187" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1187" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1187" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1187" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1187" t="n">
+        <v>14</v>
+      </c>
+      <c r="K1187" t="inlineStr">
+        <is>
+          <t>sobrecarga</t>
+        </is>
+      </c>
+      <c r="L1187" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1187" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N1187" t="inlineStr">
+        <is>
+          <t>overload</t>
+        </is>
+      </c>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>“El Agropecuario” acusa a Aída Victoria Merlano de abandonar a su hijo por reality; le mandó el ICBF</t>
+        </is>
+      </c>
+      <c r="B1188" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiygFBVV95cUxNVXVWcFNaSUVnOUVkZHlBUWwwTUJUaV85SnE4RldEUTlna0ZRMTI5Q0hpcFUwb3RmVWJEYkRPTTlaUldybWM2QzBqd3p0bGt0NTB3WlFfVlp2T1RkeWJwMlBzd05rT0Uyb0x6VWJDTkpaM3M1elJUZEFfQnh3S3RobnczNXR0ajM5SnRrRWRnTlIzOEFJdWxycVpQY0lMcVBqQXNLa2hncVlRU0FQY2xmVWdnNDRRTEo4MVdVOUcwb3ctMlVtMy1tWXZB0gHeAUFVX3lxTE0tZnRCSERndTByV0djZXcyZm9ld3RHQ0xDUnpNbHBvWW43SU8zNnAxSUpsYy1zczhoOEQtUHNSQTBpMjduR2ZjQmVBQ3p2b3dXcS1WRWRIMGhUZW0xWUhhdHphemx6SllmUmd6YzdvLTlFT0dSMlB2dWhHZGRmSmdJWXkyc280SFpPV1RSSlhYaFhkSjM1OUN4WlZxSUVfU19OTXhqZURERmtkeThsSHRjT2NLN0NlREw1VGppUnkwNWxTMElqeHVYOUpLNm41TndqVm1wcWt3VUZJTlJhdw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1188" t="inlineStr">
+        <is>
+          <t>los40.com.co</t>
+        </is>
+      </c>
+      <c r="D1188" t="inlineStr"/>
+      <c r="E1188" t="inlineStr"/>
+      <c r="F1188" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1188" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1188" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1188" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1188" t="n">
+        <v>14</v>
+      </c>
+      <c r="K1188" t="inlineStr">
+        <is>
+          <t>acusa</t>
+        </is>
+      </c>
+      <c r="L1188" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1188" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1188" t="inlineStr">
+        <is>
+          <t>accuses</t>
+        </is>
+      </c>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>“El Agropecuario” acusa a Aída Victoria Merlano de abandonar a su hijo por reality; le mandó el ICBF</t>
+        </is>
+      </c>
+      <c r="B1189" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMiygFBVV95cUxNVXVWcFNaSUVnOUVkZHlBUWwwTUJUaV85SnE4RldEUTlna0ZRMTI5Q0hpcFUwb3RmVWJEYkRPTTlaUldybWM2QzBqd3p0bGt0NTB3WlFfVlp2T1RkeWJwMlBzd05rT0Uyb0x6VWJDTkpaM3M1elJUZEFfQnh3S3RobnczNXR0ajM5SnRrRWRnTlIzOEFJdWxycVpQY0lMcVBqQXNLa2hncVlRU0FQY2xmVWdnNDRRTEo4MVdVOUcwb3ctMlVtMy1tWXZB0gHeAUFVX3lxTE0tZnRCSERndTByV0djZXcyZm9ld3RHQ0xDUnpNbHBvWW43SU8zNnAxSUpsYy1zczhoOEQtUHNSQTBpMjduR2ZjQmVBQ3p2b3dXcS1WRWRIMGhUZW0xWUhhdHphemx6SllmUmd6YzdvLTlFT0dSMlB2dWhHZGRmSmdJWXkyc280SFpPV1RSSlhYaFhkSjM1OUN4WlZxSUVfU19OTXhqZURERmtkeThsSHRjT2NLN0NlREw1VGppUnkwNWxTMElqeHVYOUpLNm41TndqVm1wcWt3VUZJTlJhdw?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1189" t="inlineStr">
+        <is>
+          <t>los40.com.co</t>
+        </is>
+      </c>
+      <c r="D1189" t="inlineStr"/>
+      <c r="E1189" t="inlineStr"/>
+      <c r="F1189" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1189" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1189" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1189" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1189" t="n">
+        <v>14</v>
+      </c>
+      <c r="K1189" t="inlineStr">
+        <is>
+          <t>abandonar</t>
+        </is>
+      </c>
+      <c r="L1189" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1189" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1189" t="inlineStr">
+        <is>
+          <t>abandon</t>
+        </is>
+      </c>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>Ex de Aída Victoria la denunció al Bienestar por “abandonar” a su hijo, esto respondió</t>
+        </is>
+      </c>
+      <c r="B1190" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi0gFBVV95cUxQRzdGdzhHVDdFM25hcDZGWFlYcm4tVnhoeWJIdUhVR29NWWVuVHh6Rk5MRzZtdDZKV1l5dzQ0a2d6Z1hxMXF0bk5JOGVGb0RNYjhmeXhKdWgwRV93NThJeU5tbzlpZEUtOUxhRVhFbmpKeWFWb1NPOC1rQXZReU5LbDhrTzFmOHJmU0RmbnFZVXNlRWNaUkUwbXV1UU8zdUpONjNqMTFlVi0ydFhUYUFjMDdQQ2NiU0poWlVaRVlqU2gzSFdma0FfQmJOLUdkWE1FREE?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1190" t="inlineStr">
+        <is>
+          <t>Eluniversal.com.co</t>
+        </is>
+      </c>
+      <c r="D1190" t="inlineStr"/>
+      <c r="E1190" t="inlineStr"/>
+      <c r="F1190" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1190" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1190" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1190" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1190" t="n">
+        <v>14</v>
+      </c>
+      <c r="K1190" t="inlineStr">
+        <is>
+          <t>abandonar</t>
+        </is>
+      </c>
+      <c r="L1190" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1190" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1190" t="inlineStr">
+        <is>
+          <t>abandon</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1190"/>
+  <dimension ref="A1:N1193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66654,6 +66654,168 @@
         </is>
       </c>
     </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>ICBF llegó a la casa de Aída Victoria Merlano tras denuncia de Juan David Tejada</t>
+        </is>
+      </c>
+      <c r="B1191" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMizgFBVV95cUxNQmpLMGZYTS1uRlk1R3lMLTVzeUhOQWRMai1pZlBmTnVKWDVfUVA3aUZXR3ZJSGUzY0dfUXRPWFlkSVhXdEt6V2F0MkdyRGFtRmk4Zkc2R2o5X3ZOQmlfbTc5bTktYU0taWRKMGpxeGF6eVpwSldDVmNvMm5GemlFazNMM01LV1ZHVFBSTGFlUHZFM0VyTGx0bHZDLXlEVXZkY3JGa0JyeTF2WmhkbjVZZjNKZzI3cmtBbGlaaHR1am5DeTMxY3NWR3c1Vk1Dd9IB2wFBVV95cUxPbF92VmZlTmd2UFFXNXM0Z09UZ1FXVGdpOEtCZ3R2RXJIYlN2SWVPdjBHOVNjZ2tzWnZTUl92Xzh1eC1kVzhzVmIyMV9XaTAtdkllN09vbTM4TjZxa2FROElVekxXTWYwbWQ1dDJ6X0JoN1BPWXFYTllLQVd2ZmVyd05ZOEJ5cGIxdWVtdS14dkF4b2xJdTNsRHA0amh1eTBySzVCdzBkYnp3VkN2SVFoQ2ZrSFNIQ25Xa0R0NThIaHY0M2dQQzQtaXc1NWIzb3NSTDNZUFRweUZWWFE?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1191" t="inlineStr">
+        <is>
+          <t>Noticias Caracol</t>
+        </is>
+      </c>
+      <c r="D1191" t="inlineStr"/>
+      <c r="E1191" t="inlineStr"/>
+      <c r="F1191" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1191" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1191" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1191" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1191" t="n">
+        <v>14</v>
+      </c>
+      <c r="K1191" t="inlineStr">
+        <is>
+          <t>denuncia</t>
+        </is>
+      </c>
+      <c r="L1191" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1191" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1191" t="inlineStr">
+        <is>
+          <t>denounces</t>
+        </is>
+      </c>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>ICBF visita la casa de Aida Victoria Merlano tras denuncia de su expareja por el cuidado de su hijo</t>
+        </is>
+      </c>
+      <c r="B1192" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi5gFBVV95cUxNMnlTcmNkczBDTzMzWkwwaGN0T3FTTkMzU2lQSHFIaWIwVlZxUEhycU5rMkNpR2JKVWoxVmFrNWx5UlFlbkdJNjduYWxLLWV2TWZQQW9pU2tjaUFXbHNid2VfR1gyaklTTUktNE51aUYySVRPa0swMVBHTDRucXE0dWNDckFjZmZ0WE9ja0l6NENiUUgydUVUTWVzbkhiaHNwaEN1LUo4NDZ0em55M25PZkM3NTRCWV9nSW9RTXp4YXpOUEd4eGNZNk15V01JYWItcGhva3E5bGM1b2p3M1FWVjJ0Sk9Xd9IB6wFBVV95cUxObjFrLWE2ZVgwTmZ3NU54Tk5zOXNFekFIQWlxeU9GTVZkV0o5WktsUWNCSG5rYnVhVnVldUoyUndiZ2FXd3pUc0hSMldUQXppVE85Y3VzWW96RXFPVXJQMlVWcVlYc2NNOE41cXdBcnVOcTBCLWJfU1FaTXR5dlZ1V3lCM3daRTNmR3FvZmZMbnJZSklSYzFIQUFqMGhCLUNvdUdDaHFYMFlqcl9CR2R5T3pVVzJVSU11aFl6UlZRdGVoMnBvV2lqM1ZkVVdXT08wZ1dyMlo2amdfSVV6NzkzU0RpZHhNQllULUNR?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1192" t="inlineStr">
+        <is>
+          <t>elpais.com.co</t>
+        </is>
+      </c>
+      <c r="D1192" t="inlineStr"/>
+      <c r="E1192" t="inlineStr"/>
+      <c r="F1192" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1192" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1192" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1192" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1192" t="n">
+        <v>14</v>
+      </c>
+      <c r="K1192" t="inlineStr">
+        <is>
+          <t>denuncia</t>
+        </is>
+      </c>
+      <c r="L1192" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1192" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1192" t="inlineStr">
+        <is>
+          <t>denounces</t>
+        </is>
+      </c>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>ICBF visita la casa de Aida Victoria Merlano tras denuncia de su expareja por el cuidado de su hijo</t>
+        </is>
+      </c>
+      <c r="B1193" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMi5gFBVV95cUxNMnlTcmNkczBDTzMzWkwwaGN0T3FTTkMzU2lQSHFIaWIwVlZxUEhycU5rMkNpR2JKVWoxVmFrNWx5UlFlbkdJNjduYWxLLWV2TWZQQW9pU2tjaUFXbHNid2VfR1gyaklTTUktNE51aUYySVRPa0swMVBHTDRucXE0dWNDckFjZmZ0WE9ja0l6NENiUUgydUVUTWVzbkhiaHNwaEN1LUo4NDZ0em55M25PZkM3NTRCWV9nSW9RTXp4YXpOUEd4eGNZNk15V01JYWItcGhva3E5bGM1b2p3M1FWVjJ0Sk9Xd9IB6wFBVV95cUxObjFrLWE2ZVgwTmZ3NU54Tk5zOXNFekFIQWlxeU9GTVZkV0o5WktsUWNCSG5rYnVhVnVldUoyUndiZ2FXd3pUc0hSMldUQXppVE85Y3VzWW96RXFPVXJQMlVWcVlYc2NNOE41cXdBcnVOcTBCLWJfU1FaTXR5dlZ1V3lCM3daRTNmR3FvZmZMbnJZSklSYzFIQUFqMGhCLUNvdUdDaHFYMFlqcl9CR2R5T3pVVzJVSU11aFl6UlZRdGVoMnBvV2lqM1ZkVVdXT08wZ1dyMlo2amdfSVV6NzkzU0RpZHhNQllULUNR?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1193" t="inlineStr">
+        <is>
+          <t>elpais.com.co</t>
+        </is>
+      </c>
+      <c r="D1193" t="inlineStr"/>
+      <c r="E1193" t="inlineStr"/>
+      <c r="F1193" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1193" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1193" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1193" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1193" t="n">
+        <v>14</v>
+      </c>
+      <c r="K1193" t="inlineStr">
+        <is>
+          <t>cuidado</t>
+        </is>
+      </c>
+      <c r="L1193" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1193" t="n">
+        <v>2</v>
+      </c>
+      <c r="N1193" t="inlineStr">
+        <is>
+          <t>care</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/df_resultado_final_astrid.xlsx
+++ b/Data/df_resultado_final_astrid.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N1193"/>
+  <dimension ref="A1:N1194"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -66816,6 +66816,60 @@
         </is>
       </c>
     </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>ICBF visitó la casa de Aida Victoria tras denuncia de su expareja, el agropecuario</t>
+        </is>
+      </c>
+      <c r="B1194" t="inlineStr">
+        <is>
+          <t>https://news.google.com./read/CBMivgFBVV95cUxPTWRQTUJ1WHpBbUNlUjJWeThoYmszN2RiZUFhNHdIVENISHNfWk1hOUx0dWJ1QmdLTzN5N1FFWkxxRkdCMWthT2FET2ctOElLYzhLWDNXc1pRNGtoczhJVU9IV0RDcThkSDVUdk83Q210RVBYcGpTUF9QY3NlNTZwVm0yYkhQeVQ4cDhBcHlFYkY0VWFzenROQmxHcHJJOTZYLUdTVW5iejByMUlYOXBPa0h4WmRweG40MnRCaVJR0gHDAUFVX3lxTE94VlVNZ0hDeGVhUldIOTJQQ0ZCUV8teHR1WEp0Y1k5N19WakRJdnRXSy1HS2RJWXg2dS14cFNDMndfUzkya3lVaEt2enk5ZGwyb2duSk5nNXdha21fMTZERzdEbUdENXZhWHJyeEdLOE1YS2J5Z2xtVW9iTDJsaG9MME9PTDVwQlp1QXpocERhZTdNa3lSOC0tdXYwMF9zQlNQb0pEUlJfZDRvU0hYMTJvTGdGS2xMZDN3ZmpfTkhZUFJoQQ?hl=es-419&amp;gl=US&amp;ceid=US%3Aes-419</t>
+        </is>
+      </c>
+      <c r="C1194" t="inlineStr">
+        <is>
+          <t>KienyKe</t>
+        </is>
+      </c>
+      <c r="D1194" t="inlineStr"/>
+      <c r="E1194" t="inlineStr"/>
+      <c r="F1194" t="n">
+        <v>0</v>
+      </c>
+      <c r="G1194" t="n">
+        <v>2026</v>
+      </c>
+      <c r="H1194" t="n">
+        <v>5</v>
+      </c>
+      <c r="I1194" t="inlineStr">
+        <is>
+          <t>jueves</t>
+        </is>
+      </c>
+      <c r="J1194" t="n">
+        <v>14</v>
+      </c>
+      <c r="K1194" t="inlineStr">
+        <is>
+          <t>denuncia</t>
+        </is>
+      </c>
+      <c r="L1194" t="inlineStr">
+        <is>
+          <t>ICBF</t>
+        </is>
+      </c>
+      <c r="M1194" t="n">
+        <v>-2</v>
+      </c>
+      <c r="N1194" t="inlineStr">
+        <is>
+          <t>denounces</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
